--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 01.02.2025 11:35:12</t>
+    <t>Период: на 14.10.2025 15:55:19</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,22 +62,46 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Желе ананас УБ 78г /56шт</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Какао-порошок 100г/40 УБ</t>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 100г /40шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 80г /48шт</t>
+  </si>
+  <si>
+    <t>Какао-порошок УБ 80г /48шт АКЦІЯ</t>
   </si>
   <si>
     <t>ДОБАВКИ</t>
@@ -89,9 +113,24 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желатин УБ 25г /42шт</t>
+  </si>
+  <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт /</t>
+  </si>
+  <si>
+    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
@@ -101,40 +140,64 @@
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
+    <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
+    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Прованські трави УБ 10г /28шт</t>
   </si>
   <si>
+    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт</t>
+    <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
     <t>СПЕЦІЇ</t>
@@ -161,7 +224,10 @@
     <t>Паприка мелена УБ 20г /34шт</t>
   </si>
   <si>
-    <t>Перець духм"яний УБ 20г /22шт</t>
+    <t>Перець духмяний УБ 15г /30шт</t>
+  </si>
+  <si>
+    <t>Перець духмяний УБ 20г /22шт</t>
   </si>
   <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
@@ -170,61 +236,79 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
+    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
+    <t>Суміш перців Класична УБ 30г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>РОШЕН</t>
   </si>
   <si>
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт ДС</t>
-  </si>
-  <si>
-    <t>БАТОН ROSHEN з начинкою 43г/180</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт ДС</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г/180 шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Батон мол-шок карамель 40г/180/30</t>
-  </si>
-  <si>
-    <t>Батон мол-шок крем-брюле 43г/180/30</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>БІСКВІТИ</t>
@@ -263,6 +347,9 @@
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -287,18 +374,27 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /25шт /</t>
+    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /25шт /</t>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -323,25 +419,37 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ВКФ 72г /22шт AR /</t>
+    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers какао-молоко ККФ 216г /16шт</t>
   </si>
   <si>
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers кокос та мигдаль ВКФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Wafers лимон ВКФ 216г /16шт</t>
+  </si>
+  <si>
     <t>Wafers лимон ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ККФ 216г /16шт IL /</t>
+    <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ</t>
@@ -383,15 +491,36 @@
     <t>Mintex+ зі смаком м'яти ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -401,6 +530,15 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -413,42 +551,129 @@
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -458,13 +683,25 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
@@ -473,13 +710,19 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
@@ -488,7 +731,7 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
@@ -500,12 +743,18 @@
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -521,18 +770,21 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Бім-Бом РЦ 200г /11шт</t>
+  </si>
+  <si>
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
     <t>Льодяник мікс РЦ 200г /24шт /</t>
   </si>
   <si>
-    <t>Льодяник мікс РЦ 200г /24шт /АКЦИЯ ВІП</t>
-  </si>
-  <si>
     <t>Молочна крапля РЦ 150г /12шт</t>
   </si>
   <si>
@@ -542,25 +794,22 @@
     <t>Шалена бджілка ВКФ 200г /12шт</t>
   </si>
   <si>
+    <t>Шалена бджілка РЦ 200г /12шт</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
-    <t>Beri РЦ 1кг /8пак</t>
-  </si>
-  <si>
     <t>Beri РЦ 1кг /8пак /</t>
   </si>
   <si>
+    <t>Coconut КрКФ 1кг /7пак</t>
+  </si>
+  <si>
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>CoffeeLike ВКФ 1кг /7пак /</t>
-  </si>
-  <si>
-    <t>CoffeeLike КрКФ 1кг /7пак /</t>
-  </si>
-  <si>
-    <t>Fudgenta ВКФ 0.785кг /9пак</t>
+    <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
@@ -569,6 +818,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
+  </si>
+  <si>
     <t>Lollipops GUM Cola КрКФ 0.92кг /9шт</t>
   </si>
   <si>
@@ -578,6 +830,9 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
+    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -626,10 +881,7 @@
     <t>Карамелькино КрКФ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Молочна крапля ВКФ 1кг /7пак</t>
-  </si>
-  <si>
-    <t>Молочна крапля КрКФ 1кг /7пак /</t>
+    <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
     <t>Рачки ВКФ 1кг /7пак /</t>
@@ -662,7 +914,7 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт ДС</t>
+    <t>Cherry Queen heart РЦ 122г /8шт</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
@@ -680,22 +932,31 @@
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
+    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦИЯ ВИП</t>
+  </si>
+  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters віски-лікер ВКФ 150г /10шт /АКЦИЯ ВИП</t>
+  </si>
+  <si>
     <t>Shooters з бренді-лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters з бренді-лікером ВКФ 150г /10шт /АКЦИЯ ВИП</t>
+  </si>
+  <si>
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Київ вечірній ККФ 176г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній ККФ 352г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній Новий Рік ККФ 176г /7шт</t>
+    <t>Shooters з ромовим лікером ВКФ 150г /10шт /АКЦИЯ ВИП</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
     <t>Стріла Подільска 200г/10</t>
@@ -704,6 +965,30 @@
     <t>ПЕЧИВО ТА КРЕКЕР ФАСОВАНІ</t>
   </si>
   <si>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
+  </si>
+  <si>
+    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -725,21 +1010,15 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з кусочками глазурі ККФ 150г /16шт</t>
-  </si>
-  <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 135г /21шт /</t>
-  </si>
-  <si>
-    <t>Lovita Jelly Cookies c желейною начинкою какао + вишня ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -755,6 +1034,12 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
+  </si>
+  <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -770,24 +1055,33 @@
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою вишня-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою какао 180г/28</t>
-  </si>
-  <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт</t>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
+  </si>
+  <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
   </si>
   <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Multicake з начинкою чорниця-крем ККФ 180г /28шт</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -797,52 +1091,88 @@
     <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ККФ 370г /24шт</t>
+  </si>
+  <si>
     <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт UA</t>
-  </si>
-  <si>
     <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з шоколадною начинкою ККФ 235г /14шт</t>
+    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт АКЦІЯ</t>
   </si>
   <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
-    <t>Candy Nut м"яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+    <t>Boo! Bear РЦ 1кг /5пак</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
+  </si>
+  <si>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Hola! Granola РЦ 0.5кг /8пак</t>
-  </si>
-  <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт /</t>
+    <t>Flaksi какао ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт /</t>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+  </si>
+  <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
   </si>
   <si>
-    <t>Sorrento ВКФ 2кг /5пак</t>
+    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Milaxy ВКФ 1кг /4пак</t>
+  </si>
+  <si>
+    <t>Sorrento ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Winter dream ВКФ 1кг /5пак</t>
   </si>
   <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
@@ -854,34 +1184,28 @@
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
+  </si>
+  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 2кг /5пак</t>
-  </si>
-  <si>
-    <t>Ромашка ВКФ 2кг /5пак АКЦІЯ</t>
+    <t>Ромашка ВКФ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
@@ -896,13 +1220,7 @@
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
-  </si>
-  <si>
-    <t>Johnny Krocker milk ВКФ 350г /12шт /</t>
-  </si>
-  <si>
-    <t>Монблан РЦ 240г /15шт</t>
+    <t>Johnny Krocker milk ВКФ 350г /12шт PL</t>
   </si>
   <si>
     <t>Монблан РЦ 240г /15шт /</t>
@@ -911,49 +1229,94 @@
     <t>ШОКОЛАД</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочный ВКФ 260г /15шт</t>
+    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
-  </si>
-  <si>
-    <t>Lacmi Bubble Crisp молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /24шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /24шт /</t>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
@@ -962,82 +1325,118 @@
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з сезамом ВКФ 90г /24шт</t>
+    <t>Lacmi молочний з сезамом ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з цілим мигдалем ВКФ 90г /21шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /16шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з цілими лісовими горіхами ВКФ 90г /17шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілими лісовими горіхами і шоколадно-карамельною начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 290г /12шт</t>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ</t>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
@@ -1046,54 +1445,48 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen екстрачорний+ціл.л.горіх 90г/18 FP</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий ВКФ 80г /20шт FP</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP /</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт UA</t>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт UA АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦІЯ</t>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
+  </si>
+  <si>
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
@@ -1103,7 +1496,31 @@
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
+    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Набір Зимові Друзі 3х20 РЦ 60г /22шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1330,6 +1747,12 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1349,7 +1772,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C362"/>
+  <dimension ref="C501"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1414,7 +1837,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>576</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1422,7 +1845,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>341801</v>
+        <v>450318</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1430,7 +1853,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>28870</v>
+        <v>96746</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1438,7 +1861,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>7960</v>
+        <v>8849</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1446,15 +1869,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>2124</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>1590</v>
+      <c r="C16" s="11" t="n">
+        <v>733</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1462,55 +1885,55 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>519</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>287</v>
+      <c r="C18" s="16" t="n">
+        <v>1747</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>476</v>
+      <c r="C19" s="16" t="n">
+        <v>1192</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>2964</v>
-      </c>
-    </row>
-    <row r="21" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B21" s="14" t="s">
+      <c r="C20" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>3663</v>
+      <c r="C21" s="11" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
       <c r="B22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="16" t="n">
-        <v>1864</v>
+      <c r="C22" s="11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>684</v>
+      <c r="C23" s="16" t="n">
+        <v>1755</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1518,23 +1941,23 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>91</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="16" t="n">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B26" s="14" t="s">
+      <c r="C25" s="11" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>6599</v>
+      <c r="C26" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1542,7 +1965,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>135</v>
+        <v>920</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1550,31 +1973,31 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="29" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B29" s="15" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="29" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B29" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="16" t="n">
-        <v>1258</v>
+      <c r="C29" s="12" t="n">
+        <v>30910</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>121</v>
+      <c r="C30" s="16" t="n">
+        <v>2217</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>415</v>
+      <c r="C31" s="16" t="n">
+        <v>13505</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1582,15 +2005,15 @@
         <v>31</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>1526</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>175</v>
+      <c r="C33" s="16" t="n">
+        <v>9852</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1598,7 +2021,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>587</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1606,15 +2029,15 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>436</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>370</v>
+      <c r="C36" s="16" t="n">
+        <v>1620</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1622,31 +2045,31 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>704</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B39" s="15" t="s">
+      <c r="C38" s="16" t="n">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="39" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="40" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B40" s="14" t="s">
+      <c r="C39" s="12" t="n">
+        <v>11653</v>
+      </c>
+    </row>
+    <row r="40" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>10648</v>
+      <c r="C40" s="11" t="n">
+        <v>701</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1654,15 +2077,15 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>451</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>777</v>
+      <c r="C42" s="16" t="n">
+        <v>1082</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1670,23 +2093,23 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>790</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="16" t="n">
-        <v>1202</v>
+      <c r="C44" s="11" t="n">
+        <v>988</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="16" t="n">
-        <v>2255</v>
+      <c r="C45" s="11" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1694,7 +2117,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>513</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1702,15 +2125,15 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>587</v>
+        <v>746</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="16" t="n">
-        <v>1328</v>
+      <c r="C48" s="11" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1718,23 +2141,23 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>472</v>
+        <v>930</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
       <c r="B50" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="16" t="n">
-        <v>1531</v>
+      <c r="C50" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>422</v>
+      <c r="C51" s="16" t="n">
+        <v>1308</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1742,7 +2165,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>238</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1750,39 +2173,39 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="54" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B54" s="13" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="54" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="12" t="n">
-        <v>312931</v>
-      </c>
-    </row>
-    <row r="55" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B55" s="14" t="s">
+      <c r="C54" s="11" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="12" t="n">
-        <v>110440</v>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C55" s="11" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="56" ht="11" customHeight="true" outlineLevel="3">
       <c r="B56" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="16" t="n">
-        <v>18966</v>
+      <c r="C56" s="11" t="n">
+        <v>451</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="true" outlineLevel="3">
       <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="16" t="n">
-        <v>3420</v>
+      <c r="C57" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -1790,7 +2213,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>10424</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1798,7 +2221,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="16" t="n">
-        <v>2880</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1806,63 +2229,63 @@
         <v>59</v>
       </c>
       <c r="C60" s="16" t="n">
-        <v>2880</v>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B61" s="15" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="61" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B61" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="16" t="n">
-        <v>5220</v>
+      <c r="C61" s="12" t="n">
+        <v>45334</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>11667</v>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C62" s="11" t="n">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C63" s="16" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="true" outlineLevel="3">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="16" t="n">
-        <v>15938</v>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C64" s="11" t="n">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>5220</v>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="true" outlineLevel="3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
       <c r="C66" s="16" t="n">
-        <v>2880</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="true" outlineLevel="3">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
       <c r="C67" s="16" t="n">
-        <v>2880</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -1870,7 +2293,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="16" t="n">
-        <v>13720</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -1878,15 +2301,15 @@
         <v>68</v>
       </c>
       <c r="C69" s="16" t="n">
-        <v>10925</v>
-      </c>
-    </row>
-    <row r="70" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B70" s="14" t="s">
+        <v>3388</v>
+      </c>
+    </row>
+    <row r="70" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="12" t="n">
-        <v>3029</v>
+      <c r="C70" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -1894,15 +2317,15 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>115</v>
+        <v>652</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="11" t="n">
-        <v>8</v>
+      <c r="C72" s="16" t="n">
+        <v>4465</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -1910,15 +2333,15 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>223</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>403</v>
+      <c r="C74" s="16" t="n">
+        <v>24019</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -1926,7 +2349,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>706</v>
+        <v>670</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -1934,7 +2357,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>34</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -1942,7 +2365,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>328</v>
+        <v>671</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -1950,7 +2373,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>843</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -1958,7 +2381,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>100</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -1966,15 +2389,15 @@
         <v>79</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="81" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B81" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B81" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>137</v>
+      <c r="C81" s="12" t="n">
+        <v>353572</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="2">
@@ -1982,47 +2405,47 @@
         <v>81</v>
       </c>
       <c r="C82" s="12" t="n">
-        <v>11345</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+        <v>30901</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>419</v>
+      <c r="C85" s="16" t="n">
+        <v>5400</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>21</v>
+      <c r="C86" s="16" t="n">
+        <v>1897</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>274</v>
+      <c r="C87" s="16" t="n">
+        <v>1080</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2030,87 +2453,87 @@
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="16" t="n">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C89" s="11" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C90" s="16" t="n">
+        <v>5866</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="16" t="n">
-        <v>2671</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C91" s="11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="16" t="n">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+        <v>5265</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C96" s="16" t="n">
+        <v>7915</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B98" s="15" t="s">
+      <c r="C97" s="16" t="n">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="98" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B98" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>195</v>
+      <c r="C98" s="12" t="n">
+        <v>7899</v>
       </c>
     </row>
     <row r="99" ht="11" customHeight="true" outlineLevel="3">
@@ -2118,7 +2541,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>291</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" ht="11" customHeight="true" outlineLevel="3">
@@ -2126,7 +2549,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>71</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" ht="11" customHeight="true" outlineLevel="3">
@@ -2134,7 +2557,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>22</v>
+        <v>721</v>
       </c>
     </row>
     <row r="102" ht="11" customHeight="true" outlineLevel="3">
@@ -2142,15 +2565,15 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>729</v>
+        <v>803</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="11" t="n">
-        <v>41</v>
+      <c r="C103" s="16" t="n">
+        <v>1882</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2158,7 +2581,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>154</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
@@ -2166,15 +2589,15 @@
         <v>104</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>104</v>
+        <v>323</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="11" t="n">
-        <v>626</v>
+      <c r="C106" s="16" t="n">
+        <v>1820</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2182,7 +2605,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>99</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2190,7 +2613,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>10</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2198,31 +2621,31 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="110" ht="11" customHeight="true" outlineLevel="3">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B111" s="15" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B111" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B112" s="14" t="s">
+      <c r="C111" s="12" t="n">
+        <v>66323</v>
+      </c>
+    </row>
+    <row r="112" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="12" t="n">
-        <v>18600</v>
+      <c r="C112" s="11" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
@@ -2230,7 +2653,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>178</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2238,7 +2661,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2246,7 +2669,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>198</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2254,63 +2677,63 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>2</v>
+        <v>671</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>74</v>
+      <c r="C117" s="16" t="n">
+        <v>1013</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="11" t="n">
-        <v>191</v>
+      <c r="C118" s="16" t="n">
+        <v>12488</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="11" t="n">
-        <v>71</v>
+      <c r="C119" s="16" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
       <c r="B120" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="11" t="n">
-        <v>12</v>
+      <c r="C120" s="16" t="n">
+        <v>12907</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
       <c r="B121" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="11" t="n">
-        <v>15</v>
+      <c r="C121" s="16" t="n">
+        <v>12925</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="11" t="n">
-        <v>160</v>
+      <c r="C122" s="16" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>594</v>
+      <c r="C123" s="16" t="n">
+        <v>12592</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2318,15 +2741,15 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>594</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>44</v>
+      <c r="C125" s="16" t="n">
+        <v>1675</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2334,7 +2757,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>881</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2342,7 +2765,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>517</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2350,7 +2773,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2358,23 +2781,23 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>517</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>277</v>
+      <c r="C130" s="16" t="n">
+        <v>1131</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>178</v>
+      <c r="C131" s="16" t="n">
+        <v>1321</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2382,7 +2805,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>199</v>
+        <v>441</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2390,7 +2813,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>267</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2398,7 +2821,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>204</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2406,15 +2829,15 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>178</v>
+        <v>517</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="11" t="n">
-        <v>160</v>
+      <c r="C136" s="16" t="n">
+        <v>1438</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2422,7 +2845,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>594</v>
+        <v>371</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2430,15 +2853,15 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>21</v>
+        <v>344</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="16" t="n">
-        <v>1565</v>
+      <c r="C139" s="11" t="n">
+        <v>129</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2446,7 +2869,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2454,7 +2877,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>178</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2462,7 +2885,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2470,15 +2893,15 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>606</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
       <c r="B144" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C144" s="11" t="n">
-        <v>22</v>
+      <c r="C144" s="16" t="n">
+        <v>1235</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2486,7 +2909,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>268</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2494,7 +2917,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>178</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2502,15 +2925,15 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="148" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B148" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="148" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B148" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="11" t="n">
-        <v>594</v>
+      <c r="C148" s="12" t="n">
+        <v>39174</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2518,7 +2941,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2526,7 +2949,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>188</v>
+        <v>485</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2534,7 +2957,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2542,7 +2965,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>341</v>
+        <v>189</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2550,7 +2973,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>178</v>
+        <v>623</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2558,7 +2981,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>62</v>
+        <v>95</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2566,7 +2989,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>639</v>
+        <v>139</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2574,7 +2997,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>594</v>
+        <v>287</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2582,7 +3005,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>25</v>
+        <v>243</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2590,7 +3013,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>45</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2598,7 +3021,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>267</v>
+        <v>330</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2606,7 +3029,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>40</v>
+        <v>877</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2614,7 +3037,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>837</v>
+        <v>538</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2622,15 +3045,15 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>594</v>
+        <v>257</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="16" t="n">
-        <v>1847</v>
+      <c r="C163" s="11" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2638,7 +3061,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>178</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2646,7 +3069,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2654,7 +3077,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>108</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2662,15 +3085,15 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>517</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="16" t="n">
-        <v>1249</v>
+      <c r="C168" s="11" t="n">
+        <v>265</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2678,7 +3101,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>68</v>
+        <v>235</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2686,7 +3109,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>8</v>
+        <v>258</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2694,7 +3117,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>47</v>
+        <v>106</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2702,7 +3125,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>111</v>
+        <v>44</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2710,7 +3133,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2718,15 +3141,15 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="175" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B175" s="14" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="175" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="12" t="n">
-        <v>15123</v>
+      <c r="C175" s="11" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2734,7 +3157,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>3</v>
+        <v>765</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2742,7 +3165,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>726</v>
+        <v>78</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2750,7 +3173,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2758,7 +3181,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>362</v>
+        <v>88</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2766,7 +3189,7 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>317</v>
+        <v>262</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -2774,15 +3197,15 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>306</v>
+        <v>260</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="16" t="n">
-        <v>1335</v>
+      <c r="C182" s="11" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -2790,7 +3213,7 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>11</v>
+        <v>329</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2798,7 +3221,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>189</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -2806,7 +3229,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>87</v>
+        <v>792</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -2814,7 +3237,7 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>113</v>
+        <v>295</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2822,7 +3245,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2830,7 +3253,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>175</v>
+        <v>695</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -2838,7 +3261,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>489</v>
+        <v>63</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2846,7 +3269,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>335</v>
+        <v>398</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -2854,7 +3277,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>173</v>
+        <v>66</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2862,7 +3285,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>235</v>
+        <v>734</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -2870,7 +3293,7 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>131</v>
+        <v>371</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2878,7 +3301,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>595</v>
+        <v>455</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -2886,7 +3309,7 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>332</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2894,7 +3317,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>585</v>
+        <v>673</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -2902,31 +3325,31 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>794</v>
+        <v>138</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="16" t="n">
-        <v>1009</v>
+      <c r="C198" s="11" t="n">
+        <v>687</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="16" t="n">
-        <v>1100</v>
+      <c r="C199" s="11" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="11" t="n">
-        <v>386</v>
+      <c r="C200" s="16" t="n">
+        <v>2304</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -2934,15 +3357,15 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>726</v>
+        <v>111</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>643</v>
+      <c r="C202" s="16" t="n">
+        <v>2305</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -2950,15 +3373,15 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="11" t="n">
-        <v>362</v>
+      <c r="C204" s="16" t="n">
+        <v>1180</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -2966,7 +3389,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>467</v>
+        <v>101</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -2974,7 +3397,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>304</v>
+        <v>133</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -2982,7 +3405,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>676</v>
+        <v>267</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -2990,15 +3413,15 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>387</v>
+        <v>331</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="16" t="n">
-        <v>1172</v>
+      <c r="C209" s="11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3006,15 +3429,15 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="211" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B211" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="211" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B211" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="12" t="n">
-        <v>2810</v>
+      <c r="C211" s="11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3022,7 +3445,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>161</v>
+        <v>85</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3030,7 +3453,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>285</v>
+        <v>104</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3038,7 +3461,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>299</v>
+        <v>44</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3046,7 +3469,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>23</v>
+        <v>193</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3054,7 +3477,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>508</v>
+        <v>295</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3062,7 +3485,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>3</v>
+        <v>311</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3070,7 +3493,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>100</v>
+        <v>830</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3078,7 +3501,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3086,7 +3509,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>202</v>
+        <v>803</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3094,7 +3517,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>83</v>
+        <v>150</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3102,7 +3525,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>350</v>
+        <v>54</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3110,7 +3533,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>73</v>
+        <v>182</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3118,15 +3541,15 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>266</v>
+        <v>993</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
       <c r="B225" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="11" t="n">
-        <v>14</v>
+      <c r="C225" s="16" t="n">
+        <v>3105</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3134,7 +3557,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>264</v>
+        <v>364</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3142,23 +3565,23 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="228" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B228" s="14" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="228" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="12" t="n">
-        <v>9307</v>
-      </c>
-    </row>
-    <row r="229" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C228" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>34</v>
+        <v>259</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3166,7 +3589,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3174,7 +3597,7 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3182,7 +3605,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>232</v>
+        <v>296</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3190,7 +3613,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>6</v>
+        <v>111</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3198,7 +3621,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>105</v>
+        <v>396</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3206,7 +3629,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3214,79 +3637,79 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="237" ht="22" customHeight="true" outlineLevel="3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="15" t="s">
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="238" ht="22" customHeight="true" outlineLevel="3">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="239" ht="22" customHeight="true" outlineLevel="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="240" ht="22" customHeight="true" outlineLevel="3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="15" t="s">
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="241" ht="22" customHeight="true" outlineLevel="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="242" ht="22" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="243" ht="22" customHeight="true" outlineLevel="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="244" ht="22" customHeight="true" outlineLevel="3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="245" ht="22" customHeight="true" outlineLevel="3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="245" ht="11" customHeight="true" outlineLevel="3">
       <c r="B245" s="15" t="s">
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>15</v>
+        <v>395</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3294,7 +3717,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>323</v>
+        <v>278</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3302,7 +3725,7 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>272</v>
+        <v>94</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3310,7 +3733,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>21</v>
+        <v>480</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3318,7 +3741,7 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>239</v>
+        <v>153</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3326,7 +3749,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>54</v>
+        <v>371</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3334,7 +3757,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>664</v>
+        <v>396</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3342,7 +3765,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>213</v>
+        <v>168</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3350,7 +3773,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>37</v>
+        <v>390</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3358,7 +3781,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>644</v>
+        <v>192</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3366,7 +3789,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>21</v>
+        <v>206</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3374,7 +3797,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>222</v>
+        <v>260</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3382,15 +3805,15 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>324</v>
+        <v>33</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="16" t="n">
-        <v>3133</v>
+      <c r="C258" s="11" t="n">
+        <v>566</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3398,23 +3821,23 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="260" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B260" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B260" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="261" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C260" s="12" t="n">
+        <v>31712</v>
+      </c>
+    </row>
+    <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>4</v>
+        <v>875</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3422,31 +3845,31 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>15</v>
+        <v>851</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="11" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="264" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B264" s="14" t="s">
+      <c r="C263" s="16" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="264" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B264" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="C264" s="12" t="n">
-        <v>15887</v>
+      <c r="C264" s="16" t="n">
+        <v>1071</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C265" s="11" t="n">
-        <v>655</v>
+      <c r="C265" s="16" t="n">
+        <v>2755</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3454,15 +3877,15 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>291</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="16" t="n">
-        <v>1490</v>
+      <c r="C267" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3470,7 +3893,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>290</v>
+        <v>322</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3478,7 +3901,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>347</v>
+        <v>301</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3486,7 +3909,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>368</v>
+        <v>587</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3494,7 +3917,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>374</v>
+        <v>26</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3502,7 +3925,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>431</v>
+        <v>320</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3510,7 +3933,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>755</v>
+        <v>422</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3518,7 +3941,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>621</v>
+        <v>767</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3526,7 +3949,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3534,7 +3957,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>320</v>
+        <v>625</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3542,7 +3965,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>681</v>
+        <v>539</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3550,23 +3973,23 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="279" ht="22" customHeight="true" outlineLevel="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280" ht="22" customHeight="true" outlineLevel="3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="280" ht="11" customHeight="true" outlineLevel="3">
       <c r="B280" s="15" t="s">
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3574,7 +3997,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>107</v>
+        <v>485</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3582,7 +4005,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>140</v>
+        <v>844</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3590,31 +4013,31 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="284" ht="22" customHeight="true" outlineLevel="3">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="11" t="n">
-        <v>1</v>
+      <c r="C284" s="16" t="n">
+        <v>2893</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
       <c r="B285" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="11" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="286" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C285" s="16" t="n">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="11" t="n">
-        <v>1</v>
+      <c r="C286" s="16" t="n">
+        <v>1369</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3622,15 +4045,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="16" t="n">
-        <v>5002</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="11" t="n">
-        <v>6</v>
+      <c r="C288" s="16" t="n">
+        <v>1240</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3638,7 +4061,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="16" t="n">
-        <v>1910</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3646,31 +4069,31 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>343</v>
+        <v>773</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="11" t="n">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="292" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B292" s="14" t="s">
+      <c r="C291" s="16" t="n">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="17" t="n">
-        <v>200</v>
+      <c r="C292" s="16" t="n">
+        <v>1401</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="11" t="n">
-        <v>64</v>
+      <c r="C293" s="16" t="n">
+        <v>1813</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3678,15 +4101,15 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B295" s="15" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B295" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="11" t="n">
-        <v>12</v>
+      <c r="C295" s="12" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -3694,15 +4117,15 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="297" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B297" s="14" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="297" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="C297" s="12" t="n">
-        <v>126190</v>
+      <c r="C297" s="11" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -3710,7 +4133,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>305</v>
+        <v>129</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -3718,55 +4141,55 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="true" outlineLevel="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="16" t="n">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="302" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C301" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="303" ht="22" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="16" t="n">
-        <v>4499</v>
-      </c>
-    </row>
-    <row r="304" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C303" s="11" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="305" ht="11" customHeight="true" outlineLevel="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>280</v>
+        <v>34</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -3774,15 +4197,15 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>67</v>
+        <v>156</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="16" t="n">
-        <v>1131</v>
+      <c r="C307" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3790,7 +4213,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3798,127 +4221,127 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="310" ht="22" customHeight="true" outlineLevel="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="312" ht="22" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="16" t="n">
-        <v>11532</v>
-      </c>
-    </row>
-    <row r="314" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C313" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="315" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B315" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B315" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="11" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="316" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C315" s="12" t="n">
+        <v>34360</v>
+      </c>
+    </row>
+    <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="317" ht="22" customHeight="true" outlineLevel="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="3">
       <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="true" outlineLevel="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="16" t="n">
-        <v>10273</v>
-      </c>
-    </row>
-    <row r="319" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C318" s="11" t="n">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="11" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C320" s="16" t="n">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="16" t="n">
-        <v>3428</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>144</v>
+      <c r="C322" s="16" t="n">
+        <v>1704</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="11" t="n">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C323" s="16" t="n">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="324" ht="22" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>84</v>
+        <v>193</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -3926,7 +4349,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>154</v>
+        <v>37</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -3934,7 +4357,7 @@
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -3942,31 +4365,31 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>25</v>
+        <v>594</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="C328" s="11" t="n">
-        <v>12</v>
+      <c r="C328" s="16" t="n">
+        <v>1349</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="330" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C329" s="16" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>564</v>
+        <v>30</v>
       </c>
     </row>
     <row r="331" ht="22" customHeight="true" outlineLevel="3">
@@ -3974,7 +4397,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>408</v>
+        <v>275</v>
       </c>
     </row>
     <row r="332" ht="22" customHeight="true" outlineLevel="3">
@@ -3982,15 +4405,15 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>268</v>
+        <v>31</v>
       </c>
     </row>
     <row r="333" ht="22" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="16" t="n">
-        <v>1248</v>
+      <c r="C333" s="11" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="334" ht="22" customHeight="true" outlineLevel="3">
@@ -3998,15 +4421,15 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="335" ht="11" customHeight="true" outlineLevel="3">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="335" ht="22" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>839</v>
+        <v>88</v>
       </c>
     </row>
     <row r="336" ht="22" customHeight="true" outlineLevel="3">
@@ -4014,31 +4437,31 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="16" t="n">
-        <v>2476</v>
+      <c r="C339" s="11" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="340" ht="22" customHeight="true" outlineLevel="3">
@@ -4046,7 +4469,7 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>690</v>
+        <v>71</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4054,15 +4477,15 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="342" ht="22" customHeight="true" outlineLevel="3">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="16" t="n">
-        <v>1763</v>
+      <c r="C342" s="11" t="n">
+        <v>364</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4078,15 +4501,15 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>8</v>
+        <v>681</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="16" t="n">
-        <v>1301</v>
+      <c r="C345" s="11" t="n">
+        <v>353</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4094,23 +4517,23 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>125</v>
+        <v>270</v>
       </c>
     </row>
     <row r="347" ht="22" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="16" t="n">
-        <v>1878</v>
+      <c r="C347" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="16" t="n">
-        <v>2470</v>
+      <c r="C348" s="11" t="n">
+        <v>974</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4118,15 +4541,15 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="true" outlineLevel="3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="16" t="n">
-        <v>1917</v>
+      <c r="C350" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4134,23 +4557,23 @@
         <v>350</v>
       </c>
       <c r="C351" s="16" t="n">
-        <v>1594</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="11" t="n">
-        <v>618</v>
+      <c r="C352" s="16" t="n">
+        <v>1945</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="C353" s="16" t="n">
-        <v>4368</v>
+      <c r="C353" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4158,23 +4581,23 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
       <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="11" t="n">
-        <v>324</v>
+      <c r="C355" s="16" t="n">
+        <v>3199</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>15</v>
+      <c r="C356" s="16" t="n">
+        <v>5251</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4182,47 +4605,1159 @@
         <v>356</v>
       </c>
       <c r="C357" s="16" t="n">
-        <v>1108</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="11" t="n">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C358" s="16" t="n">
+        <v>5116</v>
+      </c>
+    </row>
+    <row r="359" ht="22" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="16" t="n">
-        <v>19631</v>
-      </c>
-    </row>
-    <row r="360" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C359" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
       <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="16" t="n">
-        <v>7896</v>
+      <c r="C360" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="16" t="n">
-        <v>21992</v>
-      </c>
-    </row>
-    <row r="362" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B362" s="15" t="s">
+      <c r="C361" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B362" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="C362" s="16" t="n">
-        <v>8352</v>
+      <c r="C362" s="12" t="n">
+        <v>25584</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B363" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="C363" s="11" t="n">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B364" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="C364" s="11" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B365" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C365" s="11" t="n">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B366" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C366" s="11" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B367" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C367" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B368" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C368" s="11" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B369" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="C369" s="11" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B370" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C370" s="11" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B371" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="C371" s="16" t="n">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B372" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C372" s="11" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B373" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="C373" s="16" t="n">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B374" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C374" s="11" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B375" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="C375" s="16" t="n">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B376" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="C376" s="11" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B377" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C377" s="11" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B378" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="C378" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B379" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C379" s="11" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B380" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C380" s="11" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B381" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="C381" s="11" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="382" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B382" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C382" s="11" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B383" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C383" s="11" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="384" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B384" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C384" s="11" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B385" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C385" s="11" t="n">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B386" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C386" s="16" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B387" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C387" s="11" t="n">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B388" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="C388" s="11" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B389" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C389" s="11" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B390" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C390" s="11" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="391" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B391" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C391" s="11" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="392" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B392" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="C392" s="11" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="393" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B393" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C393" s="11" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B394" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C394" s="16" t="n">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B395" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="C395" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B396" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C396" s="16" t="n">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B397" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="C397" s="16" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B398" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C398" s="16" t="n">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B399" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="C399" s="11" t="n">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B400" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="C400" s="17" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B401" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C401" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B402" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C402" s="11" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B403" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="C403" s="12" t="n">
+        <v>115533</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B404" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C404" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B405" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C405" s="16" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B406" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C406" s="11" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B407" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C407" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B408" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="C408" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="409" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B409" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="11" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B410" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="11" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="411" ht="33" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="16" t="n">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B412" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="11" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="415" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B415" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="11" t="n">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B416" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="11" t="n">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="417" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B417" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="11" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B418" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="16" t="n">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="419" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B419" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="420" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B420" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="11" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B421" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="11" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B422" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="16" t="n">
+        <v>5839</v>
+      </c>
+    </row>
+    <row r="423" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B423" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B424" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="11" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="425" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B425" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="11" t="n">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B426" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="11" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B427" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B428" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="11" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B429" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="16" t="n">
+        <v>7428</v>
+      </c>
+    </row>
+    <row r="430" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B430" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B431" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="432" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B432" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="16" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="433" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B433" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="434" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B434" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="16" t="n">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="435" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B435" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C435" s="11" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="436" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B436" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C436" s="11" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="437" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B437" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C437" s="16" t="n">
+        <v>3062</v>
+      </c>
+    </row>
+    <row r="438" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B438" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C438" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="439" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B439" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C439" s="11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B440" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C440" s="16" t="n">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="441" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B441" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="442" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B442" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C442" s="11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="443" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B443" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C443" s="11" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="444" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B444" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C444" s="16" t="n">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="445" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B445" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C445" s="11" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="446" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B446" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C446" s="11" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="447" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B447" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="11" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="448" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B448" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B449" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="11" t="n">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="450" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B450" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C450" s="11" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="451" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B451" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="C451" s="11" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="452" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B452" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="C452" s="16" t="n">
+        <v>5908</v>
+      </c>
+    </row>
+    <row r="453" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B453" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="C453" s="11" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="454" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B454" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C454" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B455" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C455" s="11" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="456" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B456" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="C456" s="11" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="457" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B457" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="C457" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="458" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B458" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C458" s="16" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="459" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B459" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="C459" s="11" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="460" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B460" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C460" s="11" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="461" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B461" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B462" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C462" s="11" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B463" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C463" s="11" t="n">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="464" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B464" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="11" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="465" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B465" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="C465" s="11" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="466" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B466" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C466" s="16" t="n">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="467" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B467" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="11" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B468" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="11" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="469" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B469" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B470" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="11" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="471" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B471" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C471" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="472" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B472" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C472" s="11" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="473" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B473" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="C473" s="11" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="474" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B474" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C474" s="11" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="475" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B475" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="C475" s="11" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="476" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B476" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="C476" s="11" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="477" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B477" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="C477" s="11" t="n">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="478" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B478" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="C478" s="16" t="n">
+        <v>12267</v>
+      </c>
+    </row>
+    <row r="479" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B479" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="C479" s="11" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="480" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B480" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="C480" s="11" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="481" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B481" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="C481" s="11" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="482" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B482" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C482" s="11" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="483" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B483" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="C483" s="11" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="484" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B484" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="C484" s="11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="485" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B485" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C485" s="11" t="n">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="486" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B486" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="C486" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="487" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B487" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="C487" s="11" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="488" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B488" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="C488" s="11" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="489" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B489" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C489" s="11" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="490" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B490" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="C490" s="16" t="n">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="491" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B491" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C491" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="492" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B492" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="C492" s="11" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="493" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B493" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C493" s="16" t="n">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="494" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B494" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="C494" s="11" t="n">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="495" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B495" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="C495" s="12" t="n">
+        <v>34556</v>
+      </c>
+    </row>
+    <row r="496" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B496" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="C496" s="11" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="497" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B497" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="C497" s="16" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="498" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B498" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="C498" s="16" t="n">
+        <v>14560</v>
+      </c>
+    </row>
+    <row r="499" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B499" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="C499" s="16" t="n">
+        <v>8448</v>
+      </c>
+    </row>
+    <row r="500" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B500" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="C500" s="16" t="n">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="501" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B501" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="C501" s="16" t="n">
+        <v>6400</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 14.10.2025 15:55:19</t>
+    <t>Период: на 02.12.2025 15:35:16</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -65,25 +65,46 @@
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе полуниця УБ 78г /56шт</t>
@@ -92,12 +113,12 @@
     <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
-    <t>Какао-порошок УБ 100г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
@@ -134,6 +155,15 @@
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
@@ -158,15 +188,15 @@
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
     <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Приправа до риби УБ 25г /30шт</t>
-  </si>
-  <si>
     <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -182,24 +212,30 @@
     <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт</t>
+    <t>Суміш зелені УБ 10г /24шт</t>
+  </si>
+  <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
-    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
+    <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -236,9 +272,6 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
@@ -251,25 +284,16 @@
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
   </si>
   <si>
-    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
-    <t>Суміш перців Класична УБ 30г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>РОШЕН</t>
   </si>
   <si>
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
@@ -278,7 +302,7 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
@@ -293,19 +317,28 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
@@ -341,9 +374,15 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
@@ -374,16 +413,13 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
     <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП</t>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
@@ -392,9 +428,6 @@
     <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -416,12 +449,12 @@
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers горіх ВКФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
@@ -434,18 +467,15 @@
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers кокос та мигдаль ВКФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Wafers лимон ВКФ 216г /16шт</t>
-  </si>
-  <si>
     <t>Wafers лимон ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers молоко ВКФ 216г /16шт</t>
+  </si>
+  <si>
     <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -494,9 +524,6 @@
     <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -506,18 +533,12 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -530,12 +551,6 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -545,18 +560,15 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -566,10 +578,7 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
@@ -578,7 +587,7 @@
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
@@ -587,10 +596,7 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
@@ -599,7 +605,7 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
@@ -608,31 +614,43 @@
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
@@ -641,12 +659,6 @@
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -656,12 +668,6 @@
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -671,9 +677,6 @@
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -683,7 +686,7 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
@@ -698,10 +701,10 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
@@ -710,19 +713,13 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
@@ -731,7 +728,10 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
@@ -740,10 +740,7 @@
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ ОПТ</t>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
@@ -752,7 +749,7 @@
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
@@ -761,7 +758,7 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
@@ -770,15 +767,9 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Бім-Бом РЦ 200г /11шт</t>
-  </si>
-  <si>
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
@@ -809,6 +800,9 @@
     <t>CoffeeLike ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>CoffeeLike КрКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>Fudgenta ВКФ 0.785кг /9пак /</t>
   </si>
   <si>
@@ -824,9 +818,6 @@
     <t>Lollipops GUM Cola КрКФ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>Lollipops GUM Фруктовий мікс РЦ 0.92кг /9шт</t>
-  </si>
-  <si>
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
@@ -839,9 +830,6 @@
     <t>Milky Splash з молочною начинкою ВКФ 1кг /5пак</t>
   </si>
   <si>
-    <t>Minky Binky з желейною начинкою РЦ 1кг /6пак</t>
-  </si>
-  <si>
     <t>Mintex Mint зі смаком м'яти ВКФ 1кг /9шт</t>
   </si>
   <si>
@@ -893,9 +881,6 @@
     <t>Рошен евкаліпт-ментол КрКФ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Цитрусовий мікс РЦ 1кг /7пак /</t>
-  </si>
-  <si>
     <t>Шалена бджілка ВКФ 1кг /9пак</t>
   </si>
   <si>
@@ -914,9 +899,6 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
@@ -932,27 +914,18 @@
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦИЯ ВИП</t>
+    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
   </si>
   <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Shooters віски-лікер ВКФ 150г /10шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Shooters з бренді-лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Shooters з бренді-лікером ВКФ 150г /10шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Shooters з ромовим лікером ВКФ 150г /10шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
@@ -965,6 +938,9 @@
     <t>ПЕЧИВО ТА КРЕКЕР ФАСОВАНІ</t>
   </si>
   <si>
+    <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
+  </si>
+  <si>
     <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
   </si>
   <si>
@@ -977,9 +953,15 @@
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
   </si>
   <si>
+    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
   </si>
   <si>
@@ -1013,33 +995,21 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -1067,9 +1037,6 @@
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -1094,27 +1061,63 @@
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт</t>
-  </si>
-  <si>
     <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт АКЦІЯ</t>
   </si>
   <si>
+    <t>ПОДАРУНКИ</t>
+  </si>
+  <si>
+    <t>ПОДАРУНКИ 2026</t>
+  </si>
+  <si>
+    <t>Н/п №1 26 Солодка хатинка РЦ 274г /10шт UA+GR</t>
+  </si>
+  <si>
+    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
+  </si>
+  <si>
+    <t>Н/п №2 26 Новорічна сумочка РЦ 330г /8шт</t>
+  </si>
+  <si>
+    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
+  </si>
+  <si>
+    <t>Н/п №4 26 Новорічна ялинка РЦ 388г /9шт</t>
+  </si>
+  <si>
+    <t>Н/п №5 26 Ведмедик Roshen РЦ 426г /12шт</t>
+  </si>
+  <si>
+    <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
+  </si>
+  <si>
+    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
+  </si>
+  <si>
+    <t>Н/п №9 26 Різдвяний вінок РЦ 598г /6шт</t>
+  </si>
+  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
+    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1124,51 +1127,33 @@
     <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
-    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
-  </si>
-  <si>
-    <t>Galaretka Roshen РЦ 1кг /9пак</t>
-  </si>
-  <si>
     <t>Galaretka Roshen РЦ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
+    <t>Ko-Ko Choco White ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
     <t>KONAFETTO nero ККФ 1кг /5пак /</t>
   </si>
   <si>
-    <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
-  </si>
-  <si>
     <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
-    <t>Milaxy ВКФ 1кг /4пак</t>
-  </si>
-  <si>
     <t>Sorrento ВКФ 1кг /9пак</t>
   </si>
   <si>
@@ -1181,9 +1166,18 @@
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
+    <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1193,33 +1187,45 @@
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
+    <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
+  </si>
+  <si>
+    <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
+  </si>
+  <si>
     <t>Johnny Krocker milk ВКФ 350г /12шт PL</t>
   </si>
   <si>
@@ -1247,7 +1253,7 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
@@ -1259,9 +1265,6 @@
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1274,9 +1277,6 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1289,7 +1289,7 @@
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
@@ -1310,13 +1310,16 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
@@ -1334,36 +1337,33 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1430,13 +1430,13 @@
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
@@ -1445,40 +1445,43 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
-  </si>
-  <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
-  </si>
-  <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ</t>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
@@ -1490,24 +1493,21 @@
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>ФІГУРКИ</t>
   </si>
   <si>
-    <t>Набір Зимові Друзі 3х20 РЦ 60г /22шт</t>
-  </si>
-  <si>
     <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
   </si>
   <si>
@@ -1515,9 +1515,6 @@
   </si>
   <si>
     <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
   </si>
   <si>
     <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
@@ -1744,14 +1741,14 @@
     <xf numFmtId="52" fontId="5" fillId="5" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1772,7 +1769,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C501"/>
+  <dimension ref="C500"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1837,7 +1834,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>502</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1845,7 +1842,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>450318</v>
+        <v>467170</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1853,7 +1850,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>96746</v>
+        <v>61176</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1861,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>8849</v>
+        <v>15302</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1869,15 +1866,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>1200</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>733</v>
+      <c r="C16" s="16" t="n">
+        <v>1301</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1885,23 +1882,23 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>231</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>1747</v>
+      <c r="C18" s="11" t="n">
+        <v>869</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>1192</v>
+      <c r="C19" s="11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1909,7 +1906,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>40</v>
+        <v>887</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1917,7 +1914,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1925,23 +1922,23 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>1755</v>
+      <c r="C23" s="11" t="n">
+        <v>488</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>154</v>
+      <c r="C24" s="16" t="n">
+        <v>2061</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1949,7 +1946,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1957,7 +1954,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1</v>
+        <v>912</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1965,23 +1962,23 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>920</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="29" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B29" s="14" t="s">
+      <c r="C28" s="16" t="n">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="29" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="12" t="n">
-        <v>30910</v>
+      <c r="C29" s="11" t="n">
+        <v>448</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1989,39 +1986,39 @@
         <v>29</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>2217</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="16" t="n">
-        <v>13505</v>
+      <c r="C31" s="11" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>1767</v>
+      <c r="C32" s="11" t="n">
+        <v>668</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="16" t="n">
-        <v>9852</v>
+      <c r="C33" s="11" t="n">
+        <v>325</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>180</v>
+      <c r="C34" s="16" t="n">
+        <v>1714</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -2029,23 +2026,23 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="36" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B36" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="36" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B36" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="16" t="n">
-        <v>1620</v>
+      <c r="C36" s="12" t="n">
+        <v>20939</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>8</v>
+      <c r="C37" s="16" t="n">
+        <v>1994</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -2053,15 +2050,15 @@
         <v>37</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="39" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B39" s="14" t="s">
+        <v>10770</v>
+      </c>
+    </row>
+    <row r="39" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="12" t="n">
-        <v>11653</v>
+      <c r="C39" s="16" t="n">
+        <v>1767</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -2069,7 +2066,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>701</v>
+        <v>884</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -2077,15 +2074,15 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>34</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="16" t="n">
-        <v>1082</v>
+      <c r="C42" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -2093,7 +2090,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>158</v>
+        <v>415</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -2101,7 +2098,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>988</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -2109,39 +2106,39 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>39</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>534</v>
+      <c r="C46" s="16" t="n">
+        <v>1561</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>746</v>
+      <c r="C47" s="16" t="n">
+        <v>1469</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B49" s="15" t="s">
+      <c r="C48" s="16" t="n">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="49" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B49" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>930</v>
+      <c r="C49" s="12" t="n">
+        <v>6912</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2149,15 +2146,15 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>30</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
       <c r="B51" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="16" t="n">
-        <v>1308</v>
+      <c r="C51" s="11" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2165,7 +2162,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>68</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2173,7 +2170,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>435</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2181,7 +2178,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>179</v>
+        <v>376</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -2189,7 +2186,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>749</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2197,47 +2194,47 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="true" outlineLevel="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>10</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="16" t="n">
-        <v>1075</v>
+      <c r="C58" s="11" t="n">
+        <v>633</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="16" t="n">
-        <v>1046</v>
+      <c r="C59" s="11" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
       <c r="B60" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="16" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="61" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B61" s="14" t="s">
+      <c r="C60" s="11" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="12" t="n">
-        <v>45334</v>
+      <c r="C61" s="11" t="n">
+        <v>317</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2245,15 +2242,15 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>863</v>
+        <v>388</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="16" t="n">
-        <v>1224</v>
+      <c r="C63" s="11" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2261,47 +2258,47 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>728</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>1112</v>
+      <c r="C65" s="11" t="n">
+        <v>973</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>3395</v>
+      <c r="C66" s="11" t="n">
+        <v>349</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>1715</v>
+      <c r="C67" s="11" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="16" t="n">
-        <v>1756</v>
+      <c r="C68" s="11" t="n">
+        <v>381</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="n">
-        <v>3388</v>
+      <c r="C69" s="11" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2309,7 +2306,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2317,31 +2314,31 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>652</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="16" t="n">
-        <v>4465</v>
-      </c>
-    </row>
-    <row r="73" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B73" s="15" t="s">
+      <c r="C72" s="11" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B73" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="11" t="n">
-        <v>167</v>
+      <c r="C73" s="12" t="n">
+        <v>18023</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="16" t="n">
-        <v>24019</v>
+      <c r="C74" s="11" t="n">
+        <v>809</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2349,7 +2346,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>670</v>
+        <v>560</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2357,7 +2354,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>166</v>
+        <v>886</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -2365,15 +2362,15 @@
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>671</v>
+        <v>844</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="11" t="n">
-        <v>66</v>
+      <c r="C78" s="16" t="n">
+        <v>1442</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2381,55 +2378,55 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>273</v>
+        <v>401</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B81" s="13" t="s">
+      <c r="C80" s="16" t="n">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="81" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="12" t="n">
-        <v>353572</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B82" s="14" t="s">
+      <c r="C81" s="11" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="12" t="n">
-        <v>30901</v>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C82" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="true" outlineLevel="3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>5400</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2437,15 +2434,15 @@
         <v>85</v>
       </c>
       <c r="C86" s="16" t="n">
-        <v>1897</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>1080</v>
+      <c r="C87" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2453,39 +2450,39 @@
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="true" outlineLevel="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B90" s="15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B90" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="16" t="n">
-        <v>5866</v>
-      </c>
-    </row>
-    <row r="91" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B91" s="15" t="s">
+      <c r="C90" s="12" t="n">
+        <v>405994</v>
+      </c>
+    </row>
+    <row r="91" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B91" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>180</v>
+      <c r="C91" s="12" t="n">
+        <v>149438</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>960</v>
+      <c r="C92" s="16" t="n">
+        <v>14376</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true" outlineLevel="3">
@@ -2493,31 +2490,31 @@
         <v>92</v>
       </c>
       <c r="C93" s="16" t="n">
-        <v>5265</v>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="11" t="n">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C94" s="16" t="n">
+        <v>6520</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="true" outlineLevel="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="16" t="n">
-        <v>7915</v>
+        <v>24325</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="true" outlineLevel="3">
@@ -2525,119 +2522,119 @@
         <v>96</v>
       </c>
       <c r="C97" s="16" t="n">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B98" s="14" t="s">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="12" t="n">
-        <v>7899</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C98" s="16" t="n">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C99" s="16" t="n">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C100" s="16" t="n">
+        <v>22575</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C101" s="16" t="n">
+        <v>23386</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="16" t="n">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C103" s="11" t="n">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C105" s="16" t="n">
+        <v>29370</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="16" t="n">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C106" s="11" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="11" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C107" s="16" t="n">
+        <v>17375</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B109" s="15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B109" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="11" t="n">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C109" s="12" t="n">
+        <v>6390</v>
+      </c>
+    </row>
+    <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B111" s="14" t="s">
+      <c r="C110" s="16" t="n">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="12" t="n">
-        <v>66323</v>
+      <c r="C111" s="11" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2645,15 +2642,15 @@
         <v>111</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>125</v>
+        <v>501</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="11" t="n">
-        <v>209</v>
+      <c r="C113" s="16" t="n">
+        <v>1145</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2661,7 +2658,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>240</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2669,7 +2666,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2677,79 +2674,79 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>671</v>
+        <v>573</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="16" t="n">
-        <v>1013</v>
+      <c r="C117" s="11" t="n">
+        <v>926</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="16" t="n">
-        <v>12488</v>
+      <c r="C118" s="11" t="n">
+        <v>532</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="16" t="n">
-        <v>1500</v>
+      <c r="C119" s="11" t="n">
+        <v>238</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
       <c r="B120" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="16" t="n">
-        <v>12907</v>
+      <c r="C120" s="11" t="n">
+        <v>385</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
       <c r="B121" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="16" t="n">
-        <v>12925</v>
+      <c r="C121" s="11" t="n">
+        <v>238</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="16" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="123" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C122" s="11" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="16" t="n">
-        <v>12592</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B124" s="15" t="s">
+      <c r="C123" s="11" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B124" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>10</v>
+      <c r="C124" s="12" t="n">
+        <v>20289</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="16" t="n">
-        <v>1675</v>
+      <c r="C125" s="11" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2757,7 +2754,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>121</v>
+        <v>537</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2765,7 +2762,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2773,7 +2770,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>160</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2781,15 +2778,15 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>99</v>
+        <v>698</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="16" t="n">
-        <v>1131</v>
+      <c r="C130" s="11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2797,31 +2794,31 @@
         <v>130</v>
       </c>
       <c r="C131" s="16" t="n">
-        <v>1321</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
       <c r="B132" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="11" t="n">
-        <v>441</v>
+      <c r="C132" s="16" t="n">
+        <v>1978</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>27</v>
+      <c r="C133" s="16" t="n">
+        <v>5225</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
       <c r="B134" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>4</v>
+      <c r="C134" s="16" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2829,15 +2826,15 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>517</v>
+        <v>314</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="16" t="n">
-        <v>1438</v>
+      <c r="C136" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2845,7 +2842,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>371</v>
+        <v>218</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2853,7 +2850,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>344</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2861,7 +2858,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>129</v>
+        <v>257</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2869,15 +2866,15 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>60</v>
+        <v>214</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
       <c r="B141" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="11" t="n">
-        <v>82</v>
+      <c r="C141" s="16" t="n">
+        <v>1044</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2885,7 +2882,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>115</v>
+        <v>965</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2893,15 +2890,15 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>15</v>
+        <v>362</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
       <c r="B144" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C144" s="16" t="n">
-        <v>1235</v>
+      <c r="C144" s="11" t="n">
+        <v>424</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2909,7 +2906,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>28</v>
+        <v>464</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2917,7 +2914,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2925,15 +2922,15 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="148" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B148" s="14" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="148" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="12" t="n">
-        <v>39174</v>
+      <c r="C148" s="11" t="n">
+        <v>408</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2941,7 +2938,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>94</v>
+        <v>226</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2949,7 +2946,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>485</v>
+        <v>234</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2957,7 +2954,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>266</v>
+        <v>326</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2965,7 +2962,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>189</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2973,15 +2970,15 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>623</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>95</v>
+      <c r="C154" s="16" t="n">
+        <v>1066</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2989,7 +2986,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2997,7 +2994,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>287</v>
+        <v>36</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -3005,23 +3002,23 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="158" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B158" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="158" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B158" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="11" t="n">
-        <v>288</v>
+      <c r="C158" s="12" t="n">
+        <v>115393</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="11" t="n">
-        <v>330</v>
+      <c r="C159" s="16" t="n">
+        <v>1920</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -3029,7 +3026,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>877</v>
+        <v>211</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -3037,7 +3034,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>538</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -3045,7 +3042,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>257</v>
+        <v>476</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -3053,7 +3050,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>79</v>
+        <v>362</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -3061,7 +3058,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>22</v>
+        <v>342</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -3069,7 +3066,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>92</v>
+        <v>188</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -3077,7 +3074,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>200</v>
+        <v>458</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -3085,7 +3082,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>5</v>
+        <v>802</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -3093,15 +3090,15 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>265</v>
+        <v>547</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="11" t="n">
-        <v>235</v>
+      <c r="C169" s="16" t="n">
+        <v>2733</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3109,7 +3106,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>258</v>
+        <v>537</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -3117,7 +3114,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>106</v>
+        <v>257</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -3133,15 +3130,15 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="11" t="n">
-        <v>672</v>
+      <c r="C174" s="16" t="n">
+        <v>2562</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3149,7 +3146,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>133</v>
+        <v>452</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -3157,7 +3154,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>765</v>
+        <v>90</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3165,15 +3162,15 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>78</v>
+        <v>258</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="11" t="n">
-        <v>214</v>
+      <c r="C178" s="16" t="n">
+        <v>2693</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3181,7 +3178,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>88</v>
+        <v>641</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3189,15 +3186,15 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>262</v>
+        <v>133</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="11" t="n">
-        <v>260</v>
+      <c r="C181" s="16" t="n">
+        <v>7144</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3205,7 +3202,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>107</v>
+        <v>189</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3213,15 +3210,15 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>329</v>
+        <v>78</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>22</v>
+      <c r="C184" s="16" t="n">
+        <v>3536</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3229,7 +3226,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>792</v>
+        <v>302</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3237,15 +3234,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>295</v>
+        <v>107</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>88</v>
+      <c r="C187" s="16" t="n">
+        <v>4578</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3253,7 +3250,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>695</v>
+        <v>730</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3261,7 +3258,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>63</v>
+        <v>295</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3269,7 +3266,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>398</v>
+        <v>49</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3277,7 +3274,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>66</v>
+        <v>744</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3285,15 +3282,15 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>734</v>
+        <v>63</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="11" t="n">
-        <v>371</v>
+      <c r="C193" s="16" t="n">
+        <v>3503</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3301,7 +3298,7 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>455</v>
+        <v>584</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3309,23 +3306,23 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>1</v>
+        <v>371</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="11" t="n">
-        <v>673</v>
+      <c r="C196" s="16" t="n">
+        <v>3208</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="11" t="n">
-        <v>138</v>
+      <c r="C197" s="16" t="n">
+        <v>1970</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3333,7 +3330,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>687</v>
+        <v>949</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3341,15 +3338,15 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>141</v>
+        <v>412</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="16" t="n">
-        <v>2304</v>
+      <c r="C200" s="11" t="n">
+        <v>498</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3357,7 +3354,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3365,7 +3362,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="16" t="n">
-        <v>2305</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3373,23 +3370,23 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="204" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
       <c r="C204" s="16" t="n">
-        <v>1180</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>101</v>
+      <c r="C205" s="16" t="n">
+        <v>2789</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3397,7 +3394,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>133</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3405,23 +3402,23 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="208" ht="11" customHeight="true" outlineLevel="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="true" outlineLevel="3">
       <c r="B208" s="15" t="s">
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>331</v>
+        <v>252</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="11" t="n">
-        <v>22</v>
+      <c r="C209" s="16" t="n">
+        <v>2692</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3429,15 +3426,15 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="211" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="211" ht="22" customHeight="true" outlineLevel="3">
       <c r="B211" s="15" t="s">
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>360</v>
+        <v>247</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3445,7 +3442,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>85</v>
+        <v>238</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3453,15 +3450,15 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>104</v>
+        <v>267</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="11" t="n">
-        <v>44</v>
+      <c r="C214" s="16" t="n">
+        <v>3808</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3469,7 +3466,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>193</v>
+        <v>293</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3477,15 +3474,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>295</v>
+        <v>85</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>311</v>
+      <c r="C217" s="16" t="n">
+        <v>3828</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3493,7 +3490,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>830</v>
+        <v>749</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3501,15 +3498,15 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>18</v>
+        <v>311</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
       <c r="B220" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="11" t="n">
-        <v>803</v>
+      <c r="C220" s="16" t="n">
+        <v>7318</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3517,7 +3514,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>150</v>
+        <v>634</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3525,7 +3522,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>54</v>
+        <v>150</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3533,7 +3530,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>182</v>
+        <v>150</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3541,7 +3538,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>993</v>
+        <v>83</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3549,15 +3546,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="16" t="n">
-        <v>3105</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>364</v>
+      <c r="C226" s="16" t="n">
+        <v>1164</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3565,23 +3562,23 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>806</v>
+        <v>844</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="11" t="n">
-        <v>8</v>
+      <c r="C228" s="16" t="n">
+        <v>3941</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>259</v>
+      <c r="C229" s="16" t="n">
+        <v>5137</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3589,7 +3586,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>60</v>
+        <v>608</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3597,7 +3594,7 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>134</v>
+        <v>60</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3605,7 +3602,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3620,8 +3617,8 @@
       <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>396</v>
+      <c r="C234" s="16" t="n">
+        <v>3838</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3629,7 +3626,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>44</v>
+        <v>281</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3637,23 +3634,23 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>610</v>
+        <v>666</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="11" t="n">
-        <v>666</v>
+      <c r="C237" s="16" t="n">
+        <v>1136</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="11" t="n">
-        <v>600</v>
+      <c r="C238" s="16" t="n">
+        <v>4121</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3661,7 +3658,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>765</v>
+        <v>268</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3676,8 +3673,8 @@
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="11" t="n">
-        <v>198</v>
+      <c r="C241" s="16" t="n">
+        <v>3781</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3685,7 +3682,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>70</v>
+        <v>322</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3693,15 +3690,15 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>268</v>
+        <v>385</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>385</v>
+      <c r="C244" s="16" t="n">
+        <v>3492</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3709,7 +3706,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>395</v>
+        <v>222</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3717,15 +3714,15 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>278</v>
+        <v>94</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="11" t="n">
-        <v>94</v>
+      <c r="C247" s="16" t="n">
+        <v>4055</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3733,7 +3730,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="11" t="n">
-        <v>480</v>
+        <v>750</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3741,15 +3738,15 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>153</v>
+        <v>371</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>371</v>
+      <c r="C250" s="16" t="n">
+        <v>3031</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3757,7 +3754,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>396</v>
+        <v>478</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3765,7 +3762,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3773,7 +3770,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="11" t="n">
-        <v>390</v>
+        <v>147</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3781,7 +3778,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>192</v>
+        <v>39</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3789,7 +3786,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>206</v>
+        <v>576</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3797,15 +3794,15 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="257" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B257" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B257" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="11" t="n">
-        <v>33</v>
+      <c r="C257" s="12" t="n">
+        <v>15015</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3813,7 +3810,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>566</v>
+        <v>787</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3821,15 +3818,15 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="260" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B260" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="260" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="12" t="n">
-        <v>31712</v>
+      <c r="C260" s="11" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3837,7 +3834,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>875</v>
+        <v>173</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3845,7 +3842,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>851</v>
+        <v>710</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3853,23 +3850,23 @@
         <v>262</v>
       </c>
       <c r="C263" s="16" t="n">
-        <v>1005</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
       <c r="B264" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="C264" s="16" t="n">
-        <v>1071</v>
+      <c r="C264" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C265" s="16" t="n">
-        <v>2755</v>
+      <c r="C265" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3877,7 +3874,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3885,7 +3882,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>216</v>
+        <v>111</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3893,7 +3890,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>322</v>
+        <v>26</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3901,7 +3898,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>301</v>
+        <v>130</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3909,7 +3906,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>587</v>
+        <v>395</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3917,7 +3914,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>26</v>
+        <v>523</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3925,7 +3922,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>320</v>
+        <v>267</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3933,7 +3930,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>422</v>
+        <v>455</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3941,7 +3938,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>767</v>
+        <v>203</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3949,7 +3946,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>726</v>
+        <v>683</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3957,7 +3954,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>625</v>
+        <v>661</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3965,7 +3962,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>539</v>
+        <v>358</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3973,15 +3970,15 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>95</v>
+        <v>327</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="11" t="n">
-        <v>510</v>
+      <c r="C279" s="16" t="n">
+        <v>1190</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3989,7 +3986,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>855</v>
+        <v>768</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3997,7 +3994,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>485</v>
+        <v>383</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -4005,7 +4002,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>844</v>
+        <v>929</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -4013,87 +4010,87 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>932</v>
+        <v>794</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="16" t="n">
-        <v>2893</v>
+      <c r="C284" s="11" t="n">
+        <v>718</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
       <c r="B285" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="16" t="n">
-        <v>1185</v>
+      <c r="C285" s="11" t="n">
+        <v>627</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="16" t="n">
-        <v>1369</v>
+      <c r="C286" s="11" t="n">
+        <v>493</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="C287" s="16" t="n">
-        <v>1644</v>
+      <c r="C287" s="11" t="n">
+        <v>588</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="16" t="n">
-        <v>1240</v>
+      <c r="C288" s="11" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="16" t="n">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B290" s="15" t="s">
+      <c r="C289" s="11" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B290" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="11" t="n">
-        <v>773</v>
+      <c r="C290" s="12" t="n">
+        <v>4342</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="16" t="n">
-        <v>1932</v>
+      <c r="C291" s="11" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="16" t="n">
-        <v>1401</v>
+      <c r="C292" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="16" t="n">
-        <v>1813</v>
+      <c r="C293" s="11" t="n">
+        <v>346</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -4101,15 +4098,15 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B295" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="12" t="n">
-        <v>2020</v>
+      <c r="C295" s="11" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -4117,7 +4114,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>398</v>
+        <v>18</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4125,7 +4122,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>123</v>
+        <v>548</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -4133,7 +4130,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>129</v>
+        <v>793</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -4141,7 +4138,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>11</v>
+        <v>238</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -4149,7 +4146,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>52</v>
+        <v>329</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -4157,7 +4154,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>88</v>
+        <v>507</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4165,7 +4162,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>29</v>
+        <v>796</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -4173,7 +4170,7 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>288</v>
+        <v>29</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4181,23 +4178,23 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="306" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B306" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="306" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B306" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="11" t="n">
-        <v>156</v>
+      <c r="C306" s="12" t="n">
+        <v>18084</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -4205,7 +4202,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>23</v>
+        <v>122</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4213,7 +4210,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>101</v>
+        <v>155</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -4221,7 +4218,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>35</v>
+        <v>160</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -4229,7 +4226,7 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>63</v>
+        <v>299</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -4237,7 +4234,7 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>31</v>
+        <v>150</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -4245,7 +4242,7 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -4253,7 +4250,7 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>6</v>
+        <v>248</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
@@ -4261,15 +4258,15 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="315" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B315" s="14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="12" t="n">
-        <v>34360</v>
+      <c r="C315" s="11" t="n">
+        <v>449</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4277,7 +4274,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>139</v>
+        <v>262</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4285,15 +4282,15 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="318" ht="11" customHeight="true" outlineLevel="3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="318" ht="22" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>967</v>
+        <v>221</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4301,31 +4298,31 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>150</v>
+        <v>295</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="16" t="n">
-        <v>1057</v>
+      <c r="C320" s="11" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="16" t="n">
-        <v>1283</v>
+      <c r="C321" s="11" t="n">
+        <v>174</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="16" t="n">
-        <v>1704</v>
+      <c r="C322" s="11" t="n">
+        <v>837</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4333,111 +4330,111 @@
         <v>322</v>
       </c>
       <c r="C323" s="16" t="n">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="324" ht="22" customHeight="true" outlineLevel="3">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="325" ht="11" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="325" ht="22" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="326" ht="11" customHeight="true" outlineLevel="3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="326" ht="22" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="327" ht="11" customHeight="true" outlineLevel="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="327" ht="22" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="328" ht="11" customHeight="true" outlineLevel="3">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="328" ht="22" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="C328" s="16" t="n">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="329" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C328" s="11" t="n">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="329" ht="22" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="16" t="n">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="330" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C329" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="331" ht="22" customHeight="true" outlineLevel="3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="332" ht="22" customHeight="true" outlineLevel="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="332" ht="11" customHeight="true" outlineLevel="3">
       <c r="B332" s="15" t="s">
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="333" ht="22" customHeight="true" outlineLevel="3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="334" ht="22" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="335" ht="22" customHeight="true" outlineLevel="3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="336" ht="22" customHeight="true" outlineLevel="3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>382</v>
+        <v>490</v>
       </c>
     </row>
     <row r="337" ht="22" customHeight="true" outlineLevel="3">
@@ -4445,31 +4442,31 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="338" ht="22" customHeight="true" outlineLevel="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="338" ht="11" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="339" ht="22" customHeight="true" outlineLevel="3">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="11" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="340" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C339" s="16" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>71</v>
+        <v>381</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4477,7 +4474,7 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>646</v>
+        <v>727</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4485,7 +4482,7 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>364</v>
+        <v>20</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4493,23 +4490,23 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="11" t="n">
-        <v>681</v>
+      <c r="C344" s="16" t="n">
+        <v>1680</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="11" t="n">
-        <v>353</v>
+      <c r="C345" s="16" t="n">
+        <v>1931</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4517,15 +4514,15 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="347" ht="22" customHeight="true" outlineLevel="3">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="11" t="n">
-        <v>4</v>
+      <c r="C347" s="16" t="n">
+        <v>1614</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4533,127 +4530,127 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B349" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B349" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="11" t="n">
-        <v>461</v>
+      <c r="C349" s="12" t="n">
+        <v>8178</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B350" s="15" t="s">
+      <c r="B350" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B351" s="15" t="s">
+      <c r="C350" s="12" t="n">
+        <v>8178</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B351" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="16" t="n">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B352" s="15" t="s">
+      <c r="C351" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B352" s="18" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="16" t="n">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B353" s="15" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B353" s="18" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B354" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B354" s="18" t="s">
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B355" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B355" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="16" t="n">
-        <v>3199</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B356" s="15" t="s">
+      <c r="C355" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B356" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="16" t="n">
-        <v>5251</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B357" s="15" t="s">
+      <c r="C356" s="11" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B357" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="16" t="n">
-        <v>1582</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B358" s="15" t="s">
+      <c r="C357" s="11" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B358" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="16" t="n">
-        <v>5116</v>
-      </c>
-    </row>
-    <row r="359" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B359" s="15" t="s">
+      <c r="C358" s="11" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B359" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B360" s="15" t="s">
+      <c r="C359" s="16" t="n">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B360" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B361" s="15" t="s">
+      <c r="C360" s="16" t="n">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B361" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B362" s="14" t="s">
+      <c r="C361" s="16" t="n">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B362" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="C362" s="12" t="n">
-        <v>25584</v>
-      </c>
-    </row>
-    <row r="363" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B363" s="15" t="s">
+      <c r="C362" s="11" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B363" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="C363" s="11" t="n">
-        <v>891</v>
+      <c r="C363" s="12" t="n">
+        <v>9076</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4661,31 +4658,31 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="11" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C366" s="16" t="n">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="367" ht="22" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>13</v>
+        <v>132</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4693,7 +4690,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>226</v>
+        <v>434</v>
       </c>
     </row>
     <row r="369" ht="11" customHeight="true" outlineLevel="3">
@@ -4701,7 +4698,7 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>359</v>
+        <v>5</v>
       </c>
     </row>
     <row r="370" ht="11" customHeight="true" outlineLevel="3">
@@ -4709,15 +4706,15 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>469</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="C371" s="16" t="n">
-        <v>2451</v>
+      <c r="C371" s="11" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
@@ -4725,15 +4722,15 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>313</v>
+        <v>620</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="16" t="n">
-        <v>1057</v>
+      <c r="C373" s="11" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
@@ -4748,8 +4745,8 @@
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="C375" s="16" t="n">
-        <v>1198</v>
+      <c r="C375" s="11" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4757,7 +4754,7 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>346</v>
+        <v>544</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
@@ -4765,7 +4762,7 @@
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>164</v>
+        <v>386</v>
       </c>
     </row>
     <row r="378" ht="11" customHeight="true" outlineLevel="3">
@@ -4773,7 +4770,7 @@
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
@@ -4781,7 +4778,7 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>364</v>
+        <v>8</v>
       </c>
     </row>
     <row r="380" ht="11" customHeight="true" outlineLevel="3">
@@ -4789,7 +4786,7 @@
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>520</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" ht="11" customHeight="true" outlineLevel="3">
@@ -4797,7 +4794,7 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>716</v>
+        <v>390</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
@@ -4805,7 +4802,7 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>869</v>
+        <v>184</v>
       </c>
     </row>
     <row r="383" ht="11" customHeight="true" outlineLevel="3">
@@ -4813,7 +4810,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>41</v>
+        <v>96</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4821,23 +4818,23 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="385" ht="22" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="C386" s="16" t="n">
-        <v>1090</v>
+      <c r="C386" s="11" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="387" ht="11" customHeight="true" outlineLevel="3">
@@ -4845,7 +4842,7 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>821</v>
+        <v>366</v>
       </c>
     </row>
     <row r="388" ht="11" customHeight="true" outlineLevel="3">
@@ -4853,7 +4850,7 @@
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
     </row>
     <row r="389" ht="11" customHeight="true" outlineLevel="3">
@@ -4861,15 +4858,15 @@
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>131</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
@@ -4877,7 +4874,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="392" ht="11" customHeight="true" outlineLevel="3">
@@ -4885,15 +4882,15 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="393" ht="11" customHeight="true" outlineLevel="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
       <c r="B393" s="15" t="s">
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>114</v>
+        <v>3</v>
       </c>
     </row>
     <row r="394" ht="11" customHeight="true" outlineLevel="3">
@@ -4901,7 +4898,7 @@
         <v>393</v>
       </c>
       <c r="C394" s="16" t="n">
-        <v>1564</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="395" ht="11" customHeight="true" outlineLevel="3">
@@ -4916,24 +4913,24 @@
       <c r="B396" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="C396" s="16" t="n">
-        <v>3919</v>
+      <c r="C396" s="11" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="397" ht="11" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="16" t="n">
-        <v>2500</v>
+      <c r="C397" s="11" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="C398" s="16" t="n">
-        <v>1393</v>
+      <c r="C398" s="11" t="n">
+        <v>594</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
@@ -4941,15 +4938,15 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>758</v>
+        <v>185</v>
       </c>
     </row>
     <row r="400" ht="11" customHeight="true" outlineLevel="2">
       <c r="B400" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="17" t="n">
-        <v>67</v>
+      <c r="C400" s="19" t="n">
+        <v>307</v>
       </c>
     </row>
     <row r="401" ht="11" customHeight="true" outlineLevel="3">
@@ -4957,7 +4954,7 @@
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="402" ht="11" customHeight="true" outlineLevel="3">
@@ -4965,15 +4962,15 @@
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="403" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B403" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="12" t="n">
-        <v>115533</v>
+      <c r="C403" s="11" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="404" ht="11" customHeight="true" outlineLevel="3">
@@ -4981,15 +4978,15 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B405" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B405" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="16" t="n">
-        <v>1960</v>
+      <c r="C405" s="12" t="n">
+        <v>59482</v>
       </c>
     </row>
     <row r="406" ht="11" customHeight="true" outlineLevel="3">
@@ -4997,7 +4994,7 @@
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>172</v>
+        <v>102</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
@@ -5005,23 +5002,23 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
       <c r="B408" s="15" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="409" ht="22" customHeight="true" outlineLevel="3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
       <c r="B409" s="15" t="s">
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>720</v>
+        <v>45</v>
       </c>
     </row>
     <row r="410" ht="22" customHeight="true" outlineLevel="3">
@@ -5029,31 +5026,31 @@
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="411" ht="33" customHeight="true" outlineLevel="3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="411" ht="22" customHeight="true" outlineLevel="3">
       <c r="B411" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="C411" s="16" t="n">
-        <v>2441</v>
-      </c>
-    </row>
-    <row r="412" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C411" s="11" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="412" ht="33" customHeight="true" outlineLevel="3">
       <c r="B412" s="15" t="s">
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="413" ht="22" customHeight="true" outlineLevel="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="413" ht="33" customHeight="true" outlineLevel="3">
       <c r="B413" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="C413" s="11" t="n">
-        <v>70</v>
+      <c r="C413" s="16" t="n">
+        <v>1295</v>
       </c>
     </row>
     <row r="414" ht="22" customHeight="true" outlineLevel="3">
@@ -5061,7 +5058,7 @@
         <v>413</v>
       </c>
       <c r="C414" s="11" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="415" ht="22" customHeight="true" outlineLevel="3">
@@ -5069,15 +5066,15 @@
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
       <c r="B416" s="15" t="s">
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>421</v>
+        <v>26</v>
       </c>
     </row>
     <row r="417" ht="11" customHeight="true" outlineLevel="3">
@@ -5085,15 +5082,15 @@
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>572</v>
+        <v>388</v>
       </c>
     </row>
     <row r="418" ht="11" customHeight="true" outlineLevel="3">
       <c r="B418" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="C418" s="16" t="n">
-        <v>2999</v>
+      <c r="C418" s="11" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="419" ht="11" customHeight="true" outlineLevel="3">
@@ -5101,7 +5098,7 @@
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="420" ht="22" customHeight="true" outlineLevel="3">
@@ -5109,7 +5106,7 @@
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>292</v>
+        <v>421</v>
       </c>
     </row>
     <row r="421" ht="22" customHeight="true" outlineLevel="3">
@@ -5117,7 +5114,7 @@
         <v>420</v>
       </c>
       <c r="C421" s="11" t="n">
-        <v>170</v>
+        <v>391</v>
       </c>
     </row>
     <row r="422" ht="22" customHeight="true" outlineLevel="3">
@@ -5125,7 +5122,7 @@
         <v>421</v>
       </c>
       <c r="C422" s="16" t="n">
-        <v>5839</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="423" ht="11" customHeight="true" outlineLevel="3">
@@ -5133,15 +5130,15 @@
         <v>422</v>
       </c>
       <c r="C423" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="424" ht="22" customHeight="true" outlineLevel="3">
       <c r="B424" s="15" t="s">
         <v>423</v>
       </c>
       <c r="C424" s="11" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
     </row>
     <row r="425" ht="22" customHeight="true" outlineLevel="3">
@@ -5149,15 +5146,15 @@
         <v>424</v>
       </c>
       <c r="C425" s="11" t="n">
-        <v>723</v>
+        <v>25</v>
       </c>
     </row>
     <row r="426" ht="11" customHeight="true" outlineLevel="3">
       <c r="B426" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="C426" s="11" t="n">
-        <v>533</v>
+      <c r="C426" s="16" t="n">
+        <v>1204</v>
       </c>
     </row>
     <row r="427" ht="11" customHeight="true" outlineLevel="3">
@@ -5165,7 +5162,7 @@
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="428" ht="11" customHeight="true" outlineLevel="3">
@@ -5173,15 +5170,15 @@
         <v>427</v>
       </c>
       <c r="C428" s="11" t="n">
-        <v>178</v>
+        <v>22</v>
       </c>
     </row>
     <row r="429" ht="11" customHeight="true" outlineLevel="3">
       <c r="B429" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="C429" s="16" t="n">
-        <v>7428</v>
+      <c r="C429" s="11" t="n">
+        <v>748</v>
       </c>
     </row>
     <row r="430" ht="22" customHeight="true" outlineLevel="3">
@@ -5189,7 +5186,7 @@
         <v>429</v>
       </c>
       <c r="C430" s="11" t="n">
-        <v>77</v>
+        <v>234</v>
       </c>
     </row>
     <row r="431" ht="22" customHeight="true" outlineLevel="3">
@@ -5197,15 +5194,15 @@
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="432" ht="22" customHeight="true" outlineLevel="3">
       <c r="B432" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="C432" s="16" t="n">
-        <v>2054</v>
+      <c r="C432" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="433" ht="22" customHeight="true" outlineLevel="3">
@@ -5220,8 +5217,8 @@
       <c r="B434" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="C434" s="16" t="n">
-        <v>3118</v>
+      <c r="C434" s="11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="435" ht="22" customHeight="true" outlineLevel="3">
@@ -5229,7 +5226,7 @@
         <v>434</v>
       </c>
       <c r="C435" s="11" t="n">
-        <v>251</v>
+        <v>41</v>
       </c>
     </row>
     <row r="436" ht="22" customHeight="true" outlineLevel="3">
@@ -5237,23 +5234,23 @@
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>530</v>
+        <v>57</v>
       </c>
     </row>
     <row r="437" ht="22" customHeight="true" outlineLevel="3">
       <c r="B437" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="C437" s="16" t="n">
-        <v>3062</v>
+      <c r="C437" s="11" t="n">
+        <v>242</v>
       </c>
     </row>
     <row r="438" ht="22" customHeight="true" outlineLevel="3">
       <c r="B438" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="11" t="n">
-        <v>40</v>
+      <c r="C438" s="16" t="n">
+        <v>1240</v>
       </c>
     </row>
     <row r="439" ht="22" customHeight="true" outlineLevel="3">
@@ -5261,15 +5258,15 @@
         <v>438</v>
       </c>
       <c r="C439" s="11" t="n">
-        <v>180</v>
+        <v>301</v>
       </c>
     </row>
     <row r="440" ht="22" customHeight="true" outlineLevel="3">
       <c r="B440" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="C440" s="16" t="n">
-        <v>3672</v>
+      <c r="C440" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="441" ht="22" customHeight="true" outlineLevel="3">
@@ -5277,7 +5274,7 @@
         <v>440</v>
       </c>
       <c r="C441" s="11" t="n">
-        <v>8</v>
+        <v>220</v>
       </c>
     </row>
     <row r="442" ht="22" customHeight="true" outlineLevel="3">
@@ -5285,7 +5282,7 @@
         <v>441</v>
       </c>
       <c r="C442" s="11" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="443" ht="22" customHeight="true" outlineLevel="3">
@@ -5293,15 +5290,15 @@
         <v>442</v>
       </c>
       <c r="C443" s="11" t="n">
-        <v>294</v>
+        <v>8</v>
       </c>
     </row>
     <row r="444" ht="22" customHeight="true" outlineLevel="3">
       <c r="B444" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="C444" s="16" t="n">
-        <v>2565</v>
+      <c r="C444" s="11" t="n">
+        <v>339</v>
       </c>
     </row>
     <row r="445" ht="22" customHeight="true" outlineLevel="3">
@@ -5309,7 +5306,7 @@
         <v>444</v>
       </c>
       <c r="C445" s="11" t="n">
-        <v>17</v>
+        <v>226</v>
       </c>
     </row>
     <row r="446" ht="22" customHeight="true" outlineLevel="3">
@@ -5317,7 +5314,7 @@
         <v>445</v>
       </c>
       <c r="C446" s="11" t="n">
-        <v>137</v>
+        <v>610</v>
       </c>
     </row>
     <row r="447" ht="22" customHeight="true" outlineLevel="3">
@@ -5325,7 +5322,7 @@
         <v>446</v>
       </c>
       <c r="C447" s="11" t="n">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="448" ht="22" customHeight="true" outlineLevel="3">
@@ -5333,7 +5330,7 @@
         <v>447</v>
       </c>
       <c r="C448" s="11" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="449" ht="22" customHeight="true" outlineLevel="3">
@@ -5341,7 +5338,7 @@
         <v>448</v>
       </c>
       <c r="C449" s="11" t="n">
-        <v>864</v>
+        <v>23</v>
       </c>
     </row>
     <row r="450" ht="22" customHeight="true" outlineLevel="3">
@@ -5349,7 +5346,7 @@
         <v>449</v>
       </c>
       <c r="C450" s="11" t="n">
-        <v>481</v>
+        <v>969</v>
       </c>
     </row>
     <row r="451" ht="22" customHeight="true" outlineLevel="3">
@@ -5357,7 +5354,7 @@
         <v>450</v>
       </c>
       <c r="C451" s="11" t="n">
-        <v>528</v>
+        <v>198</v>
       </c>
     </row>
     <row r="452" ht="22" customHeight="true" outlineLevel="3">
@@ -5365,7 +5362,7 @@
         <v>451</v>
       </c>
       <c r="C452" s="16" t="n">
-        <v>5908</v>
+        <v>3688</v>
       </c>
     </row>
     <row r="453" ht="22" customHeight="true" outlineLevel="3">
@@ -5373,7 +5370,7 @@
         <v>452</v>
       </c>
       <c r="C453" s="11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="454" ht="22" customHeight="true" outlineLevel="3">
@@ -5381,7 +5378,7 @@
         <v>453</v>
       </c>
       <c r="C454" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="455" ht="22" customHeight="true" outlineLevel="3">
@@ -5389,7 +5386,7 @@
         <v>454</v>
       </c>
       <c r="C455" s="11" t="n">
-        <v>694</v>
+        <v>16</v>
       </c>
     </row>
     <row r="456" ht="11" customHeight="true" outlineLevel="3">
@@ -5397,7 +5394,7 @@
         <v>455</v>
       </c>
       <c r="C456" s="11" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="457" ht="11" customHeight="true" outlineLevel="3">
@@ -5412,8 +5409,8 @@
       <c r="B458" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="C458" s="16" t="n">
-        <v>1535</v>
+      <c r="C458" s="11" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="459" ht="11" customHeight="true" outlineLevel="3">
@@ -5421,7 +5418,7 @@
         <v>458</v>
       </c>
       <c r="C459" s="11" t="n">
-        <v>330</v>
+        <v>15</v>
       </c>
     </row>
     <row r="460" ht="22" customHeight="true" outlineLevel="3">
@@ -5429,7 +5426,7 @@
         <v>459</v>
       </c>
       <c r="C460" s="11" t="n">
-        <v>178</v>
+        <v>153</v>
       </c>
     </row>
     <row r="461" ht="22" customHeight="true" outlineLevel="3">
@@ -5437,7 +5434,7 @@
         <v>460</v>
       </c>
       <c r="C461" s="11" t="n">
-        <v>270</v>
+        <v>197</v>
       </c>
     </row>
     <row r="462" ht="22" customHeight="true" outlineLevel="3">
@@ -5445,7 +5442,7 @@
         <v>461</v>
       </c>
       <c r="C462" s="11" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="463" ht="22" customHeight="true" outlineLevel="3">
@@ -5453,7 +5450,7 @@
         <v>462</v>
       </c>
       <c r="C463" s="11" t="n">
-        <v>892</v>
+        <v>13</v>
       </c>
     </row>
     <row r="464" ht="22" customHeight="true" outlineLevel="3">
@@ -5461,7 +5458,7 @@
         <v>463</v>
       </c>
       <c r="C464" s="11" t="n">
-        <v>176</v>
+        <v>308</v>
       </c>
     </row>
     <row r="465" ht="22" customHeight="true" outlineLevel="3">
@@ -5469,15 +5466,15 @@
         <v>464</v>
       </c>
       <c r="C465" s="11" t="n">
-        <v>413</v>
+        <v>208</v>
       </c>
     </row>
     <row r="466" ht="22" customHeight="true" outlineLevel="3">
       <c r="B466" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="C466" s="16" t="n">
-        <v>2523</v>
+      <c r="C466" s="11" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="467" ht="11" customHeight="true" outlineLevel="3">
@@ -5485,7 +5482,7 @@
         <v>466</v>
       </c>
       <c r="C467" s="11" t="n">
-        <v>407</v>
+        <v>217</v>
       </c>
     </row>
     <row r="468" ht="22" customHeight="true" outlineLevel="3">
@@ -5493,15 +5490,15 @@
         <v>467</v>
       </c>
       <c r="C468" s="11" t="n">
-        <v>208</v>
+        <v>5</v>
       </c>
     </row>
     <row r="469" ht="22" customHeight="true" outlineLevel="3">
       <c r="B469" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="C469" s="11" t="n">
-        <v>1</v>
+      <c r="C469" s="16" t="n">
+        <v>1460</v>
       </c>
     </row>
     <row r="470" ht="11" customHeight="true" outlineLevel="3">
@@ -5509,7 +5506,7 @@
         <v>469</v>
       </c>
       <c r="C470" s="11" t="n">
-        <v>298</v>
+        <v>61</v>
       </c>
     </row>
     <row r="471" ht="22" customHeight="true" outlineLevel="3">
@@ -5517,7 +5514,7 @@
         <v>470</v>
       </c>
       <c r="C471" s="11" t="n">
-        <v>7</v>
+        <v>921</v>
       </c>
     </row>
     <row r="472" ht="11" customHeight="true" outlineLevel="3">
@@ -5525,15 +5522,15 @@
         <v>471</v>
       </c>
       <c r="C472" s="11" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
     </row>
     <row r="473" ht="22" customHeight="true" outlineLevel="3">
       <c r="B473" s="15" t="s">
         <v>472</v>
       </c>
-      <c r="C473" s="11" t="n">
-        <v>505</v>
+      <c r="C473" s="16" t="n">
+        <v>1352</v>
       </c>
     </row>
     <row r="474" ht="11" customHeight="true" outlineLevel="3">
@@ -5541,23 +5538,23 @@
         <v>473</v>
       </c>
       <c r="C474" s="11" t="n">
-        <v>128</v>
+        <v>11</v>
       </c>
     </row>
     <row r="475" ht="22" customHeight="true" outlineLevel="3">
       <c r="B475" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="C475" s="11" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="476" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C475" s="16" t="n">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="476" ht="11" customHeight="true" outlineLevel="3">
       <c r="B476" s="15" t="s">
         <v>475</v>
       </c>
       <c r="C476" s="11" t="n">
-        <v>640</v>
+        <v>403</v>
       </c>
     </row>
     <row r="477" ht="11" customHeight="true" outlineLevel="3">
@@ -5565,7 +5562,7 @@
         <v>476</v>
       </c>
       <c r="C477" s="11" t="n">
-        <v>764</v>
+        <v>160</v>
       </c>
     </row>
     <row r="478" ht="11" customHeight="true" outlineLevel="3">
@@ -5573,7 +5570,7 @@
         <v>477</v>
       </c>
       <c r="C478" s="16" t="n">
-        <v>12267</v>
+        <v>9094</v>
       </c>
     </row>
     <row r="479" ht="11" customHeight="true" outlineLevel="3">
@@ -5581,23 +5578,23 @@
         <v>478</v>
       </c>
       <c r="C479" s="11" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="480" ht="11" customHeight="true" outlineLevel="3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="480" ht="22" customHeight="true" outlineLevel="3">
       <c r="B480" s="15" t="s">
         <v>479</v>
       </c>
       <c r="C480" s="11" t="n">
-        <v>348</v>
+        <v>160</v>
       </c>
     </row>
     <row r="481" ht="22" customHeight="true" outlineLevel="3">
       <c r="B481" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="C481" s="11" t="n">
-        <v>160</v>
+      <c r="C481" s="16" t="n">
+        <v>4612</v>
       </c>
     </row>
     <row r="482" ht="11" customHeight="true" outlineLevel="3">
@@ -5605,7 +5602,7 @@
         <v>481</v>
       </c>
       <c r="C482" s="11" t="n">
-        <v>716</v>
+        <v>156</v>
       </c>
     </row>
     <row r="483" ht="22" customHeight="true" outlineLevel="3">
@@ -5613,15 +5610,15 @@
         <v>482</v>
       </c>
       <c r="C483" s="11" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="484" ht="11" customHeight="true" outlineLevel="3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="484" ht="22" customHeight="true" outlineLevel="3">
       <c r="B484" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="C484" s="11" t="n">
-        <v>29</v>
+      <c r="C484" s="16" t="n">
+        <v>4115</v>
       </c>
     </row>
     <row r="485" ht="11" customHeight="true" outlineLevel="3">
@@ -5629,23 +5626,23 @@
         <v>484</v>
       </c>
       <c r="C485" s="11" t="n">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="486" ht="11" customHeight="true" outlineLevel="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="486" ht="22" customHeight="true" outlineLevel="3">
       <c r="B486" s="15" t="s">
         <v>485</v>
       </c>
       <c r="C486" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="487" ht="11" customHeight="true" outlineLevel="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="487" ht="22" customHeight="true" outlineLevel="3">
       <c r="B487" s="15" t="s">
         <v>486</v>
       </c>
-      <c r="C487" s="11" t="n">
-        <v>910</v>
+      <c r="C487" s="16" t="n">
+        <v>7482</v>
       </c>
     </row>
     <row r="488" ht="11" customHeight="true" outlineLevel="3">
@@ -5653,7 +5650,7 @@
         <v>487</v>
       </c>
       <c r="C488" s="11" t="n">
-        <v>632</v>
+        <v>430</v>
       </c>
     </row>
     <row r="489" ht="11" customHeight="true" outlineLevel="3">
@@ -5661,39 +5658,39 @@
         <v>488</v>
       </c>
       <c r="C489" s="11" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
     </row>
     <row r="490" ht="11" customHeight="true" outlineLevel="3">
       <c r="B490" s="15" t="s">
         <v>489</v>
       </c>
-      <c r="C490" s="16" t="n">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="491" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C490" s="11" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="491" ht="11" customHeight="true" outlineLevel="3">
       <c r="B491" s="15" t="s">
         <v>490</v>
       </c>
       <c r="C491" s="11" t="n">
-        <v>8</v>
+        <v>649</v>
       </c>
     </row>
     <row r="492" ht="11" customHeight="true" outlineLevel="3">
       <c r="B492" s="15" t="s">
         <v>491</v>
       </c>
-      <c r="C492" s="11" t="n">
-        <v>422</v>
+      <c r="C492" s="16" t="n">
+        <v>1010</v>
       </c>
     </row>
     <row r="493" ht="22" customHeight="true" outlineLevel="3">
       <c r="B493" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="C493" s="16" t="n">
-        <v>1205</v>
+      <c r="C493" s="11" t="n">
+        <v>876</v>
       </c>
     </row>
     <row r="494" ht="22" customHeight="true" outlineLevel="3">
@@ -5701,63 +5698,55 @@
         <v>493</v>
       </c>
       <c r="C494" s="11" t="n">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="495" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B495" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="495" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B495" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="C495" s="12" t="n">
-        <v>34556</v>
-      </c>
-    </row>
-    <row r="496" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B496" s="19" t="s">
+      <c r="C495" s="11" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="496" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B496" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="C496" s="11" t="n">
-        <v>924</v>
+      <c r="C496" s="12" t="n">
+        <v>2822</v>
       </c>
     </row>
     <row r="497" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B497" s="19" t="s">
+      <c r="B497" s="18" t="s">
         <v>496</v>
       </c>
-      <c r="C497" s="16" t="n">
-        <v>1344</v>
+      <c r="C497" s="11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="498" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B498" s="19" t="s">
+      <c r="B498" s="18" t="s">
         <v>497</v>
       </c>
-      <c r="C498" s="16" t="n">
-        <v>14560</v>
+      <c r="C498" s="11" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="499" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B499" s="19" t="s">
+      <c r="B499" s="18" t="s">
         <v>498</v>
       </c>
       <c r="C499" s="16" t="n">
-        <v>8448</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="500" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B500" s="19" t="s">
+      <c r="B500" s="18" t="s">
         <v>499</v>
       </c>
-      <c r="C500" s="16" t="n">
-        <v>2880</v>
-      </c>
-    </row>
-    <row r="501" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B501" s="19" t="s">
-        <v>500</v>
-      </c>
-      <c r="C501" s="16" t="n">
-        <v>6400</v>
+      <c r="C500" s="11" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 02.12.2025 15:35:16</t>
+    <t>Период: на 23.12.2025 16:15:15</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -71,21 +71,9 @@
     <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт</t>
-  </si>
-  <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Желе вишня УБ 78г /56шт</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -98,21 +86,15 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт</t>
-  </si>
-  <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -143,12 +125,18 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт</t>
   </si>
   <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
   </si>
   <si>
@@ -182,9 +170,6 @@
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
@@ -194,10 +179,7 @@
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
-    <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
+    <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
@@ -263,9 +245,6 @@
     <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
-    <t>Перець духмяний УБ 20г /22шт</t>
-  </si>
-  <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
   </si>
   <si>
@@ -299,12 +278,18 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -326,21 +311,21 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -398,9 +383,6 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
-  </si>
-  <si>
     <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
   </si>
   <si>
@@ -413,12 +395,12 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -428,6 +410,9 @@
     <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -467,9 +452,6 @@
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
-  </si>
-  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
@@ -533,9 +515,6 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
@@ -587,9 +566,6 @@
     <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -638,9 +614,6 @@
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
   </si>
   <si>
@@ -650,9 +623,6 @@
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -686,9 +656,6 @@
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -728,9 +695,6 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
@@ -749,6 +713,9 @@
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -770,6 +737,9 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Бім-Бом РЦ 200г /11шт</t>
+  </si>
+  <si>
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
@@ -818,6 +788,9 @@
     <t>Lollipops GUM Cola КрКФ 0.92кг /9шт</t>
   </si>
   <si>
+    <t>Lollipops GUM Фруктовий мікс РЦ 0.92кг /9шт</t>
+  </si>
+  <si>
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
@@ -830,6 +803,9 @@
     <t>Milky Splash з молочною начинкою ВКФ 1кг /5пак</t>
   </si>
   <si>
+    <t>Minky Binky з желейною начинкою РЦ 1кг /6пак</t>
+  </si>
+  <si>
     <t>Mintex Mint зі смаком м'яти ВКФ 1кг /9шт</t>
   </si>
   <si>
@@ -872,13 +848,16 @@
     <t>Молочна крапля ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>Молочна крапля КрКФ 1кг /7пак /</t>
+  </si>
+  <si>
     <t>Рачки ВКФ 1кг /7пак /</t>
   </si>
   <si>
     <t>Рошен джус мікс РЦ 1кг /8пак /</t>
   </si>
   <si>
-    <t>Рошен евкаліпт-ментол КрКФ 1кг /8пак /</t>
+    <t>Цитрусовий мікс РЦ 1кг /7пак /</t>
   </si>
   <si>
     <t>Шалена бджілка ВКФ 1кг /9пак</t>
@@ -899,6 +878,9 @@
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
+    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
@@ -929,6 +911,9 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -995,21 +980,33 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 135г /21шт /</t>
   </si>
   <si>
+    <t>Lovita Jelly Cookies з желейною начинкою какао + вишня ККФ 420г /7шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
@@ -1070,30 +1067,9 @@
     <t>ПОДАРУНКИ 2026</t>
   </si>
   <si>
-    <t>Н/п №1 26 Солодка хатинка РЦ 274г /10шт UA+GR</t>
-  </si>
-  <si>
     <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
   </si>
   <si>
-    <t>Н/п №11 26 Новорічний будиночок РЦ 729г /6шт</t>
-  </si>
-  <si>
-    <t>Н/п №12 26 Годівниця для птахів РЦ 918г /2шт</t>
-  </si>
-  <si>
-    <t>Н/п №2 26 Новорічна сумочка РЦ 330г /8шт</t>
-  </si>
-  <si>
-    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
-  </si>
-  <si>
-    <t>Н/п №4 26 Новорічна ялинка РЦ 388г /9шт</t>
-  </si>
-  <si>
-    <t>Н/п №5 26 Ведмедик Roshen РЦ 426г /12шт</t>
-  </si>
-  <si>
     <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
   </si>
   <si>
@@ -1103,9 +1079,6 @@
     <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
   </si>
   <si>
-    <t>Н/п №9 26 Різдвяний вінок РЦ 598г /6шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
@@ -1127,22 +1100,28 @@
     <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
-    <t>Galaretka Roshen РЦ 1кг /9пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ko-Ko Choco White 1кг/5</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
@@ -1151,30 +1130,33 @@
     <t>KONAFETTO nero ККФ 1кг /5пак /</t>
   </si>
   <si>
+    <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
+  </si>
+  <si>
+    <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
+    <t>Milaxy ВКФ 1кг /4пак</t>
+  </si>
+  <si>
     <t>Sorrento ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Winter dream ВКФ 1кг /5пак</t>
-  </si>
-  <si>
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
-    <t>Ліщина ВКФ 1кг /6пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1187,42 +1169,42 @@
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
   </si>
   <si>
@@ -1238,15 +1220,9 @@
     <t>Lacmi Big Bite молочний ВКФ 200г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
@@ -1256,18 +1232,18 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
@@ -1289,7 +1265,10 @@
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
+  </si>
+  <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
@@ -1304,22 +1283,16 @@
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
@@ -1331,9 +1304,6 @@
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -1343,9 +1313,6 @@
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
@@ -1355,42 +1322,30 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з сезамом ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1403,21 +1358,15 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1445,9 +1394,6 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1481,7 +1427,13 @@
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
+  </si>
+  <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
@@ -1508,6 +1460,9 @@
     <t>ФІГУРКИ</t>
   </si>
   <si>
+    <t>Кролик Roshen зимовий ВКФ 100г /12шт</t>
+  </si>
+  <si>
     <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
   </si>
   <si>
@@ -1515,6 +1470,12 @@
   </si>
   <si>
     <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
   </si>
   <si>
     <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
@@ -1741,14 +1702,14 @@
     <xf numFmtId="52" fontId="5" fillId="5" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1769,7 +1730,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C500"/>
+  <dimension ref="C487"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1834,7 +1795,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>618</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1842,7 +1803,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>467170</v>
+        <v>453025</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1850,7 +1811,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>61176</v>
+        <v>84079</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1858,23 +1819,23 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>15302</v>
+        <v>7697</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="16" t="n">
-        <v>1987</v>
+      <c r="C15" s="11" t="n">
+        <v>727</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>1301</v>
+      <c r="C16" s="11" t="n">
+        <v>912</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1882,7 +1843,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>504</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
@@ -1890,7 +1851,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>869</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1898,7 +1859,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>36</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1906,7 +1867,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>887</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1914,7 +1875,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>448</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1922,7 +1883,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>42</v>
+        <v>973</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1930,15 +1891,15 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>488</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="16" t="n">
-        <v>2061</v>
+      <c r="C24" s="11" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1946,7 +1907,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>36</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1954,7 +1915,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>912</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1962,7 +1923,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>32</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1970,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>1120</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1978,39 +1939,39 @@
         <v>28</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="30" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B30" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="30" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B30" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="16" t="n">
-        <v>1004</v>
+      <c r="C30" s="12" t="n">
+        <v>34971</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>122</v>
+      <c r="C31" s="16" t="n">
+        <v>4591</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>668</v>
+      <c r="C32" s="16" t="n">
+        <v>7374</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>325</v>
+      <c r="C33" s="16" t="n">
+        <v>1767</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -2018,7 +1979,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>1714</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -2026,23 +1987,23 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="36" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B36" s="14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="12" t="n">
-        <v>20939</v>
+      <c r="C36" s="16" t="n">
+        <v>7033</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="16" t="n">
-        <v>1994</v>
+      <c r="C37" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -2050,7 +2011,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>10770</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -2058,7 +2019,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>1767</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -2066,79 +2027,79 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>884</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>350</v>
+      <c r="C41" s="16" t="n">
+        <v>1227</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>24</v>
+      <c r="C42" s="16" t="n">
+        <v>1388</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>415</v>
+      <c r="C43" s="16" t="n">
+        <v>1287</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B45" s="15" t="s">
+      <c r="C44" s="16" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="45" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B45" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>132</v>
+      <c r="C45" s="12" t="n">
+        <v>10950</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="16" t="n">
-        <v>1561</v>
+      <c r="C46" s="11" t="n">
+        <v>468</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
       <c r="B47" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="16" t="n">
-        <v>1469</v>
+      <c r="C47" s="11" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="16" t="n">
-        <v>1565</v>
-      </c>
-    </row>
-    <row r="49" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B49" s="14" t="s">
+      <c r="C48" s="11" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="49" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B49" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="12" t="n">
-        <v>6912</v>
+      <c r="C49" s="11" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2146,7 +2107,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>408</v>
+        <v>674</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2154,7 +2115,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>256</v>
+        <v>564</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2162,7 +2123,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>168</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2170,7 +2131,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>154</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2178,7 +2139,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>376</v>
+        <v>925</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -2186,7 +2147,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>120</v>
+        <v>612</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2194,7 +2155,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2202,7 +2163,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>257</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2210,7 +2171,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>633</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -2218,7 +2179,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>134</v>
+        <v>626</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2226,7 +2187,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>98</v>
+        <v>285</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2234,7 +2195,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>317</v>
+        <v>499</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2242,7 +2203,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>388</v>
+        <v>702</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2250,7 +2211,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>45</v>
+        <v>533</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2258,15 +2219,15 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>62</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="11" t="n">
-        <v>973</v>
+      <c r="C65" s="16" t="n">
+        <v>2077</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2274,15 +2235,15 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="67" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B67" s="15" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B67" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>295</v>
+      <c r="C67" s="12" t="n">
+        <v>30461</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2290,7 +2251,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>381</v>
+        <v>563</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2298,15 +2259,15 @@
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>153</v>
+        <v>884</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>197</v>
+      <c r="C70" s="16" t="n">
+        <v>1591</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2314,23 +2275,23 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>142</v>
+        <v>860</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="11" t="n">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="73" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B73" s="14" t="s">
+      <c r="C72" s="16" t="n">
+        <v>5335</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="12" t="n">
-        <v>18023</v>
+      <c r="C73" s="11" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2338,15 +2299,15 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>809</v>
+        <v>885</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>560</v>
+      <c r="C75" s="16" t="n">
+        <v>3414</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2354,15 +2315,15 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>886</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>844</v>
+      <c r="C77" s="16" t="n">
+        <v>4198</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2370,7 +2331,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>1442</v>
+        <v>10696</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2378,15 +2339,15 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>1443</v>
+      <c r="C80" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2394,7 +2355,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>433</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
@@ -2402,55 +2363,55 @@
         <v>81</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B83" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B83" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B84" s="15" t="s">
+      <c r="C83" s="12" t="n">
+        <v>368946</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B84" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="11" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C84" s="12" t="n">
+        <v>130233</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>8220</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+        <v>6589</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="16" t="n">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="87" ht="11" customHeight="true" outlineLevel="3">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>90</v>
+      <c r="C87" s="16" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>44</v>
+      <c r="C88" s="16" t="n">
+        <v>14000</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2458,31 +2419,31 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B90" s="13" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="12" t="n">
-        <v>405994</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B91" s="14" t="s">
+      <c r="C90" s="16" t="n">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="12" t="n">
-        <v>149438</v>
+      <c r="C91" s="16" t="n">
+        <v>18045</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="16" t="n">
-        <v>14376</v>
+      <c r="C92" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true" outlineLevel="3">
@@ -2490,31 +2451,31 @@
         <v>92</v>
       </c>
       <c r="C93" s="16" t="n">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="16" t="n">
-        <v>6520</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C95" s="16" t="n">
+        <v>9289</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="16" t="n">
-        <v>24325</v>
+        <v>8495</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="true" outlineLevel="3">
@@ -2522,7 +2483,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="16" t="n">
-        <v>4075</v>
+        <v>9919</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="true" outlineLevel="3">
@@ -2530,7 +2491,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="16" t="n">
-        <v>2320</v>
+        <v>17325</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
@@ -2538,7 +2499,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="16" t="n">
-        <v>1020</v>
+        <v>5955</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
@@ -2546,7 +2507,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="16" t="n">
-        <v>22575</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
@@ -2554,79 +2515,79 @@
         <v>100</v>
       </c>
       <c r="C101" s="16" t="n">
-        <v>23386</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>626</v>
+      <c r="C102" s="16" t="n">
+        <v>9110</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="11" t="n">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B104" s="15" t="s">
+      <c r="C103" s="16" t="n">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B104" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C104" s="12" t="n">
+        <v>7682</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="16" t="n">
-        <v>29370</v>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="true" outlineLevel="3">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="16" t="n">
-        <v>17375</v>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C107" s="11" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B109" s="14" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="12" t="n">
-        <v>6390</v>
+      <c r="C109" s="16" t="n">
+        <v>1394</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="16" t="n">
-        <v>1084</v>
+      <c r="C110" s="11" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2634,7 +2595,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>198</v>
+        <v>398</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2649,8 +2610,8 @@
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="16" t="n">
-        <v>1145</v>
+      <c r="C113" s="11" t="n">
+        <v>486</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2658,7 +2619,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>14</v>
+        <v>493</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2666,7 +2627,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>34</v>
+        <v>208</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2674,7 +2635,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>573</v>
+        <v>559</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2682,23 +2643,23 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="118" ht="11" customHeight="true" outlineLevel="3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B119" s="15" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B119" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="11" t="n">
-        <v>238</v>
+      <c r="C119" s="12" t="n">
+        <v>26115</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2706,7 +2667,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>385</v>
+        <v>670</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2714,7 +2675,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>238</v>
+        <v>415</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2722,63 +2683,63 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="123" ht="22" customHeight="true" outlineLevel="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B124" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="12" t="n">
-        <v>20289</v>
+      <c r="C124" s="11" t="n">
+        <v>321</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>97</v>
+      <c r="C125" s="16" t="n">
+        <v>3681</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="11" t="n">
-        <v>537</v>
+      <c r="C126" s="16" t="n">
+        <v>1700</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>130</v>
+      <c r="C127" s="16" t="n">
+        <v>2898</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="11" t="n">
-        <v>26</v>
+      <c r="C128" s="16" t="n">
+        <v>3400</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
       <c r="B129" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="11" t="n">
-        <v>698</v>
+      <c r="C129" s="16" t="n">
+        <v>3224</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2786,39 +2747,39 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="16" t="n">
-        <v>1886</v>
+      <c r="C131" s="11" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
       <c r="B132" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="16" t="n">
-        <v>1978</v>
+      <c r="C132" s="11" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="16" t="n">
-        <v>5225</v>
+      <c r="C133" s="11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
       <c r="B134" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="16" t="n">
-        <v>1400</v>
+      <c r="C134" s="11" t="n">
+        <v>142</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2826,15 +2787,15 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>314</v>
+        <v>190</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="11" t="n">
-        <v>10</v>
+      <c r="C136" s="16" t="n">
+        <v>1017</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2842,7 +2803,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>218</v>
+        <v>840</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2850,15 +2811,15 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>26</v>
+        <v>817</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="11" t="n">
-        <v>257</v>
+      <c r="C139" s="16" t="n">
+        <v>1109</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2866,23 +2827,23 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>214</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
       <c r="B141" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="16" t="n">
-        <v>1044</v>
+      <c r="C141" s="11" t="n">
+        <v>446</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="11" t="n">
-        <v>965</v>
+      <c r="C142" s="16" t="n">
+        <v>1770</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2890,7 +2851,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>362</v>
+        <v>208</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2898,7 +2859,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>424</v>
+        <v>182</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2906,7 +2867,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>464</v>
+        <v>269</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2914,7 +2875,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>418</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2922,15 +2883,15 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>718</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
       <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="11" t="n">
-        <v>408</v>
+      <c r="C148" s="16" t="n">
+        <v>1542</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2938,7 +2899,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>226</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2946,7 +2907,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>234</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2954,31 +2915,31 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B152" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B152" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>282</v>
+      <c r="C152" s="12" t="n">
+        <v>84849</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="11" t="n">
-        <v>1</v>
+      <c r="C153" s="16" t="n">
+        <v>1624</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="16" t="n">
-        <v>1066</v>
+      <c r="C154" s="11" t="n">
+        <v>513</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2986,7 +2947,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>28</v>
+        <v>316</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2994,7 +2955,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>36</v>
+        <v>584</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -3002,23 +2963,23 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="158" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B158" s="14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="158" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B158" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="12" t="n">
-        <v>115393</v>
+      <c r="C158" s="11" t="n">
+        <v>581</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="16" t="n">
-        <v>1920</v>
+      <c r="C159" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -3026,7 +2987,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>211</v>
+        <v>538</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -3034,7 +2995,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>412</v>
+        <v>556</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -3042,15 +3003,15 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>476</v>
+        <v>533</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="11" t="n">
-        <v>362</v>
+      <c r="C163" s="16" t="n">
+        <v>2725</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -3058,7 +3019,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>342</v>
+        <v>517</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -3066,7 +3027,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>188</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -3074,15 +3035,15 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>458</v>
+        <v>92</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="11" t="n">
-        <v>802</v>
+      <c r="C167" s="16" t="n">
+        <v>2173</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -3090,15 +3051,15 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>547</v>
+        <v>331</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="16" t="n">
-        <v>2733</v>
+      <c r="C169" s="11" t="n">
+        <v>882</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3106,15 +3067,15 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>537</v>
+        <v>258</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>257</v>
+      <c r="C171" s="16" t="n">
+        <v>1361</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -3122,7 +3083,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>44</v>
+        <v>447</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -3130,7 +3091,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -3138,7 +3099,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="16" t="n">
-        <v>2562</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3146,7 +3107,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>452</v>
+        <v>184</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -3154,23 +3115,23 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="11" t="n">
-        <v>258</v>
+      <c r="C177" s="16" t="n">
+        <v>2980</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="16" t="n">
-        <v>2693</v>
+      <c r="C178" s="11" t="n">
+        <v>204</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -3178,23 +3139,23 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>641</v>
+        <v>107</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>133</v>
+      <c r="C180" s="16" t="n">
+        <v>2410</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="16" t="n">
-        <v>7144</v>
+      <c r="C181" s="11" t="n">
+        <v>307</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3202,7 +3163,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>189</v>
+        <v>295</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3210,23 +3171,23 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>78</v>
+        <v>744</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="16" t="n">
-        <v>3536</v>
+      <c r="C184" s="11" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="11" t="n">
-        <v>302</v>
+      <c r="C185" s="16" t="n">
+        <v>3256</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3234,15 +3195,15 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>107</v>
+        <v>944</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="16" t="n">
-        <v>4578</v>
+      <c r="C187" s="11" t="n">
+        <v>371</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -3250,7 +3211,7 @@
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>730</v>
+        <v>543</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3258,7 +3219,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>295</v>
+        <v>551</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3266,7 +3227,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>49</v>
+        <v>942</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3274,7 +3235,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>744</v>
+        <v>201</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3282,23 +3243,23 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>63</v>
+        <v>476</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="16" t="n">
-        <v>3503</v>
+      <c r="C193" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="11" t="n">
-        <v>584</v>
+      <c r="C194" s="16" t="n">
+        <v>1534</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3306,15 +3267,15 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="196" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="16" t="n">
-        <v>3208</v>
+      <c r="C196" s="11" t="n">
+        <v>286</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3322,7 +3283,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="16" t="n">
-        <v>1970</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3330,23 +3291,23 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="199" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" ht="22" customHeight="true" outlineLevel="3">
       <c r="B199" s="15" t="s">
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>412</v>
+        <v>113</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="11" t="n">
-        <v>498</v>
+      <c r="C200" s="16" t="n">
+        <v>2541</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3354,15 +3315,15 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="16" t="n">
-        <v>1649</v>
+      <c r="C202" s="11" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3370,23 +3331,23 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="204" ht="22" customHeight="true" outlineLevel="3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
       <c r="C204" s="16" t="n">
-        <v>1107</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="16" t="n">
-        <v>2789</v>
+      <c r="C205" s="11" t="n">
+        <v>287</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3394,47 +3355,47 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="11" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="208" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C207" s="16" t="n">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="208" ht="11" customHeight="true" outlineLevel="3">
       <c r="B208" s="15" t="s">
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>252</v>
+        <v>304</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="16" t="n">
-        <v>2692</v>
+      <c r="C209" s="11" t="n">
+        <v>311</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="211" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C210" s="16" t="n">
+        <v>4478</v>
+      </c>
+    </row>
+    <row r="211" ht="11" customHeight="true" outlineLevel="3">
       <c r="B211" s="15" t="s">
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>247</v>
+        <v>626</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3442,7 +3403,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>238</v>
+        <v>150</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3450,7 +3411,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>267</v>
+        <v>223</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3458,7 +3419,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="16" t="n">
-        <v>3808</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3466,7 +3427,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>293</v>
+        <v>525</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3474,7 +3435,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>85</v>
+        <v>844</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3482,15 +3443,15 @@
         <v>216</v>
       </c>
       <c r="C217" s="16" t="n">
-        <v>3828</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="11" t="n">
-        <v>749</v>
+      <c r="C218" s="16" t="n">
+        <v>3718</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3498,15 +3459,15 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>311</v>
+        <v>592</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
       <c r="B220" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="16" t="n">
-        <v>7318</v>
+      <c r="C220" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3514,7 +3475,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>634</v>
+        <v>310</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3522,15 +3483,15 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>150</v>
+        <v>111</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="11" t="n">
-        <v>150</v>
+      <c r="C223" s="16" t="n">
+        <v>2744</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3538,15 +3499,15 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>83</v>
+        <v>220</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
       <c r="B225" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="16" t="n">
-        <v>2507</v>
+      <c r="C225" s="11" t="n">
+        <v>666</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3554,7 +3515,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="16" t="n">
-        <v>1164</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3562,15 +3523,15 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>844</v>
+        <v>907</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="16" t="n">
-        <v>3941</v>
+      <c r="C228" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3578,7 +3539,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="16" t="n">
-        <v>5137</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3586,7 +3547,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>608</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3594,31 +3555,31 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>60</v>
+        <v>385</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>310</v>
+      <c r="C232" s="16" t="n">
+        <v>2766</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="11" t="n">
-        <v>111</v>
+      <c r="C233" s="16" t="n">
+        <v>1920</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
       <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="16" t="n">
-        <v>3838</v>
+      <c r="C234" s="11" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3626,39 +3587,39 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>281</v>
+        <v>94</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="11" t="n">
-        <v>666</v>
+      <c r="C236" s="16" t="n">
+        <v>3725</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="16" t="n">
-        <v>1136</v>
+      <c r="C237" s="11" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="16" t="n">
-        <v>4121</v>
+      <c r="C238" s="11" t="n">
+        <v>371</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>268</v>
+      <c r="C239" s="16" t="n">
+        <v>1027</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3666,15 +3627,15 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>9</v>
+        <v>162</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="16" t="n">
-        <v>3781</v>
+      <c r="C241" s="11" t="n">
+        <v>502</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3682,7 +3643,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>322</v>
+        <v>263</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3690,15 +3651,15 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>385</v>
+        <v>74</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="16" t="n">
-        <v>3492</v>
+      <c r="C244" s="11" t="n">
+        <v>166</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3706,7 +3667,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>222</v>
+        <v>364</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3714,23 +3675,23 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="247" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B247" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="247" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B247" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="16" t="n">
-        <v>4055</v>
+      <c r="C247" s="12" t="n">
+        <v>28773</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="11" t="n">
-        <v>750</v>
+      <c r="C248" s="16" t="n">
+        <v>1057</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3738,7 +3699,7 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>371</v>
+        <v>458</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3746,7 +3707,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="16" t="n">
-        <v>3031</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3754,7 +3715,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>478</v>
+        <v>7</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3762,15 +3723,15 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>197</v>
+        <v>495</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="11" t="n">
-        <v>147</v>
+      <c r="C253" s="16" t="n">
+        <v>2698</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3778,7 +3739,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3786,7 +3747,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>576</v>
+        <v>216</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3794,15 +3755,15 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="257" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B257" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="257" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="12" t="n">
-        <v>15015</v>
+      <c r="C257" s="11" t="n">
+        <v>746</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3810,7 +3771,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>787</v>
+        <v>511</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3818,7 +3779,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>253</v>
+        <v>26</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3826,7 +3787,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>111</v>
+        <v>161</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3834,23 +3795,23 @@
         <v>260</v>
       </c>
       <c r="C261" s="11" t="n">
-        <v>173</v>
+        <v>632</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="11" t="n">
-        <v>710</v>
+      <c r="C262" s="16" t="n">
+        <v>1457</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="16" t="n">
-        <v>1726</v>
+      <c r="C263" s="11" t="n">
+        <v>709</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3858,7 +3819,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>40</v>
+        <v>344</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3866,7 +3827,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>216</v>
+        <v>652</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3874,7 +3835,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>16</v>
+        <v>276</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3882,7 +3843,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>111</v>
+        <v>557</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3890,7 +3851,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>26</v>
+        <v>636</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3898,31 +3859,31 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>130</v>
+        <v>293</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="11" t="n">
-        <v>395</v>
+      <c r="C270" s="16" t="n">
+        <v>1362</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>523</v>
+      <c r="C271" s="16" t="n">
+        <v>2379</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>267</v>
+      <c r="C272" s="16" t="n">
+        <v>2257</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3930,7 +3891,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>455</v>
+        <v>242</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3938,7 +3899,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>203</v>
+        <v>62</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3946,7 +3907,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>683</v>
+        <v>412</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3954,7 +3915,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>661</v>
+        <v>925</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3962,15 +3923,15 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>358</v>
+        <v>462</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="11" t="n">
-        <v>327</v>
+      <c r="C278" s="16" t="n">
+        <v>2015</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3978,7 +3939,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="16" t="n">
-        <v>1190</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3986,15 +3947,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>768</v>
+        <v>24</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>383</v>
+      <c r="C281" s="16" t="n">
+        <v>2636</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -4002,15 +3963,15 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="283" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B283" s="15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="283" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B283" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="11" t="n">
-        <v>794</v>
+      <c r="C283" s="12" t="n">
+        <v>4608</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -4018,7 +3979,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>718</v>
+        <v>880</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -4026,7 +3987,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>627</v>
+        <v>128</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -4034,7 +3995,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>493</v>
+        <v>506</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -4042,7 +4003,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>588</v>
+        <v>318</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -4050,7 +4011,7 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>226</v>
+        <v>361</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -4058,15 +4019,15 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B290" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="12" t="n">
-        <v>4342</v>
+      <c r="C290" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -4074,7 +4035,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>71</v>
+        <v>352</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -4082,7 +4043,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>100</v>
+        <v>209</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -4090,7 +4051,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>346</v>
+        <v>238</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -4098,7 +4059,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>417</v>
+        <v>161</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4106,7 +4067,7 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>77</v>
+        <v>272</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -4114,7 +4075,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>18</v>
+        <v>508</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4122,7 +4083,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>548</v>
+        <v>424</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -4130,7 +4091,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>793</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -4138,7 +4099,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>238</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -4146,15 +4107,15 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B301" s="15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B301" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="11" t="n">
-        <v>507</v>
+      <c r="C301" s="12" t="n">
+        <v>21329</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4162,7 +4123,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>796</v>
+        <v>232</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -4170,7 +4131,7 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>29</v>
+        <v>199</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4178,7 +4139,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>60</v>
+        <v>284</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -4186,15 +4147,15 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="306" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B306" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="306" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="12" t="n">
-        <v>18084</v>
+      <c r="C306" s="11" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -4202,7 +4163,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>122</v>
+        <v>324</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4210,7 +4171,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>155</v>
+        <v>78</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -4218,7 +4179,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>160</v>
+        <v>336</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -4226,7 +4187,7 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>299</v>
+        <v>715</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -4234,7 +4195,7 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>150</v>
+        <v>46</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -4242,15 +4203,15 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>248</v>
+        <v>150</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
@@ -4258,7 +4219,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="11" t="n">
-        <v>192</v>
+        <v>247</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -4266,7 +4227,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>449</v>
+        <v>238</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4274,7 +4235,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>262</v>
+        <v>438</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4282,15 +4243,15 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="true" outlineLevel="3">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>221</v>
+        <v>680</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4298,47 +4259,47 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="320" ht="11" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="320" ht="22" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="321" ht="11" customHeight="true" outlineLevel="3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="322" ht="11" customHeight="true" outlineLevel="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="323" ht="22" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="16" t="n">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C323" s="11" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="324" ht="22" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="325" ht="22" customHeight="true" outlineLevel="3">
@@ -4346,7 +4307,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>415</v>
+        <v>283</v>
       </c>
     </row>
     <row r="326" ht="22" customHeight="true" outlineLevel="3">
@@ -4354,7 +4315,7 @@
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="true" outlineLevel="3">
@@ -4362,7 +4323,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>479</v>
+        <v>72</v>
       </c>
     </row>
     <row r="328" ht="22" customHeight="true" outlineLevel="3">
@@ -4370,7 +4331,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>467</v>
+        <v>228</v>
       </c>
     </row>
     <row r="329" ht="22" customHeight="true" outlineLevel="3">
@@ -4378,15 +4339,15 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="330" ht="22" customHeight="true" outlineLevel="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>417</v>
+        <v>153</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4394,7 +4355,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4402,7 +4363,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>173</v>
+        <v>30</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4410,7 +4371,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>30</v>
+        <v>288</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4418,31 +4379,31 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>355</v>
+        <v>227</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="11" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="336" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C335" s="16" t="n">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="336" ht="22" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="337" ht="22" customHeight="true" outlineLevel="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="11" t="n">
-        <v>4</v>
+      <c r="C337" s="16" t="n">
+        <v>1734</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4450,23 +4411,23 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>523</v>
+        <v>435</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="16" t="n">
-        <v>1110</v>
+      <c r="C339" s="11" t="n">
+        <v>349</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="11" t="n">
-        <v>381</v>
+      <c r="C340" s="16" t="n">
+        <v>1534</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4474,7 +4435,7 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>727</v>
+        <v>20</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4482,15 +4443,15 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="11" t="n">
-        <v>6</v>
+      <c r="C343" s="16" t="n">
+        <v>1447</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4498,159 +4459,159 @@
         <v>343</v>
       </c>
       <c r="C344" s="16" t="n">
-        <v>1680</v>
+        <v>4394</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="16" t="n">
-        <v>1931</v>
+      <c r="C345" s="11" t="n">
+        <v>818</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="11" t="n">
-        <v>843</v>
+      <c r="C346" s="16" t="n">
+        <v>1213</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="16" t="n">
-        <v>1614</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B348" s="15" t="s">
+      <c r="C347" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B348" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B349" s="14" t="s">
+      <c r="C348" s="17" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B349" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="12" t="n">
-        <v>8178</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B350" s="17" t="s">
+      <c r="C349" s="17" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B350" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="12" t="n">
-        <v>8178</v>
+      <c r="C350" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B351" s="18" t="s">
+      <c r="B351" s="19" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B352" s="18" t="s">
+      <c r="B352" s="19" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="16" t="n">
-        <v>2463</v>
+      <c r="C352" s="11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B353" s="18" t="s">
+      <c r="B353" s="19" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B354" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C354" s="12" t="n">
+        <v>16210</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B355" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C355" s="16" t="n">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B356" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C356" s="16" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B357" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="C357" s="11" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B354" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C354" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B355" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="C355" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B356" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="C356" s="11" t="n">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B357" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="C357" s="11" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B358" s="18" t="s">
+    <row r="358" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B359" s="18" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="16" t="n">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B360" s="18" t="s">
+      <c r="C359" s="11" t="n">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="16" t="n">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B361" s="18" t="s">
+      <c r="C360" s="11" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="16" t="n">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B362" s="18" t="s">
+      <c r="C361" s="11" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="363" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B363" s="14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B363" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="C363" s="12" t="n">
-        <v>9076</v>
+      <c r="C363" s="11" t="n">
+        <v>237</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4658,7 +4619,7 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="365" ht="11" customHeight="true" outlineLevel="3">
@@ -4666,23 +4627,23 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>181</v>
+        <v>211</v>
       </c>
     </row>
     <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="16" t="n">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="367" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C366" s="11" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>132</v>
+        <v>785</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4690,7 +4651,7 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>434</v>
+        <v>145</v>
       </c>
     </row>
     <row r="369" ht="11" customHeight="true" outlineLevel="3">
@@ -4698,7 +4659,7 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="370" ht="11" customHeight="true" outlineLevel="3">
@@ -4706,7 +4667,7 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>3</v>
+        <v>379</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4714,7 +4675,7 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>92</v>
+        <v>553</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
@@ -4722,7 +4683,7 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>620</v>
+        <v>136</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
@@ -4730,7 +4691,7 @@
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
@@ -4738,7 +4699,7 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>256</v>
+        <v>694</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
@@ -4746,7 +4707,7 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>158</v>
+        <v>753</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4754,7 +4715,7 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>544</v>
+        <v>840</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
@@ -4762,7 +4723,7 @@
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>386</v>
+        <v>244</v>
       </c>
     </row>
     <row r="378" ht="11" customHeight="true" outlineLevel="3">
@@ -4770,7 +4731,7 @@
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
@@ -4778,15 +4739,15 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="380" ht="22" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="381" ht="11" customHeight="true" outlineLevel="3">
@@ -4794,7 +4755,7 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>390</v>
+        <v>209</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
@@ -4802,7 +4763,7 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>184</v>
+        <v>159</v>
       </c>
     </row>
     <row r="383" ht="11" customHeight="true" outlineLevel="3">
@@ -4810,7 +4771,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>96</v>
+        <v>232</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4818,23 +4779,23 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="385" ht="22" customHeight="true" outlineLevel="3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>126</v>
+        <v>494</v>
       </c>
     </row>
     <row r="387" ht="11" customHeight="true" outlineLevel="3">
@@ -4842,31 +4803,31 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>366</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="11" t="n">
-        <v>155</v>
+      <c r="C388" s="16" t="n">
+        <v>1104</v>
       </c>
     </row>
     <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="C389" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="390" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C389" s="16" t="n">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>2</v>
+        <v>237</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
@@ -4874,7 +4835,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="392" ht="11" customHeight="true" outlineLevel="3">
@@ -4882,31 +4843,31 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="393" ht="11" customHeight="true" outlineLevel="3">
       <c r="B393" s="15" t="s">
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
     </row>
     <row r="394" ht="11" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="16" t="n">
-        <v>2158</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B395" s="15" t="s">
+      <c r="C394" s="11" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B395" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="C395" s="11" t="n">
-        <v>40</v>
+      <c r="C395" s="17" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
@@ -4914,7 +4875,7 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="397" ht="11" customHeight="true" outlineLevel="3">
@@ -4922,7 +4883,7 @@
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>218</v>
+        <v>108</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4930,23 +4891,23 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B399" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B399" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="C399" s="11" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B400" s="14" t="s">
+      <c r="C399" s="12" t="n">
+        <v>48820</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="19" t="n">
-        <v>307</v>
+      <c r="C400" s="11" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="401" ht="11" customHeight="true" outlineLevel="3">
@@ -4954,63 +4915,63 @@
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="403" ht="11" customHeight="true" outlineLevel="3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="404" ht="33" customHeight="true" outlineLevel="3">
       <c r="B404" s="15" t="s">
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B405" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B405" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="12" t="n">
-        <v>59482</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C405" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="15" t="s">
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407" ht="22" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
       <c r="B408" s="15" t="s">
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>147</v>
+        <v>9</v>
       </c>
     </row>
     <row r="409" ht="11" customHeight="true" outlineLevel="3">
@@ -5018,63 +4979,63 @@
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="410" ht="11" customHeight="true" outlineLevel="3">
       <c r="B410" s="15" t="s">
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="411" ht="22" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="3">
       <c r="B411" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="C411" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="412" ht="33" customHeight="true" outlineLevel="3">
+      <c r="C411" s="16" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
       <c r="B412" s="15" t="s">
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="413" ht="33" customHeight="true" outlineLevel="3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
       <c r="B413" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="C413" s="16" t="n">
-        <v>1295</v>
+      <c r="C413" s="11" t="n">
+        <v>306</v>
       </c>
     </row>
     <row r="414" ht="22" customHeight="true" outlineLevel="3">
       <c r="B414" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="C414" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="415" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C414" s="16" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="3">
       <c r="B415" s="15" t="s">
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="416" ht="22" customHeight="true" outlineLevel="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="416" ht="11" customHeight="true" outlineLevel="3">
       <c r="B416" s="15" t="s">
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="417" ht="11" customHeight="true" outlineLevel="3">
@@ -5082,55 +5043,55 @@
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
       <c r="B418" s="15" t="s">
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
-        <v>198</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419" ht="11" customHeight="true" outlineLevel="3">
       <c r="B419" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="C419" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="420" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C419" s="16" t="n">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="420" ht="11" customHeight="true" outlineLevel="3">
       <c r="B420" s="15" t="s">
         <v>419</v>
       </c>
       <c r="C420" s="11" t="n">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="421" ht="11" customHeight="true" outlineLevel="3">
       <c r="B421" s="15" t="s">
         <v>420</v>
       </c>
       <c r="C421" s="11" t="n">
-        <v>391</v>
+        <v>210</v>
       </c>
     </row>
     <row r="422" ht="22" customHeight="true" outlineLevel="3">
       <c r="B422" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="C422" s="16" t="n">
-        <v>2665</v>
-      </c>
-    </row>
-    <row r="423" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C422" s="11" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
       <c r="B423" s="15" t="s">
         <v>422</v>
       </c>
       <c r="C423" s="11" t="n">
-        <v>157</v>
+        <v>10</v>
       </c>
     </row>
     <row r="424" ht="22" customHeight="true" outlineLevel="3">
@@ -5138,7 +5099,7 @@
         <v>423</v>
       </c>
       <c r="C424" s="11" t="n">
-        <v>60</v>
+        <v>243</v>
       </c>
     </row>
     <row r="425" ht="22" customHeight="true" outlineLevel="3">
@@ -5146,39 +5107,39 @@
         <v>424</v>
       </c>
       <c r="C425" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="426" ht="22" customHeight="true" outlineLevel="3">
       <c r="B426" s="15" t="s">
         <v>425</v>
       </c>
       <c r="C426" s="16" t="n">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="427" ht="22" customHeight="true" outlineLevel="3">
       <c r="B427" s="15" t="s">
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
       <c r="B428" s="15" t="s">
         <v>427</v>
       </c>
       <c r="C428" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
       <c r="B429" s="15" t="s">
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>748</v>
+        <v>383</v>
       </c>
     </row>
     <row r="430" ht="22" customHeight="true" outlineLevel="3">
@@ -5186,7 +5147,7 @@
         <v>429</v>
       </c>
       <c r="C430" s="11" t="n">
-        <v>234</v>
+        <v>90</v>
       </c>
     </row>
     <row r="431" ht="22" customHeight="true" outlineLevel="3">
@@ -5194,7 +5155,7 @@
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>12</v>
+        <v>148</v>
       </c>
     </row>
     <row r="432" ht="22" customHeight="true" outlineLevel="3">
@@ -5202,7 +5163,7 @@
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="433" ht="22" customHeight="true" outlineLevel="3">
@@ -5210,7 +5171,7 @@
         <v>432</v>
       </c>
       <c r="C433" s="11" t="n">
-        <v>220</v>
+        <v>251</v>
       </c>
     </row>
     <row r="434" ht="22" customHeight="true" outlineLevel="3">
@@ -5218,7 +5179,7 @@
         <v>433</v>
       </c>
       <c r="C434" s="11" t="n">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="435" ht="22" customHeight="true" outlineLevel="3">
@@ -5226,7 +5187,7 @@
         <v>434</v>
       </c>
       <c r="C435" s="11" t="n">
-        <v>41</v>
+        <v>157</v>
       </c>
     </row>
     <row r="436" ht="22" customHeight="true" outlineLevel="3">
@@ -5234,7 +5195,7 @@
         <v>435</v>
       </c>
       <c r="C436" s="11" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="437" ht="22" customHeight="true" outlineLevel="3">
@@ -5242,15 +5203,15 @@
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>242</v>
+        <v>521</v>
       </c>
     </row>
     <row r="438" ht="22" customHeight="true" outlineLevel="3">
       <c r="B438" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="16" t="n">
-        <v>1240</v>
+      <c r="C438" s="11" t="n">
+        <v>298</v>
       </c>
     </row>
     <row r="439" ht="22" customHeight="true" outlineLevel="3">
@@ -5258,7 +5219,7 @@
         <v>438</v>
       </c>
       <c r="C439" s="11" t="n">
-        <v>301</v>
+        <v>13</v>
       </c>
     </row>
     <row r="440" ht="22" customHeight="true" outlineLevel="3">
@@ -5266,7 +5227,7 @@
         <v>439</v>
       </c>
       <c r="C440" s="11" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
     </row>
     <row r="441" ht="22" customHeight="true" outlineLevel="3">
@@ -5274,31 +5235,31 @@
         <v>440</v>
       </c>
       <c r="C441" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="442" ht="22" customHeight="true" outlineLevel="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="442" ht="11" customHeight="true" outlineLevel="3">
       <c r="B442" s="15" t="s">
         <v>441</v>
       </c>
       <c r="C442" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="443" ht="22" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="443" ht="11" customHeight="true" outlineLevel="3">
       <c r="B443" s="15" t="s">
         <v>442</v>
       </c>
       <c r="C443" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="444" ht="22" customHeight="true" outlineLevel="3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="444" ht="11" customHeight="true" outlineLevel="3">
       <c r="B444" s="15" t="s">
         <v>443</v>
       </c>
       <c r="C444" s="11" t="n">
-        <v>339</v>
+        <v>317</v>
       </c>
     </row>
     <row r="445" ht="22" customHeight="true" outlineLevel="3">
@@ -5306,7 +5267,7 @@
         <v>444</v>
       </c>
       <c r="C445" s="11" t="n">
-        <v>226</v>
+        <v>138</v>
       </c>
     </row>
     <row r="446" ht="22" customHeight="true" outlineLevel="3">
@@ -5314,7 +5275,7 @@
         <v>445</v>
       </c>
       <c r="C446" s="11" t="n">
-        <v>610</v>
+        <v>147</v>
       </c>
     </row>
     <row r="447" ht="22" customHeight="true" outlineLevel="3">
@@ -5322,7 +5283,7 @@
         <v>446</v>
       </c>
       <c r="C447" s="11" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
     </row>
     <row r="448" ht="22" customHeight="true" outlineLevel="3">
@@ -5330,7 +5291,7 @@
         <v>447</v>
       </c>
       <c r="C448" s="11" t="n">
-        <v>48</v>
+        <v>157</v>
       </c>
     </row>
     <row r="449" ht="22" customHeight="true" outlineLevel="3">
@@ -5338,15 +5299,15 @@
         <v>448</v>
       </c>
       <c r="C449" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="450" ht="22" customHeight="true" outlineLevel="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
       <c r="B450" s="15" t="s">
         <v>449</v>
       </c>
       <c r="C450" s="11" t="n">
-        <v>969</v>
+        <v>57</v>
       </c>
     </row>
     <row r="451" ht="22" customHeight="true" outlineLevel="3">
@@ -5354,23 +5315,23 @@
         <v>450</v>
       </c>
       <c r="C451" s="11" t="n">
-        <v>198</v>
+        <v>840</v>
       </c>
     </row>
     <row r="452" ht="22" customHeight="true" outlineLevel="3">
       <c r="B452" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="C452" s="16" t="n">
-        <v>3688</v>
-      </c>
-    </row>
-    <row r="453" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C452" s="11" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="453" ht="11" customHeight="true" outlineLevel="3">
       <c r="B453" s="15" t="s">
         <v>452</v>
       </c>
       <c r="C453" s="11" t="n">
-        <v>13</v>
+        <v>247</v>
       </c>
     </row>
     <row r="454" ht="22" customHeight="true" outlineLevel="3">
@@ -5378,23 +5339,23 @@
         <v>453</v>
       </c>
       <c r="C454" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="455" ht="22" customHeight="true" outlineLevel="3">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="455" ht="11" customHeight="true" outlineLevel="3">
       <c r="B455" s="15" t="s">
         <v>454</v>
       </c>
       <c r="C455" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="456" ht="11" customHeight="true" outlineLevel="3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="456" ht="22" customHeight="true" outlineLevel="3">
       <c r="B456" s="15" t="s">
         <v>455</v>
       </c>
       <c r="C456" s="11" t="n">
-        <v>108</v>
+        <v>546</v>
       </c>
     </row>
     <row r="457" ht="11" customHeight="true" outlineLevel="3">
@@ -5402,15 +5363,15 @@
         <v>456</v>
       </c>
       <c r="C457" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="458" ht="11" customHeight="true" outlineLevel="3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="true" outlineLevel="3">
       <c r="B458" s="15" t="s">
         <v>457</v>
       </c>
       <c r="C458" s="11" t="n">
-        <v>295</v>
+        <v>15</v>
       </c>
     </row>
     <row r="459" ht="11" customHeight="true" outlineLevel="3">
@@ -5418,23 +5379,23 @@
         <v>458</v>
       </c>
       <c r="C459" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="460" ht="22" customHeight="true" outlineLevel="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="460" ht="11" customHeight="true" outlineLevel="3">
       <c r="B460" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="C460" s="11" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="461" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C460" s="16" t="n">
+        <v>6338</v>
+      </c>
+    </row>
+    <row r="461" ht="11" customHeight="true" outlineLevel="3">
       <c r="B461" s="15" t="s">
         <v>460</v>
       </c>
       <c r="C461" s="11" t="n">
-        <v>197</v>
+        <v>368</v>
       </c>
     </row>
     <row r="462" ht="22" customHeight="true" outlineLevel="3">
@@ -5442,23 +5403,23 @@
         <v>461</v>
       </c>
       <c r="C462" s="11" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
     </row>
     <row r="463" ht="22" customHeight="true" outlineLevel="3">
       <c r="B463" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="C463" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="464" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C463" s="16" t="n">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="464" ht="11" customHeight="true" outlineLevel="3">
       <c r="B464" s="15" t="s">
         <v>463</v>
       </c>
       <c r="C464" s="11" t="n">
-        <v>308</v>
+        <v>604</v>
       </c>
     </row>
     <row r="465" ht="22" customHeight="true" outlineLevel="3">
@@ -5466,15 +5427,15 @@
         <v>464</v>
       </c>
       <c r="C465" s="11" t="n">
-        <v>208</v>
+        <v>120</v>
       </c>
     </row>
     <row r="466" ht="22" customHeight="true" outlineLevel="3">
       <c r="B466" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="C466" s="11" t="n">
-        <v>27</v>
+      <c r="C466" s="16" t="n">
+        <v>1544</v>
       </c>
     </row>
     <row r="467" ht="11" customHeight="true" outlineLevel="3">
@@ -5482,7 +5443,7 @@
         <v>466</v>
       </c>
       <c r="C467" s="11" t="n">
-        <v>217</v>
+        <v>642</v>
       </c>
     </row>
     <row r="468" ht="22" customHeight="true" outlineLevel="3">
@@ -5490,7 +5451,7 @@
         <v>467</v>
       </c>
       <c r="C468" s="11" t="n">
-        <v>5</v>
+        <v>131</v>
       </c>
     </row>
     <row r="469" ht="22" customHeight="true" outlineLevel="3">
@@ -5498,39 +5459,39 @@
         <v>468</v>
       </c>
       <c r="C469" s="16" t="n">
-        <v>1460</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="470" ht="11" customHeight="true" outlineLevel="3">
       <c r="B470" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="C470" s="11" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="471" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C470" s="16" t="n">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="471" ht="11" customHeight="true" outlineLevel="3">
       <c r="B471" s="15" t="s">
         <v>470</v>
       </c>
       <c r="C471" s="11" t="n">
-        <v>921</v>
+        <v>600</v>
       </c>
     </row>
     <row r="472" ht="11" customHeight="true" outlineLevel="3">
       <c r="B472" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="C472" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="473" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C472" s="16" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="473" ht="11" customHeight="true" outlineLevel="3">
       <c r="B473" s="15" t="s">
         <v>472</v>
       </c>
-      <c r="C473" s="16" t="n">
-        <v>1352</v>
+      <c r="C473" s="11" t="n">
+        <v>188</v>
       </c>
     </row>
     <row r="474" ht="11" customHeight="true" outlineLevel="3">
@@ -5538,215 +5499,111 @@
         <v>473</v>
       </c>
       <c r="C474" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="475" ht="22" customHeight="true" outlineLevel="3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="475" ht="11" customHeight="true" outlineLevel="3">
       <c r="B475" s="15" t="s">
         <v>474</v>
       </c>
       <c r="C475" s="16" t="n">
-        <v>1458</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="476" ht="11" customHeight="true" outlineLevel="3">
       <c r="B476" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="C476" s="11" t="n">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="477" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C476" s="16" t="n">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="477" ht="22" customHeight="true" outlineLevel="3">
       <c r="B477" s="15" t="s">
         <v>476</v>
       </c>
       <c r="C477" s="11" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="478" ht="11" customHeight="true" outlineLevel="3">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="true" outlineLevel="3">
       <c r="B478" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="C478" s="16" t="n">
-        <v>9094</v>
-      </c>
-    </row>
-    <row r="479" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C478" s="11" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="479" ht="22" customHeight="true" outlineLevel="3">
       <c r="B479" s="15" t="s">
         <v>478</v>
       </c>
       <c r="C479" s="11" t="n">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="480" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B480" s="15" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="480" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B480" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="C480" s="11" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="481" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B481" s="15" t="s">
+      <c r="C480" s="12" t="n">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="481" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B481" s="19" t="s">
         <v>480</v>
       </c>
-      <c r="C481" s="16" t="n">
-        <v>4612</v>
-      </c>
-    </row>
-    <row r="482" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B482" s="15" t="s">
+      <c r="C481" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="482" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B482" s="19" t="s">
         <v>481</v>
       </c>
       <c r="C482" s="11" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="483" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B483" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="483" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B483" s="19" t="s">
         <v>482</v>
       </c>
       <c r="C483" s="11" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="484" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B484" s="15" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="484" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B484" s="19" t="s">
         <v>483</v>
       </c>
       <c r="C484" s="16" t="n">
-        <v>4115</v>
-      </c>
-    </row>
-    <row r="485" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B485" s="15" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="485" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B485" s="19" t="s">
         <v>484</v>
       </c>
-      <c r="C485" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="486" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B486" s="15" t="s">
+      <c r="C485" s="16" t="n">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="486" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B486" s="19" t="s">
         <v>485</v>
       </c>
       <c r="C486" s="11" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="487" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B487" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="487" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B487" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="C487" s="16" t="n">
-        <v>7482</v>
-      </c>
-    </row>
-    <row r="488" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B488" s="15" t="s">
-        <v>487</v>
-      </c>
-      <c r="C488" s="11" t="n">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="489" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B489" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="C489" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="490" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B490" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="C490" s="11" t="n">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="491" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B491" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="C491" s="11" t="n">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="492" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B492" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="C492" s="16" t="n">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="493" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B493" s="15" t="s">
-        <v>492</v>
-      </c>
-      <c r="C493" s="11" t="n">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="494" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B494" s="15" t="s">
-        <v>493</v>
-      </c>
-      <c r="C494" s="11" t="n">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="495" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B495" s="15" t="s">
-        <v>494</v>
-      </c>
-      <c r="C495" s="11" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="496" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B496" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="C496" s="12" t="n">
-        <v>2822</v>
-      </c>
-    </row>
-    <row r="497" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B497" s="18" t="s">
-        <v>496</v>
-      </c>
-      <c r="C497" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="498" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B498" s="18" t="s">
-        <v>497</v>
-      </c>
-      <c r="C498" s="11" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="499" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B499" s="18" t="s">
-        <v>498</v>
-      </c>
-      <c r="C499" s="16" t="n">
-        <v>2592</v>
-      </c>
-    </row>
-    <row r="500" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B500" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="C500" s="11" t="n">
-        <v>80</v>
+      <c r="C487" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:15</t>
+    <t>Период: на 16.01.2026 15:05:15</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,31 +62,28 @@
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Желе ківі УБ 78г /56шт</t>
-  </si>
-  <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Желе ківі УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Желе Лісова ягода УБ 78г /56шт</t>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
@@ -95,18 +92,12 @@
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
-    <t>Какао-порошок УБ 80г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -134,70 +125,67 @@
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
-    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
+    <t>Приправа до плову УБ 25г /36шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
+    <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до шашлику УБ 25г /34шт</t>
   </si>
   <si>
     <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Прованські трави УБ 10г /28шт</t>
-  </si>
-  <si>
-    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+    <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
@@ -236,9 +224,6 @@
     <t>Лавровий лист 10г/80</t>
   </si>
   <si>
-    <t>Паприка копчена мелена УБ 20г /34шт</t>
-  </si>
-  <si>
     <t>Паприка мелена УБ 20г /34шт</t>
   </si>
   <si>
@@ -251,12 +236,12 @@
     <t>Перець чорний горошком УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -272,24 +257,12 @@
     <t>БАТОНИ</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -299,12 +272,12 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -317,27 +290,18 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
     <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -347,9 +311,6 @@
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
-    <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>РУЛЕТ П'янка вишня ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -383,9 +344,6 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -395,30 +353,15 @@
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto dark ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -443,6 +386,9 @@
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -452,6 +398,9 @@
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers лимон ВКФ 72г /22шт AR /</t>
+  </si>
+  <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
@@ -470,9 +419,6 @@
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -512,75 +458,45 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -596,66 +512,36 @@
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -665,9 +551,6 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -677,42 +560,27 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
@@ -722,24 +590,15 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Бім-Бом РЦ 200г /11шт</t>
-  </si>
-  <si>
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
@@ -779,9 +638,6 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -794,9 +650,6 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -857,6 +710,9 @@
     <t>Рошен джус мікс РЦ 1кг /8пак /</t>
   </si>
   <si>
+    <t>Рошен евкаліпт-ментол КрКФ 1кг /8пак /</t>
+  </si>
+  <si>
     <t>Цитрусовий мікс РЦ 1кг /7пак /</t>
   </si>
   <si>
@@ -872,21 +728,12 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 256г /8шт</t>
   </si>
   <si>
@@ -908,12 +755,6 @@
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
-    <t>Київ вечірній ВКФ 176г /7шт</t>
-  </si>
-  <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -935,18 +776,9 @@
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
   </si>
   <si>
@@ -974,18 +806,12 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
@@ -995,9 +821,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
@@ -1013,9 +836,6 @@
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
@@ -1025,9 +845,6 @@
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -1040,9 +857,6 @@
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
@@ -1052,46 +866,28 @@
     <t>До кави пряжене молоко ВКФ 185г /28шт /</t>
   </si>
   <si>
-    <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
     <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт АКЦІЯ</t>
   </si>
   <si>
-    <t>ПОДАРУНКИ</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ 2026</t>
-  </si>
-  <si>
-    <t>Н/п №10 26 Новорічний камін РЦ 665г /4шт</t>
-  </si>
-  <si>
-    <t>Н/п №6 26 Веселе свято РЦ 458г /4шт</t>
-  </si>
-  <si>
-    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
-  </si>
-  <si>
-    <t>Н/п №8 26 Різдвяний ярмарок РЦ 561г /4шт</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
-    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Boo! Bear РЦ 1кг /5пак АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
@@ -1100,30 +896,24 @@
     <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак</t>
+  </si>
+  <si>
+    <t>Galaretka Roshen РЦ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
-    <t>Johnny Krocker coconut ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Ko-Ko Choco White 1кг/5</t>
-  </si>
-  <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
@@ -1136,9 +926,6 @@
     <t>Krock з арахісом ВКФ 1кг /8пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Krock з арахісом ВКФ 1кг /8пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Milaxy ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1157,9 +944,6 @@
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1178,33 +962,24 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
-  </si>
-  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
-    <t>Сливки-Ленивки 1кг ВКФ</t>
-  </si>
-  <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
     <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
+    <t>Johnny Krocker choco ВКФ 350г /12шт PL</t>
+  </si>
+  <si>
     <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
   </si>
   <si>
@@ -1229,7 +1004,7 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
@@ -1238,18 +1013,9 @@
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1265,21 +1031,12 @@
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1289,6 +1046,9 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
@@ -1304,28 +1064,25 @@
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
@@ -1337,10 +1094,7 @@
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
@@ -1379,22 +1133,19 @@
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
@@ -1403,27 +1154,18 @@
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1448,37 +1190,7 @@
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
   </si>
   <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>ФІГУРКИ</t>
-  </si>
-  <si>
-    <t>Кролик Roshen зимовий ВКФ 100г /12шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 100г /12шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 60г /20шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1705,12 +1417,6 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1730,7 +1436,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C487"/>
+  <dimension ref="C391"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1795,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>365</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1803,7 +1509,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>453025</v>
+        <v>387828</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1811,7 +1517,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>84079</v>
+        <v>75919</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1819,15 +1525,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>7697</v>
+        <v>10450</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>727</v>
+      <c r="C15" s="16" t="n">
+        <v>2571</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1835,7 +1541,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>912</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1843,15 +1549,15 @@
         <v>16</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>168</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>36</v>
+      <c r="C18" s="16" t="n">
+        <v>1231</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1859,7 +1565,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>152</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1867,7 +1573,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>440</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1875,7 +1581,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>36</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1883,7 +1589,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>973</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1891,7 +1597,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>56</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1899,7 +1605,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>103</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1907,23 +1613,23 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>392</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B27" s="15" t="s">
+      <c r="C26" s="16" t="n">
+        <v>3711</v>
+      </c>
+    </row>
+    <row r="27" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B27" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>242</v>
+      <c r="C27" s="12" t="n">
+        <v>23074</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1931,23 +1637,23 @@
         <v>27</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>2998</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="30" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B30" s="14" t="s">
+      <c r="C29" s="16" t="n">
+        <v>5969</v>
+      </c>
+    </row>
+    <row r="30" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="12" t="n">
-        <v>34971</v>
+      <c r="C30" s="16" t="n">
+        <v>1767</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1955,47 +1661,47 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>4591</v>
+        <v>9048</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>7374</v>
+      <c r="C32" s="11" t="n">
+        <v>336</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="16" t="n">
-        <v>1767</v>
+      <c r="C33" s="11" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="16" t="n">
-        <v>5308</v>
+      <c r="C34" s="11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>350</v>
+      <c r="C35" s="16" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="16" t="n">
-        <v>7033</v>
+      <c r="C36" s="11" t="n">
+        <v>484</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -2003,71 +1709,71 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>24</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="16" t="n">
-        <v>1708</v>
+      <c r="C38" s="11" t="n">
+        <v>310</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="16" t="n">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="40" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C39" s="11" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>8</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="16" t="n">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="42" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C41" s="11" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="16" t="n">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B43" s="15" t="s">
+      <c r="C42" s="11" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B43" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="16" t="n">
-        <v>1287</v>
+      <c r="C43" s="12" t="n">
+        <v>8588</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="16" t="n">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="45" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B45" s="14" t="s">
+      <c r="C44" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="12" t="n">
-        <v>10950</v>
+      <c r="C45" s="11" t="n">
+        <v>503</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -2075,7 +1781,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>468</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -2083,7 +1789,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>124</v>
+        <v>777</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -2091,7 +1797,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>872</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -2099,7 +1805,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>68</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2107,7 +1813,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>674</v>
+        <v>625</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2115,7 +1821,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>564</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2123,7 +1829,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>65</v>
+        <v>455</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -2131,15 +1837,15 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>247</v>
+        <v>494</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>925</v>
+      <c r="C54" s="16" t="n">
+        <v>1105</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -2147,7 +1853,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>612</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2155,7 +1861,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -2163,7 +1869,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>348</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2171,7 +1877,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>62</v>
+        <v>716</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -2179,7 +1885,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>626</v>
+        <v>869</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2187,7 +1893,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>285</v>
+        <v>443</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2195,7 +1901,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2203,15 +1909,15 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="63" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B63" s="15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="63" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B63" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="11" t="n">
-        <v>533</v>
+      <c r="C63" s="12" t="n">
+        <v>33807</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2219,7 +1925,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>197</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2227,39 +1933,39 @@
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>2077</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="67" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B67" s="14" t="s">
+      <c r="C66" s="16" t="n">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="12" t="n">
-        <v>30461</v>
+      <c r="C67" s="16" t="n">
+        <v>1677</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>563</v>
+      <c r="C68" s="16" t="n">
+        <v>5774</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>884</v>
+      <c r="C69" s="16" t="n">
+        <v>1533</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2267,7 +1973,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="16" t="n">
-        <v>1591</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2275,7 +1981,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>860</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2283,23 +1989,23 @@
         <v>71</v>
       </c>
       <c r="C72" s="16" t="n">
-        <v>5335</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
       <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="11" t="n">
-        <v>990</v>
+      <c r="C73" s="16" t="n">
+        <v>1783</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>885</v>
+      <c r="C74" s="16" t="n">
+        <v>9143</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2307,7 +2013,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="16" t="n">
-        <v>3414</v>
+        <v>5377</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2315,71 +2021,71 @@
         <v>75</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>234</v>
+        <v>285</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="16" t="n">
-        <v>4198</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B78" s="15" t="s">
+      <c r="C77" s="11" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B78" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="16" t="n">
-        <v>10696</v>
-      </c>
-    </row>
-    <row r="79" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B79" s="15" t="s">
+      <c r="C78" s="12" t="n">
+        <v>311909</v>
+      </c>
+    </row>
+    <row r="79" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B79" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="80" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C79" s="12" t="n">
+        <v>91186</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>90</v>
+      <c r="C80" s="16" t="n">
+        <v>3480</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>128</v>
+      <c r="C81" s="16" t="n">
+        <v>21281</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B83" s="13" t="s">
+      <c r="C82" s="16" t="n">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="12" t="n">
-        <v>368946</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B84" s="14" t="s">
+      <c r="C83" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="12" t="n">
-        <v>130233</v>
+      <c r="C84" s="16" t="n">
+        <v>8659</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="true" outlineLevel="3">
@@ -2387,7 +2093,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>6589</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="true" outlineLevel="3">
@@ -2395,7 +2101,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="16" t="n">
-        <v>3708</v>
+        <v>8811</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="true" outlineLevel="3">
@@ -2403,159 +2109,159 @@
         <v>86</v>
       </c>
       <c r="C87" s="16" t="n">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="88" ht="11" customHeight="true" outlineLevel="3">
+        <v>4844</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
       <c r="C88" s="16" t="n">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="89" ht="11" customHeight="true" outlineLevel="3">
+        <v>8724</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C89" s="16" t="n">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
       <c r="C90" s="16" t="n">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+        <v>4764</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="16" t="n">
-        <v>18045</v>
+      <c r="C91" s="11" t="n">
+        <v>356</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B93" s="15" t="s">
+      <c r="C92" s="16" t="n">
+        <v>20668</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B93" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="16" t="n">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C93" s="12" t="n">
+        <v>5235</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="16" t="n">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="true" outlineLevel="3">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="16" t="n">
-        <v>9289</v>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C95" s="11" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="16" t="n">
-        <v>8495</v>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C96" s="11" t="n">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="16" t="n">
-        <v>9919</v>
-      </c>
-    </row>
-    <row r="98" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C97" s="11" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>17325</v>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C98" s="11" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="16" t="n">
-        <v>5955</v>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C99" s="11" t="n">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="16" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C100" s="11" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="16" t="n">
-        <v>13746</v>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C101" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="16" t="n">
-        <v>9110</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C102" s="11" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="16" t="n">
-        <v>3022</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B104" s="14" t="s">
+      <c r="C103" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="12" t="n">
-        <v>7682</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C104" s="11" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="16" t="n">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B106" s="15" t="s">
+      <c r="C105" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B106" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="11" t="n">
-        <v>198</v>
+      <c r="C106" s="12" t="n">
+        <v>38027</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2563,7 +2269,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>572</v>
+        <v>464</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2571,15 +2277,15 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>931</v>
+        <v>233</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="16" t="n">
-        <v>1394</v>
+      <c r="C109" s="11" t="n">
+        <v>396</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
@@ -2587,31 +2293,31 @@
         <v>109</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>34</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="11" t="n">
-        <v>398</v>
+      <c r="C111" s="16" t="n">
+        <v>10580</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
       <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="11" t="n">
-        <v>501</v>
+      <c r="C112" s="16" t="n">
+        <v>11821</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="11" t="n">
-        <v>486</v>
+      <c r="C113" s="16" t="n">
+        <v>2160</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2619,7 +2325,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>493</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2627,7 +2333,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>208</v>
+        <v>119</v>
       </c>
     </row>
     <row r="116" ht="11" customHeight="true" outlineLevel="3">
@@ -2635,7 +2341,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>559</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" ht="11" customHeight="true" outlineLevel="3">
@@ -2643,23 +2349,23 @@
         <v>116</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="118" ht="22" customHeight="true" outlineLevel="3">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B119" s="14" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="12" t="n">
-        <v>26115</v>
+      <c r="C119" s="16" t="n">
+        <v>1943</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2667,7 +2373,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>670</v>
+        <v>133</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2675,15 +2381,15 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>415</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="11" t="n">
-        <v>26</v>
+      <c r="C122" s="16" t="n">
+        <v>1786</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2691,7 +2397,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2699,31 +2405,31 @@
         <v>123</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>321</v>
+        <v>830</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="16" t="n">
-        <v>3681</v>
+      <c r="C125" s="11" t="n">
+        <v>456</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="16" t="n">
-        <v>1700</v>
+      <c r="C126" s="11" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="16" t="n">
-        <v>2898</v>
+      <c r="C127" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2731,15 +2437,15 @@
         <v>127</v>
       </c>
       <c r="C128" s="16" t="n">
-        <v>3400</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
       <c r="B129" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="16" t="n">
-        <v>3224</v>
+      <c r="C129" s="11" t="n">
+        <v>189</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2747,7 +2453,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2755,7 +2461,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>175</v>
+        <v>298</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2763,39 +2469,39 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>71</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="134" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B134" s="15" t="s">
+      <c r="C133" s="16" t="n">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="134" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B134" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>142</v>
+      <c r="C134" s="12" t="n">
+        <v>54763</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>190</v>
+      <c r="C135" s="16" t="n">
+        <v>1227</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="16" t="n">
-        <v>1017</v>
+      <c r="C136" s="11" t="n">
+        <v>365</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2803,7 +2509,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>840</v>
+        <v>225</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2811,15 +2517,15 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>817</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="16" t="n">
-        <v>1109</v>
+      <c r="C139" s="11" t="n">
+        <v>271</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2827,7 +2533,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>3</v>
+        <v>342</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2835,15 +2541,15 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>446</v>
+        <v>86</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="16" t="n">
-        <v>1770</v>
+      <c r="C142" s="11" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2859,31 +2565,31 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>182</v>
+        <v>491</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="11" t="n">
-        <v>269</v>
+      <c r="C145" s="16" t="n">
+        <v>2677</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
       <c r="B146" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="11" t="n">
-        <v>340</v>
+      <c r="C146" s="16" t="n">
+        <v>1028</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="11" t="n">
-        <v>1</v>
+      <c r="C147" s="16" t="n">
+        <v>1702</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2891,7 +2597,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="16" t="n">
-        <v>1542</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2899,7 +2605,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>28</v>
+        <v>486</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2907,23 +2613,23 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>6</v>
+        <v>270</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
       <c r="B151" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B152" s="14" t="s">
+      <c r="C151" s="16" t="n">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B152" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="12" t="n">
-        <v>84849</v>
+      <c r="C152" s="11" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2931,7 +2637,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="16" t="n">
-        <v>1624</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2939,15 +2645,15 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>513</v>
+        <v>252</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
       <c r="B155" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="11" t="n">
-        <v>316</v>
+      <c r="C155" s="16" t="n">
+        <v>1438</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2955,7 +2661,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>584</v>
+        <v>549</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2963,15 +2669,15 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>257</v>
+        <v>807</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="11" t="n">
-        <v>581</v>
+      <c r="C158" s="16" t="n">
+        <v>2980</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2979,7 +2685,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>60</v>
+        <v>152</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2987,7 +2693,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>538</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2995,7 +2701,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>556</v>
+        <v>298</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -3003,15 +2709,15 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>533</v>
+        <v>168</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="16" t="n">
-        <v>2725</v>
+      <c r="C163" s="11" t="n">
+        <v>436</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -3019,7 +2725,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>517</v>
+        <v>144</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -3027,7 +2733,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>257</v>
+        <v>70</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -3035,15 +2741,15 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="16" t="n">
-        <v>2173</v>
+      <c r="C167" s="11" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -3051,7 +2757,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -3059,7 +2765,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>882</v>
+        <v>491</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -3067,7 +2773,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>258</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -3075,7 +2781,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="16" t="n">
-        <v>1361</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -3083,23 +2789,23 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>447</v>
+        <v>542</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
       <c r="B173" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C173" s="11" t="n">
-        <v>133</v>
+      <c r="C173" s="16" t="n">
+        <v>3021</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="16" t="n">
-        <v>4421</v>
+      <c r="C174" s="11" t="n">
+        <v>585</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -3107,23 +2813,23 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>184</v>
+        <v>274</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="11" t="n">
-        <v>78</v>
+      <c r="C176" s="16" t="n">
+        <v>2403</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="16" t="n">
-        <v>2980</v>
+      <c r="C177" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3131,23 +2837,23 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>204</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
       <c r="B179" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="11" t="n">
-        <v>107</v>
+      <c r="C179" s="16" t="n">
+        <v>3465</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="16" t="n">
-        <v>2410</v>
+      <c r="C180" s="11" t="n">
+        <v>574</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
@@ -3155,15 +2861,15 @@
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>307</v>
+        <v>375</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="11" t="n">
-        <v>295</v>
+      <c r="C182" s="16" t="n">
+        <v>2312</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3171,31 +2877,31 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>744</v>
+        <v>398</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>63</v>
+      <c r="C184" s="16" t="n">
+        <v>2363</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="16" t="n">
-        <v>3256</v>
+      <c r="C185" s="11" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
       <c r="B186" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="11" t="n">
-        <v>944</v>
+      <c r="C186" s="16" t="n">
+        <v>2094</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -3203,15 +2909,15 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>371</v>
+        <v>540</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
       <c r="B188" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="11" t="n">
-        <v>543</v>
+      <c r="C188" s="16" t="n">
+        <v>3116</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
@@ -3219,7 +2925,7 @@
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>551</v>
+        <v>485</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3227,15 +2933,15 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>942</v>
+        <v>330</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="11" t="n">
-        <v>201</v>
+      <c r="C191" s="16" t="n">
+        <v>3558</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3243,7 +2949,7 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>476</v>
+        <v>765</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
@@ -3251,15 +2957,15 @@
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="16" t="n">
-        <v>1534</v>
+      <c r="C194" s="11" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3267,23 +2973,23 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="true" outlineLevel="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>286</v>
+        <v>47</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="16" t="n">
-        <v>2734</v>
+      <c r="C197" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3291,31 +2997,31 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="199" ht="22" customHeight="true" outlineLevel="3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="15" t="s">
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="200" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B200" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B200" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="16" t="n">
-        <v>2541</v>
+      <c r="C200" s="12" t="n">
+        <v>37266</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="11" t="n">
-        <v>10</v>
+      <c r="C201" s="16" t="n">
+        <v>1721</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3323,23 +3029,23 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
       <c r="B203" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="C203" s="11" t="n">
-        <v>267</v>
+      <c r="C203" s="16" t="n">
+        <v>1170</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="16" t="n">
-        <v>1667</v>
+      <c r="C204" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3347,23 +3053,23 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>287</v>
+        <v>718</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="11" t="n">
-        <v>85</v>
+      <c r="C206" s="16" t="n">
+        <v>3803</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="16" t="n">
-        <v>2560</v>
+      <c r="C207" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3371,7 +3077,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>304</v>
+        <v>454</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3379,15 +3085,15 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>311</v>
+        <v>578</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="16" t="n">
-        <v>4478</v>
+      <c r="C210" s="11" t="n">
+        <v>683</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3395,31 +3101,31 @@
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>626</v>
+        <v>96</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="11" t="n">
-        <v>150</v>
+      <c r="C212" s="16" t="n">
+        <v>1375</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="11" t="n">
-        <v>223</v>
+      <c r="C213" s="16" t="n">
+        <v>1468</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
       <c r="B214" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="16" t="n">
-        <v>2447</v>
+      <c r="C214" s="11" t="n">
+        <v>717</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3427,7 +3133,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>525</v>
+        <v>633</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3435,31 +3141,31 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>844</v>
+        <v>759</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="16" t="n">
-        <v>1061</v>
+      <c r="C217" s="11" t="n">
+        <v>291</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="16" t="n">
-        <v>3718</v>
+      <c r="C218" s="11" t="n">
+        <v>949</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>592</v>
+      <c r="C219" s="16" t="n">
+        <v>1178</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3467,23 +3173,23 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>60</v>
+        <v>527</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
       <c r="B221" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="11" t="n">
-        <v>310</v>
+      <c r="C221" s="16" t="n">
+        <v>1219</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
       <c r="B222" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="11" t="n">
-        <v>111</v>
+      <c r="C222" s="16" t="n">
+        <v>2158</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3491,7 +3197,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="16" t="n">
-        <v>2744</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3499,7 +3205,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>220</v>
+        <v>392</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3507,15 +3213,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>666</v>
+        <v>979</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="16" t="n">
-        <v>2757</v>
+      <c r="C226" s="11" t="n">
+        <v>656</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3523,15 +3229,15 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>907</v>
+        <v>464</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="11" t="n">
-        <v>9</v>
+      <c r="C228" s="16" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3539,31 +3245,31 @@
         <v>228</v>
       </c>
       <c r="C229" s="16" t="n">
-        <v>2564</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="11" t="n">
-        <v>248</v>
+      <c r="C230" s="16" t="n">
+        <v>1201</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="11" t="n">
-        <v>385</v>
+      <c r="C231" s="16" t="n">
+        <v>1644</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="16" t="n">
-        <v>2766</v>
+      <c r="C232" s="11" t="n">
+        <v>819</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3571,7 +3277,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="16" t="n">
-        <v>1920</v>
+        <v>4404</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3579,23 +3285,23 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="235" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B235" s="15" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="235" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B235" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="11" t="n">
-        <v>94</v>
+      <c r="C235" s="12" t="n">
+        <v>2903</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="16" t="n">
-        <v>3725</v>
+      <c r="C236" s="11" t="n">
+        <v>529</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3603,7 +3309,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>750</v>
+        <v>818</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3611,15 +3317,15 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>371</v>
+        <v>386</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="16" t="n">
-        <v>1027</v>
+      <c r="C239" s="11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3627,7 +3333,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3635,7 +3341,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>502</v>
+        <v>144</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3643,7 +3349,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>263</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3651,7 +3357,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>74</v>
+        <v>150</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3659,7 +3365,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>166</v>
+        <v>205</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3667,7 +3373,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3675,23 +3381,23 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="247" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B247" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="247" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="12" t="n">
-        <v>28773</v>
-      </c>
-    </row>
-    <row r="248" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B248" s="15" t="s">
+      <c r="C247" s="11" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="248" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B248" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="16" t="n">
-        <v>1057</v>
+      <c r="C248" s="12" t="n">
+        <v>24768</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3699,15 +3405,15 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>458</v>
+        <v>502</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="16" t="n">
-        <v>1443</v>
+      <c r="C250" s="11" t="n">
+        <v>641</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3715,7 +3421,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="11" t="n">
-        <v>7</v>
+        <v>506</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3723,15 +3429,15 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>495</v>
+        <v>537</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="16" t="n">
-        <v>2698</v>
+      <c r="C253" s="11" t="n">
+        <v>201</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3739,7 +3445,7 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>40</v>
+        <v>243</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
@@ -3747,7 +3453,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="11" t="n">
-        <v>216</v>
+        <v>170</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3755,15 +3461,15 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="257" ht="11" customHeight="true" outlineLevel="3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="257" ht="22" customHeight="true" outlineLevel="3">
       <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>746</v>
+        <v>129</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3771,7 +3477,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>511</v>
+        <v>231</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3779,7 +3485,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>26</v>
+        <v>230</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3787,15 +3493,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>161</v>
+        <v>380</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="11" t="n">
-        <v>632</v>
+      <c r="C261" s="16" t="n">
+        <v>1520</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3803,87 +3509,87 @@
         <v>261</v>
       </c>
       <c r="C262" s="16" t="n">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="263" ht="11" customHeight="true" outlineLevel="3">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="263" ht="22" customHeight="true" outlineLevel="3">
       <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="264" ht="11" customHeight="true" outlineLevel="3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="264" ht="22" customHeight="true" outlineLevel="3">
       <c r="B264" s="15" t="s">
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="265" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="266" ht="11" customHeight="true" outlineLevel="3">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="266" ht="22" customHeight="true" outlineLevel="3">
       <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="267" ht="11" customHeight="true" outlineLevel="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="267" ht="22" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="268" ht="11" customHeight="true" outlineLevel="3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="268" ht="22" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="269" ht="11" customHeight="true" outlineLevel="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="270" ht="11" customHeight="true" outlineLevel="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="16" t="n">
-        <v>1362</v>
+      <c r="C270" s="11" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="16" t="n">
-        <v>2379</v>
+      <c r="C271" s="11" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="16" t="n">
-        <v>2257</v>
+      <c r="C272" s="11" t="n">
+        <v>361</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3891,7 +3597,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>242</v>
+        <v>340</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3899,23 +3605,23 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>62</v>
+        <v>250</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
       <c r="B275" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="11" t="n">
-        <v>412</v>
+      <c r="C275" s="16" t="n">
+        <v>3324</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="11" t="n">
-        <v>925</v>
+      <c r="C276" s="16" t="n">
+        <v>2071</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3923,7 +3629,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>462</v>
+        <v>851</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3931,7 +3637,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="16" t="n">
-        <v>2015</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3939,7 +3645,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="16" t="n">
-        <v>1877</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3947,31 +3653,31 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="16" t="n">
-        <v>2636</v>
+      <c r="C281" s="11" t="n">
+        <v>915</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
       <c r="B282" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="11" t="n">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="283" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B283" s="14" t="s">
+      <c r="C282" s="16" t="n">
+        <v>3168</v>
+      </c>
+    </row>
+    <row r="283" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="12" t="n">
-        <v>4608</v>
+      <c r="C283" s="16" t="n">
+        <v>2034</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3979,23 +3685,23 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="285" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B285" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B285" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="11" t="n">
-        <v>128</v>
+      <c r="C285" s="12" t="n">
+        <v>21870</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="11" t="n">
-        <v>506</v>
+      <c r="C286" s="16" t="n">
+        <v>1067</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -4003,7 +3709,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>318</v>
+        <v>400</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -4011,23 +3717,23 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="289" ht="11" customHeight="true" outlineLevel="3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="289" ht="22" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="11" t="n">
-        <v>17</v>
+      <c r="C290" s="16" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -4035,7 +3741,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>352</v>
+        <v>825</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -4043,7 +3749,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>209</v>
+        <v>148</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -4051,15 +3757,15 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>238</v>
+        <v>360</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="11" t="n">
-        <v>161</v>
+      <c r="C294" s="16" t="n">
+        <v>1226</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4067,7 +3773,7 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>272</v>
+        <v>500</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
@@ -4075,7 +3781,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>508</v>
+        <v>485</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -4083,7 +3789,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>424</v>
+        <v>659</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
@@ -4091,7 +3797,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
@@ -4099,7 +3805,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>17</v>
+        <v>678</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -4107,15 +3813,15 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B301" s="14" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="12" t="n">
-        <v>21329</v>
+      <c r="C301" s="11" t="n">
+        <v>685</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4123,15 +3829,15 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>232</v>
+        <v>800</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="11" t="n">
-        <v>199</v>
+      <c r="C303" s="16" t="n">
+        <v>1133</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -4139,7 +3845,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>284</v>
+        <v>916</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -4147,7 +3853,7 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>307</v>
+        <v>681</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -4155,15 +3861,15 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
       <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="11" t="n">
-        <v>324</v>
+      <c r="C307" s="16" t="n">
+        <v>1197</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4171,7 +3877,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>78</v>
+        <v>370</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -4179,7 +3885,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>336</v>
+        <v>191</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -4187,7 +3893,7 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>715</v>
+        <v>259</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
@@ -4195,7 +3901,7 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>46</v>
+        <v>456</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -4203,23 +3909,23 @@
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="true" outlineLevel="3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>150</v>
+        <v>599</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="11" t="n">
-        <v>247</v>
+      <c r="C314" s="16" t="n">
+        <v>2060</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -4227,7 +3933,7 @@
         <v>314</v>
       </c>
       <c r="C315" s="11" t="n">
-        <v>238</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4235,7 +3941,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>438</v>
+        <v>575</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4243,79 +3949,79 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>874</v>
+        <v>263</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="11" t="n">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="319" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B319" s="15" t="s">
+      <c r="C318" s="16" t="n">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B319" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C319" s="17" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="323" ht="22" customHeight="true" outlineLevel="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="324" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B324" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B324" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="325" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C324" s="12" t="n">
+        <v>35597</v>
+      </c>
+    </row>
+    <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="true" outlineLevel="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>30</v>
+        <v>127</v>
       </c>
     </row>
     <row r="327" ht="22" customHeight="true" outlineLevel="3">
@@ -4323,7 +4029,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>72</v>
+        <v>362</v>
       </c>
     </row>
     <row r="328" ht="22" customHeight="true" outlineLevel="3">
@@ -4331,7 +4037,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>228</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329" ht="22" customHeight="true" outlineLevel="3">
@@ -4339,23 +4045,23 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="330" ht="11" customHeight="true" outlineLevel="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="331" ht="11" customHeight="true" outlineLevel="3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="331" ht="22" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4363,47 +4069,47 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>30</v>
+        <v>469</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="11" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C333" s="16" t="n">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="335" ht="11" customHeight="true" outlineLevel="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="335" ht="22" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="16" t="n">
-        <v>1533</v>
+      <c r="C335" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="336" ht="22" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="C336" s="11" t="n">
-        <v>4</v>
+      <c r="C336" s="16" t="n">
+        <v>2614</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="16" t="n">
-        <v>1734</v>
+      <c r="C337" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4411,159 +4117,159 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>435</v>
+        <v>36</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="11" t="n">
-        <v>349</v>
+      <c r="C339" s="16" t="n">
+        <v>1008</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="16" t="n">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C340" s="11" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="16" t="n">
-        <v>1447</v>
-      </c>
-    </row>
-    <row r="344" ht="11" customHeight="true" outlineLevel="3">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="16" t="n">
-        <v>4394</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C344" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="16" t="n">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="347" ht="11" customHeight="true" outlineLevel="3">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="347" ht="22" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B348" s="14" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="17" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B349" s="18" t="s">
+      <c r="C348" s="11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="17" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B350" s="19" t="s">
+      <c r="C349" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B351" s="19" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B352" s="19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="352" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B353" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="354" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B354" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="354" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B354" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="12" t="n">
-        <v>16210</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C354" s="11" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="355" ht="22" customHeight="true" outlineLevel="3">
       <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="16" t="n">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="356" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C355" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" ht="22" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="16" t="n">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C356" s="11" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="357" ht="22" customHeight="true" outlineLevel="3">
       <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="358" ht="22" customHeight="true" outlineLevel="3">
@@ -4571,15 +4277,15 @@
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="359" ht="22" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>992</v>
+        <v>36</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
@@ -4587,7 +4293,7 @@
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>373</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
@@ -4595,7 +4301,7 @@
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>360</v>
+        <v>166</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4603,47 +4309,47 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="363" ht="11" customHeight="true" outlineLevel="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="363" ht="22" customHeight="true" outlineLevel="3">
       <c r="B363" s="15" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="364" ht="22" customHeight="true" outlineLevel="3">
       <c r="B364" s="15" t="s">
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="367" ht="22" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>785</v>
+        <v>18</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4651,23 +4357,23 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="369" ht="22" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="11" t="n">
-        <v>379</v>
+      <c r="C370" s="16" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4675,7 +4381,7 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>553</v>
+        <v>43</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
@@ -4683,7 +4389,7 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>136</v>
+        <v>274</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
@@ -4691,23 +4397,23 @@
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="375" ht="22" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>753</v>
+        <v>73</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4715,15 +4421,15 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>840</v>
+        <v>190</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="11" t="n">
-        <v>244</v>
+      <c r="C377" s="16" t="n">
+        <v>3337</v>
       </c>
     </row>
     <row r="378" ht="11" customHeight="true" outlineLevel="3">
@@ -4731,31 +4437,31 @@
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="379" ht="11" customHeight="true" outlineLevel="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="379" ht="22" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="381" ht="22" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="C381" s="11" t="n">
-        <v>209</v>
+      <c r="C381" s="16" t="n">
+        <v>2257</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
@@ -4763,15 +4469,15 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="383" ht="22" customHeight="true" outlineLevel="3">
       <c r="B383" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="11" t="n">
-        <v>232</v>
+      <c r="C383" s="16" t="n">
+        <v>4581</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4779,7 +4485,7 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>248</v>
+        <v>177</v>
       </c>
     </row>
     <row r="385" ht="11" customHeight="true" outlineLevel="3">
@@ -4787,7 +4493,7 @@
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>234</v>
+        <v>70</v>
       </c>
     </row>
     <row r="386" ht="11" customHeight="true" outlineLevel="3">
@@ -4795,7 +4501,7 @@
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>494</v>
+        <v>188</v>
       </c>
     </row>
     <row r="387" ht="11" customHeight="true" outlineLevel="3">
@@ -4803,15 +4509,15 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>40</v>
+        <v>228</v>
       </c>
     </row>
     <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="16" t="n">
-        <v>1104</v>
+      <c r="C388" s="11" t="n">
+        <v>284</v>
       </c>
     </row>
     <row r="389" ht="11" customHeight="true" outlineLevel="3">
@@ -4819,791 +4525,23 @@
         <v>388</v>
       </c>
       <c r="C389" s="16" t="n">
-        <v>1257</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="11" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="391" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C390" s="16" t="n">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="391" ht="22" customHeight="true" outlineLevel="3">
       <c r="B391" s="15" t="s">
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="392" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B392" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="C392" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="393" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B393" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="C393" s="11" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="394" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B394" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="C394" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B395" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="C395" s="17" t="n">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="396" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B396" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="C396" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="397" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B397" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="C397" s="11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="398" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B398" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="C398" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B399" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="C399" s="12" t="n">
-        <v>48820</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B400" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="C400" s="11" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B401" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="C401" s="11" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B402" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="C402" s="11" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="403" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B403" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="C403" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="404" ht="33" customHeight="true" outlineLevel="3">
-      <c r="B404" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="C404" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="405" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B405" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="C405" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="406" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B406" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="C406" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="407" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B407" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="C407" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="408" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B408" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="C408" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B409" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="C409" s="11" t="n">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="410" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B410" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C410" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B411" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="C411" s="16" t="n">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="412" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B412" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="C412" s="11" t="n">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="413" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B413" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C413" s="11" t="n">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="414" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B414" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C414" s="16" t="n">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="415" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B415" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="C415" s="11" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B416" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="C416" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="417" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B417" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="C417" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="418" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B418" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="C418" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="419" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B419" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="C419" s="16" t="n">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="420" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B420" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C420" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="421" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B421" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="C421" s="11" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="422" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B422" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="C422" s="11" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="423" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B423" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="C423" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="424" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B424" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="C424" s="11" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="425" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B425" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="C425" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="426" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B426" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="C426" s="16" t="n">
-        <v>3077</v>
-      </c>
-    </row>
-    <row r="427" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B427" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="C427" s="11" t="n">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="428" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B428" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="C428" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="429" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B429" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="C429" s="11" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="430" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B430" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="C430" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="431" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B431" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="C431" s="11" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="432" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B432" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="C432" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="433" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B433" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="C433" s="11" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="434" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B434" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="C434" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="435" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B435" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="C435" s="11" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="436" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B436" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="C436" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="437" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B437" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="C437" s="11" t="n">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="438" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B438" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="C438" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="439" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B439" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C439" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="440" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B440" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="C440" s="11" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="441" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B441" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="C441" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="442" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B442" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="C442" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="443" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B443" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="C443" s="11" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="444" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B444" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="C444" s="11" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="445" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B445" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="C445" s="11" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="446" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B446" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="C446" s="11" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="447" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B447" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="C447" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="448" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B448" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="C448" s="11" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="449" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B449" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="C449" s="11" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="450" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B450" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="C450" s="11" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="451" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B451" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="C451" s="11" t="n">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="452" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B452" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="C452" s="11" t="n">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="453" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B453" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="C453" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="454" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B454" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="C454" s="11" t="n">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="455" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B455" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="C455" s="11" t="n">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="456" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B456" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="C456" s="11" t="n">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="457" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B457" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C457" s="11" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="458" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B458" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="C458" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="459" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B459" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="C459" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="460" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B460" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="C460" s="16" t="n">
-        <v>6338</v>
-      </c>
-    </row>
-    <row r="461" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B461" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="C461" s="11" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="462" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B462" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="C462" s="11" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="463" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B463" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="C463" s="16" t="n">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="464" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B464" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="C464" s="11" t="n">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="465" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B465" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="C465" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="466" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B466" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="C466" s="16" t="n">
-        <v>1544</v>
-      </c>
-    </row>
-    <row r="467" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B467" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="C467" s="11" t="n">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="468" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B468" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="C468" s="11" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="469" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B469" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="C469" s="16" t="n">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="470" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B470" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="C470" s="16" t="n">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="471" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B471" s="15" t="s">
-        <v>470</v>
-      </c>
-      <c r="C471" s="11" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="472" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B472" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="C472" s="16" t="n">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="473" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B473" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="C473" s="11" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="474" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B474" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="C474" s="11" t="n">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="475" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B475" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="C475" s="16" t="n">
-        <v>3304</v>
-      </c>
-    </row>
-    <row r="476" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B476" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="C476" s="16" t="n">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="477" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B477" s="15" t="s">
-        <v>476</v>
-      </c>
-      <c r="C477" s="11" t="n">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="478" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B478" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="C478" s="11" t="n">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="479" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B479" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="C479" s="11" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="480" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B480" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="C480" s="12" t="n">
-        <v>4369</v>
-      </c>
-    </row>
-    <row r="481" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B481" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="C481" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="482" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B482" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="C482" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="483" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B483" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="C483" s="11" t="n">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="484" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B484" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="C484" s="16" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="485" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B485" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="C485" s="16" t="n">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="486" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B486" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="C486" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="487" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B487" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="C487" s="11" t="n">
-        <v>18</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="411">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.01.2026 15:05:15</t>
+    <t>Период: на 30.01.2026 8:15:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -74,9 +74,6 @@
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -86,12 +83,24 @@
     <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Желе ківі УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе ківі УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе Лісова ягода УБ 78г /56шт</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт</t>
+  </si>
+  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
@@ -113,15 +122,9 @@
     <t>Желатин УБ 25г /42шт</t>
   </si>
   <si>
-    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
@@ -131,19 +134,22 @@
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
-    <t>Суміш для приготування Грибного соусу УБ 36г /34шт АКЦІЯ ВІП</t>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ</t>
   </si>
   <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
-    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт АКЦІЯ ВІП</t>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /</t>
   </si>
   <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
-    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт АКЦІЯ ВІП</t>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /</t>
   </si>
   <si>
     <t>ПРИПРАВИ</t>
@@ -152,9 +158,15 @@
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до курки УБ 25г /34шт</t>
   </si>
   <si>
+    <t>Приправа до курки УБ 25г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
@@ -182,6 +194,12 @@
     <t>Приправа до шашлику УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Прованські трави УБ 10г /28шт</t>
+  </si>
+  <si>
+    <t>Прованські трави УБ 10г /28шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш зелені УБ 10г /24шт</t>
   </si>
   <si>
@@ -191,9 +209,15 @@
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
+    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
+    <t>Суміш прянощів Італійські трави УБ 10г /28шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
@@ -224,6 +248,9 @@
     <t>Лавровий лист 10г/80</t>
   </si>
   <si>
+    <t>Паприка копчена мелена УБ 20г /34шт</t>
+  </si>
+  <si>
     <t>Паприка мелена УБ 20г /34шт</t>
   </si>
   <si>
@@ -260,9 +287,15 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -272,30 +305,30 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
@@ -344,18 +377,21 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
+  </si>
+  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з молочною начинкою ВКФ 140г /15шт</t>
-  </si>
-  <si>
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
+    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
@@ -461,6 +497,9 @@
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -506,21 +545,48 @@
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Colorounds ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -551,9 +617,6 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
@@ -584,9 +647,6 @@
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
@@ -596,7 +656,7 @@
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
     <t>Джеллі РЦ 200г /13шт</t>
@@ -728,9 +788,21 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
@@ -740,6 +812,12 @@
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
@@ -755,6 +833,15 @@
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters з ромовим лікером ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт</t>
+  </si>
+  <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -866,6 +953,9 @@
     <t>До кави пряжене молоко ВКФ 185г /28шт /</t>
   </si>
   <si>
+    <t>До кави пряжене молоко ВКФ 185г /28шт /АКЦІЯ</t>
+  </si>
+  <si>
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
@@ -938,6 +1028,9 @@
     <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
@@ -962,9 +1055,15 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
+    <t>Сливки-Ленивки 1кг ВКФ</t>
+  </si>
+  <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1016,9 +1115,6 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
@@ -1037,15 +1133,9 @@
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -1061,12 +1151,6 @@
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -1082,24 +1166,15 @@
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з сезамом ВКФ 90г /22шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1115,7 +1190,7 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
@@ -1127,9 +1202,6 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -1139,24 +1211,18 @@
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
@@ -1166,15 +1232,12 @@
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
-    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
@@ -1188,9 +1251,6 @@
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1496,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C391"/>
+  <dimension ref="C411"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1501,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>530</v>
+        <v>662</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1509,7 +1569,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>387828</v>
+        <v>443092</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1517,7 +1577,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>75919</v>
+        <v>98842</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1525,7 +1585,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>10450</v>
+        <v>20435</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1533,15 +1593,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>2571</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>800</v>
+      <c r="C16" s="16" t="n">
+        <v>3078</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1557,7 +1617,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>1231</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1565,15 +1625,15 @@
         <v>18</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>224</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>56</v>
+      <c r="C20" s="16" t="n">
+        <v>3155</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1581,15 +1641,15 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>319</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
       <c r="B22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>56</v>
+      <c r="C22" s="16" t="n">
+        <v>2809</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1597,15 +1657,15 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>224</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>414</v>
+      <c r="C24" s="16" t="n">
+        <v>1398</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1613,31 +1673,31 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>450</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="16" t="n">
-        <v>3711</v>
-      </c>
-    </row>
-    <row r="27" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B27" s="14" t="s">
+      <c r="C26" s="11" t="n">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>23074</v>
+      <c r="C27" s="16" t="n">
+        <v>1828</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>2364</v>
+      <c r="C28" s="11" t="n">
+        <v>202</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1645,15 +1705,15 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>5969</v>
-      </c>
-    </row>
-    <row r="30" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B30" s="15" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="30" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B30" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="16" t="n">
-        <v>1767</v>
+      <c r="C30" s="12" t="n">
+        <v>30621</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1661,39 +1721,39 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>9048</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>336</v>
+      <c r="C32" s="16" t="n">
+        <v>11933</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>42</v>
+      <c r="C33" s="16" t="n">
+        <v>1767</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>12</v>
+      <c r="C34" s="16" t="n">
+        <v>6964</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="16" t="n">
-        <v>1093</v>
+      <c r="C35" s="11" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1701,15 +1761,15 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>484</v>
+        <v>573</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>394</v>
+      <c r="C37" s="16" t="n">
+        <v>1339</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1717,23 +1777,23 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>310</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C39" s="16" t="n">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>260</v>
+        <v>476</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1741,23 +1801,23 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="true" outlineLevel="3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B43" s="14" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="12" t="n">
-        <v>8588</v>
+      <c r="C43" s="16" t="n">
+        <v>1202</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1765,15 +1825,15 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B45" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B45" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>503</v>
+      <c r="C45" s="12" t="n">
+        <v>13478</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1781,7 +1841,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>246</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1789,15 +1849,15 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>777</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>319</v>
+      <c r="C48" s="16" t="n">
+        <v>1118</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1805,7 +1865,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>329</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1813,7 +1873,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>625</v>
+        <v>920</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1821,7 +1881,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>98</v>
+        <v>777</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1829,23 +1889,23 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>455</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
       <c r="B53" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>494</v>
+      <c r="C53" s="16" t="n">
+        <v>1174</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="16" t="n">
-        <v>1105</v>
+      <c r="C54" s="11" t="n">
+        <v>625</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1853,7 +1913,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>193</v>
+        <v>415</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1861,7 +1921,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>115</v>
+        <v>455</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1869,15 +1929,15 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>284</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>716</v>
+      <c r="C58" s="16" t="n">
+        <v>1105</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1885,7 +1945,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>869</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1893,7 +1953,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>443</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -1901,7 +1961,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>549</v>
+        <v>767</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -1909,55 +1969,55 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="63" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B63" s="14" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="63" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="12" t="n">
-        <v>33807</v>
-      </c>
-    </row>
-    <row r="64" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C63" s="11" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>316</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>1837</v>
+      <c r="C65" s="11" t="n">
+        <v>668</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="n">
-        <v>1019</v>
+      <c r="C66" s="11" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>1677</v>
+      <c r="C67" s="11" t="n">
+        <v>364</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="16" t="n">
-        <v>5774</v>
+      <c r="C68" s="11" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -1965,31 +2025,31 @@
         <v>68</v>
       </c>
       <c r="C69" s="16" t="n">
-        <v>1533</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="71" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B71" s="15" t="s">
+      <c r="C70" s="11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B71" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>450</v>
+      <c r="C71" s="12" t="n">
+        <v>34308</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="16" t="n">
-        <v>2212</v>
+      <c r="C72" s="11" t="n">
+        <v>536</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -1997,15 +2057,15 @@
         <v>72</v>
       </c>
       <c r="C73" s="16" t="n">
-        <v>1783</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="16" t="n">
-        <v>9143</v>
+      <c r="C74" s="11" t="n">
+        <v>769</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2013,47 +2073,47 @@
         <v>74</v>
       </c>
       <c r="C75" s="16" t="n">
-        <v>5377</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>285</v>
+      <c r="C76" s="16" t="n">
+        <v>7001</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B78" s="13" t="s">
+      <c r="C77" s="16" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="12" t="n">
-        <v>311909</v>
-      </c>
-    </row>
-    <row r="79" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B79" s="14" t="s">
+      <c r="C78" s="16" t="n">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="79" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="12" t="n">
-        <v>91186</v>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C79" s="16" t="n">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>3480</v>
+      <c r="C80" s="11" t="n">
+        <v>972</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2061,7 +2121,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="16" t="n">
-        <v>21281</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
@@ -2069,199 +2129,199 @@
         <v>81</v>
       </c>
       <c r="C82" s="16" t="n">
-        <v>3155</v>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="true" outlineLevel="3">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C83" s="16" t="n">
+        <v>8089</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
       <c r="C84" s="16" t="n">
-        <v>8659</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="true" outlineLevel="3">
+        <v>5377</v>
+      </c>
+    </row>
+    <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>3399</v>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C85" s="11" t="n">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="16" t="n">
-        <v>8811</v>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B87" s="15" t="s">
+      <c r="C86" s="11" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="87" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B87" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>4844</v>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B88" s="15" t="s">
+      <c r="C87" s="12" t="n">
+        <v>344250</v>
+      </c>
+    </row>
+    <row r="88" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B88" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="16" t="n">
-        <v>8724</v>
+      <c r="C88" s="12" t="n">
+        <v>54339</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="16" t="n">
-        <v>3005</v>
+      <c r="C89" s="11" t="n">
+        <v>775</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="16" t="n">
-        <v>4764</v>
-      </c>
-    </row>
-    <row r="91" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C90" s="11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" ht="11" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="92" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C91" s="16" t="n">
+        <v>17620</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="16" t="n">
-        <v>20668</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B93" s="14" t="s">
+      <c r="C92" s="11" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="12" t="n">
-        <v>5235</v>
-      </c>
-    </row>
-    <row r="94" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C93" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="16" t="n">
-        <v>1462</v>
-      </c>
-    </row>
-    <row r="95" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C94" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="96" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C95" s="16" t="n">
+        <v>6809</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C98" s="16" t="n">
+        <v>6294</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="100" ht="11" customHeight="true" outlineLevel="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="101" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C100" s="16" t="n">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" ht="11" customHeight="true" outlineLevel="3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C102" s="16" t="n">
+        <v>18242</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
       <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B104" s="15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B104" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C104" s="12" t="n">
+        <v>6761</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B106" s="14" t="s">
+      <c r="C105" s="16" t="n">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="12" t="n">
-        <v>38027</v>
+      <c r="C106" s="11" t="n">
+        <v>678</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2269,7 +2329,7 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>464</v>
+        <v>918</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
@@ -2277,7 +2337,7 @@
         <v>107</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>233</v>
+        <v>676</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2285,39 +2345,39 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>396</v>
+        <v>531</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>212</v>
+      <c r="C110" s="16" t="n">
+        <v>2084</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="16" t="n">
-        <v>10580</v>
+      <c r="C111" s="11" t="n">
+        <v>238</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
       <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="16" t="n">
-        <v>11821</v>
+      <c r="C112" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="113" ht="11" customHeight="true" outlineLevel="3">
       <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="16" t="n">
-        <v>2160</v>
+      <c r="C113" s="11" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2325,7 +2385,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2333,23 +2393,23 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="116" ht="11" customHeight="true" outlineLevel="3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B117" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B117" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>995</v>
+      <c r="C117" s="12" t="n">
+        <v>71059</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2357,15 +2417,15 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>496</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="16" t="n">
-        <v>1943</v>
+      <c r="C119" s="11" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2373,7 +2433,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>133</v>
+        <v>229</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2381,7 +2441,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>3</v>
+        <v>455</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2389,31 +2449,31 @@
         <v>121</v>
       </c>
       <c r="C122" s="16" t="n">
-        <v>1786</v>
+        <v>25880</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>1</v>
+      <c r="C123" s="16" t="n">
+        <v>16596</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
       <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>830</v>
+      <c r="C124" s="16" t="n">
+        <v>3750</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>456</v>
+      <c r="C125" s="16" t="n">
+        <v>11610</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2421,7 +2481,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>180</v>
+        <v>83</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2429,15 +2489,15 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>235</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="16" t="n">
-        <v>1736</v>
+      <c r="C128" s="11" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2445,7 +2505,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>189</v>
+        <v>691</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2453,55 +2513,55 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>1</v>
+        <v>425</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>298</v>
+      <c r="C131" s="16" t="n">
+        <v>1210</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
       <c r="B132" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="11" t="n">
-        <v>386</v>
+      <c r="C132" s="16" t="n">
+        <v>1158</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="16" t="n">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="134" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B134" s="14" t="s">
+      <c r="C133" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B134" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="12" t="n">
-        <v>54763</v>
+      <c r="C134" s="11" t="n">
+        <v>910</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="16" t="n">
-        <v>1227</v>
+      <c r="C135" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="11" t="n">
-        <v>365</v>
+      <c r="C136" s="16" t="n">
+        <v>1485</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2509,7 +2569,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>225</v>
+        <v>316</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2517,7 +2577,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>18</v>
+        <v>183</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2525,15 +2585,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>271</v>
+        <v>538</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="11" t="n">
-        <v>342</v>
+      <c r="C140" s="16" t="n">
+        <v>1450</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2541,7 +2601,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2549,15 +2609,15 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
       <c r="B143" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="11" t="n">
-        <v>208</v>
+      <c r="C143" s="16" t="n">
+        <v>1261</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2565,7 +2625,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>491</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2573,15 +2633,15 @@
         <v>144</v>
       </c>
       <c r="C145" s="16" t="n">
-        <v>2677</v>
-      </c>
-    </row>
-    <row r="146" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B146" s="15" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="146" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B146" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="16" t="n">
-        <v>1028</v>
+      <c r="C146" s="12" t="n">
+        <v>103838</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2589,15 +2649,15 @@
         <v>146</v>
       </c>
       <c r="C147" s="16" t="n">
-        <v>1702</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
       <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="16" t="n">
-        <v>1131</v>
+      <c r="C148" s="11" t="n">
+        <v>291</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2605,7 +2665,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>486</v>
+        <v>85</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2613,15 +2673,15 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>270</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
       <c r="B151" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="16" t="n">
-        <v>2954</v>
+      <c r="C151" s="11" t="n">
+        <v>282</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2629,15 +2689,15 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>250</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="16" t="n">
-        <v>2373</v>
+      <c r="C153" s="11" t="n">
+        <v>245</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2645,15 +2705,15 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>252</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
       <c r="B155" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="16" t="n">
-        <v>1438</v>
+      <c r="C155" s="11" t="n">
+        <v>157</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2661,31 +2721,31 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>549</v>
+        <v>491</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="11" t="n">
-        <v>807</v>
+      <c r="C157" s="16" t="n">
+        <v>2664</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
       <c r="B158" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="16" t="n">
-        <v>2980</v>
+      <c r="C158" s="11" t="n">
+        <v>695</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="11" t="n">
-        <v>152</v>
+      <c r="C159" s="16" t="n">
+        <v>1392</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2693,15 +2753,15 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>29</v>
+        <v>479</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
       <c r="B161" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C161" s="11" t="n">
-        <v>298</v>
+      <c r="C161" s="16" t="n">
+        <v>1084</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2709,7 +2769,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>168</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2717,15 +2777,15 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>436</v>
+        <v>264</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="11" t="n">
-        <v>144</v>
+      <c r="C164" s="16" t="n">
+        <v>2172</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2733,15 +2793,15 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>70</v>
+        <v>247</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="11" t="n">
-        <v>105</v>
+      <c r="C166" s="16" t="n">
+        <v>1938</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2749,7 +2809,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>80</v>
+        <v>223</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2757,7 +2817,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>341</v>
+        <v>847</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2765,7 +2825,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>491</v>
+        <v>284</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2773,7 +2833,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>164</v>
+        <v>697</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2781,7 +2841,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="16" t="n">
-        <v>1729</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2789,15 +2849,15 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>542</v>
+        <v>597</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
       <c r="B173" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C173" s="16" t="n">
-        <v>3021</v>
+      <c r="C173" s="11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2805,7 +2865,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>585</v>
+        <v>298</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2813,7 +2873,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>274</v>
+        <v>405</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2821,15 +2881,15 @@
         <v>175</v>
       </c>
       <c r="C176" s="16" t="n">
-        <v>2403</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="11" t="n">
-        <v>235</v>
+      <c r="C177" s="16" t="n">
+        <v>2736</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2837,47 +2897,47 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>8</v>
+        <v>131</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
       <c r="B179" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="16" t="n">
-        <v>3465</v>
-      </c>
-    </row>
-    <row r="180" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C179" s="11" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="181" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C180" s="16" t="n">
+        <v>13220</v>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="182" ht="11" customHeight="true" outlineLevel="3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
       <c r="C182" s="16" t="n">
-        <v>2312</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>398</v>
+      <c r="C183" s="16" t="n">
+        <v>16206</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2885,23 +2945,23 @@
         <v>183</v>
       </c>
       <c r="C184" s="16" t="n">
-        <v>2363</v>
-      </c>
-    </row>
-    <row r="185" ht="11" customHeight="true" outlineLevel="3">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="11" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="186" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C185" s="16" t="n">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="true" outlineLevel="3">
       <c r="B186" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="16" t="n">
-        <v>2094</v>
+      <c r="C186" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
@@ -2909,7 +2969,7 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>540</v>
+        <v>327</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
@@ -2917,15 +2977,15 @@
         <v>187</v>
       </c>
       <c r="C188" s="16" t="n">
-        <v>3116</v>
-      </c>
-    </row>
-    <row r="189" ht="11" customHeight="true" outlineLevel="3">
+        <v>11572</v>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
       <c r="C189" s="11" t="n">
-        <v>485</v>
+        <v>324</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2933,15 +2993,15 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="16" t="n">
-        <v>3558</v>
+      <c r="C191" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -2949,15 +3009,15 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>765</v>
+        <v>161</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="11" t="n">
-        <v>77</v>
+      <c r="C193" s="16" t="n">
+        <v>1321</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -2965,15 +3025,15 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="11" t="n">
-        <v>96</v>
+      <c r="C195" s="16" t="n">
+        <v>2195</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -2981,7 +3041,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>47</v>
+        <v>570</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -2989,15 +3049,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>9</v>
+        <v>259</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="11" t="n">
-        <v>377</v>
+      <c r="C198" s="16" t="n">
+        <v>2396</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3005,23 +3065,23 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="200" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B200" s="14" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="200" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="12" t="n">
-        <v>37266</v>
+      <c r="C200" s="16" t="n">
+        <v>3465</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="16" t="n">
-        <v>1721</v>
+      <c r="C201" s="11" t="n">
+        <v>409</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3029,7 +3089,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>147</v>
+        <v>304</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3037,7 +3097,7 @@
         <v>202</v>
       </c>
       <c r="C203" s="16" t="n">
-        <v>1170</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3045,31 +3105,31 @@
         <v>203</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>7</v>
+        <v>404</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>718</v>
+      <c r="C205" s="16" t="n">
+        <v>2363</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="16" t="n">
-        <v>3803</v>
+      <c r="C206" s="11" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="11" t="n">
-        <v>216</v>
+      <c r="C207" s="16" t="n">
+        <v>2017</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3077,15 +3137,15 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>454</v>
+        <v>518</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="11" t="n">
-        <v>578</v>
+      <c r="C209" s="16" t="n">
+        <v>3005</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3093,31 +3153,31 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>683</v>
+        <v>327</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
       <c r="B211" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="11" t="n">
-        <v>96</v>
+      <c r="C211" s="16" t="n">
+        <v>3393</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
       <c r="B212" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="16" t="n">
-        <v>1375</v>
+      <c r="C212" s="11" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="16" t="n">
-        <v>1468</v>
+      <c r="C213" s="11" t="n">
+        <v>279</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3125,7 +3185,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>717</v>
+        <v>238</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3133,7 +3193,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>633</v>
+        <v>68</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3141,7 +3201,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>759</v>
+        <v>140</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3149,7 +3209,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>291</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3157,23 +3217,23 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>949</v>
+        <v>378</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="16" t="n">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="220" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B220" s="15" t="s">
+      <c r="C219" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="220" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B220" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="11" t="n">
-        <v>527</v>
+      <c r="C220" s="12" t="n">
+        <v>29419</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3181,15 +3241,15 @@
         <v>220</v>
       </c>
       <c r="C221" s="16" t="n">
-        <v>1219</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
       <c r="B222" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="16" t="n">
-        <v>2158</v>
+      <c r="C222" s="11" t="n">
+        <v>354</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3197,7 +3257,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="16" t="n">
-        <v>1124</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3205,7 +3265,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>392</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3213,15 +3273,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>979</v>
+        <v>462</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>656</v>
+      <c r="C226" s="16" t="n">
+        <v>2213</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3229,39 +3289,39 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>464</v>
+        <v>216</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="16" t="n">
-        <v>2025</v>
+      <c r="C228" s="11" t="n">
+        <v>426</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="16" t="n">
-        <v>1762</v>
+      <c r="C229" s="11" t="n">
+        <v>542</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="16" t="n">
-        <v>1201</v>
+      <c r="C230" s="11" t="n">
+        <v>568</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="16" t="n">
-        <v>1644</v>
+      <c r="C231" s="11" t="n">
+        <v>202</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
@@ -3269,7 +3329,7 @@
         <v>231</v>
       </c>
       <c r="C232" s="11" t="n">
-        <v>819</v>
+        <v>915</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3277,7 +3337,7 @@
         <v>232</v>
       </c>
       <c r="C233" s="16" t="n">
-        <v>4404</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3285,15 +3345,15 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="235" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B235" s="14" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="235" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B235" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="12" t="n">
-        <v>2903</v>
+      <c r="C235" s="11" t="n">
+        <v>461</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3301,7 +3361,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>529</v>
+        <v>465</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3309,7 +3369,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>818</v>
+        <v>199</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3317,7 +3377,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>386</v>
+        <v>672</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3325,7 +3385,7 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>14</v>
+        <v>982</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3333,7 +3393,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>138</v>
+        <v>329</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3341,23 +3401,23 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>144</v>
+        <v>798</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="11" t="n">
-        <v>2</v>
+      <c r="C242" s="16" t="n">
+        <v>1495</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="11" t="n">
-        <v>150</v>
+      <c r="C243" s="16" t="n">
+        <v>1302</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3365,7 +3425,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>205</v>
+        <v>954</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3373,15 +3433,15 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>373</v>
+        <v>787</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
       <c r="B246" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="11" t="n">
-        <v>38</v>
+      <c r="C246" s="16" t="n">
+        <v>1052</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3389,23 +3449,23 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="248" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B248" s="14" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="248" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="12" t="n">
-        <v>24768</v>
+      <c r="C248" s="16" t="n">
+        <v>1141</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="11" t="n">
-        <v>502</v>
+      <c r="C249" s="16" t="n">
+        <v>1225</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3413,15 +3473,15 @@
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>641</v>
+        <v>770</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>506</v>
+      <c r="C251" s="16" t="n">
+        <v>1524</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3429,15 +3489,15 @@
         <v>251</v>
       </c>
       <c r="C252" s="11" t="n">
-        <v>537</v>
+        <v>853</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="11" t="n">
-        <v>201</v>
+      <c r="C253" s="16" t="n">
+        <v>2577</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3445,15 +3505,15 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="255" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B255" s="15" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B255" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="11" t="n">
-        <v>170</v>
+      <c r="C255" s="12" t="n">
+        <v>3133</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3461,15 +3521,15 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="257" ht="22" customHeight="true" outlineLevel="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>129</v>
+        <v>43</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3477,7 +3537,7 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>231</v>
+        <v>16</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3485,7 +3545,7 @@
         <v>258</v>
       </c>
       <c r="C259" s="11" t="n">
-        <v>230</v>
+        <v>354</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3493,87 +3553,87 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>380</v>
+        <v>16</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="16" t="n">
-        <v>1520</v>
+      <c r="C261" s="11" t="n">
+        <v>272</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="16" t="n">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="263" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C262" s="11" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="264" ht="22" customHeight="true" outlineLevel="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="264" ht="11" customHeight="true" outlineLevel="3">
       <c r="B264" s="15" t="s">
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="265" ht="22" customHeight="true" outlineLevel="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="265" ht="11" customHeight="true" outlineLevel="3">
       <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="266" ht="22" customHeight="true" outlineLevel="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="266" ht="11" customHeight="true" outlineLevel="3">
       <c r="B266" s="15" t="s">
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="267" ht="22" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="268" ht="22" customHeight="true" outlineLevel="3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="15" t="s">
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="269" ht="22" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="270" ht="22" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3581,7 +3641,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>128</v>
+        <v>570</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3589,7 +3649,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>361</v>
+        <v>217</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3597,7 +3657,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>340</v>
+        <v>164</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3605,47 +3665,47 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>250</v>
+        <v>18</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
       <c r="B275" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="16" t="n">
-        <v>3324</v>
+      <c r="C275" s="11" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="16" t="n">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="277" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B277" s="15" t="s">
+      <c r="C276" s="11" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="277" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B277" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="11" t="n">
-        <v>851</v>
+      <c r="C277" s="12" t="n">
+        <v>23908</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="16" t="n">
-        <v>1319</v>
+      <c r="C278" s="11" t="n">
+        <v>554</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="16" t="n">
-        <v>1364</v>
+      <c r="C279" s="11" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3653,7 +3713,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>6</v>
+        <v>373</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3661,23 +3721,23 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>915</v>
+        <v>416</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
       <c r="B282" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="16" t="n">
-        <v>3168</v>
+      <c r="C282" s="11" t="n">
+        <v>368</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
       <c r="B283" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="16" t="n">
-        <v>2034</v>
+      <c r="C283" s="11" t="n">
+        <v>526</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3685,23 +3745,23 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="285" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B285" s="14" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B285" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="12" t="n">
-        <v>21870</v>
-      </c>
-    </row>
-    <row r="286" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C285" s="11" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="286" ht="22" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="16" t="n">
-        <v>1067</v>
+      <c r="C286" s="11" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3709,7 +3769,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>400</v>
+        <v>226</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -3717,23 +3777,23 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="289" ht="22" customHeight="true" outlineLevel="3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="290" ht="22" customHeight="true" outlineLevel="3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="16" t="n">
-        <v>1500</v>
+      <c r="C290" s="11" t="n">
+        <v>257</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3741,71 +3801,71 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="292" ht="11" customHeight="true" outlineLevel="3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="293" ht="11" customHeight="true" outlineLevel="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="294" ht="11" customHeight="true" outlineLevel="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="294" ht="22" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="16" t="n">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="295" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C294" s="11" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="296" ht="11" customHeight="true" outlineLevel="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="297" ht="11" customHeight="true" outlineLevel="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="298" ht="11" customHeight="true" outlineLevel="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="299" ht="11" customHeight="true" outlineLevel="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="299" ht="22" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>678</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
@@ -3813,7 +3873,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>188</v>
+        <v>494</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -3821,7 +3881,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>685</v>
+        <v>288</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3829,31 +3889,31 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>800</v>
+        <v>294</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="16" t="n">
-        <v>1133</v>
+      <c r="C303" s="11" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="11" t="n">
-        <v>916</v>
+      <c r="C304" s="16" t="n">
+        <v>2206</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="11" t="n">
-        <v>681</v>
+      <c r="C305" s="16" t="n">
+        <v>1198</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -3861,7 +3921,7 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>300</v>
+        <v>654</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -3869,15 +3929,15 @@
         <v>306</v>
       </c>
       <c r="C307" s="16" t="n">
-        <v>1197</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="C308" s="11" t="n">
-        <v>370</v>
+      <c r="C308" s="16" t="n">
+        <v>2117</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3885,55 +3945,55 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>191</v>
+        <v>6</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="11" t="n">
-        <v>259</v>
+      <c r="C310" s="16" t="n">
+        <v>1753</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="11" t="n">
-        <v>456</v>
+      <c r="C311" s="16" t="n">
+        <v>3468</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="11" t="n">
-        <v>387</v>
+      <c r="C312" s="16" t="n">
+        <v>1067</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="11" t="n">
-        <v>599</v>
+      <c r="C313" s="16" t="n">
+        <v>1673</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="16" t="n">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="315" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B315" s="15" t="s">
+      <c r="C314" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B315" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="11" t="n">
-        <v>2</v>
+      <c r="C315" s="12" t="n">
+        <v>28063</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -3941,7 +4001,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>575</v>
+        <v>795</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -3949,31 +4009,31 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>263</v>
+        <v>400</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="16" t="n">
-        <v>1509</v>
-      </c>
-    </row>
-    <row r="319" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B319" s="14" t="s">
+      <c r="C318" s="11" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="319" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="17" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="320" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C319" s="11" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="320" ht="22" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="11" t="n">
-        <v>36</v>
+      <c r="C320" s="16" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
@@ -3981,7 +4041,7 @@
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>31</v>
+        <v>414</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
@@ -3989,7 +4049,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>101</v>
+        <v>286</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -3997,15 +4057,15 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B324" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="324" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="12" t="n">
-        <v>35597</v>
+      <c r="C324" s="11" t="n">
+        <v>561</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4013,7 +4073,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>68</v>
+        <v>500</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4021,47 +4081,47 @@
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="327" ht="22" customHeight="true" outlineLevel="3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="328" ht="22" customHeight="true" outlineLevel="3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="328" ht="11" customHeight="true" outlineLevel="3">
       <c r="B328" s="15" t="s">
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="329" ht="22" customHeight="true" outlineLevel="3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="330" ht="22" customHeight="true" outlineLevel="3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="331" ht="22" customHeight="true" outlineLevel="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>12</v>
+        <v>675</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4069,47 +4129,47 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>469</v>
+        <v>650</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="16" t="n">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="334" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C333" s="11" t="n">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="335" ht="22" customHeight="true" outlineLevel="3">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="336" ht="22" customHeight="true" outlineLevel="3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="336" ht="11" customHeight="true" outlineLevel="3">
       <c r="B336" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="C336" s="16" t="n">
-        <v>2614</v>
+      <c r="C336" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="11" t="n">
-        <v>6</v>
+      <c r="C337" s="16" t="n">
+        <v>1114</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4117,15 +4177,15 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>36</v>
+        <v>919</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="16" t="n">
-        <v>1008</v>
+      <c r="C339" s="11" t="n">
+        <v>242</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4133,183 +4193,183 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="341" ht="22" customHeight="true" outlineLevel="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="342" ht="22" customHeight="true" outlineLevel="3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="343" ht="22" customHeight="true" outlineLevel="3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="16" t="n">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="344" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C343" s="11" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="345" ht="22" customHeight="true" outlineLevel="3">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="346" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C345" s="16" t="n">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="16" t="n">
-        <v>4066</v>
-      </c>
-    </row>
-    <row r="347" ht="22" customHeight="true" outlineLevel="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="11" t="n">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="348" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C347" s="16" t="n">
+        <v>7021</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C348" s="16" t="n">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="true" outlineLevel="3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="351" ht="22" customHeight="true" outlineLevel="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
       <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="11" t="n">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="352" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B352" s="15" t="s">
+      <c r="C351" s="16" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B352" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="11" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="353" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C352" s="17" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="354" ht="22" customHeight="true" outlineLevel="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
       <c r="B354" s="15" t="s">
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="355" ht="22" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
       <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="356" ht="22" customHeight="true" outlineLevel="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="357" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B357" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B357" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="358" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C357" s="12" t="n">
+        <v>23440</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="359" ht="22" customHeight="true" outlineLevel="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="360" ht="22" customHeight="true" outlineLevel="3">
       <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="362" ht="22" customHeight="true" outlineLevel="3">
       <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>170</v>
+        <v>72</v>
       </c>
     </row>
     <row r="363" ht="22" customHeight="true" outlineLevel="3">
@@ -4317,7 +4377,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>149</v>
+        <v>259</v>
       </c>
     </row>
     <row r="364" ht="22" customHeight="true" outlineLevel="3">
@@ -4325,15 +4385,15 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>56</v>
+        <v>217</v>
       </c>
     </row>
     <row r="366" ht="22" customHeight="true" outlineLevel="3">
@@ -4341,7 +4401,7 @@
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>140</v>
+        <v>185</v>
       </c>
     </row>
     <row r="367" ht="22" customHeight="true" outlineLevel="3">
@@ -4349,31 +4409,31 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="368" ht="11" customHeight="true" outlineLevel="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="368" ht="22" customHeight="true" outlineLevel="3">
       <c r="B368" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="C368" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C368" s="16" t="n">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="16" t="n">
-        <v>1960</v>
+      <c r="C370" s="11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4381,23 +4441,23 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="11" t="n">
-        <v>239</v>
+      <c r="C373" s="16" t="n">
+        <v>1158</v>
       </c>
     </row>
     <row r="374" ht="22" customHeight="true" outlineLevel="3">
@@ -4405,7 +4465,7 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>186</v>
+        <v>551</v>
       </c>
     </row>
     <row r="375" ht="22" customHeight="true" outlineLevel="3">
@@ -4413,31 +4473,31 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="11" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C376" s="16" t="n">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="16" t="n">
-        <v>3337</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C377" s="11" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="379" ht="22" customHeight="true" outlineLevel="3">
@@ -4445,55 +4505,55 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="380" ht="22" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>471</v>
+        <v>42</v>
       </c>
     </row>
     <row r="381" ht="22" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="C381" s="16" t="n">
-        <v>2257</v>
-      </c>
-    </row>
-    <row r="382" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C381" s="11" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="382" ht="22" customHeight="true" outlineLevel="3">
       <c r="B382" s="15" t="s">
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="383" ht="22" customHeight="true" outlineLevel="3">
       <c r="B383" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="16" t="n">
-        <v>4581</v>
-      </c>
-    </row>
-    <row r="384" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C383" s="11" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="384" ht="22" customHeight="true" outlineLevel="3">
       <c r="B384" s="15" t="s">
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="385" ht="22" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
     </row>
     <row r="386" ht="11" customHeight="true" outlineLevel="3">
@@ -4501,7 +4561,7 @@
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>188</v>
+        <v>76</v>
       </c>
     </row>
     <row r="387" ht="11" customHeight="true" outlineLevel="3">
@@ -4509,31 +4569,31 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="388" ht="22" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="C389" s="16" t="n">
-        <v>1804</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C389" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="16" t="n">
-        <v>2325</v>
+      <c r="C390" s="11" t="n">
+        <v>354</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4541,7 +4601,167 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>194</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B392" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="C392" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="393" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B393" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C393" s="11" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="394" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B394" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="C394" s="11" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B395" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="C395" s="11" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B396" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C396" s="11" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B397" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="C397" s="11" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B398" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C398" s="11" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B399" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="C399" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B400" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="C400" s="16" t="n">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B401" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C401" s="11" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B402" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="C402" s="11" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B403" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C403" s="16" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B404" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C404" s="11" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B405" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C405" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B406" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="C406" s="11" t="n">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B407" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C407" s="16" t="n">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B408" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="C408" s="11" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B409" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="11" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="410" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B410" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="16" t="n">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="16" t="n">
+        <v>1932</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 30.01.2026 8:15:14</t>
+    <t>Период: на 11.02.2026 19:55:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -74,15 +74,9 @@
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе вишня УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -116,6 +107,9 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Ванільний цукор УБ 35г /36шт</t>
+  </si>
+  <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -125,6 +119,9 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
-    <t>Суміш прянощів Італійські трави УБ 10г /28шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
@@ -227,9 +221,6 @@
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -266,9 +257,6 @@
     <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт</t>
-  </si>
-  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -284,6 +272,9 @@
     <t>БАТОНИ</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
@@ -308,13 +299,19 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
@@ -335,6 +332,9 @@
     <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
   </si>
   <si>
+    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -383,6 +383,9 @@
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto з молочною начинкою ВКФ 140г /15шт</t>
+  </si>
+  <si>
     <t>Roshetto dark ВКФ 34г /200шт</t>
   </si>
   <si>
@@ -398,18 +401,33 @@
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
+    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
@@ -455,6 +473,9 @@
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -494,6 +515,9 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -503,9 +527,6 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -521,9 +542,6 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -536,9 +554,6 @@
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
@@ -566,6 +581,9 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -590,9 +608,6 @@
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -623,6 +638,9 @@
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -785,21 +803,12 @@
     <t>КОРОБКИ</t>
   </si>
   <si>
-    <t>Assortment Classic 154г/8</t>
-  </si>
-  <si>
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -815,18 +824,15 @@
     <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters віски-лікер ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Shooters з бренді-лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
@@ -839,7 +845,7 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
@@ -1007,7 +1013,7 @@
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
-    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+    <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
   </si>
   <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
@@ -1037,21 +1043,39 @@
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з подр. мигдалем та кокосовим кремом ВКФ 1кг /4пак</t>
   </si>
   <si>
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
@@ -1109,21 +1133,15 @@
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
@@ -1136,13 +1154,7 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
@@ -1169,10 +1181,7 @@
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
@@ -1214,25 +1223,13 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
@@ -1496,7 +1493,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C411"/>
+  <dimension ref="C410"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1561,7 +1558,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1569,7 +1566,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>443092</v>
+        <v>470059</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1577,7 +1574,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>98842</v>
+        <v>95571</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1585,7 +1582,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>20435</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1593,7 +1590,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>1931</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1601,7 +1598,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>3078</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1617,15 +1614,15 @@
         <v>17</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>2251</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>56</v>
+      <c r="C19" s="16" t="n">
+        <v>2056</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1633,7 +1630,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>3155</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1641,7 +1638,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1649,7 +1646,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>2809</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1657,7 +1654,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>8</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1665,7 +1662,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>1398</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1673,31 +1670,31 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>224</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="27" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B27" s="15" t="s">
+      <c r="C26" s="16" t="n">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="27" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B27" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="16" t="n">
-        <v>1828</v>
+      <c r="C27" s="12" t="n">
+        <v>31468</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
       <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>202</v>
+      <c r="C28" s="16" t="n">
+        <v>4939</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1705,15 +1702,15 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>2631</v>
-      </c>
-    </row>
-    <row r="30" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B30" s="14" t="s">
+        <v>10374</v>
+      </c>
+    </row>
+    <row r="30" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="12" t="n">
-        <v>30621</v>
+      <c r="C30" s="16" t="n">
+        <v>1117</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1721,7 +1718,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>3362</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1729,23 +1726,23 @@
         <v>31</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>11933</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="16" t="n">
-        <v>1767</v>
+      <c r="C33" s="11" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="16" t="n">
-        <v>6964</v>
+      <c r="C34" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1753,7 +1750,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>42</v>
+        <v>809</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -1761,31 +1758,31 @@
         <v>35</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>573</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="16" t="n">
-        <v>1339</v>
+      <c r="C37" s="11" t="n">
+        <v>149</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>182</v>
+      <c r="C38" s="16" t="n">
+        <v>1380</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="16" t="n">
-        <v>1473</v>
+      <c r="C39" s="11" t="n">
+        <v>412</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1793,7 +1790,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>476</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1801,39 +1798,39 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>252</v>
+        <v>824</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>930</v>
+      <c r="C42" s="16" t="n">
+        <v>1075</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="16" t="n">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="44" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B44" s="15" t="s">
+      <c r="C43" s="11" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B44" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B45" s="14" t="s">
+      <c r="C44" s="12" t="n">
+        <v>15559</v>
+      </c>
+    </row>
+    <row r="45" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="12" t="n">
-        <v>13478</v>
+      <c r="C45" s="11" t="n">
+        <v>822</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1841,7 +1838,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>405</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1849,15 +1846,15 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>174</v>
+        <v>819</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="16" t="n">
-        <v>1118</v>
+      <c r="C48" s="11" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1865,7 +1862,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>136</v>
+        <v>690</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1873,7 +1870,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>920</v>
+        <v>777</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1881,23 +1878,23 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>777</v>
+        <v>644</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
       <c r="B52" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>216</v>
+      <c r="C52" s="16" t="n">
+        <v>1085</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
       <c r="B53" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="16" t="n">
-        <v>1174</v>
+      <c r="C53" s="11" t="n">
+        <v>517</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1905,7 +1902,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>625</v>
+        <v>364</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1913,7 +1910,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>415</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1921,23 +1918,23 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>455</v>
+        <v>684</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="11" t="n">
-        <v>400</v>
+      <c r="C57" s="16" t="n">
+        <v>1071</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
       <c r="B58" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="16" t="n">
-        <v>1105</v>
+      <c r="C58" s="11" t="n">
+        <v>255</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1945,7 +1942,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>398</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1953,15 +1950,15 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>151</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="11" t="n">
-        <v>767</v>
+      <c r="C61" s="16" t="n">
+        <v>1179</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -1969,23 +1966,23 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="63" ht="11" customHeight="true" outlineLevel="3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="true" outlineLevel="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" ht="11" customHeight="true" outlineLevel="3">
       <c r="B64" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>24</v>
+        <v>564</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -1993,7 +1990,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>668</v>
+        <v>928</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2001,55 +1998,55 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>84</v>
+        <v>443</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="68" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B68" s="15" t="s">
+      <c r="C67" s="16" t="n">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B68" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>443</v>
+      <c r="C68" s="12" t="n">
+        <v>29370</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="n">
-        <v>1368</v>
+      <c r="C69" s="11" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="71" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B71" s="14" t="s">
+      <c r="C70" s="16" t="n">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="71" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="12" t="n">
-        <v>34308</v>
+      <c r="C71" s="16" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="11" t="n">
-        <v>536</v>
+      <c r="C72" s="16" t="n">
+        <v>2139</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2057,7 +2054,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="16" t="n">
-        <v>1334</v>
+        <v>7391</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2065,7 +2062,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>769</v>
+        <v>669</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2073,7 +2070,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="16" t="n">
-        <v>1052</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2081,15 +2078,15 @@
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>7001</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="16" t="n">
-        <v>1299</v>
+      <c r="C77" s="11" t="n">
+        <v>654</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2097,7 +2094,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>2184</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2105,135 +2102,135 @@
         <v>78</v>
       </c>
       <c r="C79" s="16" t="n">
-        <v>1051</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>972</v>
+      <c r="C80" s="16" t="n">
+        <v>4437</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>1596</v>
+      <c r="C81" s="11" t="n">
+        <v>633</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="16" t="n">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B83" s="15" t="s">
+      <c r="C82" s="11" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B83" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="16" t="n">
-        <v>8089</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B84" s="15" t="s">
+      <c r="C83" s="12" t="n">
+        <v>374488</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B84" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="16" t="n">
-        <v>5377</v>
-      </c>
-    </row>
-    <row r="85" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C84" s="12" t="n">
+        <v>39197</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="86" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C85" s="16" t="n">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="87" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B87" s="13" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="12" t="n">
-        <v>344250</v>
-      </c>
-    </row>
-    <row r="88" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B88" s="14" t="s">
+      <c r="C87" s="11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="88" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="12" t="n">
-        <v>54339</v>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C88" s="16" t="n">
+        <v>7771</v>
+      </c>
+    </row>
+    <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="true" outlineLevel="3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="true" outlineLevel="3">
       <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="16" t="n">
-        <v>17620</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C91" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="93" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C92" s="16" t="n">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>30</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="11" t="n">
-        <v>40</v>
+      <c r="C94" s="16" t="n">
+        <v>5340</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="16" t="n">
-        <v>6809</v>
+      <c r="C95" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="true" outlineLevel="3">
@@ -2241,79 +2238,79 @@
         <v>95</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>630</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>60</v>
+      <c r="C97" s="16" t="n">
+        <v>5529</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>6294</v>
+      <c r="C98" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>360</v>
+      <c r="C99" s="16" t="n">
+        <v>3149</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="16" t="n">
-        <v>1889</v>
+      <c r="C100" s="11" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
       <c r="B101" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="11" t="n">
-        <v>240</v>
+      <c r="C101" s="16" t="n">
+        <v>10948</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
       <c r="B102" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="16" t="n">
-        <v>18242</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B103" s="15" t="s">
+      <c r="C102" s="11" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B103" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="11" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B104" s="14" t="s">
+      <c r="C103" s="12" t="n">
+        <v>6187</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="12" t="n">
-        <v>6761</v>
+      <c r="C104" s="11" t="n">
+        <v>899</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="16" t="n">
-        <v>1224</v>
+      <c r="C105" s="11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="106" ht="11" customHeight="true" outlineLevel="3">
@@ -2321,23 +2318,23 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>678</v>
+        <v>440</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="11" t="n">
-        <v>918</v>
+      <c r="C107" s="16" t="n">
+        <v>1028</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>676</v>
+      <c r="C108" s="16" t="n">
+        <v>1385</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2345,7 +2342,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>531</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
@@ -2353,7 +2350,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="16" t="n">
-        <v>2084</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2361,7 +2358,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>238</v>
+        <v>162</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2377,7 +2374,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>234</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2393,7 +2390,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>166</v>
+        <v>300</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="true" outlineLevel="3">
@@ -2409,7 +2406,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="12" t="n">
-        <v>71059</v>
+        <v>92344</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2417,7 +2414,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>375</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2425,7 +2422,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>175</v>
+        <v>94</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2433,7 +2430,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>229</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2441,7 +2438,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>455</v>
+        <v>177</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2449,7 +2446,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="16" t="n">
-        <v>25880</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2457,7 +2454,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="16" t="n">
-        <v>16596</v>
+        <v>34230</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2465,7 +2462,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="16" t="n">
-        <v>3750</v>
+        <v>16996</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2473,15 +2470,15 @@
         <v>124</v>
       </c>
       <c r="C125" s="16" t="n">
-        <v>11610</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="11" t="n">
-        <v>83</v>
+      <c r="C126" s="16" t="n">
+        <v>16285</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2489,15 +2486,15 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="11" t="n">
-        <v>150</v>
+      <c r="C128" s="16" t="n">
+        <v>2030</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2505,7 +2502,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>691</v>
+        <v>74</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2513,23 +2510,23 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>425</v>
+        <v>826</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="16" t="n">
-        <v>1210</v>
+      <c r="C131" s="11" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
       <c r="B132" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="16" t="n">
-        <v>1158</v>
+      <c r="C132" s="11" t="n">
+        <v>963</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2537,7 +2534,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>3</v>
+        <v>684</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2545,7 +2542,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>910</v>
+        <v>599</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2553,15 +2550,15 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" ht="11" customHeight="true" outlineLevel="3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
       <c r="C136" s="16" t="n">
-        <v>1485</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2569,7 +2566,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>316</v>
+        <v>247</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2577,7 +2574,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>183</v>
+        <v>716</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2585,15 +2582,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>538</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="16" t="n">
-        <v>1450</v>
+      <c r="C140" s="11" t="n">
+        <v>762</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2601,23 +2598,23 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="11" t="n">
-        <v>1</v>
+      <c r="C142" s="16" t="n">
+        <v>1672</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
       <c r="B143" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="16" t="n">
-        <v>1261</v>
+      <c r="C143" s="11" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2625,31 +2622,31 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>14</v>
+        <v>153</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
       <c r="B145" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="16" t="n">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="146" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B146" s="14" t="s">
+      <c r="C145" s="11" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="146" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B146" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="12" t="n">
-        <v>103838</v>
+      <c r="C146" s="11" t="n">
+        <v>314</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="16" t="n">
-        <v>1152</v>
+      <c r="C147" s="11" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2657,15 +2654,15 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>291</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>85</v>
+      <c r="C149" s="16" t="n">
+        <v>1516</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2673,7 +2670,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>218</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2681,7 +2678,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>282</v>
+        <v>910</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2689,15 +2686,15 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="153" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B153" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="153" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B153" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="11" t="n">
-        <v>245</v>
+      <c r="C153" s="12" t="n">
+        <v>107782</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2705,7 +2702,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>329</v>
+        <v>703</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2721,15 +2718,15 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>491</v>
+        <v>383</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="16" t="n">
-        <v>2664</v>
+      <c r="C157" s="11" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2737,15 +2734,15 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>695</v>
+        <v>514</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="16" t="n">
-        <v>1392</v>
+      <c r="C159" s="11" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2753,15 +2750,15 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>479</v>
+        <v>299</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
       <c r="B161" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C161" s="16" t="n">
-        <v>1084</v>
+      <c r="C161" s="11" t="n">
+        <v>478</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2769,7 +2766,7 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>10</v>
+        <v>172</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2777,7 +2774,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>264</v>
+        <v>477</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2785,7 +2782,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="16" t="n">
-        <v>2172</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2793,15 +2790,15 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>247</v>
+        <v>685</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="16" t="n">
-        <v>1938</v>
+      <c r="C166" s="11" t="n">
+        <v>895</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2809,7 +2806,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>223</v>
+        <v>377</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2817,15 +2814,15 @@
         <v>167</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>847</v>
+        <v>474</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="11" t="n">
-        <v>284</v>
+      <c r="C169" s="16" t="n">
+        <v>1082</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2833,7 +2830,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>697</v>
+        <v>249</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2841,7 +2838,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="16" t="n">
-        <v>2870</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2849,7 +2846,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>597</v>
+        <v>245</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2857,7 +2854,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>5</v>
+        <v>960</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2865,7 +2862,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>298</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2873,15 +2870,15 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>405</v>
+        <v>475</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="16" t="n">
-        <v>2121</v>
+      <c r="C176" s="11" t="n">
+        <v>697</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2889,7 +2886,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="16" t="n">
-        <v>2736</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2897,7 +2894,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>131</v>
+        <v>601</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2905,47 +2902,47 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="180" ht="22" customHeight="true" outlineLevel="3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="16" t="n">
-        <v>13220</v>
-      </c>
-    </row>
-    <row r="181" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C180" s="11" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="11" t="n">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="182" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C181" s="16" t="n">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
       <c r="C182" s="16" t="n">
-        <v>3638</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="16" t="n">
-        <v>16206</v>
+      <c r="C183" s="11" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="16" t="n">
-        <v>1336</v>
+      <c r="C184" s="11" t="n">
+        <v>336</v>
       </c>
     </row>
     <row r="185" ht="22" customHeight="true" outlineLevel="3">
@@ -2953,7 +2950,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="16" t="n">
-        <v>1892</v>
+        <v>15191</v>
       </c>
     </row>
     <row r="186" ht="22" customHeight="true" outlineLevel="3">
@@ -2961,79 +2958,79 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" ht="11" customHeight="true" outlineLevel="3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>327</v>
+      <c r="C187" s="16" t="n">
+        <v>2609</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
       <c r="B188" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="16" t="n">
-        <v>11572</v>
-      </c>
-    </row>
-    <row r="189" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C188" s="11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>324</v>
+      <c r="C189" s="16" t="n">
+        <v>16420</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
       <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="11" t="n">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="191" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C190" s="16" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="191" ht="22" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="192" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C191" s="16" t="n">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="true" outlineLevel="3">
       <c r="B192" s="15" t="s">
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
     </row>
     <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="16" t="n">
-        <v>1321</v>
+      <c r="C193" s="11" t="n">
+        <v>292</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="11" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="195" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C194" s="16" t="n">
+        <v>10021</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="true" outlineLevel="3">
       <c r="B195" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="16" t="n">
-        <v>2195</v>
+      <c r="C195" s="11" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
@@ -3041,7 +3038,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>570</v>
+        <v>233</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3049,7 +3046,7 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>259</v>
+        <v>159</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3057,7 +3054,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="16" t="n">
-        <v>2396</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3065,7 +3062,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>362</v>
+        <v>650</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3073,7 +3070,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="16" t="n">
-        <v>3465</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3081,7 +3078,7 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>409</v>
+        <v>431</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3089,7 +3086,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>304</v>
+        <v>226</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3097,15 +3094,15 @@
         <v>202</v>
       </c>
       <c r="C203" s="16" t="n">
-        <v>2204</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="11" t="n">
-        <v>404</v>
+      <c r="C204" s="16" t="n">
+        <v>1006</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3113,7 +3110,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="16" t="n">
-        <v>2363</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3121,15 +3118,15 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>700</v>
+        <v>385</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="16" t="n">
-        <v>2017</v>
+      <c r="C207" s="11" t="n">
+        <v>896</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3137,7 +3134,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>518</v>
+        <v>301</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3145,7 +3142,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="16" t="n">
-        <v>3005</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3153,7 +3150,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>327</v>
+        <v>236</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3161,7 +3158,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="16" t="n">
-        <v>3393</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3169,15 +3166,15 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>146</v>
+        <v>637</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="11" t="n">
-        <v>279</v>
+      <c r="C213" s="16" t="n">
+        <v>1426</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3185,15 +3182,15 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>238</v>
+        <v>472</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="11" t="n">
-        <v>68</v>
+      <c r="C215" s="16" t="n">
+        <v>2755</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3201,15 +3198,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>140</v>
+        <v>18</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>480</v>
+      <c r="C217" s="16" t="n">
+        <v>3059</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3217,7 +3214,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>378</v>
+        <v>109</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3225,23 +3222,23 @@
         <v>218</v>
       </c>
       <c r="C219" s="11" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="220" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B220" s="14" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="220" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B220" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="12" t="n">
-        <v>29419</v>
+      <c r="C220" s="11" t="n">
+        <v>166</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
       <c r="B221" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="16" t="n">
-        <v>1353</v>
+      <c r="C221" s="11" t="n">
+        <v>296</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3249,15 +3246,15 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>354</v>
+        <v>231</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="16" t="n">
-        <v>1549</v>
+      <c r="C223" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3265,7 +3262,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>7</v>
+        <v>991</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3273,23 +3270,23 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="226" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B226" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="226" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B226" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="16" t="n">
-        <v>2213</v>
+      <c r="C226" s="12" t="n">
+        <v>38883</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="11" t="n">
-        <v>216</v>
+      <c r="C227" s="16" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3297,15 +3294,15 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>426</v>
+        <v>255</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>542</v>
+      <c r="C229" s="16" t="n">
+        <v>2597</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3313,7 +3310,7 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>568</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3321,23 +3318,23 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>202</v>
+        <v>662</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>915</v>
+      <c r="C232" s="16" t="n">
+        <v>3796</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="16" t="n">
-        <v>1124</v>
+      <c r="C233" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3345,7 +3342,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>855</v>
+        <v>413</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3353,7 +3350,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>461</v>
+        <v>492</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3361,7 +3358,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>465</v>
+        <v>431</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3369,7 +3366,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>199</v>
+        <v>124</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3377,7 +3374,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>672</v>
+        <v>979</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3385,15 +3382,15 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>982</v>
+        <v>579</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="11" t="n">
-        <v>329</v>
+      <c r="C240" s="16" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3401,23 +3398,23 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>798</v>
+        <v>908</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="16" t="n">
-        <v>1495</v>
+      <c r="C242" s="11" t="n">
+        <v>801</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="16" t="n">
-        <v>1302</v>
+      <c r="C243" s="11" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3425,7 +3422,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3433,23 +3430,23 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>787</v>
+        <v>766</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
       <c r="B246" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="16" t="n">
-        <v>1052</v>
+      <c r="C246" s="11" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="11" t="n">
-        <v>366</v>
+      <c r="C247" s="16" t="n">
+        <v>1098</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
@@ -3457,7 +3454,7 @@
         <v>247</v>
       </c>
       <c r="C248" s="16" t="n">
-        <v>1141</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3465,15 +3462,15 @@
         <v>248</v>
       </c>
       <c r="C249" s="16" t="n">
-        <v>1225</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="11" t="n">
-        <v>770</v>
+      <c r="C250" s="16" t="n">
+        <v>1706</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3481,23 +3478,23 @@
         <v>250</v>
       </c>
       <c r="C251" s="16" t="n">
-        <v>1524</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>853</v>
+      <c r="C252" s="16" t="n">
+        <v>1555</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="16" t="n">
-        <v>2577</v>
+      <c r="C253" s="11" t="n">
+        <v>653</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3505,15 +3502,15 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="255" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B255" s="14" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="12" t="n">
-        <v>3133</v>
+      <c r="C255" s="16" t="n">
+        <v>1434</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3521,31 +3518,31 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>31</v>
+        <v>918</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="11" t="n">
-        <v>43</v>
+      <c r="C257" s="16" t="n">
+        <v>2707</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="11" t="n">
-        <v>16</v>
+      <c r="C258" s="16" t="n">
+        <v>1444</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="11" t="n">
-        <v>354</v>
+      <c r="C259" s="16" t="n">
+        <v>2919</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
@@ -3553,15 +3550,15 @@
         <v>259</v>
       </c>
       <c r="C260" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="261" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B261" s="15" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="261" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B261" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="11" t="n">
-        <v>272</v>
+      <c r="C261" s="12" t="n">
+        <v>3414</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3569,7 +3566,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>335</v>
+        <v>24</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
@@ -3577,7 +3574,7 @@
         <v>262</v>
       </c>
       <c r="C263" s="11" t="n">
-        <v>14</v>
+        <v>158</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3585,7 +3582,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>187</v>
+        <v>421</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3593,7 +3590,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>103</v>
+        <v>280</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3601,7 +3598,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3609,7 +3606,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>461</v>
+        <v>216</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3617,7 +3614,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3625,7 +3622,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>1</v>
+        <v>331</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3633,7 +3630,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>83</v>
+        <v>177</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3641,7 +3638,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>570</v>
+        <v>258</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3649,7 +3646,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>217</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3657,7 +3654,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>164</v>
+        <v>792</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3665,7 +3662,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3673,7 +3670,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3681,15 +3678,15 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="277" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B277" s="14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="277" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="12" t="n">
-        <v>23908</v>
+      <c r="C277" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3697,15 +3694,15 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="279" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B279" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="279" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B279" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="11" t="n">
-        <v>438</v>
+      <c r="C279" s="12" t="n">
+        <v>38315</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3713,7 +3710,7 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>373</v>
+        <v>456</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
@@ -3721,7 +3718,7 @@
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>416</v>
+        <v>489</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3729,7 +3726,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>368</v>
+        <v>232</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3737,7 +3734,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>526</v>
+        <v>380</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3745,7 +3742,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>528</v>
+        <v>339</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3753,15 +3750,15 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="286" ht="22" customHeight="true" outlineLevel="3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="286" ht="11" customHeight="true" outlineLevel="3">
       <c r="B286" s="15" t="s">
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>115</v>
+        <v>474</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3769,15 +3766,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>299</v>
+        <v>86</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3785,7 +3782,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>274</v>
+        <v>141</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3793,7 +3790,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3801,23 +3798,23 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="292" ht="22" customHeight="true" outlineLevel="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="11" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="293" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C292" s="16" t="n">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>57</v>
+        <v>743</v>
       </c>
     </row>
     <row r="294" ht="22" customHeight="true" outlineLevel="3">
@@ -3825,7 +3822,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>697</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" ht="22" customHeight="true" outlineLevel="3">
@@ -3833,7 +3830,7 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="296" ht="22" customHeight="true" outlineLevel="3">
@@ -3841,7 +3838,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>198</v>
+        <v>505</v>
       </c>
     </row>
     <row r="297" ht="22" customHeight="true" outlineLevel="3">
@@ -3849,7 +3846,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="298" ht="22" customHeight="true" outlineLevel="3">
@@ -3857,7 +3854,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>119</v>
+        <v>368</v>
       </c>
     </row>
     <row r="299" ht="22" customHeight="true" outlineLevel="3">
@@ -3868,20 +3865,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="300" ht="11" customHeight="true" outlineLevel="3">
+    <row r="300" ht="22" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>288</v>
+        <v>71</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -3889,7 +3886,7 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
     </row>
     <row r="303" ht="11" customHeight="true" outlineLevel="3">
@@ -3897,31 +3894,31 @@
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="16" t="n">
-        <v>2206</v>
+      <c r="C304" s="11" t="n">
+        <v>447</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="16" t="n">
-        <v>1198</v>
+      <c r="C305" s="11" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="11" t="n">
-        <v>654</v>
+      <c r="C306" s="16" t="n">
+        <v>3428</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -3929,7 +3926,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="16" t="n">
-        <v>1063</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3937,7 +3934,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="16" t="n">
-        <v>2117</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3945,7 +3942,7 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>6</v>
+        <v>806</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -3953,15 +3950,15 @@
         <v>309</v>
       </c>
       <c r="C310" s="16" t="n">
-        <v>1753</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="16" t="n">
-        <v>3468</v>
+      <c r="C311" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
@@ -3969,7 +3966,7 @@
         <v>311</v>
       </c>
       <c r="C312" s="16" t="n">
-        <v>1067</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -3977,23 +3974,23 @@
         <v>312</v>
       </c>
       <c r="C313" s="16" t="n">
-        <v>1673</v>
+        <v>8536</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="315" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B315" s="14" t="s">
+      <c r="C314" s="16" t="n">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="12" t="n">
-        <v>28063</v>
+      <c r="C315" s="16" t="n">
+        <v>6639</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4001,15 +3998,15 @@
         <v>315</v>
       </c>
       <c r="C316" s="11" t="n">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B317" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B317" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="11" t="n">
-        <v>400</v>
+      <c r="C317" s="12" t="n">
+        <v>36057</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
@@ -4017,39 +4014,39 @@
         <v>317</v>
       </c>
       <c r="C318" s="11" t="n">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="319" ht="22" customHeight="true" outlineLevel="3">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="320" ht="22" customHeight="true" outlineLevel="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="320" ht="11" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="16" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="321" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C320" s="11" t="n">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="322" ht="11" customHeight="true" outlineLevel="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>286</v>
+        <v>900</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4057,7 +4054,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>139</v>
+        <v>456</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4065,7 +4062,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>561</v>
+        <v>182</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4073,15 +4070,15 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>500</v>
+        <v>353</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="11" t="n">
-        <v>341</v>
+      <c r="C326" s="16" t="n">
+        <v>1468</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
@@ -4089,7 +4086,7 @@
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>428</v>
+        <v>500</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4097,7 +4094,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>333</v>
+        <v>386</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4105,7 +4102,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>476</v>
+        <v>365</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4113,7 +4110,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>74</v>
+        <v>479</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4121,7 +4118,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>675</v>
+        <v>334</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4129,7 +4126,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>650</v>
+        <v>627</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4137,7 +4134,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>672</v>
+        <v>802</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4145,7 +4142,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>853</v>
+        <v>650</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4153,7 +4150,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>525</v>
+        <v>726</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4161,15 +4158,15 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>300</v>
+        <v>767</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="16" t="n">
-        <v>1114</v>
+      <c r="C337" s="11" t="n">
+        <v>463</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4177,23 +4174,23 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>919</v>
+        <v>300</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="11" t="n">
-        <v>242</v>
+      <c r="C339" s="16" t="n">
+        <v>1555</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="11" t="n">
-        <v>70</v>
+      <c r="C340" s="16" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4201,23 +4198,23 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="342" ht="22" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="343" ht="11" customHeight="true" outlineLevel="3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="343" ht="22" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>209</v>
+        <v>248</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4225,39 +4222,39 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>465</v>
+        <v>67</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="16" t="n">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C345" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="16" t="n">
-        <v>1500</v>
+      <c r="C346" s="11" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="16" t="n">
-        <v>7021</v>
-      </c>
-    </row>
-    <row r="348" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C347" s="11" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="348" ht="22" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="16" t="n">
-        <v>1237</v>
+      <c r="C348" s="11" t="n">
+        <v>486</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4265,71 +4262,71 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>163</v>
+        <v>498</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
       <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="16" t="n">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="352" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B352" s="14" t="s">
+      <c r="C351" s="11" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="352" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="17" t="n">
-        <v>290</v>
+      <c r="C352" s="11" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="C353" s="11" t="n">
-        <v>33</v>
+      <c r="C353" s="16" t="n">
+        <v>3118</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
       <c r="B354" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="11" t="n">
-        <v>30</v>
+      <c r="C354" s="16" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
       <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="11" t="n">
-        <v>100</v>
+      <c r="C355" s="16" t="n">
+        <v>8913</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="357" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B357" s="14" t="s">
+      <c r="C356" s="16" t="n">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="357" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="12" t="n">
-        <v>23440</v>
+      <c r="C357" s="11" t="n">
+        <v>928</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
@@ -4337,127 +4334,127 @@
         <v>357</v>
       </c>
       <c r="C358" s="11" t="n">
-        <v>68</v>
+        <v>163</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="360" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B360" s="15" t="s">
+      <c r="C359" s="16" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B360" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="11" t="n">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C360" s="17" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="362" ht="22" customHeight="true" outlineLevel="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="363" ht="22" customHeight="true" outlineLevel="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="363" ht="11" customHeight="true" outlineLevel="3">
       <c r="B363" s="15" t="s">
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="364" ht="22" customHeight="true" outlineLevel="3">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
       <c r="B364" s="15" t="s">
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B365" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B365" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="C365" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C365" s="12" t="n">
+        <v>11615</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="367" ht="22" customHeight="true" outlineLevel="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="368" ht="22" customHeight="true" outlineLevel="3">
       <c r="B368" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="C368" s="16" t="n">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C368" s="11" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="369" ht="22" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="371" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="371" ht="22" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="372" ht="22" customHeight="true" outlineLevel="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="373" ht="22" customHeight="true" outlineLevel="3">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="16" t="n">
-        <v>1158</v>
+      <c r="C373" s="11" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="374" ht="22" customHeight="true" outlineLevel="3">
@@ -4465,31 +4462,31 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="375" ht="22" customHeight="true" outlineLevel="3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="376" ht="22" customHeight="true" outlineLevel="3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="16" t="n">
-        <v>2888</v>
-      </c>
-    </row>
-    <row r="377" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C376" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>321</v>
+        <v>652</v>
       </c>
     </row>
     <row r="378" ht="22" customHeight="true" outlineLevel="3">
@@ -4497,7 +4494,7 @@
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="379" ht="22" customHeight="true" outlineLevel="3">
@@ -4505,7 +4502,7 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>250</v>
+        <v>24</v>
       </c>
     </row>
     <row r="380" ht="22" customHeight="true" outlineLevel="3">
@@ -4513,7 +4510,7 @@
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="381" ht="22" customHeight="true" outlineLevel="3">
@@ -4521,7 +4518,7 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>142</v>
+        <v>85</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="true" outlineLevel="3">
@@ -4529,7 +4526,7 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>281</v>
+        <v>115</v>
       </c>
     </row>
     <row r="383" ht="22" customHeight="true" outlineLevel="3">
@@ -4537,7 +4534,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>510</v>
+        <v>109</v>
       </c>
     </row>
     <row r="384" ht="22" customHeight="true" outlineLevel="3">
@@ -4545,7 +4542,7 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>66</v>
+        <v>285</v>
       </c>
     </row>
     <row r="385" ht="22" customHeight="true" outlineLevel="3">
@@ -4553,23 +4550,23 @@
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="387" ht="22" customHeight="true" outlineLevel="3">
       <c r="B387" s="15" t="s">
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>415</v>
+        <v>901</v>
       </c>
     </row>
     <row r="388" ht="22" customHeight="true" outlineLevel="3">
@@ -4577,23 +4574,23 @@
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="390" ht="22" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>354</v>
+        <v>305</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4601,7 +4598,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -4609,15 +4606,15 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="393" ht="11" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
       <c r="B393" s="15" t="s">
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>285</v>
+        <v>357</v>
       </c>
     </row>
     <row r="394" ht="22" customHeight="true" outlineLevel="3">
@@ -4625,15 +4622,15 @@
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>419</v>
+        <v>18</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
@@ -4641,15 +4638,15 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="397" ht="22" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>388</v>
+        <v>116</v>
       </c>
     </row>
     <row r="398" ht="11" customHeight="true" outlineLevel="3">
@@ -4657,7 +4654,7 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="399" ht="11" customHeight="true" outlineLevel="3">
@@ -4665,15 +4662,15 @@
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="16" t="n">
-        <v>1309</v>
+      <c r="C400" s="11" t="n">
+        <v>293</v>
       </c>
     </row>
     <row r="401" ht="11" customHeight="true" outlineLevel="3">
@@ -4681,23 +4678,23 @@
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="16" t="n">
-        <v>1125</v>
+      <c r="C403" s="11" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="404" ht="11" customHeight="true" outlineLevel="3">
@@ -4705,15 +4702,15 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="405" ht="22" customHeight="true" outlineLevel="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="405" ht="11" customHeight="true" outlineLevel="3">
       <c r="B405" s="15" t="s">
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>40</v>
+        <v>311</v>
       </c>
     </row>
     <row r="406" ht="11" customHeight="true" outlineLevel="3">
@@ -4721,15 +4718,15 @@
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>707</v>
+        <v>355</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="C407" s="16" t="n">
-        <v>1020</v>
+      <c r="C407" s="11" t="n">
+        <v>357</v>
       </c>
     </row>
     <row r="408" ht="11" customHeight="true" outlineLevel="3">
@@ -4737,7 +4734,7 @@
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>365</v>
+        <v>252</v>
       </c>
     </row>
     <row r="409" ht="11" customHeight="true" outlineLevel="3">
@@ -4745,7 +4742,7 @@
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>271</v>
+        <v>636</v>
       </c>
     </row>
     <row r="410" ht="11" customHeight="true" outlineLevel="3">
@@ -4753,15 +4750,7 @@
         <v>409</v>
       </c>
       <c r="C410" s="16" t="n">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B411" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="C411" s="16" t="n">
-        <v>1932</v>
+        <v>1687</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 11.02.2026 19:55:13</t>
+    <t>Период: на 16.02.2026 7:55:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -119,12 +119,6 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт</t>
-  </si>
-  <si>
-    <t>Лимонна кислота УБ 100г /48шт /</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
@@ -257,6 +251,9 @@
     <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Перець чорний мелений УБ 20г /38шт</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -281,6 +278,9 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 41г /180шт</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
@@ -311,15 +311,15 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
@@ -377,9 +377,6 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
-  </si>
-  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -527,6 +524,9 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -542,6 +542,9 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -608,6 +611,9 @@
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -677,9 +683,6 @@
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
-    <t>Джеллі РЦ 200г /13шт</t>
-  </si>
-  <si>
     <t>Льодяник мікс РЦ 200г /24шт /</t>
   </si>
   <si>
@@ -716,6 +719,9 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
+    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
+  </si>
+  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -926,9 +932,6 @@
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
@@ -1079,6 +1082,9 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -1091,9 +1097,6 @@
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1127,12 +1130,12 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
@@ -1142,6 +1145,12 @@
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
@@ -1151,6 +1160,9 @@
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
@@ -1178,12 +1190,18 @@
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1208,7 +1226,7 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
@@ -1223,19 +1241,13 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
-  </si>
-  <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
@@ -1493,7 +1505,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C410"/>
+  <dimension ref="C414"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1558,7 +1570,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>655</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1566,7 +1578,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>470059</v>
+        <v>376054</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1574,7 +1586,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>95571</v>
+        <v>65370</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1582,7 +1594,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>19174</v>
+        <v>9752</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1590,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>1530</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1598,7 +1610,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>1893</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1614,7 +1626,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>2603</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
@@ -1622,7 +1634,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>2056</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1630,7 +1642,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>2772</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1645,8 +1657,8 @@
       <c r="B22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="16" t="n">
-        <v>2025</v>
+      <c r="C22" s="11" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1661,8 +1673,8 @@
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="16" t="n">
-        <v>1996</v>
+      <c r="C24" s="11" t="n">
+        <v>286</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1670,7 +1682,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>276</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1678,7 +1690,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>3207</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="2">
@@ -1686,7 +1698,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>31468</v>
+        <v>18134</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1694,7 +1706,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>4939</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1702,7 +1714,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>10374</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1710,7 +1722,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>1117</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1726,7 +1738,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>8010</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1742,7 +1754,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1750,15 +1762,15 @@
         <v>34</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>809</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>213</v>
+      <c r="C36" s="16" t="n">
+        <v>1380</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1766,15 +1778,15 @@
         <v>36</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>149</v>
+        <v>412</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="16" t="n">
-        <v>1380</v>
+      <c r="C38" s="11" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1782,15 +1794,15 @@
         <v>38</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>412</v>
+        <v>819</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>232</v>
+      <c r="C40" s="16" t="n">
+        <v>1075</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1798,15 +1810,15 @@
         <v>40</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="42" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B42" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B42" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="16" t="n">
-        <v>1075</v>
+      <c r="C42" s="12" t="n">
+        <v>14356</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1814,15 +1826,15 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B44" s="14" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="44" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="12" t="n">
-        <v>15559</v>
+      <c r="C44" s="11" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1830,7 +1842,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>822</v>
+        <v>658</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1838,7 +1850,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1846,7 +1858,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>819</v>
+        <v>575</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1854,7 +1866,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>67</v>
+        <v>777</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true" outlineLevel="3">
@@ -1862,15 +1874,15 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>690</v>
+        <v>615</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
       <c r="B50" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>777</v>
+      <c r="C50" s="16" t="n">
+        <v>1062</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1878,15 +1890,15 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>644</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
       <c r="B52" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="16" t="n">
-        <v>1085</v>
+      <c r="C52" s="11" t="n">
+        <v>341</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1894,7 +1906,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>517</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1902,15 +1914,15 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>364</v>
+        <v>646</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>345</v>
+      <c r="C55" s="16" t="n">
+        <v>1071</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1918,15 +1930,15 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>684</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="16" t="n">
-        <v>1071</v>
+      <c r="C57" s="11" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -1934,15 +1946,15 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>255</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>46</v>
+      <c r="C59" s="16" t="n">
+        <v>1171</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1950,15 +1962,15 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="61" ht="11" customHeight="true" outlineLevel="3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C61" s="16" t="n">
-        <v>1179</v>
+      <c r="C61" s="11" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -1966,15 +1978,15 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="true" outlineLevel="3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="63" ht="11" customHeight="true" outlineLevel="3">
       <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>66</v>
+        <v>851</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -1982,47 +1994,47 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>564</v>
+        <v>443</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="11" t="n">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="66" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B66" s="15" t="s">
+      <c r="C65" s="16" t="n">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B66" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>443</v>
+      <c r="C66" s="12" t="n">
+        <v>23128</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="16" t="n">
-        <v>2978</v>
-      </c>
-    </row>
-    <row r="68" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B68" s="14" t="s">
+      <c r="C67" s="11" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="12" t="n">
-        <v>29370</v>
+      <c r="C68" s="16" t="n">
+        <v>2383</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>116</v>
+      <c r="C69" s="16" t="n">
+        <v>1965</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2030,7 +2042,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="16" t="n">
-        <v>2479</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2038,15 +2050,15 @@
         <v>70</v>
       </c>
       <c r="C71" s="16" t="n">
-        <v>2025</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
       <c r="B72" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="16" t="n">
-        <v>2139</v>
+      <c r="C72" s="11" t="n">
+        <v>427</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2054,7 +2066,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="16" t="n">
-        <v>7391</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2062,31 +2074,31 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>669</v>
+        <v>767</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
       <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="16" t="n">
-        <v>3911</v>
+      <c r="C75" s="11" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="16" t="n">
-        <v>1805</v>
+      <c r="C76" s="11" t="n">
+        <v>290</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="11" t="n">
-        <v>654</v>
+      <c r="C77" s="16" t="n">
+        <v>1516</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2094,23 +2106,23 @@
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>1091</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="16" t="n">
-        <v>1516</v>
+      <c r="C79" s="11" t="n">
+        <v>937</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="16" t="n">
-        <v>4437</v>
+      <c r="C80" s="11" t="n">
+        <v>532</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2118,39 +2130,39 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B82" s="15" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B82" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B83" s="13" t="s">
+      <c r="C82" s="12" t="n">
+        <v>310684</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B83" s="14" t="s">
         <v>82</v>
       </c>
       <c r="C83" s="12" t="n">
-        <v>374488</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B84" s="14" t="s">
+        <v>30008</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="12" t="n">
-        <v>39197</v>
+      <c r="C84" s="16" t="n">
+        <v>1965</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>2115</v>
+      <c r="C85" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="true" outlineLevel="3">
@@ -2158,15 +2170,15 @@
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>270</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2174,7 +2186,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="16" t="n">
-        <v>7771</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2182,7 +2194,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2206,7 +2218,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="16" t="n">
-        <v>1974</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true" outlineLevel="3">
@@ -2214,7 +2226,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="true" outlineLevel="3">
@@ -2222,7 +2234,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="16" t="n">
-        <v>5340</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="true" outlineLevel="3">
@@ -2246,7 +2258,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="16" t="n">
-        <v>5529</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="true" outlineLevel="3">
@@ -2254,23 +2266,23 @@
         <v>97</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="16" t="n">
-        <v>3149</v>
+      <c r="C99" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>240</v>
+      <c r="C100" s="16" t="n">
+        <v>2369</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
@@ -2278,7 +2290,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="16" t="n">
-        <v>10948</v>
+        <v>8818</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
@@ -2286,7 +2298,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>270</v>
+        <v>390</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="2">
@@ -2294,7 +2306,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="12" t="n">
-        <v>6187</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2302,7 +2314,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>899</v>
+        <v>398</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
@@ -2318,23 +2330,23 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>440</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="16" t="n">
-        <v>1028</v>
+      <c r="C107" s="11" t="n">
+        <v>585</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="16" t="n">
-        <v>1385</v>
+      <c r="C108" s="11" t="n">
+        <v>475</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2342,15 +2354,15 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>258</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="16" t="n">
-        <v>1263</v>
+      <c r="C110" s="11" t="n">
+        <v>311</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2358,7 +2370,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2374,7 +2386,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>350</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2390,7 +2402,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>300</v>
+        <v>97</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="true" outlineLevel="3">
@@ -2406,7 +2418,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="12" t="n">
-        <v>92344</v>
+        <v>79480</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2414,7 +2426,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2422,7 +2434,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2430,7 +2442,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>378</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2438,7 +2450,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>177</v>
+        <v>690</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2446,7 +2458,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="16" t="n">
-        <v>1304</v>
+        <v>31155</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2454,7 +2466,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="16" t="n">
-        <v>34230</v>
+        <v>15821</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2462,7 +2474,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="16" t="n">
-        <v>16996</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2470,31 +2482,31 @@
         <v>124</v>
       </c>
       <c r="C125" s="16" t="n">
-        <v>7500</v>
+        <v>14335</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="16" t="n">
-        <v>16285</v>
+      <c r="C126" s="11" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>78</v>
+      <c r="C127" s="16" t="n">
+        <v>1744</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
       <c r="B128" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="16" t="n">
-        <v>2030</v>
+      <c r="C128" s="11" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2502,7 +2514,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>74</v>
+        <v>540</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2510,7 +2522,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>826</v>
+        <v>117</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2518,7 +2530,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>117</v>
+        <v>687</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2526,7 +2538,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>963</v>
+        <v>680</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2534,7 +2546,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>684</v>
+        <v>331</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2542,23 +2554,23 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="135" ht="11" customHeight="true" outlineLevel="3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="11" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="136" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C135" s="16" t="n">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="16" t="n">
-        <v>2439</v>
+      <c r="C136" s="11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
@@ -2566,7 +2578,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>247</v>
+        <v>428</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2574,7 +2586,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>716</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2582,7 +2594,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>3</v>
+        <v>495</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2590,7 +2602,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>762</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2598,15 +2610,15 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>1</v>
+        <v>721</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="16" t="n">
-        <v>1672</v>
+      <c r="C142" s="11" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2614,7 +2626,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>218</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2622,7 +2634,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2630,7 +2642,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2638,7 +2650,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>314</v>
+        <v>59</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2646,7 +2658,7 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2654,15 +2666,15 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>1</v>
+        <v>528</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="16" t="n">
-        <v>1516</v>
+      <c r="C149" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2670,7 +2682,7 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>3</v>
+        <v>756</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -2678,23 +2690,23 @@
         <v>150</v>
       </c>
       <c r="C151" s="11" t="n">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B152" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B152" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="153" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B153" s="14" t="s">
+      <c r="C152" s="12" t="n">
+        <v>95811</v>
+      </c>
+    </row>
+    <row r="153" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B153" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="12" t="n">
-        <v>107782</v>
+      <c r="C153" s="11" t="n">
+        <v>703</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2702,7 +2714,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>703</v>
+        <v>133</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2710,7 +2722,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>157</v>
+        <v>374</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2718,7 +2730,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>383</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2726,7 +2738,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>285</v>
+        <v>207</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2734,7 +2746,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>514</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2742,7 +2754,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2750,7 +2762,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>299</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2758,7 +2770,7 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>478</v>
+        <v>122</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -2766,23 +2778,23 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>172</v>
+        <v>449</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="11" t="n">
-        <v>477</v>
+      <c r="C163" s="16" t="n">
+        <v>3689</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="16" t="n">
-        <v>3742</v>
+      <c r="C164" s="11" t="n">
+        <v>243</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2790,7 +2802,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>685</v>
+        <v>893</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2798,7 +2810,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>895</v>
+        <v>285</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2806,23 +2818,23 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>377</v>
+        <v>472</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="11" t="n">
-        <v>474</v>
+      <c r="C168" s="16" t="n">
+        <v>1036</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
       <c r="B169" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="16" t="n">
-        <v>1082</v>
+      <c r="C169" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2830,7 +2842,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>249</v>
+        <v>111</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2838,7 +2850,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="16" t="n">
-        <v>5117</v>
+        <v>4943</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2846,7 +2858,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>245</v>
+        <v>199</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2854,7 +2866,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>960</v>
+        <v>822</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2862,7 +2874,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2870,7 +2882,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2878,23 +2890,23 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>697</v>
+        <v>213</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="16" t="n">
-        <v>2783</v>
+      <c r="C177" s="11" t="n">
+        <v>653</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="11" t="n">
-        <v>601</v>
+      <c r="C178" s="16" t="n">
+        <v>2724</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2902,7 +2914,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>298</v>
+        <v>224</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2910,15 +2922,15 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>384</v>
+        <v>298</v>
       </c>
     </row>
     <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="16" t="n">
-        <v>2048</v>
+      <c r="C181" s="11" t="n">
+        <v>370</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -2926,15 +2938,15 @@
         <v>181</v>
       </c>
       <c r="C182" s="16" t="n">
-        <v>2723</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>123</v>
+      <c r="C183" s="16" t="n">
+        <v>2723</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2942,47 +2954,47 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="185" ht="22" customHeight="true" outlineLevel="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="16" t="n">
-        <v>15191</v>
+      <c r="C185" s="11" t="n">
+        <v>325</v>
       </c>
     </row>
     <row r="186" ht="22" customHeight="true" outlineLevel="3">
       <c r="B186" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="11" t="n">
-        <v>446</v>
+      <c r="C186" s="16" t="n">
+        <v>14008</v>
       </c>
     </row>
     <row r="187" ht="22" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="16" t="n">
-        <v>2609</v>
-      </c>
-    </row>
-    <row r="188" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C187" s="11" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="true" outlineLevel="3">
       <c r="B188" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="11" t="n">
-        <v>34</v>
+      <c r="C188" s="16" t="n">
+        <v>1940</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="16" t="n">
-        <v>16420</v>
+      <c r="C189" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -2990,15 +3002,15 @@
         <v>189</v>
       </c>
       <c r="C190" s="16" t="n">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="191" ht="22" customHeight="true" outlineLevel="3">
+        <v>15237</v>
+      </c>
+    </row>
+    <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
       <c r="C191" s="16" t="n">
-        <v>1401</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="192" ht="22" customHeight="true" outlineLevel="3">
@@ -3006,39 +3018,39 @@
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="193" ht="11" customHeight="true" outlineLevel="3">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>292</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="16" t="n">
-        <v>10021</v>
-      </c>
-    </row>
-    <row r="195" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C194" s="11" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="11" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="196" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C195" s="16" t="n">
+        <v>8838</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>233</v>
+        <v>198</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3046,15 +3058,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="16" t="n">
-        <v>2398</v>
+      <c r="C198" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3062,7 +3074,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>650</v>
+        <v>154</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3070,7 +3082,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="16" t="n">
-        <v>3862</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3078,31 +3090,31 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>431</v>
+        <v>366</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>226</v>
+      <c r="C202" s="16" t="n">
+        <v>3710</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
       <c r="B203" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="C203" s="16" t="n">
-        <v>2374</v>
+      <c r="C203" s="11" t="n">
+        <v>321</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="16" t="n">
-        <v>1006</v>
+      <c r="C204" s="11" t="n">
+        <v>212</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3110,7 +3122,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="16" t="n">
-        <v>3443</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3118,15 +3130,15 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>385</v>
+        <v>474</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
       <c r="B207" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="11" t="n">
-        <v>896</v>
+      <c r="C207" s="16" t="n">
+        <v>3443</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3134,15 +3146,15 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>301</v>
+        <v>226</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
       <c r="B209" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="16" t="n">
-        <v>1873</v>
+      <c r="C209" s="11" t="n">
+        <v>895</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3150,7 +3162,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>236</v>
+        <v>205</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3158,7 +3170,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="16" t="n">
-        <v>2363</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3166,7 +3178,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>637</v>
+        <v>236</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3174,7 +3186,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="16" t="n">
-        <v>1426</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3182,7 +3194,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>472</v>
+        <v>385</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3190,7 +3202,7 @@
         <v>214</v>
       </c>
       <c r="C215" s="16" t="n">
-        <v>2755</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3198,7 +3210,7 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>18</v>
+        <v>406</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3206,7 +3218,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="16" t="n">
-        <v>3059</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3214,15 +3226,15 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>535</v>
+      <c r="C219" s="16" t="n">
+        <v>2943</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3230,7 +3242,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>166</v>
+        <v>109</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3238,7 +3250,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>296</v>
+        <v>215</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3246,7 +3258,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>231</v>
+        <v>291</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3254,7 +3266,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3262,7 +3274,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>991</v>
+        <v>211</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3270,23 +3282,23 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="226" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B226" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C226" s="11" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="226" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B226" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="C226" s="12" t="n">
-        <v>38883</v>
-      </c>
-    </row>
-    <row r="227" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B227" s="15" t="s">
+    <row r="227" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B227" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="16" t="n">
-        <v>1093</v>
+      <c r="C227" s="12" t="n">
+        <v>32694</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3294,23 +3306,23 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>255</v>
+        <v>968</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="16" t="n">
-        <v>2597</v>
+      <c r="C229" s="11" t="n">
+        <v>236</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="11" t="n">
-        <v>7</v>
+      <c r="C230" s="16" t="n">
+        <v>2336</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3318,23 +3330,23 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>662</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="16" t="n">
-        <v>3796</v>
+      <c r="C232" s="11" t="n">
+        <v>567</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="11" t="n">
-        <v>216</v>
+      <c r="C233" s="16" t="n">
+        <v>2854</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3342,7 +3354,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>413</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3350,7 +3362,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>492</v>
+        <v>216</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3358,7 +3370,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>431</v>
+        <v>405</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3366,7 +3378,7 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>124</v>
+        <v>444</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3374,7 +3386,7 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>979</v>
+        <v>397</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
@@ -3382,15 +3394,15 @@
         <v>238</v>
       </c>
       <c r="C239" s="11" t="n">
-        <v>579</v>
+        <v>103</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="16" t="n">
-        <v>1093</v>
+      <c r="C240" s="11" t="n">
+        <v>885</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3398,7 +3410,7 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>908</v>
+        <v>375</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3406,7 +3418,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="11" t="n">
-        <v>801</v>
+        <v>966</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3414,7 +3426,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>218</v>
+        <v>874</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3422,7 +3434,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>953</v>
+        <v>714</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3430,7 +3442,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>766</v>
+        <v>200</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3438,31 +3450,31 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>600</v>
+        <v>842</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
       <c r="B247" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="16" t="n">
-        <v>1098</v>
+      <c r="C247" s="11" t="n">
+        <v>688</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="16" t="n">
-        <v>2058</v>
+      <c r="C248" s="11" t="n">
+        <v>501</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="16" t="n">
-        <v>2538</v>
+      <c r="C249" s="11" t="n">
+        <v>996</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3470,7 +3482,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="16" t="n">
-        <v>1706</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3478,7 +3490,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="16" t="n">
-        <v>1397</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3486,31 +3498,31 @@
         <v>251</v>
       </c>
       <c r="C252" s="16" t="n">
-        <v>1555</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="11" t="n">
-        <v>653</v>
+      <c r="C253" s="16" t="n">
+        <v>1097</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
       <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C254" s="11" t="n">
-        <v>704</v>
+      <c r="C254" s="16" t="n">
+        <v>1276</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="16" t="n">
-        <v>1434</v>
+      <c r="C255" s="11" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3518,7 +3530,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>918</v>
+        <v>550</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3526,15 +3538,15 @@
         <v>256</v>
       </c>
       <c r="C257" s="16" t="n">
-        <v>2707</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="16" t="n">
-        <v>1444</v>
+      <c r="C258" s="11" t="n">
+        <v>786</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3542,23 +3554,23 @@
         <v>258</v>
       </c>
       <c r="C259" s="16" t="n">
-        <v>2919</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="11" t="n">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="261" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B261" s="14" t="s">
+      <c r="C260" s="16" t="n">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="261" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="12" t="n">
-        <v>3414</v>
+      <c r="C261" s="16" t="n">
+        <v>2232</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3566,15 +3578,15 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="263" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B263" s="15" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="263" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B263" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="11" t="n">
-        <v>158</v>
+      <c r="C263" s="12" t="n">
+        <v>2800</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3582,7 +3594,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>421</v>
+        <v>22</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3590,7 +3602,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>280</v>
+        <v>63</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3598,7 +3610,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>14</v>
+        <v>388</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3606,7 +3618,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>216</v>
+        <v>182</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3614,7 +3626,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3622,7 +3634,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>331</v>
+        <v>186</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3630,7 +3642,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>177</v>
+        <v>70</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3638,7 +3650,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>258</v>
+        <v>161</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3646,7 +3658,7 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>271</v>
+        <v>111</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
@@ -3654,7 +3666,7 @@
         <v>272</v>
       </c>
       <c r="C273" s="11" t="n">
-        <v>792</v>
+        <v>253</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3662,7 +3674,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>27</v>
+        <v>217</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3670,7 +3682,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>88</v>
+        <v>784</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3678,7 +3690,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>140</v>
+        <v>22</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3686,7 +3698,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3694,15 +3706,15 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="279" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B279" s="14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="279" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="12" t="n">
-        <v>38315</v>
+      <c r="C279" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3710,15 +3722,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="281" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B281" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B281" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>489</v>
+      <c r="C281" s="12" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3726,7 +3738,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>232</v>
+        <v>451</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3734,7 +3746,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3742,7 +3754,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>339</v>
+        <v>227</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3750,7 +3762,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>354</v>
+        <v>376</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3758,7 +3770,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>474</v>
+        <v>83</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3766,15 +3778,15 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="true" outlineLevel="3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>86</v>
+        <v>452</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3782,15 +3794,15 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="290" ht="11" customHeight="true" outlineLevel="3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>270</v>
+        <v>83</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -3798,15 +3810,15 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>200</v>
+        <v>137</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="16" t="n">
-        <v>1584</v>
+      <c r="C292" s="11" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3814,23 +3826,23 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="294" ht="22" customHeight="true" outlineLevel="3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="11" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="295" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C294" s="16" t="n">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true" outlineLevel="3">
       <c r="B295" s="15" t="s">
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>27</v>
+        <v>303</v>
       </c>
     </row>
     <row r="296" ht="22" customHeight="true" outlineLevel="3">
@@ -3838,7 +3850,7 @@
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>505</v>
+        <v>282</v>
       </c>
     </row>
     <row r="297" ht="22" customHeight="true" outlineLevel="3">
@@ -3846,7 +3858,7 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" ht="22" customHeight="true" outlineLevel="3">
@@ -3854,7 +3866,7 @@
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>368</v>
+        <v>396</v>
       </c>
     </row>
     <row r="299" ht="22" customHeight="true" outlineLevel="3">
@@ -3862,7 +3874,7 @@
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="300" ht="22" customHeight="true" outlineLevel="3">
@@ -3870,7 +3882,7 @@
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>250</v>
+        <v>326</v>
       </c>
     </row>
     <row r="301" ht="22" customHeight="true" outlineLevel="3">
@@ -3878,23 +3890,23 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="302" ht="11" customHeight="true" outlineLevel="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="302" ht="22" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="303" ht="11" customHeight="true" outlineLevel="3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -3902,7 +3914,7 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>447</v>
+        <v>286</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
@@ -3910,15 +3922,15 @@
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>160</v>
+        <v>302</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="16" t="n">
-        <v>3428</v>
+      <c r="C306" s="11" t="n">
+        <v>145</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -3926,7 +3938,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="16" t="n">
-        <v>2359</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3934,47 +3946,47 @@
         <v>307</v>
       </c>
       <c r="C308" s="16" t="n">
-        <v>1553</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="11" t="n">
-        <v>806</v>
+      <c r="C309" s="16" t="n">
+        <v>1037</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="16" t="n">
-        <v>3127</v>
+      <c r="C310" s="11" t="n">
+        <v>667</v>
       </c>
     </row>
     <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="11" t="n">
-        <v>6</v>
+      <c r="C311" s="16" t="n">
+        <v>2234</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="16" t="n">
-        <v>2019</v>
+      <c r="C312" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
       <c r="B313" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="16" t="n">
-        <v>8536</v>
+      <c r="C313" s="11" t="n">
+        <v>552</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
@@ -3982,7 +3994,7 @@
         <v>313</v>
       </c>
       <c r="C314" s="16" t="n">
-        <v>1014</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
@@ -3990,31 +4002,31 @@
         <v>314</v>
       </c>
       <c r="C315" s="16" t="n">
-        <v>6639</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
       <c r="B316" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="11" t="n">
+      <c r="C316" s="16" t="n">
+        <v>5406</v>
+      </c>
+    </row>
+    <row r="317" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B317" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="C317" s="11" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B317" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="C317" s="12" t="n">
-        <v>36057</v>
-      </c>
-    </row>
-    <row r="318" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B318" s="15" t="s">
+    <row r="318" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B318" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="11" t="n">
-        <v>509</v>
+      <c r="C318" s="12" t="n">
+        <v>31514</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4022,7 +4034,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -4030,15 +4042,15 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="true" outlineLevel="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>450</v>
+        <v>360</v>
       </c>
     </row>
     <row r="322" ht="22" customHeight="true" outlineLevel="3">
@@ -4046,15 +4058,15 @@
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="323" ht="22" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>456</v>
+        <v>900</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4062,7 +4074,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4070,23 +4082,23 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>353</v>
+        <v>159</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="16" t="n">
-        <v>1468</v>
+      <c r="C326" s="11" t="n">
+        <v>262</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="11" t="n">
-        <v>500</v>
+      <c r="C327" s="16" t="n">
+        <v>1228</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4094,7 +4106,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>386</v>
+        <v>500</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4102,7 +4114,7 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>365</v>
+        <v>334</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
@@ -4110,7 +4122,7 @@
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>479</v>
+        <v>346</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4118,7 +4130,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>334</v>
+        <v>442</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4126,7 +4138,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>627</v>
+        <v>241</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4134,7 +4146,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>802</v>
+        <v>600</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4142,7 +4154,7 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>650</v>
+        <v>568</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4150,7 +4162,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>726</v>
+        <v>650</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4158,7 +4170,7 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>767</v>
+        <v>608</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
@@ -4166,7 +4178,7 @@
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>463</v>
+        <v>738</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4174,15 +4186,15 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="16" t="n">
-        <v>1555</v>
+      <c r="C339" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4190,7 +4202,7 @@
         <v>339</v>
       </c>
       <c r="C340" s="16" t="n">
-        <v>1093</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4198,15 +4210,15 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="342" ht="22" customHeight="true" outlineLevel="3">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
       <c r="B342" s="15" t="s">
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>275</v>
+        <v>160</v>
       </c>
     </row>
     <row r="343" ht="22" customHeight="true" outlineLevel="3">
@@ -4214,15 +4226,15 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="344" ht="11" customHeight="true" outlineLevel="3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>67</v>
+        <v>199</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4230,71 +4242,71 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="346" ht="22" customHeight="true" outlineLevel="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="347" ht="11" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="347" ht="22" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="348" ht="22" customHeight="true" outlineLevel="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="true" outlineLevel="3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
       <c r="C350" s="11" t="n">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="351" ht="11" customHeight="true" outlineLevel="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="true" outlineLevel="3">
       <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="352" ht="22" customHeight="true" outlineLevel="3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="352" ht="11" customHeight="true" outlineLevel="3">
       <c r="B352" s="15" t="s">
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="C353" s="16" t="n">
-        <v>3118</v>
+      <c r="C353" s="11" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4302,63 +4314,63 @@
         <v>353</v>
       </c>
       <c r="C354" s="16" t="n">
-        <v>1500</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
       <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="16" t="n">
-        <v>8913</v>
+      <c r="C355" s="11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="16" t="n">
-        <v>3156</v>
+      <c r="C356" s="11" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="11" t="n">
-        <v>928</v>
+      <c r="C357" s="16" t="n">
+        <v>8045</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="11" t="n">
-        <v>163</v>
+      <c r="C358" s="16" t="n">
+        <v>2466</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="16" t="n">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B360" s="14" t="s">
+      <c r="C359" s="11" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="17" t="n">
+      <c r="C360" s="16" t="n">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B361" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="C361" s="17" t="n">
         <v>694</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B361" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="C361" s="11" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4366,7 +4378,7 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4374,7 +4386,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>604</v>
+        <v>29</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4382,23 +4394,23 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B365" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C365" s="11" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B365" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="C365" s="12" t="n">
-        <v>11615</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B366" s="15" t="s">
+    <row r="366" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B366" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="11" t="n">
-        <v>47</v>
+      <c r="C366" s="12" t="n">
+        <v>10589</v>
       </c>
     </row>
     <row r="367" ht="11" customHeight="true" outlineLevel="3">
@@ -4406,15 +4418,15 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="368" ht="22" customHeight="true" outlineLevel="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="15" t="s">
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>521</v>
+        <v>46</v>
       </c>
     </row>
     <row r="369" ht="22" customHeight="true" outlineLevel="3">
@@ -4422,7 +4434,7 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>23</v>
+        <v>483</v>
       </c>
     </row>
     <row r="370" ht="22" customHeight="true" outlineLevel="3">
@@ -4430,7 +4442,7 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="371" ht="22" customHeight="true" outlineLevel="3">
@@ -4438,15 +4450,15 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="372" ht="11" customHeight="true" outlineLevel="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="372" ht="22" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>640</v>
+        <v>120</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
@@ -4454,71 +4466,71 @@
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="374" ht="22" customHeight="true" outlineLevel="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="375" ht="11" customHeight="true" outlineLevel="3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="375" ht="22" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="376" ht="11" customHeight="true" outlineLevel="3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="377" ht="11" customHeight="true" outlineLevel="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="377" ht="22" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="378" ht="22" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
       <c r="C378" s="11" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="379" ht="22" customHeight="true" outlineLevel="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="381" ht="22" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>85</v>
+        <v>374</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="true" outlineLevel="3">
@@ -4526,7 +4538,7 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>115</v>
+        <v>182</v>
       </c>
     </row>
     <row r="383" ht="22" customHeight="true" outlineLevel="3">
@@ -4534,7 +4546,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
     </row>
     <row r="384" ht="22" customHeight="true" outlineLevel="3">
@@ -4542,7 +4554,7 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>285</v>
+        <v>10</v>
       </c>
     </row>
     <row r="385" ht="22" customHeight="true" outlineLevel="3">
@@ -4550,7 +4562,7 @@
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>137</v>
+        <v>74</v>
       </c>
     </row>
     <row r="386" ht="22" customHeight="true" outlineLevel="3">
@@ -4558,7 +4570,7 @@
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>228</v>
+        <v>69</v>
       </c>
     </row>
     <row r="387" ht="22" customHeight="true" outlineLevel="3">
@@ -4566,7 +4578,7 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>901</v>
+        <v>109</v>
       </c>
     </row>
     <row r="388" ht="22" customHeight="true" outlineLevel="3">
@@ -4574,23 +4586,23 @@
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="390" ht="11" customHeight="true" outlineLevel="3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="390" ht="22" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>305</v>
+        <v>48</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4598,7 +4610,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -4606,7 +4618,7 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>41</v>
+        <v>396</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4614,7 +4626,7 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>357</v>
+        <v>10</v>
       </c>
     </row>
     <row r="394" ht="22" customHeight="true" outlineLevel="3">
@@ -4622,15 +4634,15 @@
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="395" ht="22" customHeight="true" outlineLevel="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
@@ -4638,7 +4650,7 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>178</v>
+        <v>305</v>
       </c>
     </row>
     <row r="397" ht="22" customHeight="true" outlineLevel="3">
@@ -4646,55 +4658,55 @@
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="398" ht="22" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="399" ht="22" customHeight="true" outlineLevel="3">
       <c r="B399" s="15" t="s">
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="400" ht="22" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="401" ht="22" customHeight="true" outlineLevel="3">
       <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="402" ht="11" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="403" ht="11" customHeight="true" outlineLevel="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="11" t="n">
-        <v>57</v>
+      <c r="C403" s="16" t="n">
+        <v>1930</v>
       </c>
     </row>
     <row r="404" ht="11" customHeight="true" outlineLevel="3">
@@ -4702,7 +4714,7 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>220</v>
+        <v>271</v>
       </c>
     </row>
     <row r="405" ht="11" customHeight="true" outlineLevel="3">
@@ -4710,7 +4722,7 @@
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>311</v>
+        <v>28</v>
       </c>
     </row>
     <row r="406" ht="11" customHeight="true" outlineLevel="3">
@@ -4718,7 +4730,7 @@
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>355</v>
+        <v>254</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
@@ -4726,7 +4738,7 @@
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>357</v>
+        <v>111</v>
       </c>
     </row>
     <row r="408" ht="11" customHeight="true" outlineLevel="3">
@@ -4734,7 +4746,7 @@
         <v>407</v>
       </c>
       <c r="C408" s="11" t="n">
-        <v>252</v>
+        <v>360</v>
       </c>
     </row>
     <row r="409" ht="11" customHeight="true" outlineLevel="3">
@@ -4742,15 +4754,47 @@
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>636</v>
+        <v>56</v>
       </c>
     </row>
     <row r="410" ht="11" customHeight="true" outlineLevel="3">
       <c r="B410" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C410" s="16" t="n">
-        <v>1687</v>
+      <c r="C410" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="11" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="412" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B412" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="11" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="413" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="11" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="16" t="n">
+        <v>1279</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 16.02.2026 7:55:14</t>
+    <t>Период: на 23.02.2026 11:15:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -92,9 +92,6 @@
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Какао-порошок 22% УБ 60г /26шт</t>
-  </si>
-  <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт /</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
@@ -272,15 +272,12 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 41г /180шт</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
@@ -296,7 +293,7 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
@@ -305,9 +302,6 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
@@ -320,6 +314,12 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
@@ -455,9 +455,6 @@
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 216г /16шт</t>
-  </si>
-  <si>
     <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -515,18 +512,12 @@
     <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -542,9 +533,6 @@
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -554,9 +542,6 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
@@ -584,9 +569,6 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -611,9 +593,6 @@
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -647,6 +626,9 @@
     <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -659,12 +641,12 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -683,6 +665,9 @@
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
+    <t>Джеллі РЦ 200г /13шт</t>
+  </si>
+  <si>
     <t>Льодяник мікс РЦ 200г /24шт /</t>
   </si>
   <si>
@@ -692,12 +677,6 @@
     <t>Рошен евкаліпт-ментол РЦ 200г /12шт</t>
   </si>
   <si>
-    <t>Шалена бджілка ВКФ 200г /12шт</t>
-  </si>
-  <si>
-    <t>Шалена бджілка РЦ 200г /12шт</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
@@ -719,9 +698,6 @@
     <t>Korivka Roshen ВКФ 1кг /7пак /</t>
   </si>
   <si>
-    <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Korivka Roshen ВКФ 1кг /7пак /АКЦІЯ 1</t>
   </si>
   <si>
@@ -809,21 +785,18 @@
     <t>КОРОБКИ</t>
   </si>
   <si>
+    <t>Assortment Classic 154г/8</t>
+  </si>
+  <si>
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Assortment Elegant 145г/8</t>
-  </si>
-  <si>
     <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 256г /8шт</t>
-  </si>
-  <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
@@ -851,6 +824,9 @@
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
+    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -884,9 +860,6 @@
     <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
   </si>
   <si>
-    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
-  </si>
-  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -953,9 +926,6 @@
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -968,9 +938,6 @@
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з начинкою какао-горіх ККФ 235г /14шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
@@ -1016,6 +983,9 @@
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
+    <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
     <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -1082,9 +1052,6 @@
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
-  </si>
-  <si>
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -1130,6 +1097,9 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
@@ -1160,21 +1130,27 @@
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
@@ -1187,21 +1163,24 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
-  </si>
-  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1217,9 +1196,6 @@
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1244,19 +1220,22 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
+  </si>
+  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
-  </si>
-  <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
@@ -1505,7 +1484,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C414"/>
+  <dimension ref="C407"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1570,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>605</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1578,7 +1557,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>376054</v>
+        <v>379208</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1586,7 +1565,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>65370</v>
+        <v>102966</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1594,23 +1573,23 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>9752</v>
+        <v>9465</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="16" t="n">
-        <v>1160</v>
+      <c r="C15" s="11" t="n">
+        <v>880</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>1133</v>
+      <c r="C16" s="11" t="n">
+        <v>669</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1625,16 +1604,16 @@
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>1049</v>
+      <c r="C18" s="11" t="n">
+        <v>645</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>1146</v>
+      <c r="C19" s="11" t="n">
+        <v>604</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1642,7 +1621,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>1808</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1658,7 +1637,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>530</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1674,31 +1653,31 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B26" s="15" t="s">
+      <c r="C25" s="16" t="n">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B26" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="16" t="n">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="27" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B27" s="14" t="s">
+      <c r="C26" s="12" t="n">
+        <v>36647</v>
+      </c>
+    </row>
+    <row r="27" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>18134</v>
+      <c r="C27" s="16" t="n">
+        <v>1958</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -1706,7 +1685,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>3728</v>
+        <v>8052</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1714,7 +1693,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>3346</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1722,7 +1701,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>1081</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1730,31 +1709,31 @@
         <v>30</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>1767</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="16" t="n">
-        <v>3962</v>
+      <c r="C32" s="11" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>42</v>
+      <c r="C33" s="16" t="n">
+        <v>2264</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>18</v>
+      <c r="C34" s="16" t="n">
+        <v>2388</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -1770,7 +1749,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>1380</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1794,7 +1773,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>819</v>
+        <v>793</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
@@ -1802,7 +1781,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="16" t="n">
-        <v>1075</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1818,7 +1797,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>14356</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1826,7 +1805,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>798</v>
+        <v>613</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1842,7 +1821,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>658</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1858,7 +1837,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>575</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1874,15 +1853,15 @@
         <v>48</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>615</v>
+        <v>575</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
       <c r="B50" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="16" t="n">
-        <v>1062</v>
+      <c r="C50" s="11" t="n">
+        <v>926</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1898,7 +1877,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>341</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1906,7 +1885,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>345</v>
+        <v>305</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -1914,7 +1893,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>646</v>
+        <v>503</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -1930,7 +1909,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>179</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1938,7 +1917,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -1946,7 +1925,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>323</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -1954,7 +1933,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="16" t="n">
-        <v>1171</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1962,7 +1941,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>551</v>
+        <v>469</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="true" outlineLevel="3">
@@ -1978,7 +1957,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>396</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -1986,7 +1965,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>851</v>
+        <v>701</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -1994,7 +1973,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2002,7 +1981,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>2830</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="2">
@@ -2010,7 +1989,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="12" t="n">
-        <v>23128</v>
+        <v>44854</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -2018,7 +1997,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>41</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
@@ -2026,7 +2005,7 @@
         <v>67</v>
       </c>
       <c r="C68" s="16" t="n">
-        <v>2383</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="69" ht="11" customHeight="true" outlineLevel="3">
@@ -2034,7 +2013,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="16" t="n">
-        <v>1965</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2042,7 +2021,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="16" t="n">
-        <v>1864</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2050,7 +2029,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="16" t="n">
-        <v>6171</v>
+        <v>9365</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2058,7 +2037,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>427</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2066,7 +2045,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="16" t="n">
-        <v>3670</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
@@ -2074,7 +2053,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>767</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2082,15 +2061,15 @@
         <v>74</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>560</v>
+        <v>416</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>290</v>
+      <c r="C76" s="16" t="n">
+        <v>3293</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -2098,7 +2077,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>1516</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2106,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="16" t="n">
-        <v>1539</v>
+        <v>21138</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
@@ -2114,7 +2093,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>937</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2122,7 +2101,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>532</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
@@ -2130,7 +2109,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>466</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="1">
@@ -2138,7 +2117,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="12" t="n">
-        <v>310684</v>
+        <v>276242</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="2">
@@ -2146,15 +2125,15 @@
         <v>82</v>
       </c>
       <c r="C83" s="12" t="n">
-        <v>30008</v>
+        <v>20670</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="16" t="n">
-        <v>1965</v>
+      <c r="C84" s="11" t="n">
+        <v>805</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="true" outlineLevel="3">
@@ -2162,7 +2141,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>50</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="true" outlineLevel="3">
@@ -2170,23 +2149,23 @@
         <v>85</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>21</v>
+      <c r="C87" s="16" t="n">
+        <v>3611</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="16" t="n">
-        <v>5346</v>
+      <c r="C88" s="11" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2194,15 +2173,15 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="90" ht="11" customHeight="true" outlineLevel="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="true" outlineLevel="3">
@@ -2210,39 +2189,39 @@
         <v>90</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>40</v>
+        <v>459</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="true" outlineLevel="3">
       <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="16" t="n">
-        <v>1389</v>
+      <c r="C92" s="11" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="11" t="n">
-        <v>240</v>
+      <c r="C93" s="16" t="n">
+        <v>2984</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="16" t="n">
-        <v>3750</v>
+      <c r="C94" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="n">
-        <v>60</v>
+      <c r="C95" s="16" t="n">
+        <v>3374</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="true" outlineLevel="3">
@@ -2250,15 +2229,15 @@
         <v>95</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>21</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="16" t="n">
-        <v>4639</v>
+      <c r="C97" s="11" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="true" outlineLevel="3">
@@ -2266,7 +2245,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>300</v>
+        <v>844</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="true" outlineLevel="3">
@@ -2274,15 +2253,15 @@
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
       <c r="B100" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="16" t="n">
-        <v>2369</v>
+      <c r="C100" s="11" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
@@ -2290,7 +2269,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="16" t="n">
-        <v>8818</v>
+        <v>7178</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
@@ -2298,7 +2277,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>390</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103" ht="11" customHeight="true" outlineLevel="2">
@@ -2306,7 +2285,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="12" t="n">
-        <v>2744</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="104" ht="11" customHeight="true" outlineLevel="3">
@@ -2314,7 +2293,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>398</v>
+        <v>218</v>
       </c>
     </row>
     <row r="105" ht="11" customHeight="true" outlineLevel="3">
@@ -2330,7 +2309,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>359</v>
+        <v>400</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2338,15 +2317,15 @@
         <v>106</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>585</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>475</v>
+      <c r="C108" s="16" t="n">
+        <v>1238</v>
       </c>
     </row>
     <row r="109" ht="11" customHeight="true" outlineLevel="3">
@@ -2354,15 +2333,15 @@
         <v>108</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
     </row>
     <row r="110" ht="11" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>311</v>
+      <c r="C110" s="16" t="n">
+        <v>1081</v>
       </c>
     </row>
     <row r="111" ht="11" customHeight="true" outlineLevel="3">
@@ -2370,7 +2349,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>96</v>
+        <v>49</v>
       </c>
     </row>
     <row r="112" ht="11" customHeight="true" outlineLevel="3">
@@ -2386,7 +2365,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="11" t="n">
-        <v>198</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2402,7 +2381,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>97</v>
+        <v>301</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="true" outlineLevel="3">
@@ -2418,7 +2397,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="12" t="n">
-        <v>79480</v>
+        <v>66209</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
@@ -2426,7 +2405,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>128</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2434,7 +2413,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>78</v>
+        <v>760</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
@@ -2442,7 +2421,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2450,7 +2429,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>690</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2458,7 +2437,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="16" t="n">
-        <v>31155</v>
+        <v>28380</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2466,7 +2445,7 @@
         <v>122</v>
       </c>
       <c r="C123" s="16" t="n">
-        <v>15821</v>
+        <v>10171</v>
       </c>
     </row>
     <row r="124" ht="11" customHeight="true" outlineLevel="3">
@@ -2474,7 +2453,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="16" t="n">
-        <v>6825</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
@@ -2482,7 +2461,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="16" t="n">
-        <v>14335</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2490,7 +2469,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2498,7 +2477,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="16" t="n">
-        <v>1744</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2506,7 +2485,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2514,7 +2493,7 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>540</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
@@ -2522,7 +2501,7 @@
         <v>129</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
@@ -2530,7 +2509,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>687</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2545,8 +2524,8 @@
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>331</v>
+      <c r="C133" s="16" t="n">
+        <v>1974</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2554,7 +2533,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" ht="22" customHeight="true" outlineLevel="3">
@@ -2562,7 +2541,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="16" t="n">
-        <v>2157</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2570,15 +2549,15 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>35</v>
+        <v>184</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="11" t="n">
-        <v>428</v>
+      <c r="C137" s="16" t="n">
+        <v>1357</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2594,7 +2573,7 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>495</v>
+        <v>229</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
@@ -2610,7 +2589,7 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>721</v>
+        <v>835</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -2618,7 +2597,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>94</v>
+        <v>149</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2626,7 +2605,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2634,7 +2613,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>151</v>
+        <v>262</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2642,7 +2621,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>294</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2650,15 +2629,15 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="11" t="n">
-        <v>1</v>
+      <c r="C147" s="16" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2666,15 +2645,15 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>528</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>3</v>
+      <c r="C149" s="16" t="n">
+        <v>1207</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2682,23 +2661,23 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="151" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B151" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="151" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B151" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="152" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B152" s="14" t="s">
+      <c r="C151" s="12" t="n">
+        <v>79137</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B152" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="12" t="n">
-        <v>95811</v>
+      <c r="C152" s="11" t="n">
+        <v>512</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2706,7 +2685,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>703</v>
+        <v>519</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2714,7 +2693,7 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -2722,7 +2701,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>374</v>
+        <v>223</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2730,7 +2709,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>33</v>
+        <v>111</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2738,7 +2717,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>207</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2746,7 +2725,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>5</v>
+        <v>143</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2754,7 +2733,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2762,7 +2741,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>43</v>
+        <v>108</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2770,23 +2749,23 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>122</v>
+        <v>435</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="11" t="n">
-        <v>449</v>
+      <c r="C162" s="16" t="n">
+        <v>3633</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
       <c r="B163" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="16" t="n">
-        <v>3689</v>
+      <c r="C163" s="11" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2794,7 +2773,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>243</v>
+        <v>887</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2802,7 +2781,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>893</v>
+        <v>470</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2810,7 +2789,7 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>285</v>
+        <v>698</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
@@ -2818,7 +2797,7 @@
         <v>166</v>
       </c>
       <c r="C167" s="11" t="n">
-        <v>472</v>
+        <v>642</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
@@ -2826,7 +2805,7 @@
         <v>167</v>
       </c>
       <c r="C168" s="16" t="n">
-        <v>1036</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2834,7 +2813,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>1</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2842,15 +2821,15 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>111</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="16" t="n">
-        <v>4943</v>
+      <c r="C171" s="11" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2858,7 +2837,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>199</v>
+        <v>74</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2866,7 +2845,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>822</v>
+        <v>211</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2874,7 +2853,7 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>184</v>
+        <v>693</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
@@ -2882,7 +2861,7 @@
         <v>174</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>1</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2890,15 +2869,15 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>213</v>
+        <v>363</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="11" t="n">
-        <v>653</v>
+      <c r="C177" s="16" t="n">
+        <v>1566</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2906,7 +2885,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="16" t="n">
-        <v>2724</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
@@ -2914,7 +2893,7 @@
         <v>178</v>
       </c>
       <c r="C179" s="11" t="n">
-        <v>224</v>
+        <v>109</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2922,55 +2901,55 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="181" ht="11" customHeight="true" outlineLevel="3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="11" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="182" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C181" s="16" t="n">
+        <v>13669</v>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="16" t="n">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="183" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C182" s="11" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
       <c r="C183" s="16" t="n">
-        <v>2723</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="11" t="n">
-        <v>112</v>
+      <c r="C184" s="16" t="n">
+        <v>14903</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="11" t="n">
-        <v>325</v>
+      <c r="C185" s="16" t="n">
+        <v>1182</v>
       </c>
     </row>
     <row r="186" ht="22" customHeight="true" outlineLevel="3">
       <c r="B186" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="16" t="n">
-        <v>14008</v>
+      <c r="C186" s="11" t="n">
+        <v>818</v>
       </c>
     </row>
     <row r="187" ht="22" customHeight="true" outlineLevel="3">
@@ -2978,55 +2957,55 @@
         <v>186</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="188" ht="22" customHeight="true" outlineLevel="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" ht="11" customHeight="true" outlineLevel="3">
       <c r="B188" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="16" t="n">
-        <v>1940</v>
+      <c r="C188" s="11" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="190" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C189" s="16" t="n">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="true" outlineLevel="3">
       <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="16" t="n">
-        <v>15237</v>
+      <c r="C190" s="11" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="16" t="n">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="192" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C191" s="11" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="15" t="s">
         <v>191</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="true" outlineLevel="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3034,23 +3013,23 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>281</v>
+        <v>202</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="16" t="n">
-        <v>8838</v>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C195" s="11" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>198</v>
+        <v>321</v>
       </c>
     </row>
     <row r="197" ht="11" customHeight="true" outlineLevel="3">
@@ -3058,15 +3037,15 @@
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>145</v>
+        <v>198</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
       <c r="B198" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="11" t="n">
-        <v>1</v>
+      <c r="C198" s="16" t="n">
+        <v>2251</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3074,7 +3053,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>154</v>
+        <v>299</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3082,7 +3061,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="16" t="n">
-        <v>2278</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3090,15 +3069,15 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>366</v>
+        <v>226</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="16" t="n">
-        <v>3710</v>
+      <c r="C202" s="11" t="n">
+        <v>892</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3106,23 +3085,23 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>321</v>
+        <v>670</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="11" t="n">
-        <v>212</v>
+      <c r="C204" s="16" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="16" t="n">
-        <v>2318</v>
+      <c r="C205" s="11" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3130,7 +3109,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>474</v>
+        <v>225</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3138,7 +3117,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="16" t="n">
-        <v>3443</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3146,7 +3125,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>226</v>
+        <v>672</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3154,7 +3133,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>895</v>
+        <v>201</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3162,7 +3141,7 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>205</v>
+        <v>340</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
@@ -3170,7 +3149,7 @@
         <v>210</v>
       </c>
       <c r="C211" s="16" t="n">
-        <v>1754</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3178,15 +3157,15 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>236</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="16" t="n">
-        <v>2363</v>
+      <c r="C213" s="11" t="n">
+        <v>385</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3194,15 +3173,15 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>385</v>
+        <v>329</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="16" t="n">
-        <v>1185</v>
+      <c r="C215" s="11" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
@@ -3210,15 +3189,15 @@
         <v>215</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>406</v>
+        <v>292</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="16" t="n">
-        <v>2691</v>
+      <c r="C217" s="11" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3226,23 +3205,23 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>24</v>
+        <v>115</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="16" t="n">
-        <v>2943</v>
-      </c>
-    </row>
-    <row r="220" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B220" s="15" t="s">
+      <c r="C219" s="11" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="220" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B220" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="11" t="n">
-        <v>109</v>
+      <c r="C220" s="12" t="n">
+        <v>40057</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3250,7 +3229,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>215</v>
+        <v>813</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3258,15 +3237,15 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>291</v>
+        <v>171</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="11" t="n">
-        <v>231</v>
+      <c r="C223" s="16" t="n">
+        <v>1976</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3274,7 +3253,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>211</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3282,23 +3261,23 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>474</v>
+        <v>979</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="227" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B227" s="14" t="s">
+      <c r="C226" s="16" t="n">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="227" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B227" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="12" t="n">
-        <v>32694</v>
+      <c r="C227" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3306,7 +3285,7 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>968</v>
+        <v>386</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3314,15 +3293,15 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>236</v>
+        <v>410</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
       <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="16" t="n">
-        <v>2336</v>
+      <c r="C230" s="11" t="n">
+        <v>325</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3330,15 +3309,15 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>7</v>
+        <v>302</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>567</v>
+      <c r="C232" s="16" t="n">
+        <v>1153</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3346,15 +3325,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="16" t="n">
-        <v>2854</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
       <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>10</v>
+      <c r="C234" s="16" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3362,15 +3341,15 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>216</v>
+        <v>781</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
       <c r="B236" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="11" t="n">
-        <v>405</v>
+      <c r="C236" s="16" t="n">
+        <v>1178</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3378,23 +3357,23 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>444</v>
+        <v>293</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="11" t="n">
-        <v>397</v>
+      <c r="C238" s="16" t="n">
+        <v>1250</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>103</v>
+      <c r="C239" s="16" t="n">
+        <v>1127</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3402,39 +3381,39 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>885</v>
+        <v>648</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="11" t="n">
-        <v>375</v>
+      <c r="C241" s="16" t="n">
+        <v>1336</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="11" t="n">
-        <v>966</v>
+      <c r="C242" s="16" t="n">
+        <v>1521</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="11" t="n">
-        <v>874</v>
+      <c r="C243" s="16" t="n">
+        <v>2946</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="11" t="n">
-        <v>714</v>
+      <c r="C244" s="16" t="n">
+        <v>1368</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3442,7 +3421,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>200</v>
+        <v>793</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3450,7 +3429,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>842</v>
+        <v>910</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3458,23 +3437,23 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>688</v>
+        <v>621</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="11" t="n">
-        <v>501</v>
+      <c r="C248" s="16" t="n">
+        <v>1451</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="11" t="n">
-        <v>996</v>
+      <c r="C249" s="16" t="n">
+        <v>1798</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3482,7 +3461,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="16" t="n">
-        <v>1832</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3490,7 +3469,7 @@
         <v>250</v>
       </c>
       <c r="C251" s="16" t="n">
-        <v>1970</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3498,7 +3477,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="16" t="n">
-        <v>1602</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3506,23 +3485,23 @@
         <v>252</v>
       </c>
       <c r="C253" s="16" t="n">
-        <v>1097</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
       <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C254" s="16" t="n">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="255" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B255" s="15" t="s">
+      <c r="C254" s="11" t="n">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B255" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="11" t="n">
-        <v>638</v>
+      <c r="C255" s="12" t="n">
+        <v>2364</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3530,15 +3509,15 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>550</v>
+        <v>140</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
       <c r="B257" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="16" t="n">
-        <v>1120</v>
+      <c r="C257" s="11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
@@ -3546,31 +3525,31 @@
         <v>257</v>
       </c>
       <c r="C258" s="11" t="n">
-        <v>786</v>
+        <v>248</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="16" t="n">
-        <v>2243</v>
+      <c r="C259" s="11" t="n">
+        <v>169</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="16" t="n">
-        <v>1146</v>
+      <c r="C260" s="11" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="16" t="n">
-        <v>2232</v>
+      <c r="C261" s="11" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3578,15 +3557,15 @@
         <v>261</v>
       </c>
       <c r="C262" s="11" t="n">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="263" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B263" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="263" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="12" t="n">
-        <v>2800</v>
+      <c r="C263" s="11" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3594,7 +3573,7 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>22</v>
+        <v>258</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
@@ -3602,7 +3581,7 @@
         <v>264</v>
       </c>
       <c r="C265" s="11" t="n">
-        <v>63</v>
+        <v>177</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3610,7 +3589,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>388</v>
+        <v>353</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3618,7 +3597,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>182</v>
+        <v>27</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3626,7 +3605,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>14</v>
+        <v>121</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3634,7 +3613,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>186</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3642,7 +3621,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3650,7 +3629,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>161</v>
+        <v>239</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3658,15 +3637,15 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="273" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B273" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="273" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B273" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="11" t="n">
-        <v>253</v>
+      <c r="C273" s="12" t="n">
+        <v>21575</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3674,7 +3653,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>217</v>
+        <v>426</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3682,7 +3661,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>784</v>
+        <v>407</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3690,7 +3669,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>22</v>
+        <v>195</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3698,7 +3677,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3706,7 +3685,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3714,7 +3693,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>9</v>
+        <v>305</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3722,15 +3701,15 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="281" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B281" s="14" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="12" t="n">
-        <v>24350</v>
+      <c r="C281" s="11" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
@@ -3738,7 +3717,7 @@
         <v>281</v>
       </c>
       <c r="C282" s="11" t="n">
-        <v>451</v>
+        <v>124</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3746,7 +3725,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>480</v>
+        <v>242</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3754,7 +3733,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>227</v>
+        <v>164</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3762,7 +3741,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>376</v>
+        <v>786</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3770,31 +3749,31 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="287" ht="11" customHeight="true" outlineLevel="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="287" ht="22" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="288" ht="11" customHeight="true" outlineLevel="3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="289" ht="11" customHeight="true" outlineLevel="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" ht="22" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
     </row>
     <row r="290" ht="22" customHeight="true" outlineLevel="3">
@@ -3802,39 +3781,39 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="291" ht="11" customHeight="true" outlineLevel="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="292" ht="11" customHeight="true" outlineLevel="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="293" ht="11" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="294" ht="11" customHeight="true" outlineLevel="3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="294" ht="22" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="16" t="n">
-        <v>1206</v>
+      <c r="C294" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -3842,71 +3821,71 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="true" outlineLevel="3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
       <c r="C296" s="11" t="n">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="297" ht="22" customHeight="true" outlineLevel="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="297" ht="11" customHeight="true" outlineLevel="3">
       <c r="B297" s="15" t="s">
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="11" t="n">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C298" s="16" t="n">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C299" s="16" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="true" outlineLevel="3">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="302" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C301" s="16" t="n">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="11" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="303" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C302" s="16" t="n">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="11" t="n">
-        <v>67</v>
+      <c r="C303" s="16" t="n">
+        <v>2593</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
@@ -3914,47 +3893,47 @@
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>286</v>
+        <v>880</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="11" t="n">
-        <v>302</v>
+      <c r="C305" s="16" t="n">
+        <v>1014</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="11" t="n">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="307" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B307" s="15" t="s">
+      <c r="C306" s="16" t="n">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B307" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="16" t="n">
-        <v>2637</v>
+      <c r="C307" s="12" t="n">
+        <v>30172</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="C308" s="16" t="n">
-        <v>1467</v>
+      <c r="C308" s="11" t="n">
+        <v>622</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
       <c r="B309" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="16" t="n">
-        <v>1037</v>
+      <c r="C309" s="11" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
@@ -3962,23 +3941,23 @@
         <v>309</v>
       </c>
       <c r="C310" s="11" t="n">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="311" ht="11" customHeight="true" outlineLevel="3">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="16" t="n">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C311" s="11" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>6</v>
+        <v>900</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -3986,23 +3965,23 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>552</v>
+        <v>292</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="16" t="n">
-        <v>2431</v>
+      <c r="C314" s="11" t="n">
+        <v>572</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="16" t="n">
-        <v>1014</v>
+      <c r="C315" s="11" t="n">
+        <v>571</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4010,7 +3989,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="16" t="n">
-        <v>5406</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -4018,15 +3997,15 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="318" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B318" s="14" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="12" t="n">
-        <v>31514</v>
+      <c r="C318" s="11" t="n">
+        <v>380</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
@@ -4034,7 +4013,7 @@
         <v>318</v>
       </c>
       <c r="C319" s="11" t="n">
-        <v>340</v>
+        <v>321</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -4042,7 +4021,7 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>400</v>
+        <v>373</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
@@ -4050,23 +4029,23 @@
         <v>320</v>
       </c>
       <c r="C321" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
       <c r="C322" s="11" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="323" ht="22" customHeight="true" outlineLevel="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="323" ht="11" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>900</v>
+        <v>506</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4074,7 +4053,7 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>196</v>
+        <v>398</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4082,7 +4061,7 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>159</v>
+        <v>485</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
@@ -4090,15 +4069,15 @@
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>262</v>
+        <v>772</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="16" t="n">
-        <v>1228</v>
+      <c r="C327" s="11" t="n">
+        <v>656</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4106,7 +4085,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>500</v>
+        <v>417</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4114,15 +4093,15 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>334</v>
+        <v>300</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="11" t="n">
-        <v>346</v>
+      <c r="C330" s="16" t="n">
+        <v>1081</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4130,7 +4109,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="11" t="n">
-        <v>442</v>
+        <v>848</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4138,23 +4117,23 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="333" ht="11" customHeight="true" outlineLevel="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="333" ht="22" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>568</v>
+        <v>120</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4162,7 +4141,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>650</v>
+        <v>46</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4170,15 +4149,15 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="337" ht="11" customHeight="true" outlineLevel="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="337" ht="22" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>738</v>
+        <v>75</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4186,31 +4165,31 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>300</v>
+        <v>410</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="16" t="n">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C340" s="11" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="341" ht="22" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>987</v>
+        <v>161</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4218,7 +4197,7 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>160</v>
+        <v>260</v>
       </c>
     </row>
     <row r="343" ht="22" customHeight="true" outlineLevel="3">
@@ -4226,15 +4205,15 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="344" ht="22" customHeight="true" outlineLevel="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="11" t="n">
-        <v>199</v>
+      <c r="C344" s="16" t="n">
+        <v>2303</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4242,55 +4221,55 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>67</v>
+        <v>500</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="347" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C346" s="16" t="n">
+        <v>6531</v>
+      </c>
+    </row>
+    <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="11" t="n">
-        <v>170</v>
+      <c r="C347" s="16" t="n">
+        <v>2886</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C348" s="16" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B350" s="15" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B350" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="351" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C350" s="17" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="351" ht="11" customHeight="true" outlineLevel="3">
       <c r="B351" s="15" t="s">
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>381</v>
+        <v>9</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
@@ -4298,31 +4277,31 @@
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="353" ht="22" customHeight="true" outlineLevel="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>146</v>
+        <v>100</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
       <c r="B354" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="16" t="n">
-        <v>3813</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B355" s="15" t="s">
+      <c r="C354" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B355" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="11" t="n">
-        <v>15</v>
+      <c r="C355" s="12" t="n">
+        <v>11783</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
@@ -4330,55 +4309,55 @@
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
       <c r="B357" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="16" t="n">
-        <v>8045</v>
-      </c>
-    </row>
-    <row r="358" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C357" s="11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="358" ht="22" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="16" t="n">
-        <v>2466</v>
-      </c>
-    </row>
-    <row r="359" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C358" s="11" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="359" ht="22" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
       <c r="C359" s="11" t="n">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="360" ht="11" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="360" ht="22" customHeight="true" outlineLevel="3">
       <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="16" t="n">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="361" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B361" s="14" t="s">
+      <c r="C360" s="11" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="17" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="362" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C361" s="11" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="362" ht="22" customHeight="true" outlineLevel="3">
       <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4386,7 +4365,7 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>29</v>
+        <v>334</v>
       </c>
     </row>
     <row r="364" ht="11" customHeight="true" outlineLevel="3">
@@ -4394,31 +4373,31 @@
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="365" ht="11" customHeight="true" outlineLevel="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="365" ht="22" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="366" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B366" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="12" t="n">
-        <v>10589</v>
-      </c>
-    </row>
-    <row r="367" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C366" s="11" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="367" ht="22" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4426,23 +4405,23 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="369" ht="22" customHeight="true" outlineLevel="3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
       <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="371" ht="22" customHeight="true" outlineLevel="3">
@@ -4450,7 +4429,7 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
     </row>
     <row r="372" ht="22" customHeight="true" outlineLevel="3">
@@ -4458,23 +4437,23 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="373" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="373" ht="22" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="374" ht="11" customHeight="true" outlineLevel="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="374" ht="22" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>242</v>
+        <v>110</v>
       </c>
     </row>
     <row r="375" ht="22" customHeight="true" outlineLevel="3">
@@ -4482,15 +4461,15 @@
         <v>374</v>
       </c>
       <c r="C375" s="11" t="n">
-        <v>194</v>
+        <v>10</v>
       </c>
     </row>
     <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="11" t="n">
-        <v>170</v>
+      <c r="C376" s="16" t="n">
+        <v>1504</v>
       </c>
     </row>
     <row r="377" ht="22" customHeight="true" outlineLevel="3">
@@ -4498,39 +4477,39 @@
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="378" ht="22" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="379" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C378" s="16" t="n">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="379" ht="22" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="380" ht="11" customHeight="true" outlineLevel="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="380" ht="22" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="381" ht="11" customHeight="true" outlineLevel="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="381" ht="22" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>374</v>
+        <v>130</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="true" outlineLevel="3">
@@ -4538,7 +4517,7 @@
         <v>381</v>
       </c>
       <c r="C382" s="11" t="n">
-        <v>182</v>
+        <v>90</v>
       </c>
     </row>
     <row r="383" ht="22" customHeight="true" outlineLevel="3">
@@ -4546,15 +4525,15 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="384" ht="22" customHeight="true" outlineLevel="3">
       <c r="B384" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="C384" s="11" t="n">
-        <v>10</v>
+      <c r="C384" s="16" t="n">
+        <v>1138</v>
       </c>
     </row>
     <row r="385" ht="22" customHeight="true" outlineLevel="3">
@@ -4562,7 +4541,7 @@
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>74</v>
+        <v>176</v>
       </c>
     </row>
     <row r="386" ht="22" customHeight="true" outlineLevel="3">
@@ -4570,7 +4549,7 @@
         <v>385</v>
       </c>
       <c r="C386" s="11" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="387" ht="22" customHeight="true" outlineLevel="3">
@@ -4578,23 +4557,23 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="388" ht="22" customHeight="true" outlineLevel="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
       <c r="C388" s="11" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>137</v>
+        <v>254</v>
       </c>
     </row>
     <row r="390" ht="22" customHeight="true" outlineLevel="3">
@@ -4602,7 +4581,7 @@
         <v>389</v>
       </c>
       <c r="C390" s="11" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4610,7 +4589,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>180</v>
+        <v>14</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -4618,7 +4597,7 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>396</v>
+        <v>213</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4626,23 +4605,23 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="394" ht="22" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="394" ht="11" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
       <c r="C394" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="395" ht="22" customHeight="true" outlineLevel="3">
       <c r="B395" s="15" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>20</v>
+        <v>542</v>
       </c>
     </row>
     <row r="396" ht="11" customHeight="true" outlineLevel="3">
@@ -4650,63 +4629,63 @@
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="397" ht="22" customHeight="true" outlineLevel="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
       <c r="C397" s="11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="398" ht="22" customHeight="true" outlineLevel="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="399" ht="22" customHeight="true" outlineLevel="3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="399" ht="11" customHeight="true" outlineLevel="3">
       <c r="B399" s="15" t="s">
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="401" ht="22" customHeight="true" outlineLevel="3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
       <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="402" ht="11" customHeight="true" outlineLevel="3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="402" ht="22" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="403" ht="22" customHeight="true" outlineLevel="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="403" ht="11" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="16" t="n">
-        <v>1930</v>
+      <c r="C403" s="11" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="404" ht="11" customHeight="true" outlineLevel="3">
@@ -4714,7 +4693,7 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>271</v>
+        <v>29</v>
       </c>
     </row>
     <row r="405" ht="11" customHeight="true" outlineLevel="3">
@@ -4722,7 +4701,7 @@
         <v>404</v>
       </c>
       <c r="C405" s="11" t="n">
-        <v>28</v>
+        <v>282</v>
       </c>
     </row>
     <row r="406" ht="11" customHeight="true" outlineLevel="3">
@@ -4730,71 +4709,15 @@
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
     </row>
     <row r="407" ht="11" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="C407" s="11" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B408" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="C408" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B409" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="C409" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="410" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B410" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C410" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B411" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="C411" s="11" t="n">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="412" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B412" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="C412" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="413" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B413" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C413" s="11" t="n">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="414" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B414" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C414" s="16" t="n">
-        <v>1279</v>
+      <c r="C407" s="16" t="n">
+        <v>1561</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="441">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.02.2026 11:15:14</t>
+    <t>Период: на 19.03.2026 20:05:31</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -74,9 +74,6 @@
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе вишня УБ 78г /56шт</t>
-  </si>
-  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
@@ -92,9 +89,18 @@
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Какао-порошок 22% УБ 60г /26шт</t>
+  </si>
+  <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
+    <t>Какао-порошок УБ 80г /48шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -104,7 +110,10 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
-    <t>Ванільний цукор УБ 35г /36шт</t>
+    <t>Ванільний цукор УБ 10г /58шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Глазур декоративна біла УБ 75г /40шт</t>
   </si>
   <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
@@ -113,15 +122,27 @@
     <t>Желатин УБ 25г /42шт</t>
   </si>
   <si>
+    <t>Желатин УБ 25г /42шт АКЦІЯ</t>
+  </si>
+  <si>
     <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт /</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №1 УБ 7г /55шт</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №2 УБ 7г /55шт</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №2 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Посипка декоративна №3 УБ 7г /55шт</t>
+  </si>
+  <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
@@ -197,6 +218,9 @@
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
+    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
@@ -206,6 +230,9 @@
     <t>Суміш прянощів Італійські трави УБ 10г /28шт</t>
   </si>
   <si>
+    <t>Суміш прянощів Італійські трави УБ 10г /28шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Томати з часником та базиліком УБ 20г /30шт</t>
   </si>
   <si>
@@ -218,9 +245,6 @@
     <t>СПЕЦІЇ</t>
   </si>
   <si>
-    <t>Гвоздика ціла УБ 10г /30шт</t>
-  </si>
-  <si>
     <t>Кориця мелена УБ 15г /38шт</t>
   </si>
   <si>
@@ -251,13 +275,16 @@
     <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Перець чорний горошком УБ 20г /32шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
@@ -275,15 +302,18 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
+    <t>Батон ROSHEN Truffle Sparkling Wine ВКФ 39г /180шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -293,6 +323,9 @@
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -302,30 +335,27 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
+  </si>
+  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>БІСКВІТИ</t>
   </si>
   <si>
@@ -353,21 +383,12 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -377,6 +398,9 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
+    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт</t>
+  </si>
+  <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
@@ -404,9 +428,6 @@
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
@@ -437,15 +458,9 @@
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
-    <t>Wafers какао-молоко ККФ 216г /16шт</t>
-  </si>
-  <si>
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
@@ -455,9 +470,6 @@
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -503,6 +515,9 @@
     <t>Yummi Gummi Apples ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Apples ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -512,6 +527,9 @@
     <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Cactus ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -521,16 +539,10 @@
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
@@ -539,12 +551,18 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
@@ -569,6 +587,9 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -590,21 +611,12 @@
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -617,18 +629,30 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
   </si>
   <si>
     <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -638,13 +662,19 @@
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Slices ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
@@ -656,9 +686,6 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -677,6 +704,9 @@
     <t>Рошен евкаліпт-ментол РЦ 200г /12шт</t>
   </si>
   <si>
+    <t>Шалена бджілка ВКФ 200г /12шт</t>
+  </si>
+  <si>
     <t>КАРАМЕЛЬ ВАГОВА</t>
   </si>
   <si>
@@ -788,10 +818,7 @@
     <t>Assortment Classic 154г/8</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
+    <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
@@ -860,6 +887,9 @@
     <t>Lovita Blondie Brownie з лимоном ККФ 152г /21шт</t>
   </si>
   <si>
+    <t>Lovita Brownie з какао ККФ 152г /21шт</t>
+  </si>
+  <si>
     <t>Lovita Cake Cookies з вишнево-ванільною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
@@ -872,6 +902,9 @@
     <t>Lovita Classic Cookies арахіс ККФ 150г /16шт</t>
   </si>
   <si>
+    <t>Lovita Classic Cookies арахіс ККФ 150г /16шт DE</t>
+  </si>
+  <si>
     <t>Lovita Classic Cookies з какао і кусочками глазурі ККФ 150г /16шт</t>
   </si>
   <si>
@@ -905,6 +938,9 @@
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
+    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
+  </si>
+  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
@@ -914,9 +950,15 @@
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою какао ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
@@ -926,6 +968,9 @@
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
+  </si>
+  <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
   </si>
   <si>
@@ -980,6 +1025,9 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>KONAFETTO blanc ВКФ 1кг /5пак HAL</t>
+  </si>
+  <si>
     <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
   </si>
   <si>
@@ -1016,9 +1064,6 @@
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з мигдалем та кокосовим кремом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1028,9 +1073,6 @@
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1040,19 +1082,13 @@
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
-    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ 1</t>
   </si>
   <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
@@ -1061,9 +1097,15 @@
     <t>Сливки-Ленивки 1кг ВКФ</t>
   </si>
   <si>
+    <t>Сливки-Ленивки ВКФ 1кг АКЦІЯ</t>
+  </si>
+  <si>
     <t>Червоний мак ВКФ 1кг /7пак</t>
   </si>
   <si>
+    <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
@@ -1091,19 +1133,22 @@
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
   </si>
   <si>
+    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт</t>
   </si>
   <si>
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
@@ -1112,13 +1157,13 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
+    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
@@ -1127,13 +1172,25 @@
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
@@ -1142,7 +1199,7 @@
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
@@ -1151,12 +1208,21 @@
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
   </si>
   <si>
@@ -1166,16 +1232,28 @@
     <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
@@ -1193,12 +1271,18 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1220,10 +1304,13 @@
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
@@ -1238,7 +1325,22 @@
     <t>Roshen чорний термостійкий РЦ 80г /13шт HAL</t>
   </si>
   <si>
+    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
+  </si>
+  <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
+  </si>
+  <si>
+    <t>ФІГУРКИ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 40г /24шт</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1465,6 +1567,12 @@
     <xf numFmtId="51" fontId="6" fillId="6" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1484,7 +1592,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C407"/>
+  <dimension ref="C441"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1549,7 +1657,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>521</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1557,7 +1665,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>379208</v>
+        <v>543300</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1565,7 +1673,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>102966</v>
+        <v>120980</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1573,15 +1681,15 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>9465</v>
+        <v>17389</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
       <c r="B15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>880</v>
+      <c r="C15" s="16" t="n">
+        <v>1770</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
@@ -1589,7 +1697,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>669</v>
+        <v>643</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1604,32 +1712,32 @@
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>645</v>
+      <c r="C18" s="16" t="n">
+        <v>1919</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>604</v>
+      <c r="C19" s="16" t="n">
+        <v>1929</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>1146</v>
+      <c r="C20" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
       <c r="B21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>8</v>
+      <c r="C21" s="16" t="n">
+        <v>2181</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1637,15 +1745,15 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>648</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>414</v>
+      <c r="C23" s="16" t="n">
+        <v>1505</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -1653,23 +1761,23 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>278</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="16" t="n">
-        <v>3779</v>
-      </c>
-    </row>
-    <row r="26" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B26" s="14" t="s">
+      <c r="C25" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>36647</v>
+      <c r="C26" s="16" t="n">
+        <v>3441</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -1677,15 +1785,15 @@
         <v>26</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="28" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B28" s="15" t="s">
+        <v>3540</v>
+      </c>
+    </row>
+    <row r="28" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B28" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <v>8052</v>
+      <c r="C28" s="12" t="n">
+        <v>44787</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1693,7 +1801,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>1009</v>
+        <v>6049</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
@@ -1701,15 +1809,15 @@
         <v>29</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>1767</v>
+        <v>12959</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="16" t="n">
-        <v>15040</v>
+      <c r="C31" s="11" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -1717,15 +1825,15 @@
         <v>31</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>42</v>
+        <v>844</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="16" t="n">
-        <v>2264</v>
+      <c r="C33" s="11" t="n">
+        <v>672</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1733,31 +1841,31 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>2388</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>149</v>
+      <c r="C35" s="16" t="n">
+        <v>2160</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="16" t="n">
-        <v>1369</v>
+      <c r="C36" s="11" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
       <c r="B37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>412</v>
+      <c r="C37" s="16" t="n">
+        <v>3037</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1765,47 +1873,47 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>232</v>
+        <v>906</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
       <c r="B39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>793</v>
+      <c r="C39" s="16" t="n">
+        <v>3457</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="16" t="n">
-        <v>1049</v>
+      <c r="C40" s="11" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B42" s="14" t="s">
+      <c r="C41" s="16" t="n">
+        <v>3497</v>
+      </c>
+    </row>
+    <row r="42" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="12" t="n">
-        <v>12000</v>
+      <c r="C42" s="11" t="n">
+        <v>149</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
       <c r="B43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>613</v>
+      <c r="C43" s="16" t="n">
+        <v>1247</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -1813,7 +1921,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>100</v>
+        <v>412</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
@@ -1821,7 +1929,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>456</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -1829,7 +1937,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>67</v>
+        <v>705</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1837,7 +1945,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>446</v>
+        <v>903</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
@@ -1845,15 +1953,15 @@
         <v>47</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="49" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B49" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B49" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>575</v>
+      <c r="C49" s="12" t="n">
+        <v>16724</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1861,7 +1969,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>926</v>
+        <v>994</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1869,7 +1977,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>445</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1877,7 +1985,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>216</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1885,23 +1993,23 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>305</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
       <c r="B54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>503</v>
+      <c r="C54" s="16" t="n">
+        <v>1588</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
       <c r="B55" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="16" t="n">
-        <v>1071</v>
+      <c r="C55" s="11" t="n">
+        <v>267</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -1909,7 +2017,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>93</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
@@ -1917,7 +2025,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>18</v>
+        <v>542</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -1925,15 +2033,15 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>127</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="16" t="n">
-        <v>1047</v>
+      <c r="C59" s="11" t="n">
+        <v>826</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -1941,23 +2049,23 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="true" outlineLevel="3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="61" ht="11" customHeight="true" outlineLevel="3">
       <c r="B61" s="15" t="s">
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="11" t="n">
-        <v>194</v>
+      <c r="C62" s="16" t="n">
+        <v>1003</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -1965,7 +2073,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>701</v>
+        <v>586</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -1973,7 +2081,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>413</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -1981,15 +2089,15 @@
         <v>64</v>
       </c>
       <c r="C65" s="16" t="n">
-        <v>2372</v>
-      </c>
-    </row>
-    <row r="66" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B66" s="14" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B66" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="12" t="n">
-        <v>44854</v>
+      <c r="C66" s="11" t="n">
+        <v>224</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -1997,39 +2105,39 @@
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>130</v>
+        <v>256</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="16" t="n">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="69" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C68" s="11" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="n">
-        <v>1695</v>
+      <c r="C69" s="11" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="n">
-        <v>1556</v>
+      <c r="C70" s="11" t="n">
+        <v>978</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>9365</v>
+      <c r="C71" s="11" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2037,31 +2145,31 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>179</v>
+        <v>905</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
       <c r="B73" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C73" s="16" t="n">
-        <v>3067</v>
+      <c r="C73" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B75" s="15" t="s">
+      <c r="C74" s="16" t="n">
+        <v>5053</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B75" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="11" t="n">
-        <v>416</v>
+      <c r="C75" s="12" t="n">
+        <v>42080</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
@@ -2069,7 +2177,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>3293</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
@@ -2077,23 +2185,23 @@
         <v>76</v>
       </c>
       <c r="C77" s="16" t="n">
-        <v>1097</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
       <c r="B78" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="16" t="n">
-        <v>21138</v>
+      <c r="C78" s="11" t="n">
+        <v>356</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>113</v>
+      <c r="C79" s="16" t="n">
+        <v>4042</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2101,55 +2209,55 @@
         <v>79</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>100</v>
+        <v>944</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="11" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B82" s="13" t="s">
+      <c r="C81" s="16" t="n">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B82" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="12" t="n">
-        <v>276242</v>
-      </c>
-    </row>
-    <row r="83" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B83" s="14" t="s">
+      <c r="C82" s="16" t="n">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="12" t="n">
-        <v>20670</v>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C83" s="11" t="n">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="11" t="n">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C84" s="16" t="n">
+        <v>3497</v>
+      </c>
+    </row>
+    <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C85" s="16" t="n">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true" outlineLevel="3">
       <c r="B86" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>50</v>
+      <c r="C86" s="16" t="n">
+        <v>4305</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2157,7 +2265,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="16" t="n">
-        <v>3611</v>
+        <v>10038</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
@@ -2165,47 +2273,47 @@
         <v>87</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>210</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
       <c r="B89" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C89" s="16" t="n">
+        <v>8982</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="91" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B91" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="91" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B91" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="92" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B92" s="15" t="s">
+      <c r="C91" s="12" t="n">
+        <v>422320</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B92" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>-30</v>
+      <c r="C92" s="12" t="n">
+        <v>51377</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="16" t="n">
-        <v>2984</v>
+      <c r="C93" s="11" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="true" outlineLevel="3">
@@ -2213,7 +2321,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="true" outlineLevel="3">
@@ -2221,7 +2329,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="16" t="n">
-        <v>3374</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="true" outlineLevel="3">
@@ -2229,31 +2337,31 @@
         <v>95</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>390</v>
+        <v>521</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="98" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C97" s="16" t="n">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="11" t="n">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C98" s="16" t="n">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>180</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="true" outlineLevel="3">
@@ -2261,7 +2369,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>-30</v>
+        <v>600</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
@@ -2269,7 +2377,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="16" t="n">
-        <v>7178</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
@@ -2277,95 +2385,95 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="103" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B103" s="14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B103" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C103" s="12" t="n">
-        <v>4099</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C103" s="16" t="n">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C104" s="16" t="n">
+        <v>5625</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="107" ht="11" customHeight="true" outlineLevel="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="11" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="108" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C107" s="16" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="16" t="n">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="109" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C108" s="11" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="11" t="n">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="110" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C109" s="16" t="n">
+        <v>14090</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
       <c r="C110" s="16" t="n">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="111" ht="11" customHeight="true" outlineLevel="3">
+        <v>9750</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="true" outlineLevel="3">
       <c r="B111" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="112" ht="11" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="true" outlineLevel="3">
       <c r="B112" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B113" s="15" t="s">
+      <c r="C112" s="16" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="113" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B113" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="11" t="n">
-        <v>80</v>
+      <c r="C113" s="12" t="n">
+        <v>6722</v>
       </c>
     </row>
     <row r="114" ht="11" customHeight="true" outlineLevel="3">
@@ -2373,7 +2481,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>4</v>
+        <v>805</v>
       </c>
     </row>
     <row r="115" ht="11" customHeight="true" outlineLevel="3">
@@ -2381,31 +2489,31 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="true" outlineLevel="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="116" ht="11" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B117" s="14" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="117" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="12" t="n">
-        <v>66209</v>
+      <c r="C117" s="11" t="n">
+        <v>886</v>
       </c>
     </row>
     <row r="118" ht="11" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="11" t="n">
-        <v>61</v>
+      <c r="C118" s="16" t="n">
+        <v>1444</v>
       </c>
     </row>
     <row r="119" ht="11" customHeight="true" outlineLevel="3">
@@ -2413,15 +2521,15 @@
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>760</v>
+        <v>626</v>
       </c>
     </row>
     <row r="120" ht="11" customHeight="true" outlineLevel="3">
       <c r="B120" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="11" t="n">
-        <v>39</v>
+      <c r="C120" s="16" t="n">
+        <v>1252</v>
       </c>
     </row>
     <row r="121" ht="11" customHeight="true" outlineLevel="3">
@@ -2429,39 +2537,39 @@
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>319</v>
+        <v>123</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="16" t="n">
-        <v>28380</v>
+      <c r="C122" s="11" t="n">
+        <v>394</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="16" t="n">
-        <v>10171</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B124" s="15" t="s">
+      <c r="C123" s="11" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B124" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="16" t="n">
-        <v>5750</v>
+      <c r="C124" s="12" t="n">
+        <v>51414</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="16" t="n">
-        <v>7810</v>
+      <c r="C125" s="11" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2469,15 +2577,15 @@
         <v>125</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>41</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="16" t="n">
-        <v>1460</v>
+      <c r="C127" s="11" t="n">
+        <v>809</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2485,7 +2593,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>68</v>
+        <v>603</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2493,31 +2601,31 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>244</v>
+        <v>566</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>128</v>
+      <c r="C130" s="16" t="n">
+        <v>24470</v>
       </c>
     </row>
     <row r="131" ht="11" customHeight="true" outlineLevel="3">
       <c r="B131" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>377</v>
+      <c r="C131" s="16" t="n">
+        <v>5858</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
       <c r="B132" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="11" t="n">
-        <v>680</v>
+      <c r="C132" s="16" t="n">
+        <v>5225</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
@@ -2525,7 +2633,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="16" t="n">
-        <v>1974</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2533,15 +2641,15 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="135" ht="22" customHeight="true" outlineLevel="3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
       <c r="C135" s="16" t="n">
-        <v>1879</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2549,15 +2657,15 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="16" t="n">
-        <v>1357</v>
+      <c r="C137" s="11" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
@@ -2565,7 +2673,7 @@
         <v>137</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>3</v>
+        <v>604</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
@@ -2573,15 +2681,15 @@
         <v>138</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>229</v>
+        <v>599</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="11" t="n">
-        <v>1</v>
+      <c r="C140" s="16" t="n">
+        <v>1701</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
@@ -2589,15 +2697,15 @@
         <v>140</v>
       </c>
       <c r="C141" s="11" t="n">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="142" ht="11" customHeight="true" outlineLevel="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="11" t="n">
-        <v>149</v>
+      <c r="C142" s="16" t="n">
+        <v>1548</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2605,7 +2713,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>83</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2613,7 +2721,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>262</v>
+        <v>416</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2621,7 +2729,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>252</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -2629,15 +2737,15 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>1</v>
+        <v>605</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="16" t="n">
-        <v>1009</v>
+      <c r="C147" s="11" t="n">
+        <v>366</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
@@ -2645,15 +2753,15 @@
         <v>147</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
       <c r="B149" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="16" t="n">
-        <v>1207</v>
+      <c r="C149" s="11" t="n">
+        <v>562</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2661,15 +2769,15 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="151" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B151" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="151" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B151" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="12" t="n">
-        <v>79137</v>
+      <c r="C151" s="16" t="n">
+        <v>1768</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
@@ -2677,7 +2785,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>512</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2685,7 +2793,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>519</v>
+        <v>167</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
@@ -2693,15 +2801,15 @@
         <v>153</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="155" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B155" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="155" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B155" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="11" t="n">
-        <v>223</v>
+      <c r="C155" s="12" t="n">
+        <v>109957</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2709,7 +2817,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>111</v>
+        <v>173</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
@@ -2717,7 +2825,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>10</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2725,7 +2833,7 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>143</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
@@ -2733,15 +2841,15 @@
         <v>158</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>172</v>
+        <v>281</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
       <c r="B160" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="11" t="n">
-        <v>108</v>
+      <c r="C160" s="16" t="n">
+        <v>3959</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2749,15 +2857,15 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>435</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="16" t="n">
-        <v>3633</v>
+      <c r="C162" s="11" t="n">
+        <v>455</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2765,7 +2873,7 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>230</v>
+        <v>544</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
@@ -2773,7 +2881,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>887</v>
+        <v>338</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -2781,7 +2889,7 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>470</v>
+        <v>288</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2789,23 +2897,23 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>698</v>
+        <v>56</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="11" t="n">
-        <v>642</v>
+      <c r="C167" s="16" t="n">
+        <v>3403</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="16" t="n">
-        <v>3440</v>
+      <c r="C168" s="11" t="n">
+        <v>497</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2813,7 +2921,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>192</v>
+        <v>665</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2821,7 +2929,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2829,7 +2937,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>138</v>
+        <v>297</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2837,7 +2945,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>74</v>
+        <v>598</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2845,7 +2953,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>211</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2853,15 +2961,15 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>693</v>
+        <v>518</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="11" t="n">
-        <v>298</v>
+      <c r="C175" s="16" t="n">
+        <v>7335</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2869,31 +2977,31 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>363</v>
+        <v>816</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
       <c r="B177" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="16" t="n">
-        <v>1566</v>
+      <c r="C177" s="11" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
       <c r="B178" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="16" t="n">
-        <v>2723</v>
+      <c r="C178" s="11" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
       <c r="B179" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="11" t="n">
-        <v>109</v>
+      <c r="C179" s="16" t="n">
+        <v>4777</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -2901,31 +3009,31 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>252</v>
+        <v>298</v>
       </c>
     </row>
     <row r="181" ht="22" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="16" t="n">
-        <v>13669</v>
-      </c>
-    </row>
-    <row r="182" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C181" s="11" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="15" t="s">
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="183" ht="22" customHeight="true" outlineLevel="3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="16" t="n">
-        <v>1690</v>
+      <c r="C183" s="11" t="n">
+        <v>925</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -2933,87 +3041,87 @@
         <v>183</v>
       </c>
       <c r="C184" s="16" t="n">
-        <v>14903</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
       <c r="B185" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="16" t="n">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="186" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C185" s="11" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="186" ht="11" customHeight="true" outlineLevel="3">
       <c r="B186" s="15" t="s">
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>818</v>
+        <v>68</v>
       </c>
     </row>
     <row r="187" ht="22" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C187" s="16" t="n">
+        <v>11796</v>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="true" outlineLevel="3">
       <c r="B188" s="15" t="s">
         <v>187</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="189" ht="11" customHeight="true" outlineLevel="3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
       <c r="C189" s="16" t="n">
-        <v>8499</v>
-      </c>
-    </row>
-    <row r="190" ht="22" customHeight="true" outlineLevel="3">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="190" ht="11" customHeight="true" outlineLevel="3">
       <c r="B190" s="15" t="s">
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>153</v>
+        <v>642</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="11" t="n">
-        <v>96</v>
+      <c r="C191" s="16" t="n">
+        <v>11503</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
       <c r="B192" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="11" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="193" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C192" s="16" t="n">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
       <c r="C193" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" ht="11" customHeight="true" outlineLevel="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>202</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
@@ -3021,23 +3129,23 @@
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>593</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="11" t="n">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="197" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C196" s="16" t="n">
+        <v>6578</v>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3045,7 +3153,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="16" t="n">
-        <v>2251</v>
+        <v>8202</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3053,7 +3161,7 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>299</v>
+        <v>433</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3061,7 +3169,7 @@
         <v>199</v>
       </c>
       <c r="C200" s="16" t="n">
-        <v>3443</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
@@ -3069,23 +3177,23 @@
         <v>200</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>226</v>
+        <v>163</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
       <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="11" t="n">
-        <v>892</v>
+      <c r="C202" s="16" t="n">
+        <v>2016</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
       <c r="B203" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="C203" s="11" t="n">
-        <v>670</v>
+      <c r="C203" s="16" t="n">
+        <v>1115</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
@@ -3093,23 +3201,23 @@
         <v>203</v>
       </c>
       <c r="C204" s="16" t="n">
-        <v>1093</v>
+        <v>4784</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
       <c r="B205" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="11" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="206" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C205" s="16" t="n">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="206" ht="22" customHeight="true" outlineLevel="3">
       <c r="B206" s="15" t="s">
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>225</v>
+        <v>37</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3117,7 +3225,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="16" t="n">
-        <v>2363</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3125,7 +3233,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>672</v>
+        <v>662</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3133,7 +3241,7 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>201</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
@@ -3141,15 +3249,15 @@
         <v>209</v>
       </c>
       <c r="C210" s="11" t="n">
-        <v>340</v>
+        <v>447</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
       <c r="B211" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="16" t="n">
-        <v>2442</v>
+      <c r="C211" s="11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3157,7 +3265,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>24</v>
+        <v>228</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3165,7 +3273,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>385</v>
+        <v>17</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3173,23 +3281,23 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>329</v>
+        <v>858</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="11" t="n">
-        <v>78</v>
+      <c r="C215" s="16" t="n">
+        <v>3311</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="11" t="n">
-        <v>292</v>
+      <c r="C216" s="16" t="n">
+        <v>2359</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3197,7 +3305,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>281</v>
+        <v>523</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3205,31 +3313,31 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>115</v>
+        <v>56</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
       <c r="B219" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="220" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B220" s="14" t="s">
+      <c r="C219" s="16" t="n">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="220" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B220" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="12" t="n">
-        <v>40057</v>
+      <c r="C220" s="11" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
       <c r="B221" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="11" t="n">
-        <v>813</v>
+      <c r="C221" s="16" t="n">
+        <v>1477</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3237,15 +3345,15 @@
         <v>221</v>
       </c>
       <c r="C222" s="11" t="n">
-        <v>171</v>
+        <v>760</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="16" t="n">
-        <v>1976</v>
+      <c r="C223" s="11" t="n">
+        <v>406</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3253,7 +3361,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>7</v>
+        <v>559</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3261,15 +3369,15 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>979</v>
+        <v>754</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="16" t="n">
-        <v>3675</v>
+      <c r="C226" s="11" t="n">
+        <v>602</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3277,7 +3385,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>216</v>
+        <v>297</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3285,23 +3393,23 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>386</v>
+        <v>328</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="11" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="230" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B230" s="15" t="s">
+      <c r="C229" s="16" t="n">
+        <v>5417</v>
+      </c>
+    </row>
+    <row r="230" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B230" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="11" t="n">
-        <v>325</v>
+      <c r="C230" s="12" t="n">
+        <v>35500</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
@@ -3309,15 +3417,15 @@
         <v>230</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>302</v>
+        <v>838</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="16" t="n">
-        <v>1153</v>
+      <c r="C232" s="11" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3325,15 +3433,15 @@
         <v>232</v>
       </c>
       <c r="C233" s="16" t="n">
-        <v>1154</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
       <c r="B234" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="16" t="n">
-        <v>1332</v>
+      <c r="C234" s="11" t="n">
+        <v>610</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3341,7 +3449,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>781</v>
+        <v>555</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3349,7 +3457,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="16" t="n">
-        <v>1178</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3357,23 +3465,23 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>293</v>
+        <v>216</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="16" t="n">
-        <v>1250</v>
+      <c r="C238" s="11" t="n">
+        <v>273</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="16" t="n">
-        <v>1127</v>
+      <c r="C239" s="11" t="n">
+        <v>203</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3381,15 +3489,15 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>648</v>
+        <v>316</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="16" t="n">
-        <v>1336</v>
+      <c r="C241" s="11" t="n">
+        <v>255</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
@@ -3397,7 +3505,7 @@
         <v>241</v>
       </c>
       <c r="C242" s="16" t="n">
-        <v>1521</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3405,7 +3513,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="16" t="n">
-        <v>2946</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3413,7 +3521,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="16" t="n">
-        <v>1368</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3421,7 +3529,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>793</v>
+        <v>589</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3429,7 +3537,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>910</v>
+        <v>718</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3437,39 +3545,39 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>621</v>
+        <v>257</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="16" t="n">
-        <v>1451</v>
+      <c r="C248" s="11" t="n">
+        <v>878</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="16" t="n">
-        <v>1798</v>
+      <c r="C249" s="11" t="n">
+        <v>931</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
       <c r="B250" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="16" t="n">
-        <v>1158</v>
+      <c r="C250" s="11" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="16" t="n">
-        <v>1708</v>
+      <c r="C251" s="11" t="n">
+        <v>676</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
@@ -3477,7 +3585,7 @@
         <v>251</v>
       </c>
       <c r="C252" s="16" t="n">
-        <v>1447</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3485,31 +3593,31 @@
         <v>252</v>
       </c>
       <c r="C253" s="16" t="n">
-        <v>3911</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
       <c r="B254" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C254" s="11" t="n">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="255" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B255" s="14" t="s">
+      <c r="C254" s="16" t="n">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="12" t="n">
-        <v>2364</v>
+      <c r="C255" s="16" t="n">
+        <v>1864</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
       <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="11" t="n">
-        <v>140</v>
+      <c r="C256" s="16" t="n">
+        <v>1231</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3517,55 +3625,55 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>15</v>
+        <v>542</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="11" t="n">
-        <v>248</v>
+      <c r="C258" s="16" t="n">
+        <v>1676</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="11" t="n">
-        <v>169</v>
+      <c r="C259" s="16" t="n">
+        <v>2132</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="11" t="n">
-        <v>126</v>
+      <c r="C260" s="16" t="n">
+        <v>1147</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
       <c r="B261" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="11" t="n">
-        <v>77</v>
+      <c r="C261" s="16" t="n">
+        <v>2057</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="11" t="n">
-        <v>100</v>
+      <c r="C262" s="16" t="n">
+        <v>1456</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="11" t="n">
-        <v>89</v>
+      <c r="C263" s="16" t="n">
+        <v>2462</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3573,15 +3681,15 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="265" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B265" s="15" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="265" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B265" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="C265" s="11" t="n">
-        <v>177</v>
+      <c r="C265" s="12" t="n">
+        <v>2165</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3589,7 +3697,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>353</v>
+        <v>165</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -3597,7 +3705,7 @@
         <v>266</v>
       </c>
       <c r="C267" s="11" t="n">
-        <v>27</v>
+        <v>177</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3605,7 +3713,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3613,7 +3721,7 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>12</v>
+        <v>148</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
@@ -3621,7 +3729,7 @@
         <v>269</v>
       </c>
       <c r="C270" s="11" t="n">
-        <v>140</v>
+        <v>77</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
@@ -3629,7 +3737,7 @@
         <v>270</v>
       </c>
       <c r="C271" s="11" t="n">
-        <v>239</v>
+        <v>120</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -3637,15 +3745,15 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="273" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B273" s="14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="273" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B273" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="12" t="n">
-        <v>21575</v>
+      <c r="C273" s="11" t="n">
+        <v>258</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
@@ -3653,7 +3761,7 @@
         <v>273</v>
       </c>
       <c r="C274" s="11" t="n">
-        <v>426</v>
+        <v>56</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3661,7 +3769,7 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>407</v>
+        <v>180</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -3669,7 +3777,7 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>195</v>
+        <v>27</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
@@ -3677,7 +3785,7 @@
         <v>276</v>
       </c>
       <c r="C277" s="11" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
@@ -3685,7 +3793,7 @@
         <v>277</v>
       </c>
       <c r="C278" s="11" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
@@ -3693,7 +3801,7 @@
         <v>278</v>
       </c>
       <c r="C279" s="11" t="n">
-        <v>305</v>
+        <v>140</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -3701,23 +3809,23 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="281" ht="22" customHeight="true" outlineLevel="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
       <c r="C281" s="11" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="282" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B282" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="282" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B282" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="11" t="n">
-        <v>124</v>
+      <c r="C282" s="12" t="n">
+        <v>33918</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3725,7 +3833,7 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
@@ -3733,7 +3841,7 @@
         <v>283</v>
       </c>
       <c r="C284" s="11" t="n">
-        <v>164</v>
+        <v>313</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3741,7 +3849,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>786</v>
+        <v>430</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3749,39 +3857,39 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="287" ht="22" customHeight="true" outlineLevel="3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="15" t="s">
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="true" outlineLevel="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="289" ht="22" customHeight="true" outlineLevel="3">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="289" ht="11" customHeight="true" outlineLevel="3">
       <c r="B289" s="15" t="s">
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="290" ht="22" customHeight="true" outlineLevel="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true" outlineLevel="3">
       <c r="B290" s="15" t="s">
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>42</v>
+        <v>308</v>
       </c>
     </row>
     <row r="291" ht="22" customHeight="true" outlineLevel="3">
@@ -3789,31 +3897,31 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="292" ht="22" customHeight="true" outlineLevel="3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true" outlineLevel="3">
       <c r="B292" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" ht="22" customHeight="true" outlineLevel="3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="293" ht="11" customHeight="true" outlineLevel="3">
       <c r="B293" s="15" t="s">
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="294" ht="22" customHeight="true" outlineLevel="3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="294" ht="11" customHeight="true" outlineLevel="3">
       <c r="B294" s="15" t="s">
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -3821,15 +3929,15 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>246</v>
+        <v>379</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="11" t="n">
-        <v>176</v>
+      <c r="C296" s="16" t="n">
+        <v>1653</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3837,87 +3945,87 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="298" ht="11" customHeight="true" outlineLevel="3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="16" t="n">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="299" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C298" s="11" t="n">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="299" ht="22" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="16" t="n">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="300" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C299" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="301" ht="11" customHeight="true" outlineLevel="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="true" outlineLevel="3">
       <c r="B301" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="16" t="n">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="302" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C301" s="11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="302" ht="22" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="16" t="n">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="303" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C302" s="11" t="n">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="16" t="n">
-        <v>2593</v>
-      </c>
-    </row>
-    <row r="304" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C303" s="11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="304" ht="22" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="305" ht="11" customHeight="true" outlineLevel="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="16" t="n">
-        <v>1014</v>
+      <c r="C305" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="16" t="n">
-        <v>3261</v>
-      </c>
-    </row>
-    <row r="307" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B307" s="14" t="s">
+      <c r="C306" s="11" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B307" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="12" t="n">
-        <v>30172</v>
+      <c r="C307" s="11" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -3925,7 +4033,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>622</v>
+        <v>446</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -3933,15 +4041,15 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>400</v>
+        <v>553</v>
       </c>
     </row>
     <row r="310" ht="11" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="11" t="n">
-        <v>612</v>
+      <c r="C310" s="16" t="n">
+        <v>1164</v>
       </c>
     </row>
     <row r="311" ht="22" customHeight="true" outlineLevel="3">
@@ -3949,15 +4057,15 @@
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="312" ht="22" customHeight="true" outlineLevel="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="11" t="n">
-        <v>900</v>
+      <c r="C312" s="16" t="n">
+        <v>2207</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -3965,23 +4073,23 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>292</v>
+        <v>55</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="11" t="n">
-        <v>572</v>
+      <c r="C314" s="16" t="n">
+        <v>1542</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="11" t="n">
-        <v>571</v>
+      <c r="C315" s="16" t="n">
+        <v>1225</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -3989,7 +4097,7 @@
         <v>315</v>
       </c>
       <c r="C316" s="16" t="n">
-        <v>1945</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
@@ -3997,23 +4105,23 @@
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="11" t="n">
-        <v>380</v>
+      <c r="C318" s="16" t="n">
+        <v>2197</v>
       </c>
     </row>
     <row r="319" ht="11" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="11" t="n">
-        <v>321</v>
+      <c r="C319" s="16" t="n">
+        <v>8061</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -4021,23 +4129,23 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>373</v>
+        <v>468</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="11" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="322" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B322" s="15" t="s">
+      <c r="C321" s="16" t="n">
+        <v>5802</v>
+      </c>
+    </row>
+    <row r="322" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B322" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>440</v>
+      <c r="C322" s="12" t="n">
+        <v>27452</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4045,7 +4153,7 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>506</v>
+        <v>662</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
@@ -4053,31 +4161,31 @@
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="11" t="n">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="326" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C325" s="16" t="n">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="326" ht="22" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="327" ht="11" customHeight="true" outlineLevel="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="327" ht="22" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>656</v>
+        <v>900</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4085,7 +4193,7 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>417</v>
+        <v>831</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
@@ -4093,23 +4201,23 @@
         <v>328</v>
       </c>
       <c r="C329" s="11" t="n">
-        <v>300</v>
+        <v>469</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="16" t="n">
-        <v>1081</v>
+      <c r="C330" s="11" t="n">
+        <v>467</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="11" t="n">
-        <v>848</v>
+      <c r="C331" s="16" t="n">
+        <v>1625</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4117,23 +4225,23 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="333" ht="22" customHeight="true" outlineLevel="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="15" t="s">
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="334" ht="22" customHeight="true" outlineLevel="3">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="3">
       <c r="B334" s="15" t="s">
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>120</v>
+        <v>169</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
@@ -4141,7 +4249,7 @@
         <v>334</v>
       </c>
       <c r="C335" s="11" t="n">
-        <v>46</v>
+        <v>483</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4149,15 +4257,15 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="337" ht="22" customHeight="true" outlineLevel="3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
       <c r="C337" s="11" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
@@ -4165,15 +4273,15 @@
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="339" ht="22" customHeight="true" outlineLevel="3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="339" ht="11" customHeight="true" outlineLevel="3">
       <c r="B339" s="15" t="s">
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>410</v>
+        <v>232</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4181,15 +4289,15 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="341" ht="22" customHeight="true" outlineLevel="3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="3">
       <c r="B341" s="15" t="s">
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4197,23 +4305,23 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="343" ht="22" customHeight="true" outlineLevel="3">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="15" t="s">
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>47</v>
+        <v>415</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="16" t="n">
-        <v>2303</v>
+      <c r="C344" s="11" t="n">
+        <v>187</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
@@ -4221,47 +4329,47 @@
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="16" t="n">
-        <v>6531</v>
+      <c r="C346" s="11" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
       <c r="B347" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="16" t="n">
-        <v>2886</v>
+      <c r="C347" s="11" t="n">
+        <v>848</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
       <c r="B348" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="16" t="n">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="349" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C348" s="11" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="350" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B350" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="350" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="17" t="n">
-        <v>177</v>
+      <c r="C350" s="11" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4269,7 +4377,7 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>9</v>
+        <v>107</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
@@ -4277,15 +4385,15 @@
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="353" ht="11" customHeight="true" outlineLevel="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>100</v>
+        <v>158</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4293,23 +4401,23 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="355" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B355" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="355" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B355" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="12" t="n">
-        <v>11783</v>
+      <c r="C355" s="11" t="n">
+        <v>331</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="11" t="n">
-        <v>18</v>
+      <c r="C356" s="16" t="n">
+        <v>5568</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4317,47 +4425,47 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="358" ht="22" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="11" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="359" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C358" s="16" t="n">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="360" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C359" s="16" t="n">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="360" ht="11" customHeight="true" outlineLevel="3">
       <c r="B360" s="15" t="s">
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="361" ht="22" customHeight="true" outlineLevel="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="11" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="362" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C361" s="16" t="n">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="15" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>12</v>
+        <v>134</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4365,39 +4473,39 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="364" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B364" s="15" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B364" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="11" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="365" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C364" s="17" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="365" ht="11" customHeight="true" outlineLevel="3">
       <c r="B365" s="15" t="s">
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="15" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="367" ht="22" customHeight="true" outlineLevel="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" ht="11" customHeight="true" outlineLevel="3">
       <c r="B367" s="15" t="s">
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4405,15 +4513,15 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="369" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B369" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B369" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="C369" s="11" t="n">
-        <v>36</v>
+      <c r="C369" s="12" t="n">
+        <v>103620</v>
       </c>
     </row>
     <row r="370" ht="11" customHeight="true" outlineLevel="3">
@@ -4421,23 +4529,23 @@
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="371" ht="22" customHeight="true" outlineLevel="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="371" ht="11" customHeight="true" outlineLevel="3">
       <c r="B371" s="15" t="s">
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="372" ht="22" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="372" ht="11" customHeight="true" outlineLevel="3">
       <c r="B372" s="15" t="s">
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="373" ht="22" customHeight="true" outlineLevel="3">
@@ -4445,7 +4553,7 @@
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>38</v>
+        <v>256</v>
       </c>
     </row>
     <row r="374" ht="22" customHeight="true" outlineLevel="3">
@@ -4453,55 +4561,55 @@
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="375" ht="22" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="375" ht="33" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="C375" s="11" t="n">
-        <v>10</v>
+      <c r="C375" s="16" t="n">
+        <v>13102</v>
       </c>
     </row>
     <row r="376" ht="22" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="16" t="n">
-        <v>1504</v>
+      <c r="C376" s="11" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="377" ht="22" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="11" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="378" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C377" s="16" t="n">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="16" t="n">
-        <v>1451</v>
-      </c>
-    </row>
-    <row r="379" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C378" s="11" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="15" t="s">
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="11" t="n">
-        <v>28</v>
+      <c r="C380" s="16" t="n">
+        <v>9189</v>
       </c>
     </row>
     <row r="381" ht="22" customHeight="true" outlineLevel="3">
@@ -4509,79 +4617,79 @@
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
     </row>
     <row r="382" ht="22" customHeight="true" outlineLevel="3">
       <c r="B382" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="C382" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="383" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C382" s="16" t="n">
+        <v>7717</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="3">
       <c r="B383" s="15" t="s">
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="384" ht="22" customHeight="true" outlineLevel="3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="384" ht="11" customHeight="true" outlineLevel="3">
       <c r="B384" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="C384" s="16" t="n">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="385" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C384" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="3">
       <c r="B385" s="15" t="s">
         <v>384</v>
       </c>
       <c r="C385" s="11" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="386" ht="22" customHeight="true" outlineLevel="3">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="386" ht="11" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="C386" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="387" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C386" s="16" t="n">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="387" ht="11" customHeight="true" outlineLevel="3">
       <c r="B387" s="15" t="s">
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C388" s="16" t="n">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>254</v>
+        <v>158</v>
       </c>
     </row>
     <row r="390" ht="22" customHeight="true" outlineLevel="3">
       <c r="B390" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="11" t="n">
-        <v>89</v>
+      <c r="C390" s="16" t="n">
+        <v>5081</v>
       </c>
     </row>
     <row r="391" ht="22" customHeight="true" outlineLevel="3">
@@ -4589,7 +4697,7 @@
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
@@ -4597,7 +4705,7 @@
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="393" ht="22" customHeight="true" outlineLevel="3">
@@ -4605,15 +4713,15 @@
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="394" ht="11" customHeight="true" outlineLevel="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="394" ht="22" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="11" t="n">
-        <v>109</v>
+      <c r="C394" s="16" t="n">
+        <v>8420</v>
       </c>
     </row>
     <row r="395" ht="22" customHeight="true" outlineLevel="3">
@@ -4621,55 +4729,55 @@
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="396" ht="22" customHeight="true" outlineLevel="3">
       <c r="B396" s="15" t="s">
         <v>395</v>
       </c>
       <c r="C396" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="397" ht="22" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C397" s="16" t="n">
+        <v>9007</v>
+      </c>
+    </row>
+    <row r="398" ht="22" customHeight="true" outlineLevel="3">
       <c r="B398" s="15" t="s">
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="399" ht="22" customHeight="true" outlineLevel="3">
       <c r="B399" s="15" t="s">
         <v>398</v>
       </c>
       <c r="C399" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="400" ht="22" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="401" ht="22" customHeight="true" outlineLevel="3">
       <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>562</v>
+        <v>892</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="true" outlineLevel="3">
@@ -4677,47 +4785,319 @@
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="403" ht="11" customHeight="true" outlineLevel="3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="403" ht="22" customHeight="true" outlineLevel="3">
       <c r="B403" s="15" t="s">
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="404" ht="22" customHeight="true" outlineLevel="3">
       <c r="B404" s="15" t="s">
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
       <c r="B405" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="11" t="n">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C405" s="16" t="n">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="15" t="s">
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="407" ht="22" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="C407" s="16" t="n">
-        <v>1561</v>
+      <c r="C407" s="11" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B408" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="C408" s="11" t="n">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="409" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B409" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="11" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B410" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="16" t="n">
+        <v>11639</v>
+      </c>
+    </row>
+    <row r="411" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B411" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="11" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B412" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="11" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B413" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B414" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="11" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B415" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="11" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B416" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="11" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="417" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B417" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="11" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B418" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="11" t="n">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="419" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B419" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="11" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="420" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B420" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C420" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B421" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C421" s="16" t="n">
+        <v>4051</v>
+      </c>
+    </row>
+    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B422" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="C422" s="11" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B423" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="C423" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B424" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C424" s="11" t="n">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B425" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C425" s="11" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B426" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C426" s="11" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B427" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="C427" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B428" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C428" s="11" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B429" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C429" s="11" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B430" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C430" s="11" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B431" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C431" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="432" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B432" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C432" s="11" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B433" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C433" s="11" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="434" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B434" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="C434" s="11" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B435" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="C435" s="11" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="436" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B436" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="C436" s="16" t="n">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="437" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B437" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="C437" s="16" t="n">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="438" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B438" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="C438" s="12" t="n">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="439" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B439" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="C439" s="16" t="n">
+        <v>4795</v>
+      </c>
+    </row>
+    <row r="440" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B440" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="C440" s="11" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="441" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B441" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="16" t="n">
+        <v>2880</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/Sorce/balanceKR.xlsx
+++ b/client/public/Sorce/balanceKR.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="476">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 19.03.2026 20:05:31</t>
+    <t>Период: на 05.04.2026 19:35:16</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -74,6 +74,12 @@
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
@@ -83,15 +89,15 @@
     <t>Желе Лісова ягода УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
-    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
@@ -128,12 +134,18 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Лимонна кислота УБ 100г /48шт /</t>
+  </si>
+  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
     <t>Посипка декоративна №1 УБ 7г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №1 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Посипка декоративна №2 УБ 7г /55шт</t>
   </si>
   <si>
@@ -143,6 +155,9 @@
     <t>Посипка декоративна №3 УБ 7г /55шт</t>
   </si>
   <si>
+    <t>Посипка декоративна №3 УБ 7г /55шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
@@ -188,6 +203,9 @@
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
+    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Приправа до плову УБ 25г /36шт</t>
   </si>
   <si>
@@ -242,6 +260,9 @@
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
+    <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -287,6 +308,9 @@
     <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
+  </si>
+  <si>
     <t>Суміш перців Класична УБ 30г /24шт</t>
   </si>
   <si>
@@ -314,6 +338,9 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
+    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -341,19 +368,16 @@
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /</t>
   </si>
   <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
+    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>БІСКВІТИ</t>
@@ -362,9 +386,6 @@
     <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Золотий ключик ВКФ 300г /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
@@ -413,9 +434,6 @@
     <t>Roshetto milk ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
@@ -455,21 +473,45 @@
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers какао ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers какао ККФ 72г /22шт AR /</t>
   </si>
   <si>
+    <t>Wafers какао-молоко ККФ 216г /16шт</t>
+  </si>
+  <si>
+    <t>Wafers какао-молоко ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers кокос та мигдаль ВКФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers кокос та мигдаль ВКФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers лимон ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
+    <t>Wafers лимон ККФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Wafers молоко ВКФ 216г /16шт</t>
+  </si>
+  <si>
+    <t>Wafers молоко ВКФ 216г /16шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
@@ -479,9 +521,6 @@
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers молоко ККФ 216г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>КАРАМЕЛЬ 200/300</t>
   </si>
   <si>
@@ -527,9 +566,6 @@
     <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cactus ВКФ 165г /14шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -542,6 +578,9 @@
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
@@ -551,6 +590,9 @@
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -611,9 +653,15 @@
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
+    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -623,6 +671,9 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -644,9 +695,6 @@
     <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Rabbits ВКФ 165г /14шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
   </si>
   <si>
@@ -674,6 +722,9 @@
     <t>Yummi Gummi Sour Slices ВКФ 165г /14шт АКЦІЯ ВІП</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
   </si>
   <si>
@@ -686,6 +737,9 @@
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова TP</t>
+  </si>
+  <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
@@ -809,6 +863,9 @@
     <t>Шалена бджілка ВКФ 1кг /9пак</t>
   </si>
   <si>
+    <t>Шалена бджілка ВКФ 1кг /9пак АКЦІЯ</t>
+  </si>
+  <si>
     <t>Шипучка РЦ 1кг /7пак</t>
   </si>
   <si>
@@ -995,12 +1052,12 @@
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
   </si>
   <si>
-    <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
   </si>
   <si>
@@ -1022,9 +1079,18 @@
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
+    <t>Johnny Krocker coconut ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Johnny Krocker milk ВКФ 1кг /4шт PL</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 1кг /4шт ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
+    <t>Ko-Ko Choco White 1кг/5</t>
+  </si>
+  <si>
     <t>KONAFETTO blanc ВКФ 1кг /5пак HAL</t>
   </si>
   <si>
@@ -1052,9 +1118,6 @@
     <t>Кара-Кум ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Кара-Кум ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1076,9 +1139,6 @@
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
-    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1091,6 +1151,9 @@
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ 1</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1148,6 +1211,9 @@
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
@@ -1160,6 +1226,9 @@
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
+    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
+  </si>
+  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1187,12 +1256,12 @@
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
   </si>
   <si>
@@ -1253,12 +1322,12 @@
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
   </si>
   <si>
+    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1286,39 +1355,75 @@
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
+    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
+    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова UA</t>
+  </si>
+  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
+    <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
+    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Roshen чорний з підсоленим подрібн. мигдалем ВКФ 85г /35шт /</t>
   </si>
   <si>
@@ -1334,10 +1439,10 @@
     <t>ФІГУРКИ</t>
   </si>
   <si>
-    <t>Кролик Roshen весняний ВКФ 25г /35шт</t>
-  </si>
-  <si>
     <t>Кролик Roshen весняний ВКФ 25г /35шт АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Кролик Roshen весняний ВКФ 25г /35шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Кролик Roshen весняний ВКФ 40г /24шт</t>
@@ -1592,7 +1697,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C441"/>
+  <dimension ref="C476"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1657,7 +1762,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>579</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -1665,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>543300</v>
+        <v>578339</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -1673,7 +1778,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>120980</v>
+        <v>123847</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -1681,7 +1786,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>17389</v>
+        <v>18380</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true" outlineLevel="3">
@@ -1689,15 +1794,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>1770</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true" outlineLevel="3">
       <c r="B16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>643</v>
+      <c r="C16" s="16" t="n">
+        <v>1034</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true" outlineLevel="3">
@@ -1712,16 +1817,16 @@
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>1919</v>
+      <c r="C18" s="11" t="n">
+        <v>602</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>1929</v>
+      <c r="C19" s="11" t="n">
+        <v>898</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
@@ -1729,7 +1834,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>8</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -1737,7 +1842,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>2181</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -1745,7 +1850,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
@@ -1753,15 +1858,15 @@
         <v>22</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>1505</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>27</v>
+      <c r="C24" s="16" t="n">
+        <v>1120</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
@@ -1769,7 +1874,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
@@ -1777,23 +1882,23 @@
         <v>25</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>3441</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="16" t="n">
-        <v>3540</v>
-      </c>
-    </row>
-    <row r="28" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B28" s="14" t="s">
+      <c r="C27" s="11" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="12" t="n">
-        <v>44787</v>
+      <c r="C28" s="16" t="n">
+        <v>2557</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true" outlineLevel="3">
@@ -1801,15 +1906,15 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>6049</v>
-      </c>
-    </row>
-    <row r="30" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B30" s="15" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="30" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B30" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="16" t="n">
-        <v>12959</v>
+      <c r="C30" s="12" t="n">
+        <v>45220</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
@@ -1817,15 +1922,15 @@
         <v>30</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>150</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>844</v>
+      <c r="C32" s="16" t="n">
+        <v>3833</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
@@ -1833,7 +1938,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>672</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
@@ -1841,23 +1946,23 @@
         <v>33</v>
       </c>
       <c r="C34" s="16" t="n">
-        <v>7190</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
       <c r="B35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="16" t="n">
-        <v>2160</v>
+      <c r="C35" s="11" t="n">
+        <v>392</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
       <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>42</v>
+      <c r="C36" s="16" t="n">
+        <v>2022</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true" outlineLevel="3">
@@ -1865,7 +1970,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>3037</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
@@ -1873,7 +1978,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>906</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -1881,15 +1986,15 @@
         <v>38</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>3457</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>55</v>
+      <c r="C40" s="16" t="n">
+        <v>1167</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
@@ -1897,15 +2002,15 @@
         <v>40</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>3497</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>149</v>
+      <c r="C42" s="16" t="n">
+        <v>3245</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true" outlineLevel="3">
@@ -1913,31 +2018,31 @@
         <v>42</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>1247</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
       <c r="B44" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>412</v>
+      <c r="C44" s="16" t="n">
+        <v>3795</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>230</v>
+      <c r="C45" s="16" t="n">
+        <v>5891</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
       <c r="B46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>705</v>
+      <c r="C46" s="16" t="n">
+        <v>3630</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -1945,23 +2050,23 @@
         <v>46</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>903</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B49" s="14" t="s">
+      <c r="C48" s="16" t="n">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="49" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B49" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="12" t="n">
-        <v>16724</v>
+      <c r="C49" s="11" t="n">
+        <v>412</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -1969,7 +2074,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>994</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -1977,7 +2082,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>100</v>
+        <v>622</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -1985,7 +2090,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>600</v>
+        <v>833</v>
       </c>
     </row>
     <row r="53" ht="11" customHeight="true" outlineLevel="3">
@@ -1993,15 +2098,15 @@
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B54" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B54" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="16" t="n">
-        <v>1588</v>
+      <c r="C54" s="12" t="n">
+        <v>20598</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -2009,7 +2114,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>267</v>
+        <v>743</v>
       </c>
     </row>
     <row r="56" ht="11" customHeight="true" outlineLevel="3">
@@ -2017,15 +2122,15 @@
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>146</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" ht="11" customHeight="true" outlineLevel="3">
       <c r="B57" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="11" t="n">
-        <v>542</v>
+      <c r="C57" s="16" t="n">
+        <v>1599</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2033,15 +2138,15 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>286</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
       <c r="B59" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>826</v>
+      <c r="C59" s="16" t="n">
+        <v>1553</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2049,7 +2154,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>305</v>
+        <v>573</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2057,15 +2162,15 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>6</v>
+        <v>963</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
       <c r="B62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>1003</v>
+      <c r="C62" s="11" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2073,7 +2178,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>586</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2081,15 +2186,15 @@
         <v>63</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>209</v>
+        <v>646</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
       <c r="B65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="16" t="n">
-        <v>1333</v>
+      <c r="C65" s="11" t="n">
+        <v>911</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
@@ -2097,7 +2202,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>224</v>
+        <v>565</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
@@ -2105,23 +2210,23 @@
         <v>66</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>256</v>
+        <v>432</v>
       </c>
     </row>
     <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C68" s="16" t="n">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>66</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
@@ -2129,15 +2234,15 @@
         <v>69</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>978</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
       <c r="B71" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>219</v>
+      <c r="C71" s="16" t="n">
+        <v>1128</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2145,7 +2250,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>905</v>
+        <v>995</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2153,39 +2258,39 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>23</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="16" t="n">
-        <v>5053</v>
-      </c>
-    </row>
-    <row r="75" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B75" s="14" t="s">
+      <c r="C74" s="11" t="n">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B75" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="12" t="n">
-        <v>42080</v>
+      <c r="C75" s="11" t="n">
+        <v>546</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="16" t="n">
-        <v>1822</v>
+      <c r="C76" s="11" t="n">
+        <v>461</v>
       </c>
     </row>
     <row r="77" ht="11" customHeight="true" outlineLevel="3">
       <c r="B77" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C77" s="16" t="n">
-        <v>1167</v>
+      <c r="C77" s="11" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="78" ht="11" customHeight="true" outlineLevel="3">
@@ -2193,63 +2298,63 @@
         <v>77</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>356</v>
+        <v>425</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="16" t="n">
-        <v>4042</v>
+      <c r="C79" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
       <c r="B80" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C80" s="11" t="n">
-        <v>944</v>
+      <c r="C80" s="16" t="n">
+        <v>4169</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="16" t="n">
-        <v>1451</v>
-      </c>
-    </row>
-    <row r="82" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B82" s="15" t="s">
+      <c r="C81" s="11" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B82" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="16" t="n">
-        <v>2915</v>
+      <c r="C82" s="12" t="n">
+        <v>39649</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>907</v>
+      <c r="C83" s="16" t="n">
+        <v>2221</v>
       </c>
     </row>
     <row r="84" ht="11" customHeight="true" outlineLevel="3">
       <c r="B84" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="16" t="n">
-        <v>3497</v>
+      <c r="C84" s="11" t="n">
+        <v>975</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
       <c r="B85" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>1077</v>
+      <c r="C85" s="11" t="n">
+        <v>557</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2257,23 +2362,23 @@
         <v>85</v>
       </c>
       <c r="C86" s="16" t="n">
-        <v>4305</v>
+        <v>4835</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
       <c r="B87" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>10038</v>
+      <c r="C87" s="11" t="n">
+        <v>958</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>430</v>
+      <c r="C88" s="16" t="n">
+        <v>1175</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2281,95 +2386,95 @@
         <v>88</v>
       </c>
       <c r="C89" s="16" t="n">
-        <v>8982</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
       <c r="B90" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="91" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B91" s="13" t="s">
+      <c r="C90" s="16" t="n">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="91" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B91" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="12" t="n">
-        <v>422320</v>
-      </c>
-    </row>
-    <row r="92" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B92" s="14" t="s">
+      <c r="C91" s="16" t="n">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B92" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C92" s="12" t="n">
-        <v>51377</v>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C92" s="11" t="n">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true" outlineLevel="3">
       <c r="B93" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C93" s="16" t="n">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true" outlineLevel="3">
       <c r="B94" s="15" t="s">
         <v>93</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="true" outlineLevel="3">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true" outlineLevel="3">
       <c r="B95" s="15" t="s">
         <v>94</v>
       </c>
       <c r="C95" s="16" t="n">
-        <v>4562</v>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="true" outlineLevel="3">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="97" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C96" s="16" t="n">
+        <v>14366</v>
+      </c>
+    </row>
+    <row r="97" ht="11" customHeight="true" outlineLevel="3">
       <c r="B97" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="16" t="n">
-        <v>1187</v>
+      <c r="C97" s="11" t="n">
+        <v>482</v>
       </c>
     </row>
     <row r="98" ht="11" customHeight="true" outlineLevel="3">
       <c r="B98" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="16" t="n">
-        <v>4253</v>
-      </c>
-    </row>
-    <row r="99" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B99" s="15" t="s">
+      <c r="C98" s="11" t="n">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B99" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B100" s="15" t="s">
+      <c r="C99" s="12" t="n">
+        <v>454492</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B100" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>600</v>
+      <c r="C100" s="12" t="n">
+        <v>57889</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="true" outlineLevel="3">
@@ -2377,7 +2482,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="16" t="n">
-        <v>2329</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="true" outlineLevel="3">
@@ -2385,7 +2490,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>150</v>
+        <v>510</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="true" outlineLevel="3">
@@ -2393,63 +2498,63 @@
         <v>102</v>
       </c>
       <c r="C103" s="16" t="n">
-        <v>4185</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="16" t="n">
-        <v>5625</v>
+      <c r="C104" s="11" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C105" s="16" t="n">
+        <v>8807</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true" outlineLevel="3">
       <c r="B106" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="true" outlineLevel="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" ht="11" customHeight="true" outlineLevel="3">
       <c r="B107" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="16" t="n">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C107" s="11" t="n">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="11" t="n">
-        <v>210</v>
+      <c r="C108" s="16" t="n">
+        <v>3644</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="true" outlineLevel="3">
       <c r="B109" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="16" t="n">
-        <v>14090</v>
+      <c r="C109" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
       <c r="B110" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="16" t="n">
-        <v>9750</v>
+      <c r="C110" s="11" t="n">
+        <v>304</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="true" outlineLevel="3">
@@ -2457,7 +2562,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>50</v>
+        <v>600</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="true" outlineLevel="3">
@@ -2465,79 +2570,79 @@
         <v>111</v>
       </c>
       <c r="C112" s="16" t="n">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="113" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B113" s="14" t="s">
+        <v>6075</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B113" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="12" t="n">
-        <v>6722</v>
-      </c>
-    </row>
-    <row r="114" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C113" s="16" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="true" outlineLevel="3">
       <c r="B114" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="11" t="n">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="115" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C114" s="16" t="n">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="true" outlineLevel="3">
       <c r="B115" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="116" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C115" s="16" t="n">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="true" outlineLevel="3">
       <c r="B116" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="117" ht="11" customHeight="true" outlineLevel="3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="true" outlineLevel="3">
       <c r="B117" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="11" t="n">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="118" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C117" s="16" t="n">
+        <v>12429</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="true" outlineLevel="3">
       <c r="B118" s="15" t="s">
         <v>117</v>
       </c>
       <c r="C118" s="16" t="n">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="119" ht="11" customHeight="true" outlineLevel="3">
+        <v>5008</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="true" outlineLevel="3">
       <c r="B119" s="15" t="s">
         <v>118</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="120" ht="11" customHeight="true" outlineLevel="3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="true" outlineLevel="3">
       <c r="B120" s="15" t="s">
         <v>119</v>
       </c>
       <c r="C120" s="16" t="n">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="121" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B121" s="15" t="s">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B121" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="11" t="n">
-        <v>123</v>
+      <c r="C121" s="12" t="n">
+        <v>6022</v>
       </c>
     </row>
     <row r="122" ht="11" customHeight="true" outlineLevel="3">
@@ -2545,7 +2650,7 @@
         <v>121</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>394</v>
+        <v>694</v>
       </c>
     </row>
     <row r="123" ht="11" customHeight="true" outlineLevel="3">
@@ -2553,31 +2658,31 @@
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="124" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B124" s="14" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B124" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="12" t="n">
-        <v>51414</v>
+      <c r="C124" s="11" t="n">
+        <v>731</v>
       </c>
     </row>
     <row r="125" ht="11" customHeight="true" outlineLevel="3">
       <c r="B125" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>105</v>
+      <c r="C125" s="16" t="n">
+        <v>1633</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
       <c r="B126" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="11" t="n">
-        <v>601</v>
+      <c r="C126" s="16" t="n">
+        <v>1640</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
@@ -2585,7 +2690,7 @@
         <v>126</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>809</v>
+        <v>47</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2593,7 +2698,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>603</v>
+        <v>336</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2601,39 +2706,39 @@
         <v>128</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>566</v>
+        <v>62</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="16" t="n">
-        <v>24470</v>
-      </c>
-    </row>
-    <row r="131" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B131" s="15" t="s">
+      <c r="C130" s="11" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="131" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B131" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="16" t="n">
-        <v>5858</v>
+      <c r="C131" s="12" t="n">
+        <v>53259</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
       <c r="B132" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="16" t="n">
-        <v>5225</v>
+      <c r="C132" s="11" t="n">
+        <v>582</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="16" t="n">
-        <v>2747</v>
+      <c r="C133" s="11" t="n">
+        <v>552</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2641,15 +2746,15 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>174</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
       <c r="B135" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="16" t="n">
-        <v>1133</v>
+      <c r="C135" s="11" t="n">
+        <v>513</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
@@ -2657,55 +2762,55 @@
         <v>135</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>152</v>
+        <v>665</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="11" t="n">
-        <v>88</v>
+      <c r="C137" s="16" t="n">
+        <v>21408</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
       <c r="B138" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="11" t="n">
-        <v>604</v>
+      <c r="C138" s="16" t="n">
+        <v>2931</v>
       </c>
     </row>
     <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="11" t="n">
-        <v>599</v>
+      <c r="C139" s="16" t="n">
+        <v>3972</v>
       </c>
     </row>
     <row r="140" ht="11" customHeight="true" outlineLevel="3">
       <c r="B140" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="16" t="n">
-        <v>1701</v>
+      <c r="C140" s="11" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
       <c r="B141" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="11" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="142" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C141" s="16" t="n">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="142" ht="11" customHeight="true" outlineLevel="3">
       <c r="B142" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="16" t="n">
-        <v>1548</v>
+      <c r="C142" s="11" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
@@ -2713,7 +2818,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>313</v>
+        <v>156</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -2721,7 +2826,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>416</v>
+        <v>454</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -2729,15 +2834,15 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>3</v>
+        <v>538</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
       <c r="B146" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="11" t="n">
-        <v>605</v>
+      <c r="C146" s="16" t="n">
+        <v>1644</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
@@ -2745,15 +2850,15 @@
         <v>146</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="148" ht="11" customHeight="true" outlineLevel="3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="true" outlineLevel="3">
       <c r="B148" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="11" t="n">
-        <v>33</v>
+      <c r="C148" s="16" t="n">
+        <v>1427</v>
       </c>
     </row>
     <row r="149" ht="11" customHeight="true" outlineLevel="3">
@@ -2761,7 +2866,7 @@
         <v>148</v>
       </c>
       <c r="C149" s="11" t="n">
-        <v>562</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
@@ -2769,23 +2874,23 @@
         <v>149</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>52</v>
+        <v>948</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
       <c r="B151" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="16" t="n">
-        <v>1768</v>
+      <c r="C151" s="11" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>3</v>
+      <c r="C152" s="16" t="n">
+        <v>1636</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
@@ -2793,23 +2898,23 @@
         <v>152</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>167</v>
+        <v>646</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="155" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B155" s="14" t="s">
+      <c r="C154" s="16" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="155" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B155" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="12" t="n">
-        <v>109957</v>
+      <c r="C155" s="16" t="n">
+        <v>1179</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -2817,15 +2922,15 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>173</v>
+        <v>275</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="11" t="n">
-        <v>407</v>
+      <c r="C157" s="16" t="n">
+        <v>1641</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -2833,15 +2938,15 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>49</v>
+        <v>242</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="11" t="n">
-        <v>281</v>
+      <c r="C159" s="16" t="n">
+        <v>1648</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -2849,7 +2954,7 @@
         <v>159</v>
       </c>
       <c r="C160" s="16" t="n">
-        <v>3959</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
@@ -2857,15 +2962,15 @@
         <v>160</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>19</v>
+        <v>147</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
       <c r="B162" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="11" t="n">
-        <v>455</v>
+      <c r="C162" s="16" t="n">
+        <v>1645</v>
       </c>
     </row>
     <row r="163" ht="11" customHeight="true" outlineLevel="3">
@@ -2873,23 +2978,23 @@
         <v>162</v>
       </c>
       <c r="C163" s="11" t="n">
-        <v>544</v>
+        <v>330</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="11" t="n">
-        <v>338</v>
+      <c r="C164" s="16" t="n">
+        <v>1645</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
       <c r="B165" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="11" t="n">
-        <v>288</v>
+      <c r="C165" s="16" t="n">
+        <v>1471</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
@@ -2897,23 +3002,23 @@
         <v>165</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="16" t="n">
-        <v>3403</v>
-      </c>
-    </row>
-    <row r="168" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B168" s="15" t="s">
+      <c r="C167" s="11" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="168" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B168" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="11" t="n">
-        <v>497</v>
+      <c r="C168" s="12" t="n">
+        <v>94604</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -2921,7 +3026,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>665</v>
+        <v>41</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
@@ -2929,7 +3034,7 @@
         <v>169</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
@@ -2937,7 +3042,7 @@
         <v>170</v>
       </c>
       <c r="C171" s="11" t="n">
-        <v>297</v>
+        <v>123</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -2945,7 +3050,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>598</v>
+        <v>53</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -2953,7 +3058,7 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>413</v>
+        <v>803</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
@@ -2961,15 +3066,15 @@
         <v>173</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>518</v>
+        <v>138</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="16" t="n">
-        <v>7335</v>
+      <c r="C175" s="11" t="n">
+        <v>473</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
@@ -2977,7 +3082,7 @@
         <v>175</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>816</v>
+        <v>269</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -2985,7 +3090,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>143</v>
+        <v>324</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -2993,31 +3098,31 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
       <c r="B179" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="16" t="n">
-        <v>4777</v>
+      <c r="C179" s="11" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
       <c r="B180" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="11" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="181" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C180" s="16" t="n">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="181" ht="11" customHeight="true" outlineLevel="3">
       <c r="B181" s="15" t="s">
         <v>180</v>
       </c>
       <c r="C181" s="11" t="n">
-        <v>37</v>
+        <v>484</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
@@ -3025,7 +3130,7 @@
         <v>181</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>334</v>
+        <v>657</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
@@ -3033,15 +3138,15 @@
         <v>182</v>
       </c>
       <c r="C183" s="11" t="n">
-        <v>925</v>
+        <v>50</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
       <c r="B184" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="16" t="n">
-        <v>2723</v>
+      <c r="C184" s="11" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3049,7 +3154,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>148</v>
+        <v>340</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3057,31 +3162,31 @@
         <v>185</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="187" ht="22" customHeight="true" outlineLevel="3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="16" t="n">
-        <v>11796</v>
-      </c>
-    </row>
-    <row r="188" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C187" s="11" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="188" ht="11" customHeight="true" outlineLevel="3">
       <c r="B188" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="11" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="189" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C188" s="16" t="n">
+        <v>6616</v>
+      </c>
+    </row>
+    <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="16" t="n">
-        <v>1266</v>
+      <c r="C189" s="11" t="n">
+        <v>601</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3089,15 +3194,15 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>642</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
       <c r="B191" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="16" t="n">
-        <v>11503</v>
+      <c r="C191" s="11" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="192" ht="11" customHeight="true" outlineLevel="3">
@@ -3105,47 +3210,47 @@
         <v>191</v>
       </c>
       <c r="C192" s="16" t="n">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="true" outlineLevel="3">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="193" ht="11" customHeight="true" outlineLevel="3">
       <c r="B193" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="11" t="n">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="194" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C193" s="16" t="n">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="194" ht="11" customHeight="true" outlineLevel="3">
       <c r="B194" s="15" t="s">
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" ht="11" customHeight="true" outlineLevel="3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="true" outlineLevel="3">
       <c r="B195" s="15" t="s">
         <v>194</v>
       </c>
       <c r="C195" s="11" t="n">
-        <v>62</v>
+        <v>110</v>
       </c>
     </row>
     <row r="196" ht="11" customHeight="true" outlineLevel="3">
       <c r="B196" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="16" t="n">
-        <v>6578</v>
-      </c>
-    </row>
-    <row r="197" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C196" s="11" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="197" ht="11" customHeight="true" outlineLevel="3">
       <c r="B197" s="15" t="s">
         <v>196</v>
       </c>
       <c r="C197" s="11" t="n">
-        <v>98</v>
+        <v>871</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3153,7 +3258,7 @@
         <v>197</v>
       </c>
       <c r="C198" s="16" t="n">
-        <v>8202</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
@@ -3161,47 +3266,47 @@
         <v>198</v>
       </c>
       <c r="C199" s="11" t="n">
-        <v>433</v>
+        <v>148</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
       <c r="B200" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="16" t="n">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="201" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C200" s="11" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="true" outlineLevel="3">
       <c r="B201" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="11" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="202" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C201" s="16" t="n">
+        <v>11744</v>
+      </c>
+    </row>
+    <row r="202" ht="22" customHeight="true" outlineLevel="3">
       <c r="B202" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="16" t="n">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="203" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C202" s="11" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="true" outlineLevel="3">
       <c r="B203" s="15" t="s">
         <v>202</v>
       </c>
       <c r="C203" s="16" t="n">
-        <v>1115</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="16" t="n">
-        <v>4784</v>
+      <c r="C204" s="11" t="n">
+        <v>604</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3209,31 +3314,31 @@
         <v>204</v>
       </c>
       <c r="C205" s="16" t="n">
-        <v>3443</v>
-      </c>
-    </row>
-    <row r="206" ht="22" customHeight="true" outlineLevel="3">
+        <v>11465</v>
+      </c>
+    </row>
+    <row r="206" ht="11" customHeight="true" outlineLevel="3">
       <c r="B206" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="207" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C206" s="16" t="n">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="207" ht="22" customHeight="true" outlineLevel="3">
       <c r="B207" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="16" t="n">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="208" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C207" s="11" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="true" outlineLevel="3">
       <c r="B208" s="15" t="s">
         <v>207</v>
       </c>
       <c r="C208" s="11" t="n">
-        <v>662</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3241,23 +3346,23 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="11" t="n">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="211" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C210" s="16" t="n">
+        <v>6505</v>
+      </c>
+    </row>
+    <row r="211" ht="22" customHeight="true" outlineLevel="3">
       <c r="B211" s="15" t="s">
         <v>210</v>
       </c>
       <c r="C211" s="11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3265,15 +3370,15 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>228</v>
+        <v>689</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
       <c r="B213" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="11" t="n">
-        <v>17</v>
+      <c r="C213" s="16" t="n">
+        <v>7582</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3281,23 +3386,23 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>858</v>
+        <v>436</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
       <c r="B215" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="16" t="n">
-        <v>3311</v>
+      <c r="C215" s="11" t="n">
+        <v>807</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="16" t="n">
-        <v>2359</v>
+      <c r="C216" s="11" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
@@ -3305,7 +3410,7 @@
         <v>216</v>
       </c>
       <c r="C217" s="11" t="n">
-        <v>523</v>
+        <v>20</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
@@ -3313,7 +3418,7 @@
         <v>217</v>
       </c>
       <c r="C218" s="11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3321,7 +3426,7 @@
         <v>218</v>
       </c>
       <c r="C219" s="16" t="n">
-        <v>3287</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
@@ -3329,7 +3434,7 @@
         <v>219</v>
       </c>
       <c r="C220" s="11" t="n">
-        <v>186</v>
+        <v>637</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3337,23 +3442,23 @@
         <v>220</v>
       </c>
       <c r="C221" s="16" t="n">
-        <v>1477</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
       <c r="B222" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="11" t="n">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="223" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C222" s="16" t="n">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="223" ht="22" customHeight="true" outlineLevel="3">
       <c r="B223" s="15" t="s">
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>406</v>
+        <v>110</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3361,7 +3466,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="11" t="n">
-        <v>559</v>
+        <v>761</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3369,7 +3474,7 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>754</v>
+        <v>587</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
@@ -3377,7 +3482,7 @@
         <v>225</v>
       </c>
       <c r="C226" s="11" t="n">
-        <v>602</v>
+        <v>442</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
@@ -3385,7 +3490,7 @@
         <v>226</v>
       </c>
       <c r="C227" s="11" t="n">
-        <v>297</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" ht="11" customHeight="true" outlineLevel="3">
@@ -3393,47 +3498,47 @@
         <v>227</v>
       </c>
       <c r="C228" s="11" t="n">
-        <v>328</v>
+        <v>184</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
       <c r="B229" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="16" t="n">
-        <v>5417</v>
-      </c>
-    </row>
-    <row r="230" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B230" s="14" t="s">
+      <c r="C229" s="11" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B230" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="12" t="n">
-        <v>35500</v>
+      <c r="C230" s="11" t="n">
+        <v>888</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="11" t="n">
-        <v>838</v>
+      <c r="C231" s="16" t="n">
+        <v>2192</v>
       </c>
     </row>
     <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="11" t="n">
-        <v>260</v>
+      <c r="C232" s="16" t="n">
+        <v>2359</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
       <c r="B233" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="16" t="n">
-        <v>1414</v>
+      <c r="C233" s="11" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="234" ht="11" customHeight="true" outlineLevel="3">
@@ -3441,7 +3546,7 @@
         <v>233</v>
       </c>
       <c r="C234" s="11" t="n">
-        <v>610</v>
+        <v>63</v>
       </c>
     </row>
     <row r="235" ht="11" customHeight="true" outlineLevel="3">
@@ -3449,7 +3554,7 @@
         <v>234</v>
       </c>
       <c r="C235" s="11" t="n">
-        <v>555</v>
+        <v>241</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3457,7 +3562,7 @@
         <v>235</v>
       </c>
       <c r="C236" s="16" t="n">
-        <v>2158</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
@@ -3465,23 +3570,23 @@
         <v>236</v>
       </c>
       <c r="C237" s="11" t="n">
-        <v>216</v>
+        <v>76</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
       <c r="B238" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="11" t="n">
-        <v>273</v>
+      <c r="C238" s="16" t="n">
+        <v>1159</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>203</v>
+      <c r="C239" s="16" t="n">
+        <v>1040</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
@@ -3489,7 +3594,7 @@
         <v>239</v>
       </c>
       <c r="C240" s="11" t="n">
-        <v>316</v>
+        <v>99</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
@@ -3497,31 +3602,31 @@
         <v>240</v>
       </c>
       <c r="C241" s="11" t="n">
-        <v>255</v>
+        <v>186</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="16" t="n">
-        <v>1347</v>
+      <c r="C242" s="11" t="n">
+        <v>609</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
       <c r="B243" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="16" t="n">
-        <v>1503</v>
+      <c r="C243" s="11" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
       <c r="B244" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="16" t="n">
-        <v>1398</v>
+      <c r="C244" s="11" t="n">
+        <v>324</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3529,7 +3634,7 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>589</v>
+        <v>191</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
@@ -3537,7 +3642,7 @@
         <v>245</v>
       </c>
       <c r="C246" s="11" t="n">
-        <v>718</v>
+        <v>129</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3545,15 +3650,15 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="248" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B248" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="248" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B248" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="11" t="n">
-        <v>878</v>
+      <c r="C248" s="12" t="n">
+        <v>43062</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
@@ -3561,7 +3666,7 @@
         <v>248</v>
       </c>
       <c r="C249" s="11" t="n">
-        <v>931</v>
+        <v>797</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3569,23 +3674,23 @@
         <v>249</v>
       </c>
       <c r="C250" s="11" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
       <c r="B251" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="11" t="n">
-        <v>676</v>
+      <c r="C251" s="16" t="n">
+        <v>1413</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="16" t="n">
-        <v>1032</v>
+      <c r="C252" s="11" t="n">
+        <v>471</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
@@ -3593,7 +3698,7 @@
         <v>252</v>
       </c>
       <c r="C253" s="16" t="n">
-        <v>2647</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3601,23 +3706,23 @@
         <v>253</v>
       </c>
       <c r="C254" s="16" t="n">
-        <v>1196</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="16" t="n">
-        <v>1864</v>
+      <c r="C255" s="11" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
       <c r="B256" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="16" t="n">
-        <v>1231</v>
+      <c r="C256" s="11" t="n">
+        <v>208</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3625,31 +3730,31 @@
         <v>256</v>
       </c>
       <c r="C257" s="11" t="n">
-        <v>542</v>
+        <v>321</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="16" t="n">
-        <v>1676</v>
+      <c r="C258" s="11" t="n">
+        <v>485</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
       <c r="B259" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="16" t="n">
-        <v>2132</v>
+      <c r="C259" s="11" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="16" t="n">
-        <v>1147</v>
+      <c r="C260" s="11" t="n">
+        <v>731</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3657,7 +3762,7 @@
         <v>260</v>
       </c>
       <c r="C261" s="16" t="n">
-        <v>2057</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
@@ -3665,15 +3770,15 @@
         <v>261</v>
       </c>
       <c r="C262" s="16" t="n">
-        <v>1456</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="16" t="n">
-        <v>2462</v>
+      <c r="C263" s="11" t="n">
+        <v>644</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -3681,15 +3786,15 @@
         <v>263</v>
       </c>
       <c r="C264" s="11" t="n">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="265" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B265" s="14" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="265" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B265" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C265" s="12" t="n">
-        <v>2165</v>
+      <c r="C265" s="11" t="n">
+        <v>436</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -3697,15 +3802,15 @@
         <v>265</v>
       </c>
       <c r="C266" s="11" t="n">
-        <v>165</v>
+        <v>908</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
       <c r="B267" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="11" t="n">
-        <v>177</v>
+      <c r="C267" s="16" t="n">
+        <v>1072</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
@@ -3713,7 +3818,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>141</v>
+        <v>508</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
@@ -3721,47 +3826,47 @@
         <v>268</v>
       </c>
       <c r="C269" s="11" t="n">
-        <v>148</v>
+        <v>793</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="11" t="n">
-        <v>77</v>
+      <c r="C270" s="16" t="n">
+        <v>1108</v>
       </c>
     </row>
     <row r="271" ht="11" customHeight="true" outlineLevel="3">
       <c r="B271" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="11" t="n">
-        <v>120</v>
+      <c r="C271" s="16" t="n">
+        <v>3041</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
       <c r="B272" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="11" t="n">
-        <v>342</v>
+      <c r="C272" s="16" t="n">
+        <v>1606</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="11" t="n">
-        <v>258</v>
+      <c r="C273" s="16" t="n">
+        <v>1923</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="11" t="n">
-        <v>56</v>
+      <c r="C274" s="16" t="n">
+        <v>2519</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
@@ -3769,63 +3874,63 @@
         <v>274</v>
       </c>
       <c r="C275" s="11" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
       <c r="B276" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="11" t="n">
-        <v>27</v>
+      <c r="C276" s="16" t="n">
+        <v>1675</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="11" t="n">
-        <v>89</v>
+      <c r="C277" s="16" t="n">
+        <v>1648</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="11" t="n">
-        <v>12</v>
+      <c r="C278" s="16" t="n">
+        <v>1389</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="11" t="n">
-        <v>140</v>
+      <c r="C279" s="16" t="n">
+        <v>2374</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
       <c r="B280" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="C280" s="11" t="n">
-        <v>189</v>
+      <c r="C280" s="16" t="n">
+        <v>1353</v>
       </c>
     </row>
     <row r="281" ht="11" customHeight="true" outlineLevel="3">
       <c r="B281" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="282" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B282" s="14" t="s">
+      <c r="C281" s="16" t="n">
+        <v>3901</v>
+      </c>
+    </row>
+    <row r="282" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B282" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="12" t="n">
-        <v>33918</v>
+      <c r="C282" s="11" t="n">
+        <v>163</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -3833,15 +3938,15 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="284" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B284" s="15" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="284" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B284" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="11" t="n">
-        <v>313</v>
+      <c r="C284" s="12" t="n">
+        <v>1622</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -3849,7 +3954,7 @@
         <v>284</v>
       </c>
       <c r="C285" s="11" t="n">
-        <v>430</v>
+        <v>76</v>
       </c>
     </row>
     <row r="286" ht="11" customHeight="true" outlineLevel="3">
@@ -3857,7 +3962,7 @@
         <v>285</v>
       </c>
       <c r="C286" s="11" t="n">
-        <v>208</v>
+        <v>41</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
@@ -3865,7 +3970,7 @@
         <v>286</v>
       </c>
       <c r="C287" s="11" t="n">
-        <v>163</v>
+        <v>97</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
@@ -3873,7 +3978,7 @@
         <v>287</v>
       </c>
       <c r="C288" s="11" t="n">
-        <v>646</v>
+        <v>77</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -3881,7 +3986,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>280</v>
+        <v>77</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -3889,15 +3994,15 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="291" ht="22" customHeight="true" outlineLevel="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="291" ht="11" customHeight="true" outlineLevel="3">
       <c r="B291" s="15" t="s">
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>334</v>
+        <v>230</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -3905,7 +4010,7 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>297</v>
+        <v>258</v>
       </c>
     </row>
     <row r="293" ht="11" customHeight="true" outlineLevel="3">
@@ -3913,7 +4018,7 @@
         <v>292</v>
       </c>
       <c r="C293" s="11" t="n">
-        <v>196</v>
+        <v>127</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -3921,7 +4026,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -3929,15 +4034,15 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>379</v>
+        <v>27</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="16" t="n">
-        <v>1653</v>
+      <c r="C296" s="11" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
@@ -3945,71 +4050,71 @@
         <v>296</v>
       </c>
       <c r="C297" s="11" t="n">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="298" ht="22" customHeight="true" outlineLevel="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="15" t="s">
         <v>297</v>
       </c>
       <c r="C298" s="11" t="n">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="true" outlineLevel="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="15" t="s">
         <v>298</v>
       </c>
       <c r="C299" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="true" outlineLevel="3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="15" t="s">
         <v>299</v>
       </c>
       <c r="C300" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B301" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B301" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="302" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C301" s="12" t="n">
+        <v>33624</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true" outlineLevel="3">
       <c r="B302" s="15" t="s">
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="303" ht="22" customHeight="true" outlineLevel="3">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="303" ht="11" customHeight="true" outlineLevel="3">
       <c r="B303" s="15" t="s">
         <v>302</v>
       </c>
       <c r="C303" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="304" ht="22" customHeight="true" outlineLevel="3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="15" t="s">
         <v>303</v>
       </c>
       <c r="C304" s="11" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="true" outlineLevel="3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="15" t="s">
         <v>304</v>
       </c>
       <c r="C305" s="11" t="n">
-        <v>23</v>
+        <v>155</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
@@ -4017,7 +4122,7 @@
         <v>305</v>
       </c>
       <c r="C306" s="11" t="n">
-        <v>230</v>
+        <v>42</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -4025,7 +4130,7 @@
         <v>306</v>
       </c>
       <c r="C307" s="11" t="n">
-        <v>115</v>
+        <v>513</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
@@ -4033,7 +4138,7 @@
         <v>307</v>
       </c>
       <c r="C308" s="11" t="n">
-        <v>446</v>
+        <v>231</v>
       </c>
     </row>
     <row r="309" ht="11" customHeight="true" outlineLevel="3">
@@ -4041,31 +4146,31 @@
         <v>308</v>
       </c>
       <c r="C309" s="11" t="n">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="310" ht="11" customHeight="true" outlineLevel="3">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="true" outlineLevel="3">
       <c r="B310" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="16" t="n">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="311" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C310" s="11" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true" outlineLevel="3">
       <c r="B311" s="15" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="11" t="n">
-        <v>55</v>
+        <v>299</v>
       </c>
     </row>
     <row r="312" ht="11" customHeight="true" outlineLevel="3">
       <c r="B312" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="16" t="n">
-        <v>2207</v>
+      <c r="C312" s="11" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="313" ht="11" customHeight="true" outlineLevel="3">
@@ -4073,23 +4178,23 @@
         <v>312</v>
       </c>
       <c r="C313" s="11" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="314" ht="11" customHeight="true" outlineLevel="3">
       <c r="B314" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="16" t="n">
-        <v>1542</v>
+      <c r="C314" s="11" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="315" ht="11" customHeight="true" outlineLevel="3">
       <c r="B315" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="16" t="n">
-        <v>1225</v>
+      <c r="C315" s="11" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="316" ht="11" customHeight="true" outlineLevel="3">
@@ -4097,95 +4202,95 @@
         <v>315</v>
       </c>
       <c r="C316" s="16" t="n">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="317" ht="11" customHeight="true" outlineLevel="3">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="317" ht="22" customHeight="true" outlineLevel="3">
       <c r="B317" s="15" t="s">
         <v>316</v>
       </c>
       <c r="C317" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="318" ht="11" customHeight="true" outlineLevel="3">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="318" ht="22" customHeight="true" outlineLevel="3">
       <c r="B318" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="16" t="n">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="319" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C318" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="319" ht="22" customHeight="true" outlineLevel="3">
       <c r="B319" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="16" t="n">
-        <v>8061</v>
-      </c>
-    </row>
-    <row r="320" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C319" s="11" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="320" ht="22" customHeight="true" outlineLevel="3">
       <c r="B320" s="15" t="s">
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="321" ht="11" customHeight="true" outlineLevel="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="true" outlineLevel="3">
       <c r="B321" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="16" t="n">
-        <v>5802</v>
-      </c>
-    </row>
-    <row r="322" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B322" s="14" t="s">
+      <c r="C321" s="11" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B322" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="12" t="n">
-        <v>27452</v>
-      </c>
-    </row>
-    <row r="323" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C322" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="323" ht="22" customHeight="true" outlineLevel="3">
       <c r="B323" s="15" t="s">
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="324" ht="11" customHeight="true" outlineLevel="3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="324" ht="22" customHeight="true" outlineLevel="3">
       <c r="B324" s="15" t="s">
         <v>323</v>
       </c>
       <c r="C324" s="11" t="n">
-        <v>400</v>
+        <v>82</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
       <c r="B325" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="16" t="n">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C325" s="11" t="n">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="15" t="s">
         <v>325</v>
       </c>
       <c r="C326" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="327" ht="22" customHeight="true" outlineLevel="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="15" t="s">
         <v>326</v>
       </c>
       <c r="C327" s="11" t="n">
-        <v>900</v>
+        <v>272</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4193,23 +4298,23 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>831</v>
+        <v>466</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="11" t="n">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="330" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C329" s="16" t="n">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="330" ht="22" customHeight="true" outlineLevel="3">
       <c r="B330" s="15" t="s">
         <v>329</v>
       </c>
       <c r="C330" s="11" t="n">
-        <v>467</v>
+        <v>33</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
@@ -4217,7 +4322,7 @@
         <v>330</v>
       </c>
       <c r="C331" s="16" t="n">
-        <v>1625</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4225,7 +4330,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>500</v>
+        <v>33</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
@@ -4233,7 +4338,7 @@
         <v>332</v>
       </c>
       <c r="C333" s="11" t="n">
-        <v>586</v>
+        <v>906</v>
       </c>
     </row>
     <row r="334" ht="11" customHeight="true" outlineLevel="3">
@@ -4241,15 +4346,15 @@
         <v>333</v>
       </c>
       <c r="C334" s="11" t="n">
-        <v>169</v>
+        <v>947</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="11" t="n">
-        <v>483</v>
+      <c r="C335" s="16" t="n">
+        <v>2448</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4257,23 +4362,23 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>281</v>
+        <v>33</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="11" t="n">
-        <v>22</v>
+      <c r="C337" s="16" t="n">
+        <v>1665</v>
       </c>
     </row>
     <row r="338" ht="11" customHeight="true" outlineLevel="3">
       <c r="B338" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="C338" s="11" t="n">
-        <v>208</v>
+      <c r="C338" s="16" t="n">
+        <v>10658</v>
       </c>
     </row>
     <row r="339" ht="11" customHeight="true" outlineLevel="3">
@@ -4281,23 +4386,23 @@
         <v>338</v>
       </c>
       <c r="C339" s="11" t="n">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
       <c r="B340" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="11" t="n">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="341" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B341" s="15" t="s">
+      <c r="C340" s="16" t="n">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="341" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B341" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C341" s="11" t="n">
-        <v>135</v>
+      <c r="C341" s="12" t="n">
+        <v>26158</v>
       </c>
     </row>
     <row r="342" ht="11" customHeight="true" outlineLevel="3">
@@ -4305,7 +4410,7 @@
         <v>341</v>
       </c>
       <c r="C342" s="11" t="n">
-        <v>743</v>
+        <v>694</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
@@ -4313,31 +4418,31 @@
         <v>342</v>
       </c>
       <c r="C343" s="11" t="n">
-        <v>415</v>
+        <v>75</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
       <c r="B344" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="11" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="345" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C344" s="16" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="true" outlineLevel="3">
       <c r="B345" s="15" t="s">
         <v>344</v>
       </c>
       <c r="C345" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="346" ht="11" customHeight="true" outlineLevel="3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="true" outlineLevel="3">
       <c r="B346" s="15" t="s">
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>384</v>
+        <v>819</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4345,7 +4450,7 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>848</v>
+        <v>831</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4353,23 +4458,23 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="true" outlineLevel="3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="349" ht="11" customHeight="true" outlineLevel="3">
       <c r="B349" s="15" t="s">
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>2</v>
+        <v>460</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>69</v>
+      <c r="C350" s="16" t="n">
+        <v>2163</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4377,7 +4482,7 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>107</v>
+        <v>56</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
@@ -4385,15 +4490,15 @@
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="353" ht="22" customHeight="true" outlineLevel="3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="353" ht="11" customHeight="true" outlineLevel="3">
       <c r="B353" s="15" t="s">
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>158</v>
+        <v>225</v>
       </c>
     </row>
     <row r="354" ht="11" customHeight="true" outlineLevel="3">
@@ -4401,7 +4506,7 @@
         <v>353</v>
       </c>
       <c r="C354" s="11" t="n">
-        <v>137</v>
+        <v>219</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4409,15 +4514,15 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>331</v>
+        <v>170</v>
       </c>
     </row>
     <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="16" t="n">
-        <v>5568</v>
+      <c r="C356" s="11" t="n">
+        <v>526</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4425,23 +4530,23 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>60</v>
+        <v>226</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
       <c r="B358" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="16" t="n">
-        <v>2179</v>
+      <c r="C358" s="11" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
       <c r="B359" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="16" t="n">
-        <v>3986</v>
+      <c r="C359" s="11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
@@ -4449,15 +4554,15 @@
         <v>359</v>
       </c>
       <c r="C360" s="11" t="n">
-        <v>27</v>
+        <v>103</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
       <c r="B361" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="16" t="n">
-        <v>1207</v>
+      <c r="C361" s="11" t="n">
+        <v>427</v>
       </c>
     </row>
     <row r="362" ht="11" customHeight="true" outlineLevel="3">
@@ -4465,7 +4570,7 @@
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>134</v>
+        <v>692</v>
       </c>
     </row>
     <row r="363" ht="11" customHeight="true" outlineLevel="3">
@@ -4473,15 +4578,15 @@
         <v>362</v>
       </c>
       <c r="C363" s="11" t="n">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="364" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B364" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B364" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="17" t="n">
-        <v>195</v>
+      <c r="C364" s="16" t="n">
+        <v>1546</v>
       </c>
     </row>
     <row r="365" ht="11" customHeight="true" outlineLevel="3">
@@ -4489,7 +4594,7 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>30</v>
+        <v>284</v>
       </c>
     </row>
     <row r="366" ht="11" customHeight="true" outlineLevel="3">
@@ -4497,7 +4602,7 @@
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>9</v>
+        <v>614</v>
       </c>
     </row>
     <row r="367" ht="11" customHeight="true" outlineLevel="3">
@@ -4505,7 +4610,7 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>97</v>
+        <v>254</v>
       </c>
     </row>
     <row r="368" ht="11" customHeight="true" outlineLevel="3">
@@ -4513,23 +4618,23 @@
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="369" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B369" s="14" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="369" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B369" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="C369" s="12" t="n">
-        <v>103620</v>
-      </c>
-    </row>
-    <row r="370" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C369" s="11" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="370" ht="22" customHeight="true" outlineLevel="3">
       <c r="B370" s="15" t="s">
         <v>369</v>
       </c>
       <c r="C370" s="11" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4537,7 +4642,7 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>2</v>
+        <v>181</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
@@ -4545,55 +4650,55 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="373" ht="22" customHeight="true" outlineLevel="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="15" t="s">
         <v>372</v>
       </c>
       <c r="C373" s="11" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="374" ht="22" customHeight="true" outlineLevel="3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="374" ht="11" customHeight="true" outlineLevel="3">
       <c r="B374" s="15" t="s">
         <v>373</v>
       </c>
       <c r="C374" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="375" ht="33" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="375" ht="11" customHeight="true" outlineLevel="3">
       <c r="B375" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="C375" s="16" t="n">
-        <v>13102</v>
-      </c>
-    </row>
-    <row r="376" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C375" s="11" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="376" ht="11" customHeight="true" outlineLevel="3">
       <c r="B376" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="377" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C376" s="16" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="377" ht="11" customHeight="true" outlineLevel="3">
       <c r="B377" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="16" t="n">
-        <v>3136</v>
+      <c r="C377" s="11" t="n">
+        <v>422</v>
       </c>
     </row>
     <row r="378" ht="11" customHeight="true" outlineLevel="3">
       <c r="B378" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="11" t="n">
-        <v>493</v>
+      <c r="C378" s="16" t="n">
+        <v>1964</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
@@ -4601,7 +4706,7 @@
         <v>378</v>
       </c>
       <c r="C379" s="11" t="n">
-        <v>22</v>
+        <v>926</v>
       </c>
     </row>
     <row r="380" ht="11" customHeight="true" outlineLevel="3">
@@ -4609,23 +4714,23 @@
         <v>379</v>
       </c>
       <c r="C380" s="16" t="n">
-        <v>9189</v>
-      </c>
-    </row>
-    <row r="381" ht="22" customHeight="true" outlineLevel="3">
+        <v>3343</v>
+      </c>
+    </row>
+    <row r="381" ht="11" customHeight="true" outlineLevel="3">
       <c r="B381" s="15" t="s">
         <v>380</v>
       </c>
       <c r="C381" s="11" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="382" ht="22" customHeight="true" outlineLevel="3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="382" ht="11" customHeight="true" outlineLevel="3">
       <c r="B382" s="15" t="s">
         <v>381</v>
       </c>
       <c r="C382" s="16" t="n">
-        <v>7717</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="383" ht="11" customHeight="true" outlineLevel="3">
@@ -4633,7 +4738,7 @@
         <v>382</v>
       </c>
       <c r="C383" s="11" t="n">
-        <v>196</v>
+        <v>480</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
@@ -4641,23 +4746,23 @@
         <v>383</v>
       </c>
       <c r="C384" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="385" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B385" s="15" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="385" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B385" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="11" t="n">
-        <v>657</v>
+      <c r="C385" s="17" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="386" ht="11" customHeight="true" outlineLevel="3">
       <c r="B386" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="C386" s="16" t="n">
-        <v>1279</v>
+      <c r="C386" s="11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="387" ht="11" customHeight="true" outlineLevel="3">
@@ -4665,63 +4770,63 @@
         <v>386</v>
       </c>
       <c r="C387" s="11" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="388" ht="11" customHeight="true" outlineLevel="3">
       <c r="B388" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="16" t="n">
-        <v>3331</v>
-      </c>
-    </row>
-    <row r="389" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C388" s="11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="389" ht="11" customHeight="true" outlineLevel="3">
       <c r="B389" s="15" t="s">
         <v>388</v>
       </c>
       <c r="C389" s="11" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="390" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B390" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="390" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B390" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="16" t="n">
-        <v>5081</v>
-      </c>
-    </row>
-    <row r="391" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C390" s="12" t="n">
+        <v>138114</v>
+      </c>
+    </row>
+    <row r="391" ht="11" customHeight="true" outlineLevel="3">
       <c r="B391" s="15" t="s">
         <v>390</v>
       </c>
       <c r="C391" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="392" ht="22" customHeight="true" outlineLevel="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="392" ht="11" customHeight="true" outlineLevel="3">
       <c r="B392" s="15" t="s">
         <v>391</v>
       </c>
       <c r="C392" s="11" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="393" ht="11" customHeight="true" outlineLevel="3">
       <c r="B393" s="15" t="s">
         <v>392</v>
       </c>
       <c r="C393" s="11" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="394" ht="22" customHeight="true" outlineLevel="3">
       <c r="B394" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="16" t="n">
-        <v>8420</v>
+      <c r="C394" s="11" t="n">
+        <v>374</v>
       </c>
     </row>
     <row r="395" ht="22" customHeight="true" outlineLevel="3">
@@ -4729,23 +4834,23 @@
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="396" ht="22" customHeight="true" outlineLevel="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="396" ht="33" customHeight="true" outlineLevel="3">
       <c r="B396" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="C396" s="11" t="n">
-        <v>352</v>
+      <c r="C396" s="16" t="n">
+        <v>11044</v>
       </c>
     </row>
     <row r="397" ht="22" customHeight="true" outlineLevel="3">
       <c r="B397" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="16" t="n">
-        <v>9007</v>
+      <c r="C397" s="11" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="398" ht="22" customHeight="true" outlineLevel="3">
@@ -4753,39 +4858,39 @@
         <v>397</v>
       </c>
       <c r="C398" s="11" t="n">
-        <v>192</v>
+        <v>24</v>
       </c>
     </row>
     <row r="399" ht="22" customHeight="true" outlineLevel="3">
       <c r="B399" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="C399" s="11" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="400" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C399" s="16" t="n">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="400" ht="11" customHeight="true" outlineLevel="3">
       <c r="B400" s="15" t="s">
         <v>399</v>
       </c>
       <c r="C400" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="401" ht="22" customHeight="true" outlineLevel="3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="401" ht="11" customHeight="true" outlineLevel="3">
       <c r="B401" s="15" t="s">
         <v>400</v>
       </c>
       <c r="C401" s="11" t="n">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="402" ht="22" customHeight="true" outlineLevel="3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="402" ht="11" customHeight="true" outlineLevel="3">
       <c r="B402" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="C402" s="11" t="n">
-        <v>294</v>
+      <c r="C402" s="16" t="n">
+        <v>7989</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
@@ -4793,7 +4898,7 @@
         <v>402</v>
       </c>
       <c r="C403" s="11" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="404" ht="22" customHeight="true" outlineLevel="3">
@@ -4801,7 +4906,7 @@
         <v>403</v>
       </c>
       <c r="C404" s="11" t="n">
-        <v>18</v>
+        <v>102</v>
       </c>
     </row>
     <row r="405" ht="22" customHeight="true" outlineLevel="3">
@@ -4809,55 +4914,55 @@
         <v>404</v>
       </c>
       <c r="C405" s="16" t="n">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="406" ht="22" customHeight="true" outlineLevel="3">
+        <v>6043</v>
+      </c>
+    </row>
+    <row r="406" ht="11" customHeight="true" outlineLevel="3">
       <c r="B406" s="15" t="s">
         <v>405</v>
       </c>
       <c r="C406" s="11" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="407" ht="22" customHeight="true" outlineLevel="3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="407" ht="11" customHeight="true" outlineLevel="3">
       <c r="B407" s="15" t="s">
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="408" ht="22" customHeight="true" outlineLevel="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="408" ht="11" customHeight="true" outlineLevel="3">
       <c r="B408" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="C408" s="11" t="n">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="409" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C408" s="16" t="n">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="409" ht="11" customHeight="true" outlineLevel="3">
       <c r="B409" s="15" t="s">
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="true" outlineLevel="3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="410" ht="11" customHeight="true" outlineLevel="3">
       <c r="B410" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C410" s="16" t="n">
-        <v>11639</v>
-      </c>
-    </row>
-    <row r="411" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C410" s="11" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="411" ht="11" customHeight="true" outlineLevel="3">
       <c r="B411" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="C411" s="11" t="n">
-        <v>156</v>
+      <c r="C411" s="16" t="n">
+        <v>10029</v>
       </c>
     </row>
     <row r="412" ht="22" customHeight="true" outlineLevel="3">
@@ -4865,7 +4970,7 @@
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>245</v>
+        <v>109</v>
       </c>
     </row>
     <row r="413" ht="22" customHeight="true" outlineLevel="3">
@@ -4873,23 +4978,23 @@
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
       <c r="B414" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="C414" s="11" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C414" s="16" t="n">
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="415" ht="22" customHeight="true" outlineLevel="3">
       <c r="B415" s="15" t="s">
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>571</v>
+        <v>72</v>
       </c>
     </row>
     <row r="416" ht="22" customHeight="true" outlineLevel="3">
@@ -4897,15 +5002,15 @@
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>127</v>
+        <v>66</v>
       </c>
     </row>
     <row r="417" ht="22" customHeight="true" outlineLevel="3">
       <c r="B417" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="C417" s="11" t="n">
-        <v>474</v>
+      <c r="C417" s="16" t="n">
+        <v>6647</v>
       </c>
     </row>
     <row r="418" ht="22" customHeight="true" outlineLevel="3">
@@ -4913,7 +5018,7 @@
         <v>417</v>
       </c>
       <c r="C418" s="11" t="n">
-        <v>608</v>
+        <v>666</v>
       </c>
     </row>
     <row r="419" ht="22" customHeight="true" outlineLevel="3">
@@ -4921,31 +5026,31 @@
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>367</v>
+        <v>264</v>
       </c>
     </row>
     <row r="420" ht="22" customHeight="true" outlineLevel="3">
       <c r="B420" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="C420" s="11" t="n">
-        <v>54</v>
+      <c r="C420" s="16" t="n">
+        <v>7848</v>
       </c>
     </row>
     <row r="421" ht="22" customHeight="true" outlineLevel="3">
       <c r="B421" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="C421" s="16" t="n">
-        <v>4051</v>
-      </c>
-    </row>
-    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C421" s="11" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
       <c r="B422" s="15" t="s">
         <v>421</v>
       </c>
       <c r="C422" s="11" t="n">
-        <v>718</v>
+        <v>101</v>
       </c>
     </row>
     <row r="423" ht="22" customHeight="true" outlineLevel="3">
@@ -4953,63 +5058,63 @@
         <v>422</v>
       </c>
       <c r="C423" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="424" ht="22" customHeight="true" outlineLevel="3">
       <c r="B424" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="C424" s="11" t="n">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C424" s="16" t="n">
+        <v>7776</v>
+      </c>
+    </row>
+    <row r="425" ht="22" customHeight="true" outlineLevel="3">
       <c r="B425" s="15" t="s">
         <v>424</v>
       </c>
       <c r="C425" s="11" t="n">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="426" ht="22" customHeight="true" outlineLevel="3">
       <c r="B426" s="15" t="s">
         <v>425</v>
       </c>
       <c r="C426" s="11" t="n">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="427" ht="22" customHeight="true" outlineLevel="3">
       <c r="B427" s="15" t="s">
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
       <c r="B428" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="C428" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C428" s="16" t="n">
+        <v>7046</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
       <c r="B429" s="15" t="s">
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="430" ht="11" customHeight="true" outlineLevel="3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="430" ht="22" customHeight="true" outlineLevel="3">
       <c r="B430" s="15" t="s">
         <v>429</v>
       </c>
       <c r="C430" s="11" t="n">
-        <v>756</v>
+        <v>78</v>
       </c>
     </row>
     <row r="431" ht="22" customHeight="true" outlineLevel="3">
@@ -5017,87 +5122,367 @@
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="432" ht="11" customHeight="true" outlineLevel="3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="432" ht="22" customHeight="true" outlineLevel="3">
       <c r="B432" s="15" t="s">
         <v>431</v>
       </c>
       <c r="C432" s="11" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="433" ht="22" customHeight="true" outlineLevel="3">
       <c r="B433" s="15" t="s">
         <v>432</v>
       </c>
-      <c r="C433" s="11" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="434" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C433" s="16" t="n">
+        <v>8624</v>
+      </c>
+    </row>
+    <row r="434" ht="22" customHeight="true" outlineLevel="3">
       <c r="B434" s="15" t="s">
         <v>433</v>
       </c>
       <c r="C434" s="11" t="n">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="435" ht="11" customHeight="true" outlineLevel="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="435" ht="22" customHeight="true" outlineLevel="3">
       <c r="B435" s="15" t="s">
         <v>434</v>
       </c>
       <c r="C435" s="11" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="436" ht="11" customHeight="true" outlineLevel="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="436" ht="22" customHeight="true" outlineLevel="3">
       <c r="B436" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="C436" s="16" t="n">
-        <v>2922</v>
+      <c r="C436" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="437" ht="11" customHeight="true" outlineLevel="3">
       <c r="B437" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="C437" s="16" t="n">
-        <v>1177</v>
+      <c r="C437" s="11" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="438" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B438" s="18" t="s">
+      <c r="B438" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="12" t="n">
-        <v>7850</v>
-      </c>
-    </row>
-    <row r="439" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B439" s="19" t="s">
+      <c r="C438" s="11" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="439" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B439" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="C439" s="16" t="n">
-        <v>4795</v>
-      </c>
-    </row>
-    <row r="440" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B440" s="19" t="s">
+      <c r="C439" s="11" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B440" s="15" t="s">
         <v>439</v>
       </c>
       <c r="C440" s="11" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="441" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B441" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C441" s="11" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="442" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B442" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C442" s="11" t="n">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="443" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B443" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C443" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="444" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B444" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="C444" s="16" t="n">
+        <v>6384</v>
+      </c>
+    </row>
+    <row r="445" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B445" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="C445" s="11" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="446" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B446" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="C446" s="16" t="n">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="447" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B447" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C447" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="448" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B448" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="C448" s="11" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="449" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B449" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C449" s="16" t="n">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B450" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="C450" s="11" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="451" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B451" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="C451" s="16" t="n">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="452" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B452" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="C452" s="11" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="453" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B453" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="C453" s="16" t="n">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="454" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B454" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C454" s="11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B455" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="C455" s="16" t="n">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="456" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B456" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="C456" s="11" t="n">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="457" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B457" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="C457" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B458" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C458" s="16" t="n">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="459" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B459" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="C459" s="11" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="460" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B460" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C460" s="11" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="461" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B461" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="16" t="n">
+        <v>4938</v>
+      </c>
+    </row>
+    <row r="462" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B462" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C462" s="11" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B463" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C463" s="11" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="464" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B464" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="C464" s="16" t="n">
+        <v>5038</v>
+      </c>
+    </row>
+    <row r="465" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B465" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="C465" s="16" t="n">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="466" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B466" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C466" s="11" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="467" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B467" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C467" s="16" t="n">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="468" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B468" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C468" s="11" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="469" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B469" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C469" s="11" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="470" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B470" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C470" s="11" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="471" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B471" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C471" s="16" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="472" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B472" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C472" s="16" t="n">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="473" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B473" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C473" s="12" t="n">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="474" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B474" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="C474" s="11" t="n">
         <v>175</v>
       </c>
     </row>
-    <row r="441" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B441" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="C441" s="16" t="n">
-        <v>2880</v>
+    <row r="475" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B475" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C475" s="16" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="476" ht="11" customHeight="true" outlineLevel="4">
+      <c r="B476" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="C476" s="11" t="n">
+        <v>528</v>
       </c>
     </row>
   </sheetData>
